--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -35,9 +35,6 @@
     <t>Ống D650</t>
   </si>
   <si>
-    <t>Mét</t>
-  </si>
-  <si>
     <t>S400</t>
   </si>
   <si>
@@ -84,6 +81,9 @@
   </si>
   <si>
     <t>WEIGHT</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
 </sst>
 </file>
@@ -463,62 +463,62 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3">
         <v>150000</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3">
         <v>350000</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -529,16 +529,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>180000</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -549,36 +549,36 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>450000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3">
         <v>75000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\quote-web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8775" windowHeight="7215"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <t>DonVi</t>
   </si>
   <si>
-    <t>LoaiTinhgia</t>
+    <t>LoaiTinhGia</t>
   </si>
 </sst>
 </file>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8775" windowHeight="7215"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8775" windowHeight="8505"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,21 +50,12 @@
     <t>TenSP</t>
   </si>
   <si>
-    <t>SS400</t>
-  </si>
-  <si>
-    <t>Thép SS400</t>
-  </si>
-  <si>
     <t>kg</t>
   </si>
   <si>
     <t>cái</t>
   </si>
   <si>
-    <t>LENGTH</t>
-  </si>
-  <si>
     <t>PIECE</t>
   </si>
   <si>
@@ -84,6 +75,15 @@
   </si>
   <si>
     <t>LoaiTinhGia</t>
+  </si>
+  <si>
+    <t>Cyclone D1000</t>
+  </si>
+  <si>
+    <t>CYCD1000</t>
+  </si>
+  <si>
+    <t>LINEAR</t>
   </si>
 </sst>
 </file>
@@ -457,8 +457,8 @@
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -469,16 +469,16 @@
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -492,13 +492,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3">
         <v>150000</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -512,13 +512,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3">
         <v>350000</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -532,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3">
         <v>180000</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -552,33 +552,33 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3">
         <v>450000</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3">
         <v>75000</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
   <si>
     <t>CT90D650</t>
   </si>
@@ -35,12 +35,6 @@
     <t>Ống D650</t>
   </si>
   <si>
-    <t>S400</t>
-  </si>
-  <si>
-    <t>Inox 304</t>
-  </si>
-  <si>
     <t>ONG650</t>
   </si>
   <si>
@@ -84,6 +78,25 @@
   </si>
   <si>
     <t>LINEAR</t>
+  </si>
+  <si>
+    <t>DacTinh</t>
+  </si>
+  <si>
+    <t>XuatXu</t>
+  </si>
+  <si>
+    <t>Ống tròn xoắn</t>
+  </si>
+  <si>
+    <t>Hàng mới 100%
+Do System Fan sản xuất</t>
+  </si>
+  <si>
+    <t>Thép SS400</t>
+  </si>
+  <si>
+    <t>Tôn mạ kẽm</t>
   </si>
 </sst>
 </file>
@@ -450,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -459,69 +472,88 @@
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="15.140625" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3">
         <v>150000</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3">
         <v>350000</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -529,19 +561,25 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3">
         <v>180000</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -549,39 +587,49 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3">
         <v>450000</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3">
         <v>75000</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -589,7 +637,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -597,7 +645,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -605,7 +653,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -613,7 +661,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\quote-web-main\quote-web-main\quote-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8775" windowHeight="8505"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,41 +24,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
-  <si>
-    <t>CT90D650</t>
-  </si>
-  <si>
-    <t>Cút 90 D650</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="300">
   <si>
     <t>Ống D650</t>
   </si>
   <si>
-    <t>ONG650</t>
-  </si>
-  <si>
     <t>MaSP</t>
   </si>
   <si>
     <t>TenSP</t>
   </si>
   <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>cái</t>
-  </si>
-  <si>
-    <t>PIECE</t>
-  </si>
-  <si>
-    <t>WEIGHT</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>VatLieu</t>
   </si>
   <si>
@@ -66,18 +42,6 @@
   </si>
   <si>
     <t>DonVi</t>
-  </si>
-  <si>
-    <t>LoaiTinhGia</t>
-  </si>
-  <si>
-    <t>Cyclone D1000</t>
-  </si>
-  <si>
-    <t>CYCD1000</t>
-  </si>
-  <si>
-    <t>LINEAR</t>
   </si>
   <si>
     <t>DacTinh</t>
@@ -97,6 +61,871 @@
   </si>
   <si>
     <t>Tôn mạ kẽm</t>
+  </si>
+  <si>
+    <t>ONGD100</t>
+  </si>
+  <si>
+    <t>Ống D100</t>
+  </si>
+  <si>
+    <t>Mét</t>
+  </si>
+  <si>
+    <t>ONGD150</t>
+  </si>
+  <si>
+    <t>Ống D150</t>
+  </si>
+  <si>
+    <t>ONGD200</t>
+  </si>
+  <si>
+    <t>Ống D200</t>
+  </si>
+  <si>
+    <t>ONGD250</t>
+  </si>
+  <si>
+    <t>Ống D250</t>
+  </si>
+  <si>
+    <t>ONGD300</t>
+  </si>
+  <si>
+    <t>Ống D300</t>
+  </si>
+  <si>
+    <t>ONGD350</t>
+  </si>
+  <si>
+    <t>Ống D350</t>
+  </si>
+  <si>
+    <t>ONGD400</t>
+  </si>
+  <si>
+    <t>Ống D400</t>
+  </si>
+  <si>
+    <t>ONGD450</t>
+  </si>
+  <si>
+    <t>Ống D450</t>
+  </si>
+  <si>
+    <t>ONGD500</t>
+  </si>
+  <si>
+    <t>Ống D500</t>
+  </si>
+  <si>
+    <t>ONGD550</t>
+  </si>
+  <si>
+    <t>Ống D550</t>
+  </si>
+  <si>
+    <t>ONGD600</t>
+  </si>
+  <si>
+    <t>Ống D600</t>
+  </si>
+  <si>
+    <t>ONGD650</t>
+  </si>
+  <si>
+    <t>ONGD700</t>
+  </si>
+  <si>
+    <t>Ống D700</t>
+  </si>
+  <si>
+    <t>ONGD750</t>
+  </si>
+  <si>
+    <t>Ống D750</t>
+  </si>
+  <si>
+    <t>ONGD800</t>
+  </si>
+  <si>
+    <t>Ống D800</t>
+  </si>
+  <si>
+    <t>ONGD850</t>
+  </si>
+  <si>
+    <t>Ống D850</t>
+  </si>
+  <si>
+    <t>ONGD900</t>
+  </si>
+  <si>
+    <t>Ống D900</t>
+  </si>
+  <si>
+    <t>ONGD950</t>
+  </si>
+  <si>
+    <t>Ống D950</t>
+  </si>
+  <si>
+    <t>ONGD1000</t>
+  </si>
+  <si>
+    <t>Ống D1000</t>
+  </si>
+  <si>
+    <t>ONGD1050</t>
+  </si>
+  <si>
+    <t>Ống D1050</t>
+  </si>
+  <si>
+    <t>ONGD1100</t>
+  </si>
+  <si>
+    <t>Ống D1100</t>
+  </si>
+  <si>
+    <t>ONGD1150</t>
+  </si>
+  <si>
+    <t>Ống D1150</t>
+  </si>
+  <si>
+    <t>ONGD1200</t>
+  </si>
+  <si>
+    <t>Ống D1200</t>
+  </si>
+  <si>
+    <t>CUT90D100</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D100</t>
+  </si>
+  <si>
+    <t>Chiếc</t>
+  </si>
+  <si>
+    <t>CUT90D150</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D150</t>
+  </si>
+  <si>
+    <t>CUT90D200</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D200</t>
+  </si>
+  <si>
+    <t>CUT90D250</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D250</t>
+  </si>
+  <si>
+    <t>CUT90D300</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D300</t>
+  </si>
+  <si>
+    <t>CUT90D350</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D350</t>
+  </si>
+  <si>
+    <t>CUT90D400</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D400</t>
+  </si>
+  <si>
+    <t>CUT90D450</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D450</t>
+  </si>
+  <si>
+    <t>CUT90D500</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D500</t>
+  </si>
+  <si>
+    <t>CUT90D550</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D550</t>
+  </si>
+  <si>
+    <t>CUT90D600</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D600</t>
+  </si>
+  <si>
+    <t>CUT90D650</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D650</t>
+  </si>
+  <si>
+    <t>CUT90D700</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D700</t>
+  </si>
+  <si>
+    <t>CUT90D750</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D750</t>
+  </si>
+  <si>
+    <t>CUT90D800</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D800</t>
+  </si>
+  <si>
+    <t>CUT90D850</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D850</t>
+  </si>
+  <si>
+    <t>CUT90D900</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D900</t>
+  </si>
+  <si>
+    <t>CUT90D950</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D950</t>
+  </si>
+  <si>
+    <t>CUT90D1000</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D1000</t>
+  </si>
+  <si>
+    <t>CUT90D1050</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D1050</t>
+  </si>
+  <si>
+    <t>CUT90D1100</t>
+  </si>
+  <si>
+    <t>Cút 90 độ D1100</t>
+  </si>
+  <si>
+    <t>CUT45D100</t>
+  </si>
+  <si>
+    <t>COND150D100D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D150 về D100 rẽ nhánh D100</t>
+  </si>
+  <si>
+    <t>COND200D150D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D200 về D150 rẽ nhánh D100</t>
+  </si>
+  <si>
+    <t>COND200D200D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D200 về D200 rẽ nhánh D100</t>
+  </si>
+  <si>
+    <t>COND250D200D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D250 về D200 rẽ nhánh D100</t>
+  </si>
+  <si>
+    <t>COND250D250D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D250 về D250 rẽ nhánh D100</t>
+  </si>
+  <si>
+    <t>ONGMEMD100</t>
+  </si>
+  <si>
+    <t>Ống mềm D100</t>
+  </si>
+  <si>
+    <t>PVC</t>
+  </si>
+  <si>
+    <t>ONGMEMD150</t>
+  </si>
+  <si>
+    <t>Ống mềm D150</t>
+  </si>
+  <si>
+    <t>ONGMEMD200</t>
+  </si>
+  <si>
+    <t>Ống mềm D200</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD100</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D100</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD150</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D150</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD200</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D200</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD250</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D250</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD300</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D300</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD350</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D350</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD400</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D400</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD450</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D450</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD500</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D500</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD550</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D550</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD600</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D600</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD650</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D650</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD700</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D700</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD750</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D750</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD800</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D800</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD850</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D850</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD900</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D900</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD950</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D950</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD1000</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D1000</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD1050</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D1050</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD1100</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D1100</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD1150</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D1150</t>
+  </si>
+  <si>
+    <t>ONGTIEUAMD1200</t>
+  </si>
+  <si>
+    <t>Ống tiêu âm D1200</t>
+  </si>
+  <si>
+    <t>VANCOD100</t>
+  </si>
+  <si>
+    <t>Van cơ D100</t>
+  </si>
+  <si>
+    <t>Sơn toàn bộ chống rỉ
+Sơn phủ toàn bộ bề mặt màu ghi</t>
+  </si>
+  <si>
+    <t>VANCOD150</t>
+  </si>
+  <si>
+    <t>Van cơ D150</t>
+  </si>
+  <si>
+    <t>VANCOD200</t>
+  </si>
+  <si>
+    <t>Van cơ D200</t>
+  </si>
+  <si>
+    <t>VANCOD250</t>
+  </si>
+  <si>
+    <t>Van cơ D250</t>
+  </si>
+  <si>
+    <t>VANCOD300</t>
+  </si>
+  <si>
+    <t>Van cơ D300</t>
+  </si>
+  <si>
+    <t>VANCOD350</t>
+  </si>
+  <si>
+    <t>Van cơ D350</t>
+  </si>
+  <si>
+    <t>VANCOD400</t>
+  </si>
+  <si>
+    <t>Van cơ D400</t>
+  </si>
+  <si>
+    <t>VANCOD450</t>
+  </si>
+  <si>
+    <t>Van cơ D450</t>
+  </si>
+  <si>
+    <t>VANCOD500</t>
+  </si>
+  <si>
+    <t>Van cơ D500</t>
+  </si>
+  <si>
+    <t>VANCOD550</t>
+  </si>
+  <si>
+    <t>Van cơ D550</t>
+  </si>
+  <si>
+    <t>VANCOD600</t>
+  </si>
+  <si>
+    <t>Van cơ D600</t>
+  </si>
+  <si>
+    <t>VANCOD650</t>
+  </si>
+  <si>
+    <t>Van cơ D650</t>
+  </si>
+  <si>
+    <t>VANCOD700</t>
+  </si>
+  <si>
+    <t>Van cơ D700</t>
+  </si>
+  <si>
+    <t>VANCOD750</t>
+  </si>
+  <si>
+    <t>Van cơ D750</t>
+  </si>
+  <si>
+    <t>VANCOD800</t>
+  </si>
+  <si>
+    <t>Van cơ D800</t>
+  </si>
+  <si>
+    <t>VANCOD850</t>
+  </si>
+  <si>
+    <t>Van cơ D850</t>
+  </si>
+  <si>
+    <t>VANCOD900</t>
+  </si>
+  <si>
+    <t>Van cơ D900</t>
+  </si>
+  <si>
+    <t>VANCOD950</t>
+  </si>
+  <si>
+    <t>Van cơ D950</t>
+  </si>
+  <si>
+    <t>VANCOD1000</t>
+  </si>
+  <si>
+    <t>Van cơ D1000</t>
+  </si>
+  <si>
+    <t>VANCOD1050</t>
+  </si>
+  <si>
+    <t>Van cơ D1050</t>
+  </si>
+  <si>
+    <t>VANCOD1100</t>
+  </si>
+  <si>
+    <t>Van cơ D1100</t>
+  </si>
+  <si>
+    <t>VANCOD1150</t>
+  </si>
+  <si>
+    <t>Van cơ D1150</t>
+  </si>
+  <si>
+    <t>VANCOD1200</t>
+  </si>
+  <si>
+    <t>Van cơ D1200</t>
+  </si>
+  <si>
+    <t>VANXILANHD100</t>
+  </si>
+  <si>
+    <t>Van xi lanh D100</t>
+  </si>
+  <si>
+    <t>VANXILANHD150</t>
+  </si>
+  <si>
+    <t>Van xi lanh D150</t>
+  </si>
+  <si>
+    <t>VANXILANHD200</t>
+  </si>
+  <si>
+    <t>Van xi lanh D200</t>
+  </si>
+  <si>
+    <t>VANXILANHD250</t>
+  </si>
+  <si>
+    <t>Van xi lanh D250</t>
+  </si>
+  <si>
+    <t>VANXILANHD300</t>
+  </si>
+  <si>
+    <t>Van xi lanh D300</t>
+  </si>
+  <si>
+    <t>VANXILANHD350</t>
+  </si>
+  <si>
+    <t>Van xi lanh D350</t>
+  </si>
+  <si>
+    <t>VANXILANHD400</t>
+  </si>
+  <si>
+    <t>Van xi lanh D400</t>
+  </si>
+  <si>
+    <t>VANXILANHD450</t>
+  </si>
+  <si>
+    <t>Van xi lanh D450</t>
+  </si>
+  <si>
+    <t>VANXILANHD500</t>
+  </si>
+  <si>
+    <t>Van xi lanh D500</t>
+  </si>
+  <si>
+    <t>VANXILANHD550</t>
+  </si>
+  <si>
+    <t>Van xi lanh D550</t>
+  </si>
+  <si>
+    <t>VANXILANHD600</t>
+  </si>
+  <si>
+    <t>Van xi lanh D600</t>
+  </si>
+  <si>
+    <t>VANXILANHD650</t>
+  </si>
+  <si>
+    <t>Van xi lanh D650</t>
+  </si>
+  <si>
+    <t>VANXILANHD700</t>
+  </si>
+  <si>
+    <t>Van xi lanh D700</t>
+  </si>
+  <si>
+    <t>VANXILANHD750</t>
+  </si>
+  <si>
+    <t>Van xi lanh D750</t>
+  </si>
+  <si>
+    <t>VANXILANHD800</t>
+  </si>
+  <si>
+    <t>Van xi lanh D800</t>
+  </si>
+  <si>
+    <t>VANXILANHD850</t>
+  </si>
+  <si>
+    <t>Van xi lanh D850</t>
+  </si>
+  <si>
+    <t>VANXILANHD900</t>
+  </si>
+  <si>
+    <t>Van xi lanh D900</t>
+  </si>
+  <si>
+    <t>VANXILANHD950</t>
+  </si>
+  <si>
+    <t>Van xi lanh D950</t>
+  </si>
+  <si>
+    <t>VANXILANHD1000</t>
+  </si>
+  <si>
+    <t>Van xi lanh D1000</t>
+  </si>
+  <si>
+    <t>VANXILANHD1050</t>
+  </si>
+  <si>
+    <t>Van xi lanh D1050</t>
+  </si>
+  <si>
+    <t>VANXILANHD1100</t>
+  </si>
+  <si>
+    <t>Van xi lanh D1100</t>
+  </si>
+  <si>
+    <t>VANXILANHD1150</t>
+  </si>
+  <si>
+    <t>Van xi lanh D1150</t>
+  </si>
+  <si>
+    <t>VANXILANHD1200</t>
+  </si>
+  <si>
+    <t>Van xi lanh D1200</t>
+  </si>
+  <si>
+    <t>BICHD100</t>
+  </si>
+  <si>
+    <t>Bích D100</t>
+  </si>
+  <si>
+    <t>BICHD150</t>
+  </si>
+  <si>
+    <t>Bích D150</t>
+  </si>
+  <si>
+    <t>BICHD200</t>
+  </si>
+  <si>
+    <t>Bích D200</t>
+  </si>
+  <si>
+    <t>BICHD250</t>
+  </si>
+  <si>
+    <t>Bích D250</t>
+  </si>
+  <si>
+    <t>BICHD300</t>
+  </si>
+  <si>
+    <t>Bích D300</t>
+  </si>
+  <si>
+    <t>BICHD350</t>
+  </si>
+  <si>
+    <t>Bích D350</t>
+  </si>
+  <si>
+    <t>BICHD400</t>
+  </si>
+  <si>
+    <t>Bích D400</t>
+  </si>
+  <si>
+    <t>BICHD450</t>
+  </si>
+  <si>
+    <t>Bích D450</t>
+  </si>
+  <si>
+    <t>BICHD500</t>
+  </si>
+  <si>
+    <t>Bích D500</t>
+  </si>
+  <si>
+    <t>BICHD550</t>
+  </si>
+  <si>
+    <t>Bích D550</t>
+  </si>
+  <si>
+    <t>BICHD600</t>
+  </si>
+  <si>
+    <t>Bích D600</t>
+  </si>
+  <si>
+    <t>BICHD650</t>
+  </si>
+  <si>
+    <t>Bích D650</t>
+  </si>
+  <si>
+    <t>BICHD700</t>
+  </si>
+  <si>
+    <t>Bích D700</t>
+  </si>
+  <si>
+    <t>BICHD750</t>
+  </si>
+  <si>
+    <t>Bích D750</t>
+  </si>
+  <si>
+    <t>BICHD800</t>
+  </si>
+  <si>
+    <t>Bích D800</t>
+  </si>
+  <si>
+    <t>BICHD850</t>
+  </si>
+  <si>
+    <t>Bích D850</t>
+  </si>
+  <si>
+    <t>BICHD900</t>
+  </si>
+  <si>
+    <t>Bích D900</t>
+  </si>
+  <si>
+    <t>BICHD950</t>
+  </si>
+  <si>
+    <t>Bích D950</t>
+  </si>
+  <si>
+    <t>BICHD1000</t>
+  </si>
+  <si>
+    <t>Bích D1000</t>
+  </si>
+  <si>
+    <t>BICHD1050</t>
+  </si>
+  <si>
+    <t>Bích D1050</t>
+  </si>
+  <si>
+    <t>BICHD1100</t>
+  </si>
+  <si>
+    <t>Bích D1100</t>
   </si>
 </sst>
 </file>
@@ -106,7 +935,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,8 +957,18 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12.5"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -139,6 +978,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -167,25 +1012,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Dấu phẩy 2" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -463,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -471,203 +1324,3131 @@
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="15.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="2">
+        <v>120000</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2">
+        <v>160000</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2">
+        <v>210000</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2">
+        <v>250000</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2">
+        <v>310000</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="2">
+        <v>330000</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="2">
+        <v>420000</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="2">
+        <v>460000</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="2">
+        <v>660000</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2">
+        <v>700000</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2">
+        <v>750000</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2">
+        <v>830000</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2">
+        <v>880000</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2">
+        <v>950000</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1030000</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1150000</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1190000</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1280000</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1350000</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1450000</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1580000</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1680000</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1880000</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="2">
+        <v>75000</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="2">
+        <v>123000</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" s="2">
+        <v>180000</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="2">
+        <v>285000</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="2">
+        <v>405000</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="2">
+        <v>495000</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="2">
+        <v>660000</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="2">
+        <v>840000</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1552500</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1905000</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="2">
+        <v>2130000</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2535000</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" s="2">
+        <v>2812500</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3255000</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3570000</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="2">
+        <v>4080000</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F41" s="2">
+        <v>4605000</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" s="2">
+        <v>4965000</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F43" s="2">
+        <v>5550000</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" s="2">
+        <v>6165000</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F45" s="2">
+        <v>9135000</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F46" s="3">
+        <v>34500</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F47" s="3">
+        <v>135000</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="3">
+        <v>135000</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="3">
+        <v>180000</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F50" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="3">
+        <v>210000</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F52" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F53" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="3">
+        <v>280000</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F55" s="3">
+        <v>550000</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F56" s="3">
+        <v>900000</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1050000</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1450000</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1780000</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F61" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F62" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F63" s="3">
+        <v>3300000</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F64" s="3">
+        <v>3800000</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F65" s="3">
+        <v>4500000</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F66" s="3">
+        <v>4800000</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F67" s="3">
+        <v>5200000</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F68" s="3">
+        <v>5600000</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F69" s="3">
+        <v>6500000</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F70" s="3">
+        <v>7200000</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F71" s="3">
+        <v>7600000</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F72" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F73" s="3">
+        <v>8900000</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F74" s="3">
+        <v>9600000</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F75" s="3">
+        <v>10680000</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F76" s="3">
+        <v>11680000</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F77" s="3">
+        <v>12500000</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3">
-        <v>150000</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="D78" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F78" s="3">
+        <v>240000</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3">
-        <v>350000</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3">
-        <v>180000</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3">
-        <v>450000</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3">
-        <v>75000</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="D79" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F79" s="3">
+        <v>320000</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F80" s="3">
+        <v>420000</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F81" s="3">
+        <v>500000</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F82" s="3">
+        <v>620000</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F83" s="3">
+        <v>660000</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F84" s="3">
+        <v>840000</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F85" s="3">
+        <v>890000</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F86" s="3">
+        <v>1980000</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F87" s="3">
+        <v>2100000</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F88" s="3">
+        <v>2250000</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F89" s="3">
+        <v>2490000</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F90" s="3">
+        <v>2640000</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F91" s="3">
+        <v>2850000</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F92" s="3">
+        <v>3090000</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F93" s="3">
+        <v>3450000</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F94" s="3">
+        <v>7600000</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F95" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F96" s="3">
+        <v>8900000</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F97" s="3">
+        <v>9600000</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F98" s="3">
+        <v>10680000</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F99" s="3">
+        <v>11680000</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F100" s="3">
+        <v>13680000</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F101" s="3">
+        <v>800000</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F102" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F103" s="3">
+        <v>1008000</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F104" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F105" s="3">
+        <v>1488000</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F106" s="3">
+        <v>1584000</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F107" s="3">
+        <v>2016000</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F108" s="3">
+        <v>2136000</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F109" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F110" s="3">
+        <v>3780000</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F111" s="3">
+        <v>4050000</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F112" s="3">
+        <v>4482000</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F113" s="3">
+        <v>4752000</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F114" s="3">
+        <v>5130000</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F115" s="3">
+        <v>5562000</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F116" s="3">
+        <v>6210000</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F117" s="3">
+        <v>13680000</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F118" s="3">
+        <v>14400000</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F119" s="3">
+        <v>16020000</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F120" s="3">
+        <v>17280000</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F121" s="3">
+        <v>19224000</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F122" s="3">
+        <v>21024000</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F123" s="3">
+        <v>24624000</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F124" s="3">
+        <v>15000</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F125" s="3">
+        <v>19500</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F126" s="3">
+        <v>25000</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F127" s="3">
+        <v>30000</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F128" s="3">
+        <v>40000</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F129" s="3">
+        <v>45000</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F130" s="3">
+        <v>78000</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F131" s="3">
+        <v>87000</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F132" s="3">
+        <v>96000</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F133" s="3">
+        <v>105000</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F134" s="3">
+        <v>114000</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F135" s="3">
+        <v>142500</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F136" s="3">
+        <v>153000</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F137" s="3">
+        <v>163500</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F138" s="3">
+        <v>232500</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F139" s="3">
+        <v>247500</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F140" s="3">
+        <v>295500</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F141" s="3">
+        <v>312000</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F142" s="3">
+        <v>410000</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F143" s="3">
+        <v>434000</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F144" s="3">
+        <v>469500</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="176">
   <si>
     <t>Ống D650</t>
   </si>
@@ -494,16 +494,293 @@
   </si>
   <si>
     <t>Bích D1100</t>
+  </si>
+  <si>
+    <t>Quạt ly tâm chạy gián tiếp
+gối bi ngâm dầu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 16.000-22.000m3/h
+Residual pressure / Áp suất: P = 3000-4200 Pa
+Rate Power / Công suất định mức: P =18.5 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <t>Bộ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">THÁP LỌC D2000
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H=mm
+2 dàn phun mưa 
+1 lớp đệm
+1 lớp tách ẩm</t>
+    </r>
+  </si>
+  <si>
+    <t>Thép SS400
+?mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SÀN THAO TÁC LẤY MẪU KHÍ THẢI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kích thước: ?x?x?mm
+Sàn thao tác làm dày 3mm-u100
+mặt sàn lưới dập dãn dày 3mm, bao gồm thang leo có lồng bảo vệ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HÙNG THAN HOẠT TÍNH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kích thước: DxRxCmm
+ Có ? khay đựng than kích thước:?x?x?mm
+? viên than kích thước 100x100x100mm
+có cửa thay than</t>
+    </r>
+  </si>
+  <si>
+    <t>Thép SS400
+1,5mm</t>
+  </si>
+  <si>
+    <t>VAN XOAY 1.5 30V/P</t>
+  </si>
+  <si>
+    <t>Đường ống nối từ thùng lọc đến tháp lọc D?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ỐNG KHÓI D?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kích thước: D?x?mm,  giá đỡ ống thoát khí </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TỦ HÚT BỤI STHB-8 15KW
+25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TỦ HÚT BỤI STHB-1 1.5KW
+6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TỦ HÚT BỤI STHB-2 2.2KW
+6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TỦ HÚT BỤI STHB-3 3KW
+6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TỦ HÚT BỤI STHB-4 4KW
+8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TỦ HÚT BỤI STHB-5 5.5KW
+12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TỦ HÚT BỤI STHB-6 7.5KW
+16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TỦ HÚT BỤI STHB-7 1KW
+24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CYCLONE D?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>thân vỏ 2mm , H=?mm
+khung đỡ thép hộp 50x50x2,3mm</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,8 +812,84 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -555,8 +908,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -579,31 +938,202 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Dấu phẩy 2" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2"/>
@@ -884,15 +1414,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="17" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="14" style="38" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -908,7 +1438,7 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -916,2674 +1446,2981 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="33">
         <v>120000</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="33">
         <v>160000</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B4" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="33">
         <v>210000</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B5" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="33">
         <v>250000</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="B6" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="33">
         <v>310000</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="B7" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="33">
         <v>330000</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="B8" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="33">
         <v>420000</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="B9" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="33">
         <v>460000</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="B10" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="33">
         <v>660000</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="B11" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="33">
         <v>700000</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="B12" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="33">
         <v>750000</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="B13" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="33">
         <v>830000</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="B14" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="33">
         <v>880000</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="B15" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="33">
         <v>950000</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="B16" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="33">
         <v>1030000</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="B17" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="33">
         <v>1150000</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="B18" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="33">
         <v>1190000</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="B19" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="33">
         <v>1280000</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="B20" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="33">
         <v>1350000</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="B21" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="33">
         <v>1450000</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="B22" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="33">
         <v>1580000</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="B23" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="33">
         <v>1680000</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="B24" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="33">
         <v>1880000</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="B25" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="33">
         <v>75000</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="2">
+      <c r="B26" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="33">
         <v>123000</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="2">
+      <c r="B27" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="33">
         <v>180000</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="2">
+      <c r="B28" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="33">
         <v>285000</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="2">
+      <c r="B29" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="33">
         <v>405000</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="B30" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="33">
         <v>495000</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="B31" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="33">
         <v>660000</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="2">
+      <c r="B32" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="33">
         <v>840000</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="2">
+      <c r="B33" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="33">
         <v>1552500</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="2">
+      <c r="B34" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="33">
         <v>1905000</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="2">
+      <c r="B35" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="33">
         <v>2130000</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="2">
+      <c r="B36" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="33">
         <v>2535000</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="2">
+      <c r="B37" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="33">
         <v>2812500</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="2">
+      <c r="B38" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="33">
         <v>3255000</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="2">
+      <c r="B39" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="33">
         <v>3570000</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E40" s="2">
+      <c r="B40" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="33">
         <v>4080000</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E41" s="2">
+      <c r="B41" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="33">
         <v>4605000</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="2">
+      <c r="B42" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="33">
         <v>4965000</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="2">
+      <c r="B43" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="33">
         <v>5550000</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="2">
+      <c r="B44" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="33">
         <v>6165000</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="2">
+      <c r="B45" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="33">
         <v>9135000</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="30" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="B46" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="34">
         <v>34500</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="F46" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="B47" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="34">
         <v>135000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="F47" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="B48" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="34">
         <v>135000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="F48" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="3">
+      <c r="B49" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="34">
         <v>180000</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="F49" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="3">
+      <c r="B50" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="34">
         <v>190000</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="F50" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E51" s="3">
+      <c r="B51" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="34">
         <v>210000</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="C52" s="16"/>
+      <c r="D52" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="34">
         <v>160000</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="3">
+      <c r="C53" s="16"/>
+      <c r="D53" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="34">
         <v>220000</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="C54" s="16"/>
+      <c r="D54" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="34">
         <v>280000</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="3">
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="34">
         <v>550000</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="3">
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="34">
         <v>900000</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="34">
         <v>1050000</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E58" s="3">
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="34">
         <v>1450000</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="34">
         <v>1780000</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="34">
         <v>2000000</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E61" s="3">
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="34">
         <v>2500000</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F61" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="34">
         <v>2800000</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="3">
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="34">
         <v>3300000</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="3">
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="34">
         <v>3800000</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="3">
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="34">
         <v>4500000</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="34">
         <v>4800000</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="3">
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="34">
         <v>5200000</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="3">
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="34">
         <v>5600000</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="3">
+      <c r="B69" s="16"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="34">
         <v>6500000</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="3">
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="34">
         <v>7200000</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="3">
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="34">
         <v>7600000</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="34">
         <v>8000000</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="3">
+      <c r="B73" s="16"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="34">
         <v>8900000</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="3">
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="34">
         <v>9600000</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="3">
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="34">
         <v>10680000</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="34">
         <v>11680000</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="3">
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="34">
         <v>12500000</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="3">
+      <c r="B78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="34">
         <v>240000</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="3">
+      <c r="B79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="34">
         <v>320000</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="3">
+      <c r="B80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="34">
         <v>420000</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="B81" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="34">
         <v>500000</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="3">
+      <c r="B82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="34">
         <v>620000</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="B83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="34">
         <v>660000</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" s="3">
+      <c r="B84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="34">
         <v>840000</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E85" s="3">
+      <c r="B85" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="34">
         <v>890000</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" s="3">
+      <c r="B86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="34">
         <v>1980000</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B87" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="3">
+      <c r="B87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="34">
         <v>2100000</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="3">
+      <c r="B88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="34">
         <v>2250000</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B89" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="B89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="34">
         <v>2490000</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E90" s="3">
+      <c r="B90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="34">
         <v>2640000</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="B91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="34">
         <v>2850000</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="B92" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E92" s="3">
+      <c r="B92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="34">
         <v>3090000</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B93" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E93" s="3">
+      <c r="B93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="34">
         <v>3450000</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="B94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="34">
         <v>7600000</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="3">
+      <c r="B95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="34">
         <v>8000000</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="B96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="34">
         <v>8900000</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="3">
+      <c r="B97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D97" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="34">
         <v>9600000</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B98" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E98" s="3">
+      <c r="B98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="34">
         <v>10680000</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B99" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E99" s="3">
+      <c r="B99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="34">
         <v>11680000</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B100" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="B100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="34">
         <v>13680000</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="B101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="34">
         <v>800000</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="3">
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="34">
         <v>1000000</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="3">
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="34">
         <v>1008000</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E104" s="3">
+      <c r="B104" s="16"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="34">
         <v>1200000</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E105" s="3">
+      <c r="B105" s="16"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="34">
         <v>1488000</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E106" s="3">
+      <c r="B106" s="16"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="34">
         <v>1584000</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
+      <c r="A107" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" s="3">
+      <c r="B107" s="16"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="34">
         <v>2016000</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E108" s="3">
+      <c r="B108" s="16"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="34">
         <v>2136000</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
+      <c r="A109" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E109" s="3">
+      <c r="B109" s="16"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="34">
         <v>3000000</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E110" s="3">
+      <c r="B110" s="16"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="34">
         <v>3780000</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E111" s="3">
+      <c r="B111" s="16"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="34">
         <v>4050000</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E112" s="3">
+      <c r="B112" s="16"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="34">
         <v>4482000</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
+      <c r="A113" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E113" s="3">
+      <c r="B113" s="16"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="34">
         <v>4752000</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E114" s="3">
+      <c r="B114" s="16"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="34">
         <v>5130000</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
+      <c r="A115" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E115" s="3">
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="34">
         <v>5562000</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E116" s="3">
+      <c r="B116" s="16"/>
+      <c r="C116" s="16"/>
+      <c r="D116" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="34">
         <v>6210000</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
+      <c r="A117" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E117" s="3">
+      <c r="B117" s="16"/>
+      <c r="C117" s="16"/>
+      <c r="D117" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="34">
         <v>13680000</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
+      <c r="A118" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E118" s="3">
+      <c r="B118" s="16"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="34">
         <v>14400000</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
+      <c r="A119" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E119" s="3">
+      <c r="B119" s="16"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="34">
         <v>16020000</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
+      <c r="A120" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" s="3">
+      <c r="B120" s="16"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="34">
         <v>17280000</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
+      <c r="A121" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E121" s="3">
+      <c r="B121" s="16"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="34">
         <v>19224000</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E122" s="3">
+      <c r="B122" s="16"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="34">
         <v>21024000</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E123" s="3">
+      <c r="B123" s="16"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="34">
         <v>24624000</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B124" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E124" s="3">
+      <c r="B124" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D124" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="34">
         <v>15000</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B125" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E125" s="3">
+      <c r="B125" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D125" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="34">
         <v>19500</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B126" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E126" s="3">
+      <c r="B126" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D126" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" s="34">
         <v>25000</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="B127" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E127" s="3">
+      <c r="B127" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D127" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="34">
         <v>30000</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F127" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
+      <c r="A128" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="B128" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E128" s="3">
+      <c r="B128" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D128" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="34">
         <v>40000</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
+      <c r="A129" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E129" s="3">
+      <c r="B129" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" s="34">
         <v>45000</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
+      <c r="A130" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="B130" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E130" s="3">
+      <c r="B130" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="34">
         <v>78000</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
+      <c r="A131" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E131" s="3">
+      <c r="B131" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D131" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" s="34">
         <v>87000</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
+      <c r="A132" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B132" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E132" s="3">
+      <c r="B132" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D132" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="34">
         <v>96000</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
+      <c r="A133" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E133" s="3">
+      <c r="B133" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" s="34">
         <v>105000</v>
       </c>
-      <c r="F133" s="3" t="s">
+      <c r="F133" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
+      <c r="A134" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B134" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E134" s="3">
+      <c r="B134" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D134" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="34">
         <v>114000</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="F134" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
+      <c r="A135" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E135" s="3">
+      <c r="B135" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D135" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="34">
         <v>142500</v>
       </c>
-      <c r="F135" s="3" t="s">
+      <c r="F135" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
+      <c r="A136" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B136" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E136" s="3">
+      <c r="B136" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" s="34">
         <v>153000</v>
       </c>
-      <c r="F136" s="3" t="s">
+      <c r="F136" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="s">
+      <c r="A137" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E137" s="3">
+      <c r="B137" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D137" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" s="34">
         <v>163500</v>
       </c>
-      <c r="F137" s="3" t="s">
+      <c r="F137" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
+      <c r="A138" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E138" s="3">
+      <c r="B138" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D138" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" s="34">
         <v>232500</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="F138" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="s">
+      <c r="A139" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B139" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E139" s="3">
+      <c r="B139" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D139" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="34">
         <v>247500</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="F139" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="s">
+      <c r="A140" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E140" s="3">
+      <c r="B140" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D140" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" s="34">
         <v>295500</v>
       </c>
-      <c r="F140" s="3" t="s">
+      <c r="F140" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
+      <c r="A141" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E141" s="3">
+      <c r="B141" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D141" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="34">
         <v>312000</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="F141" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
+      <c r="A142" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B142" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E142" s="3">
+      <c r="B142" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D142" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="34">
         <v>410000</v>
       </c>
-      <c r="F142" s="3" t="s">
+      <c r="F142" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="s">
+      <c r="A143" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E143" s="3">
+      <c r="B143" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D143" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="34">
         <v>434000</v>
       </c>
-      <c r="F143" s="3" t="s">
+      <c r="F143" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
+      <c r="A144" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E144" s="3">
+      <c r="B144" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D144" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="34">
         <v>469500</v>
       </c>
-      <c r="F144" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="F144" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" s="4" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="34">
+        <v>47979000</v>
+      </c>
+      <c r="F145" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G145" s="5"/>
+    </row>
+    <row r="146" spans="1:7" s="11" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D146" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E146" s="35"/>
+      <c r="F146" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="G146" s="12"/>
+    </row>
+    <row r="147" spans="1:7" s="11" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D147" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E147" s="35"/>
+      <c r="F147" s="31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" s="11" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D148" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E148" s="35"/>
+      <c r="F148" s="31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" s="19" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B149" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D149" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="E149" s="36"/>
+      <c r="F149" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="G149" s="11"/>
+    </row>
+    <row r="150" spans="1:7" s="22" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B150" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C150" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D150" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="E150" s="37"/>
+      <c r="F150" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B151" s="7"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="34">
+        <v>13880000</v>
+      </c>
+      <c r="F151" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="B152" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D152" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="46">
+        <v>32680000</v>
+      </c>
+      <c r="F152" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="B153" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D153" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="46">
+        <v>36800000</v>
+      </c>
+      <c r="F153" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="B154" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D154" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="46">
+        <v>43680000</v>
+      </c>
+      <c r="F154" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="B155" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="46">
+        <v>48680000</v>
+      </c>
+      <c r="F155" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="B156" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D156" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="46">
+        <v>54680000</v>
+      </c>
+      <c r="F156" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="B157" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D157" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="46">
+        <v>69860000</v>
+      </c>
+      <c r="F157" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="B158" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D158" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="46">
+        <v>99680000</v>
+      </c>
+      <c r="F158" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" s="39" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B159" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D159" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" s="45"/>
+      <c r="F159" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G159" s="5"/>
+    </row>
+    <row r="160" spans="1:7" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="B160" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="E160" s="45"/>
+      <c r="F160" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G160" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -806,11 +806,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12.5"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -887,6 +882,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -991,51 +993,45 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1047,7 +1043,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1056,28 +1052,28 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1086,50 +1082,65 @@
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1417,28 +1428,28 @@
   <dimension ref="A1:G160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" style="17" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="17" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="17" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="14" style="38" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="39" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="39" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="14" style="49" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="36" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1446,2981 +1457,2981 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="16" t="s">
+      <c r="B2" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="42">
         <v>120000</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="16" t="s">
+      <c r="B3" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="42">
         <v>160000</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="16" t="s">
+      <c r="B4" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="42">
         <v>210000</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="16" t="s">
+      <c r="B5" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="42">
         <v>250000</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="16" t="s">
+      <c r="B6" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="42">
         <v>310000</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="16" t="s">
+      <c r="B7" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="42">
         <v>330000</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="B8" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="42">
         <v>420000</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="16" t="s">
+      <c r="B9" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="42">
         <v>460000</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="B10" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="42">
         <v>660000</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="16" t="s">
+      <c r="B11" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="42">
         <v>700000</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="16" t="s">
+      <c r="B12" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="42">
         <v>750000</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="16" t="s">
+      <c r="B13" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="42">
         <v>830000</v>
       </c>
-      <c r="F13" s="30" t="s">
+      <c r="F13" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="16" t="s">
+      <c r="B14" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="42">
         <v>880000</v>
       </c>
-      <c r="F14" s="30" t="s">
+      <c r="F14" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="16" t="s">
+      <c r="B15" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="42">
         <v>950000</v>
       </c>
-      <c r="F15" s="30" t="s">
+      <c r="F15" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="16" t="s">
+      <c r="B16" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="42">
         <v>1030000</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="F16" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="16" t="s">
+      <c r="B17" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="42">
         <v>1150000</v>
       </c>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="16" t="s">
+      <c r="B18" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="42">
         <v>1190000</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="16" t="s">
+      <c r="B19" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="42">
         <v>1280000</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="16" t="s">
+      <c r="B20" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="42">
         <v>1350000</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="16" t="s">
+      <c r="B21" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="42">
         <v>1450000</v>
       </c>
-      <c r="F21" s="30" t="s">
+      <c r="F21" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="16" t="s">
+      <c r="B22" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="42">
         <v>1580000</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="16" t="s">
+      <c r="B23" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="42">
         <v>1680000</v>
       </c>
-      <c r="F23" s="30" t="s">
+      <c r="F23" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="16" t="s">
+      <c r="B24" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="42">
         <v>1880000</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="33">
+      <c r="B25" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="42">
         <v>75000</v>
       </c>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="33">
+      <c r="B26" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="42">
         <v>123000</v>
       </c>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="33">
+      <c r="B27" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="42">
         <v>180000</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="33">
+      <c r="B28" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="42">
         <v>285000</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="33">
+      <c r="B29" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="42">
         <v>405000</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="33">
+      <c r="B30" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="42">
         <v>495000</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="33">
+      <c r="B31" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="42">
         <v>660000</v>
       </c>
-      <c r="F31" s="30" t="s">
+      <c r="F31" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="33">
+      <c r="B32" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="42">
         <v>840000</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F32" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="33">
+      <c r="B33" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="42">
         <v>1552500</v>
       </c>
-      <c r="F33" s="30" t="s">
+      <c r="F33" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="33">
+      <c r="B34" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="42">
         <v>1905000</v>
       </c>
-      <c r="F34" s="30" t="s">
+      <c r="F34" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="33">
+      <c r="B35" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="42">
         <v>2130000</v>
       </c>
-      <c r="F35" s="30" t="s">
+      <c r="F35" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="33">
+      <c r="B36" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="42">
         <v>2535000</v>
       </c>
-      <c r="F36" s="30" t="s">
+      <c r="F36" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="33">
+      <c r="B37" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="42">
         <v>2812500</v>
       </c>
-      <c r="F37" s="30" t="s">
+      <c r="F37" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="33">
+      <c r="B38" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="42">
         <v>3255000</v>
       </c>
-      <c r="F38" s="30" t="s">
+      <c r="F38" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="33">
+      <c r="B39" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="42">
         <v>3570000</v>
       </c>
-      <c r="F39" s="30" t="s">
+      <c r="F39" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E40" s="33">
+      <c r="B40" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="42">
         <v>4080000</v>
       </c>
-      <c r="F40" s="30" t="s">
+      <c r="F40" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E41" s="33">
+      <c r="B41" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="42">
         <v>4605000</v>
       </c>
-      <c r="F41" s="30" t="s">
+      <c r="F41" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="33">
+      <c r="B42" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="42">
         <v>4965000</v>
       </c>
-      <c r="F42" s="30" t="s">
+      <c r="F42" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="33">
+      <c r="B43" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="42">
         <v>5550000</v>
       </c>
-      <c r="F43" s="30" t="s">
+      <c r="F43" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="33">
+      <c r="B44" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="42">
         <v>6165000</v>
       </c>
-      <c r="F44" s="30" t="s">
+      <c r="F44" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="33">
+      <c r="B45" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="42">
         <v>9135000</v>
       </c>
-      <c r="F45" s="30" t="s">
+      <c r="F45" s="28" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" s="34">
+      <c r="B46" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="43">
         <v>34500</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="F46" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="34">
+      <c r="B47" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="43">
         <v>135000</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="34">
+      <c r="B48" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="43">
         <v>135000</v>
       </c>
-      <c r="F48" s="16" t="s">
+      <c r="F48" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="34">
+      <c r="B49" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="43">
         <v>180000</v>
       </c>
-      <c r="F49" s="16" t="s">
+      <c r="F49" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="34">
+      <c r="B50" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="43">
         <v>190000</v>
       </c>
-      <c r="F50" s="16" t="s">
+      <c r="F50" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E51" s="34">
+      <c r="B51" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="43">
         <v>210000</v>
       </c>
-      <c r="F51" s="16" t="s">
+      <c r="F51" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="34">
+      <c r="C52" s="14"/>
+      <c r="D52" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="43">
         <v>160000</v>
       </c>
-      <c r="F52" s="16" t="s">
+      <c r="F52" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="34">
+      <c r="C53" s="14"/>
+      <c r="D53" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="43">
         <v>220000</v>
       </c>
-      <c r="F53" s="16" t="s">
+      <c r="F53" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" s="34">
+      <c r="C54" s="14"/>
+      <c r="D54" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="43">
         <v>280000</v>
       </c>
-      <c r="F54" s="16" t="s">
+      <c r="F54" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="34">
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="43">
         <v>550000</v>
       </c>
-      <c r="F55" s="16" t="s">
+      <c r="F55" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="34">
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="43">
         <v>900000</v>
       </c>
-      <c r="F56" s="16" t="s">
+      <c r="F56" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E57" s="34">
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="43">
         <v>1050000</v>
       </c>
-      <c r="F57" s="16" t="s">
+      <c r="F57" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E58" s="34">
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="43">
         <v>1450000</v>
       </c>
-      <c r="F58" s="16" t="s">
+      <c r="F58" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" s="34">
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="43">
         <v>1780000</v>
       </c>
-      <c r="F59" s="16" t="s">
+      <c r="F59" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E60" s="34">
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="43">
         <v>2000000</v>
       </c>
-      <c r="F60" s="16" t="s">
+      <c r="F60" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E61" s="34">
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="43">
         <v>2500000</v>
       </c>
-      <c r="F61" s="16" t="s">
+      <c r="F61" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="34">
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="43">
         <v>2800000</v>
       </c>
-      <c r="F62" s="16" t="s">
+      <c r="F62" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="34">
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="43">
         <v>3300000</v>
       </c>
-      <c r="F63" s="16" t="s">
+      <c r="F63" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="34">
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="43">
         <v>3800000</v>
       </c>
-      <c r="F64" s="16" t="s">
+      <c r="F64" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="34">
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="43">
         <v>4500000</v>
       </c>
-      <c r="F65" s="16" t="s">
+      <c r="F65" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="34">
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="43">
         <v>4800000</v>
       </c>
-      <c r="F66" s="16" t="s">
+      <c r="F66" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="34">
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="43">
         <v>5200000</v>
       </c>
-      <c r="F67" s="16" t="s">
+      <c r="F67" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="34">
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="43">
         <v>5600000</v>
       </c>
-      <c r="F68" s="16" t="s">
+      <c r="F68" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="34">
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="43">
         <v>6500000</v>
       </c>
-      <c r="F69" s="16" t="s">
+      <c r="F69" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="34">
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="43">
         <v>7200000</v>
       </c>
-      <c r="F70" s="16" t="s">
+      <c r="F70" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="34">
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="43">
         <v>7600000</v>
       </c>
-      <c r="F71" s="16" t="s">
+      <c r="F71" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="34">
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="43">
         <v>8000000</v>
       </c>
-      <c r="F72" s="16" t="s">
+      <c r="F72" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="34">
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="43">
         <v>8900000</v>
       </c>
-      <c r="F73" s="16" t="s">
+      <c r="F73" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="34">
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="43">
         <v>9600000</v>
       </c>
-      <c r="F74" s="16" t="s">
+      <c r="F74" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="34">
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="43">
         <v>10680000</v>
       </c>
-      <c r="F75" s="16" t="s">
+      <c r="F75" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="34">
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="43">
         <v>11680000</v>
       </c>
-      <c r="F76" s="16" t="s">
+      <c r="F76" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="34">
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="43">
         <v>12500000</v>
       </c>
-      <c r="F77" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="16" t="s">
+      <c r="F77" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="34">
+      <c r="B78" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="43">
         <v>240000</v>
       </c>
-      <c r="F78" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="16" t="s">
+      <c r="F78" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A79" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D79" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="34">
+      <c r="B79" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="43">
         <v>320000</v>
       </c>
-      <c r="F79" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="16" t="s">
+      <c r="F79" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A80" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="34">
+      <c r="B80" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="43">
         <v>420000</v>
       </c>
-      <c r="F80" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="16" t="s">
+      <c r="F80" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="34">
+      <c r="B81" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="43">
         <v>500000</v>
       </c>
-      <c r="F81" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="16" t="s">
+      <c r="F81" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A82" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D82" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="34">
+      <c r="B82" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="43">
         <v>620000</v>
       </c>
-      <c r="F82" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="16" t="s">
+      <c r="F82" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A83" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="34">
+      <c r="B83" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="43">
         <v>660000</v>
       </c>
-      <c r="F83" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
+      <c r="F83" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A84" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D84" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" s="34">
+      <c r="B84" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="43">
         <v>840000</v>
       </c>
-      <c r="F84" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
+      <c r="F84" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A85" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D85" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E85" s="34">
+      <c r="B85" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="43">
         <v>890000</v>
       </c>
-      <c r="F85" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="16" t="s">
+      <c r="F85" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A86" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D86" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" s="34">
+      <c r="B86" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="43">
         <v>1980000</v>
       </c>
-      <c r="F86" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
+      <c r="F86" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A87" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="34">
+      <c r="B87" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="43">
         <v>2100000</v>
       </c>
-      <c r="F87" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="16" t="s">
+      <c r="F87" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A88" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D88" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="34">
+      <c r="B88" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="43">
         <v>2250000</v>
       </c>
-      <c r="F88" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
+      <c r="F88" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A89" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D89" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="34">
+      <c r="B89" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="43">
         <v>2490000</v>
       </c>
-      <c r="F89" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="16" t="s">
+      <c r="F89" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A90" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D90" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E90" s="34">
+      <c r="B90" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="43">
         <v>2640000</v>
       </c>
-      <c r="F90" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
+      <c r="F90" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A91" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D91" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E91" s="34">
+      <c r="B91" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="43">
         <v>2850000</v>
       </c>
-      <c r="F91" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="16" t="s">
+      <c r="F91" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A92" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D92" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E92" s="34">
+      <c r="B92" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="43">
         <v>3090000</v>
       </c>
-      <c r="F92" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
+      <c r="F92" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A93" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D93" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E93" s="34">
+      <c r="B93" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="43">
         <v>3450000</v>
       </c>
-      <c r="F93" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="16" t="s">
+      <c r="F93" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A94" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D94" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E94" s="34">
+      <c r="B94" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="43">
         <v>7600000</v>
       </c>
-      <c r="F94" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="16" t="s">
+      <c r="F94" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A95" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D95" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="34">
+      <c r="B95" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="43">
         <v>8000000</v>
       </c>
-      <c r="F95" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="16" t="s">
+      <c r="F95" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A96" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="34">
+      <c r="B96" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="43">
         <v>8900000</v>
       </c>
-      <c r="F96" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
+      <c r="F96" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A97" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D97" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="34">
+      <c r="B97" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="43">
         <v>9600000</v>
       </c>
-      <c r="F97" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="16" t="s">
+      <c r="F97" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A98" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D98" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E98" s="34">
+      <c r="B98" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="43">
         <v>10680000</v>
       </c>
-      <c r="F98" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="16" t="s">
+      <c r="F98" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A99" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D99" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E99" s="34">
+      <c r="B99" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="43">
         <v>11680000</v>
       </c>
-      <c r="F99" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="16" t="s">
+      <c r="F99" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A100" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="34">
+      <c r="B100" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="43">
         <v>13680000</v>
       </c>
-      <c r="F100" s="16" t="s">
+      <c r="F100" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B101" s="16"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="34">
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="43">
         <v>800000</v>
       </c>
-      <c r="F101" s="16" t="s">
+      <c r="F101" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B102" s="16"/>
-      <c r="C102" s="16"/>
-      <c r="D102" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="34">
+      <c r="B102" s="14"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="43">
         <v>1000000</v>
       </c>
-      <c r="F102" s="16" t="s">
+      <c r="F102" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="16"/>
-      <c r="C103" s="16"/>
-      <c r="D103" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="34">
+      <c r="B103" s="14"/>
+      <c r="C103" s="14"/>
+      <c r="D103" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="43">
         <v>1008000</v>
       </c>
-      <c r="F103" s="16" t="s">
+      <c r="F103" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="16"/>
-      <c r="C104" s="16"/>
-      <c r="D104" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E104" s="34">
+      <c r="B104" s="14"/>
+      <c r="C104" s="14"/>
+      <c r="D104" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="43">
         <v>1200000</v>
       </c>
-      <c r="F104" s="16" t="s">
+      <c r="F104" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B105" s="16"/>
-      <c r="C105" s="16"/>
-      <c r="D105" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E105" s="34">
+      <c r="B105" s="14"/>
+      <c r="C105" s="14"/>
+      <c r="D105" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="43">
         <v>1488000</v>
       </c>
-      <c r="F105" s="16" t="s">
+      <c r="F105" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B106" s="16"/>
-      <c r="C106" s="16"/>
-      <c r="D106" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E106" s="34">
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="43">
         <v>1584000</v>
       </c>
-      <c r="F106" s="16" t="s">
+      <c r="F106" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B107" s="16"/>
-      <c r="C107" s="16"/>
-      <c r="D107" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" s="34">
+      <c r="B107" s="14"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="43">
         <v>2016000</v>
       </c>
-      <c r="F107" s="16" t="s">
+      <c r="F107" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A108" s="16" t="s">
+      <c r="A108" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B108" s="16"/>
-      <c r="C108" s="16"/>
-      <c r="D108" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E108" s="34">
+      <c r="B108" s="14"/>
+      <c r="C108" s="14"/>
+      <c r="D108" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="43">
         <v>2136000</v>
       </c>
-      <c r="F108" s="16" t="s">
+      <c r="F108" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A109" s="16" t="s">
+      <c r="A109" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B109" s="16"/>
-      <c r="C109" s="16"/>
-      <c r="D109" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E109" s="34">
+      <c r="B109" s="14"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="43">
         <v>3000000</v>
       </c>
-      <c r="F109" s="16" t="s">
+      <c r="F109" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A110" s="16" t="s">
+      <c r="A110" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="B110" s="16"/>
-      <c r="C110" s="16"/>
-      <c r="D110" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E110" s="34">
+      <c r="B110" s="14"/>
+      <c r="C110" s="14"/>
+      <c r="D110" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="43">
         <v>3780000</v>
       </c>
-      <c r="F110" s="16" t="s">
+      <c r="F110" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A111" s="16" t="s">
+      <c r="A111" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
-      <c r="D111" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E111" s="34">
+      <c r="B111" s="14"/>
+      <c r="C111" s="14"/>
+      <c r="D111" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="43">
         <v>4050000</v>
       </c>
-      <c r="F111" s="16" t="s">
+      <c r="F111" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A112" s="16" t="s">
+      <c r="A112" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B112" s="16"/>
-      <c r="C112" s="16"/>
-      <c r="D112" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E112" s="34">
+      <c r="B112" s="14"/>
+      <c r="C112" s="14"/>
+      <c r="D112" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="43">
         <v>4482000</v>
       </c>
-      <c r="F112" s="16" t="s">
+      <c r="F112" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A113" s="16" t="s">
+      <c r="A113" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B113" s="16"/>
-      <c r="C113" s="16"/>
-      <c r="D113" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E113" s="34">
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="43">
         <v>4752000</v>
       </c>
-      <c r="F113" s="16" t="s">
+      <c r="F113" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A114" s="16" t="s">
+      <c r="A114" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B114" s="16"/>
-      <c r="C114" s="16"/>
-      <c r="D114" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E114" s="34">
+      <c r="B114" s="14"/>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="43">
         <v>5130000</v>
       </c>
-      <c r="F114" s="16" t="s">
+      <c r="F114" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A115" s="16" t="s">
+      <c r="A115" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E115" s="34">
+      <c r="B115" s="14"/>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="43">
         <v>5562000</v>
       </c>
-      <c r="F115" s="16" t="s">
+      <c r="F115" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A116" s="16" t="s">
+      <c r="A116" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B116" s="16"/>
-      <c r="C116" s="16"/>
-      <c r="D116" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E116" s="34">
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="43">
         <v>6210000</v>
       </c>
-      <c r="F116" s="16" t="s">
+      <c r="F116" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A117" s="16" t="s">
+      <c r="A117" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B117" s="16"/>
-      <c r="C117" s="16"/>
-      <c r="D117" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E117" s="34">
+      <c r="B117" s="14"/>
+      <c r="C117" s="14"/>
+      <c r="D117" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="43">
         <v>13680000</v>
       </c>
-      <c r="F117" s="16" t="s">
+      <c r="F117" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A118" s="16" t="s">
+      <c r="A118" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="B118" s="16"/>
-      <c r="C118" s="16"/>
-      <c r="D118" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E118" s="34">
+      <c r="B118" s="14"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="43">
         <v>14400000</v>
       </c>
-      <c r="F118" s="16" t="s">
+      <c r="F118" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A119" s="16" t="s">
+      <c r="A119" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B119" s="16"/>
-      <c r="C119" s="16"/>
-      <c r="D119" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E119" s="34">
+      <c r="B119" s="14"/>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="43">
         <v>16020000</v>
       </c>
-      <c r="F119" s="16" t="s">
+      <c r="F119" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A120" s="16" t="s">
+      <c r="A120" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B120" s="16"/>
-      <c r="C120" s="16"/>
-      <c r="D120" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" s="34">
+      <c r="B120" s="14"/>
+      <c r="C120" s="14"/>
+      <c r="D120" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="43">
         <v>17280000</v>
       </c>
-      <c r="F120" s="16" t="s">
+      <c r="F120" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A121" s="16" t="s">
+      <c r="A121" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="B121" s="16"/>
-      <c r="C121" s="16"/>
-      <c r="D121" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E121" s="34">
+      <c r="B121" s="14"/>
+      <c r="C121" s="14"/>
+      <c r="D121" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="43">
         <v>19224000</v>
       </c>
-      <c r="F121" s="16" t="s">
+      <c r="F121" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A122" s="16" t="s">
+      <c r="A122" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B122" s="16"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E122" s="34">
+      <c r="B122" s="14"/>
+      <c r="C122" s="14"/>
+      <c r="D122" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="43">
         <v>21024000</v>
       </c>
-      <c r="F122" s="16" t="s">
+      <c r="F122" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A123" s="16" t="s">
+      <c r="A123" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B123" s="16"/>
-      <c r="C123" s="16"/>
-      <c r="D123" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E123" s="34">
+      <c r="B123" s="14"/>
+      <c r="C123" s="14"/>
+      <c r="D123" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="43">
         <v>24624000</v>
       </c>
-      <c r="F123" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="16" t="s">
+      <c r="F123" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A124" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B124" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D124" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E124" s="34">
+      <c r="B124" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D124" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="43">
         <v>15000</v>
       </c>
-      <c r="F124" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="16" t="s">
+      <c r="F124" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A125" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B125" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D125" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E125" s="34">
+      <c r="B125" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="43">
         <v>19500</v>
       </c>
-      <c r="F125" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="16" t="s">
+      <c r="F125" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A126" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B126" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D126" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E126" s="34">
+      <c r="B126" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" s="43">
         <v>25000</v>
       </c>
-      <c r="F126" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="16" t="s">
+      <c r="F126" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A127" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="B127" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D127" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E127" s="34">
+      <c r="B127" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="43">
         <v>30000</v>
       </c>
-      <c r="F127" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="16" t="s">
+      <c r="F127" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A128" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B128" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D128" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E128" s="34">
+      <c r="B128" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D128" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="43">
         <v>40000</v>
       </c>
-      <c r="F128" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="16" t="s">
+      <c r="F128" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A129" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B129" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D129" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E129" s="34">
+      <c r="B129" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D129" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" s="43">
         <v>45000</v>
       </c>
-      <c r="F129" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="16" t="s">
+      <c r="F129" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A130" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B130" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D130" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E130" s="34">
+      <c r="B130" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D130" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="43">
         <v>78000</v>
       </c>
-      <c r="F130" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="16" t="s">
+      <c r="F130" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A131" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B131" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D131" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E131" s="34">
+      <c r="B131" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C131" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D131" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" s="43">
         <v>87000</v>
       </c>
-      <c r="F131" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="16" t="s">
+      <c r="F131" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A132" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B132" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D132" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E132" s="34">
+      <c r="B132" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="43">
         <v>96000</v>
       </c>
-      <c r="F132" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="16" t="s">
+      <c r="F132" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A133" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B133" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D133" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E133" s="34">
+      <c r="B133" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" s="43">
         <v>105000</v>
       </c>
-      <c r="F133" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="16" t="s">
+      <c r="F133" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A134" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B134" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D134" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E134" s="34">
+      <c r="B134" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D134" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="43">
         <v>114000</v>
       </c>
-      <c r="F134" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="16" t="s">
+      <c r="F134" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A135" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="B135" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D135" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E135" s="34">
+      <c r="B135" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D135" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="43">
         <v>142500</v>
       </c>
-      <c r="F135" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="16" t="s">
+      <c r="F135" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A136" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B136" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E136" s="34">
+      <c r="B136" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" s="43">
         <v>153000</v>
       </c>
-      <c r="F136" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="16" t="s">
+      <c r="F136" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A137" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="B137" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D137" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E137" s="34">
+      <c r="B137" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D137" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" s="43">
         <v>163500</v>
       </c>
-      <c r="F137" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="16" t="s">
+      <c r="F137" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A138" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B138" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D138" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E138" s="34">
+      <c r="B138" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D138" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" s="43">
         <v>232500</v>
       </c>
-      <c r="F138" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="16" t="s">
+      <c r="F138" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A139" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B139" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D139" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E139" s="34">
+      <c r="B139" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D139" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="43">
         <v>247500</v>
       </c>
-      <c r="F139" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="16" t="s">
+      <c r="F139" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A140" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B140" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D140" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E140" s="34">
+      <c r="B140" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" s="43">
         <v>295500</v>
       </c>
-      <c r="F140" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="16" t="s">
+      <c r="F140" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A141" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="B141" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D141" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E141" s="34">
+      <c r="B141" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="43">
         <v>312000</v>
       </c>
-      <c r="F141" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="16" t="s">
+      <c r="F141" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A142" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B142" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D142" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E142" s="34">
+      <c r="B142" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D142" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="43">
         <v>410000</v>
       </c>
-      <c r="F142" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="16" t="s">
+      <c r="F142" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A143" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="B143" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D143" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E143" s="34">
+      <c r="B143" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D143" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="43">
         <v>434000</v>
       </c>
-      <c r="F143" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="16" t="s">
+      <c r="F143" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A144" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B144" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D144" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E144" s="34">
+      <c r="B144" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D144" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="43">
         <v>469500</v>
       </c>
-      <c r="F144" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" s="4" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="6" t="s">
+      <c r="F144" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" s="2" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B145" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C145" s="8" t="s">
+      <c r="B145" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D145" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E145" s="34">
+      <c r="D145" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="43">
         <v>47979000</v>
       </c>
-      <c r="F145" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G145" s="5"/>
-    </row>
-    <row r="146" spans="1:7" s="11" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="15" t="s">
+      <c r="F145" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G145" s="3"/>
+    </row>
+    <row r="146" spans="1:7" s="9" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="B146" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D146" s="14" t="s">
+      <c r="B146" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D146" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="E146" s="35"/>
-      <c r="F146" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="G146" s="12"/>
-    </row>
-    <row r="147" spans="1:7" s="11" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="6" t="s">
+      <c r="E146" s="44"/>
+      <c r="F146" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="G146" s="10"/>
+    </row>
+    <row r="147" spans="1:7" s="9" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B147" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C147" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D147" s="14" t="s">
+      <c r="C147" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D147" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="E147" s="35"/>
-      <c r="F147" s="31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" s="11" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="18" t="s">
+      <c r="E147" s="44"/>
+      <c r="F147" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" s="9" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="B148" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D148" s="14" t="s">
+      <c r="B148" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D148" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="E148" s="35"/>
-      <c r="F148" s="31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" s="19" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="6" t="s">
+      <c r="E148" s="44"/>
+      <c r="F148" s="29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" s="17" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B149" s="20" t="s">
+      <c r="B149" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C149" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D149" s="21" t="s">
+      <c r="C149" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D149" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="E149" s="36"/>
-      <c r="F149" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="G149" s="11"/>
-    </row>
-    <row r="150" spans="1:7" s="22" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="27" t="s">
+      <c r="E149" s="45"/>
+      <c r="F149" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="G149" s="9"/>
+    </row>
+    <row r="150" spans="1:7" s="20" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="B150" s="24" t="s">
+      <c r="B150" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="C150" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D150" s="26" t="s">
+      <c r="C150" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D150" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="E150" s="37"/>
-      <c r="F150" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="18" t="s">
+      <c r="E150" s="46"/>
+      <c r="F150" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="21" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B151" s="7"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E151" s="34">
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="43">
         <v>13880000</v>
       </c>
-      <c r="F151" s="29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="40" t="s">
+      <c r="F151" s="27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" s="21" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="B152" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C152" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D152" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E152" s="46">
+      <c r="B152" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D152" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="47">
         <v>32680000</v>
       </c>
-      <c r="F152" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="40" t="s">
+      <c r="F152" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" s="21" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B153" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C153" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D153" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E153" s="46">
+      <c r="B153" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D153" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="47">
         <v>36800000</v>
       </c>
-      <c r="F153" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="40" t="s">
+      <c r="F153" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" s="21" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="B154" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C154" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D154" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E154" s="46">
+      <c r="B154" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D154" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="47">
         <v>43680000</v>
       </c>
-      <c r="F154" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="40" t="s">
+      <c r="F154" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" s="21" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B155" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D155" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E155" s="46">
+      <c r="B155" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="47">
         <v>48680000</v>
       </c>
-      <c r="F155" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="40" t="s">
+      <c r="F155" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" s="21" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="B156" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D156" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E156" s="46">
+      <c r="B156" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D156" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="47">
         <v>54680000</v>
       </c>
-      <c r="F156" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="40" t="s">
+      <c r="F156" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" s="21" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="B157" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C157" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D157" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E157" s="46">
+      <c r="B157" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D157" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="47">
         <v>69860000</v>
       </c>
-      <c r="F157" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" s="23" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="40" t="s">
+      <c r="F157" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" s="21" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="B158" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D158" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E158" s="46">
+      <c r="B158" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D158" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="47">
         <v>99680000</v>
       </c>
-      <c r="F158" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" s="39" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="40" t="s">
+      <c r="F158" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" s="30" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="B159" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C159" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D159" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E159" s="45"/>
-      <c r="F159" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="G159" s="5"/>
-    </row>
-    <row r="160" spans="1:7" s="22" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="44" t="s">
+      <c r="B159" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D159" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" s="48"/>
+      <c r="F159" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G159" s="3"/>
+    </row>
+    <row r="160" spans="1:7" s="20" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="B160" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C160" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D160" s="26" t="s">
+      <c r="B160" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="E160" s="45"/>
-      <c r="F160" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="G160" s="5"/>
+      <c r="E160" s="48"/>
+      <c r="F160" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G160" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="176">
   <si>
     <t>Ống D650</t>
   </si>
@@ -494,16 +494,117 @@
   </si>
   <si>
     <t>Bích D1100</t>
+  </si>
+  <si>
+    <t>Quạt ly tâm chạy gián tiếp
+gối bi ngâm dầu</t>
+  </si>
+  <si>
+    <t>Bộ</t>
+  </si>
+  <si>
+    <t>Thép SS400
+?mm</t>
+  </si>
+  <si>
+    <t>Thép SS400
+1,5mm</t>
+  </si>
+  <si>
+    <t>VAN XOAY 1.5 30V/P</t>
+  </si>
+  <si>
+    <t>Đường ống nối từ thùng lọc đến tháp lọc D?</t>
+  </si>
+  <si>
+    <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7
+Extraction performance / Hiệu suất hút : Q= 16.000-22.000m3/h
+Residual pressure / Áp suất: P = 3000-4200 Pa
+Rate Power / Công suất định mức: P =18.5 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+  </si>
+  <si>
+    <t>THÁP LỌC D2000
+H=mm
+2 dàn phun mưa 
+1 lớp đệm
+1 lớp tách ẩm</t>
+  </si>
+  <si>
+    <t>THÙNG THAN HOẠT TÍNH 
+Kích thước: DxRxCmm
+ Có ? khay đựng than kích thước:?x?x?mm
+? viên than kích thước 100x100x100mm
+có cửa thay than</t>
+  </si>
+  <si>
+    <t>SÀN THAO TÁC LẤY MẪU KHÍ THẢI
+Kích thước: ?x?x?mm
+Sàn thao tác làm dày 3mm-u100
+mặt sàn lưới dập dãn dày 3mm, bao gồm thang leo có lồng bảo vệ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ỐNG KHÓI D?
+Kích thước: D?x?mm,  giá đỡ ống thoát khí </t>
+  </si>
+  <si>
+    <t>TỦ HÚT BỤI STHB-1 1.5KW
+6 túi D150xL500
+Lưu lượng:  m3/h</t>
+  </si>
+  <si>
+    <t>TỦ HÚT BỤI STHB-2 2.2KW
+6 túi D150xL500
+Lưu lượng:  m3/h</t>
+  </si>
+  <si>
+    <t>TỦ HÚT BỤI STHB-3 3KW
+6 túi D150xL500
+Lưu lượng:  m3/h</t>
+  </si>
+  <si>
+    <t>TỦ HÚT BỤI STHB-4 4KW
+8 túi D150xL500
+Lưu lượng:  m3/h</t>
+  </si>
+  <si>
+    <t>TỦ HÚT BỤI STHB-5 5.5KW
+12 túi D150xL500
+Lưu lượng:  m3/h</t>
+  </si>
+  <si>
+    <t>TỦ HÚT BỤI STHB-6 7.5KW
+16 túi D150xL500
+Lưu lượng:  m3/h</t>
+  </si>
+  <si>
+    <t>TỦ HÚT BỤI STHB-7 1KW
+24 túi D150xL500
+Lưu lượng:  m3/h</t>
+  </si>
+  <si>
+    <t>TỦ HÚT BỤI STHB-8 15KW
+25 túi D150xL500
+Lưu lượng:  m3/h</t>
+  </si>
+  <si>
+    <t>CYCLONE D?
+thân vỏ 2mm , H=?mm
+khung đỡ thép hộp 50x50x2,3mm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,9 +632,60 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12.5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -556,7 +708,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -575,8 +727,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -599,18 +757,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -619,7 +848,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -631,21 +860,103 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Dấu phẩy 2" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2"/>
@@ -926,2706 +1237,3013 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="14" style="13" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" style="50" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="45" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="45" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="44" customWidth="1"/>
+    <col min="5" max="5" width="14" style="46" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="14">
         <v>120000</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="14">
         <v>160000</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="14">
         <v>210000</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="14">
         <v>250000</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="14">
         <v>310000</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="14">
         <v>330000</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="14">
         <v>420000</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="14">
         <v>460000</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="14">
         <v>660000</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="14">
         <v>700000</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="14">
         <v>750000</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="14">
         <v>830000</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="14">
         <v>880000</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="14">
         <v>950000</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="14">
         <v>1030000</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="14">
         <v>1150000</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="14">
         <v>1190000</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="14">
         <v>1280000</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="B20" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="14">
         <v>1350000</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="B21" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="14">
         <v>1450000</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="14">
         <v>1580000</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="B23" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="14">
         <v>1680000</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="B24" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="14">
         <v>1880000</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="6">
+      <c r="B25" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="14">
         <v>75000</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="6">
+      <c r="B26" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="14">
         <v>123000</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="6">
+      <c r="B27" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="14">
         <v>180000</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="6">
+      <c r="B28" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="14">
         <v>285000</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="6">
+      <c r="B29" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="14">
         <v>405000</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="6">
+      <c r="B30" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="14">
         <v>495000</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="6">
+      <c r="B31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="14">
         <v>660000</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="6">
+      <c r="B32" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="14">
         <v>840000</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="6">
+      <c r="B33" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="14">
         <v>1552500</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="6">
+      <c r="B34" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="14">
         <v>1905000</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="6">
+      <c r="B35" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="14">
         <v>2130000</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="6">
+      <c r="B36" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="14">
         <v>2535000</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="6">
+      <c r="B37" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="14">
         <v>2812500</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="6">
+      <c r="B38" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="14">
         <v>3255000</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="6">
+      <c r="B39" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="14">
         <v>3570000</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E40" s="6">
+      <c r="B40" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="14">
         <v>4080000</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E41" s="6">
+      <c r="B41" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="14">
         <v>4605000</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="6">
+      <c r="B42" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="14">
         <v>4965000</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="6">
+      <c r="B43" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="14">
         <v>5550000</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="6">
+      <c r="B44" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="14">
         <v>6165000</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="6">
+      <c r="B45" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="14">
         <v>9135000</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" s="8">
+      <c r="B46" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="16">
         <v>34500</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="8">
+      <c r="B47" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="16">
         <v>135000</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="8">
+      <c r="B48" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="16">
         <v>135000</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="8">
+      <c r="B49" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="16">
         <v>180000</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="8">
+      <c r="B50" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="16">
         <v>190000</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E51" s="8">
+      <c r="B51" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="16">
         <v>210000</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="8">
+      <c r="C52" s="12"/>
+      <c r="D52" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="16">
         <v>160000</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="8">
+      <c r="C53" s="12"/>
+      <c r="D53" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="16">
         <v>220000</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" s="8">
+      <c r="C54" s="12"/>
+      <c r="D54" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="16">
         <v>280000</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="8">
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="16">
         <v>550000</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="8">
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="16">
         <v>900000</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E57" s="8">
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="16">
         <v>1050000</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E58" s="8">
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="16">
         <v>1450000</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" s="8">
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="16">
         <v>1780000</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E60" s="8">
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="16">
         <v>2000000</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F60" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E61" s="8">
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="16">
         <v>2500000</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F61" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="8">
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="16">
         <v>2800000</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="8">
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="16">
         <v>3300000</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="8">
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="16">
         <v>3800000</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="8">
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="16">
         <v>4500000</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="8">
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="16">
         <v>4800000</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F66" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="8">
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="16">
         <v>5200000</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="8">
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="16">
         <v>5600000</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="8">
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="16">
         <v>6500000</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="F69" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="8">
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="16">
         <v>7200000</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="8">
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="16">
         <v>7600000</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="8">
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="16">
         <v>8000000</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F72" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="8">
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="16">
         <v>8900000</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F73" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="8">
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="16">
         <v>9600000</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="8">
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="16">
         <v>10680000</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="8">
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="16">
         <v>11680000</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F76" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="8">
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="16">
         <v>12500000</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="8">
+      <c r="B78" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="16">
         <v>240000</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F78" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="8">
+      <c r="B79" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="16">
         <v>320000</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F79" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="8">
+      <c r="B80" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="16">
         <v>420000</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="F80" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="8">
+      <c r="B81" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="16">
         <v>500000</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="8">
+      <c r="B82" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="16">
         <v>620000</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B83" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="8">
+      <c r="B83" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="16">
         <v>660000</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="F83" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" s="8">
+      <c r="B84" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="16">
         <v>840000</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B85" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E85" s="8">
+      <c r="B85" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="16">
         <v>890000</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" s="8">
+      <c r="B86" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="16">
         <v>1980000</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F86" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B87" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="8">
+      <c r="B87" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="16">
         <v>2100000</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="F87" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="8">
+      <c r="B88" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="16">
         <v>2250000</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="F88" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B89" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="8">
+      <c r="B89" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="16">
         <v>2490000</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F89" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E90" s="8">
+      <c r="B90" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="16">
         <v>2640000</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F90" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E91" s="8">
+      <c r="B91" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="16">
         <v>2850000</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="F91" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B92" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E92" s="8">
+      <c r="B92" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="16">
         <v>3090000</v>
       </c>
-      <c r="F92" s="4" t="s">
+      <c r="F92" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B93" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E93" s="8">
+      <c r="B93" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="16">
         <v>3450000</v>
       </c>
-      <c r="F93" s="4" t="s">
+      <c r="F93" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E94" s="8">
+      <c r="B94" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="16">
         <v>7600000</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="F94" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B95" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="8">
+      <c r="B95" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="16">
         <v>8000000</v>
       </c>
-      <c r="F95" s="4" t="s">
+      <c r="F95" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B96" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="8">
+      <c r="B96" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="16">
         <v>8900000</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="F96" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B97" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="8">
+      <c r="B97" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="16">
         <v>9600000</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="F97" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B98" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E98" s="8">
+      <c r="B98" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="16">
         <v>10680000</v>
       </c>
-      <c r="F98" s="4" t="s">
+      <c r="F98" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B99" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E99" s="8">
+      <c r="B99" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="16">
         <v>11680000</v>
       </c>
-      <c r="F99" s="4" t="s">
+      <c r="F99" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B100" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="8">
+      <c r="B100" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="16">
         <v>13680000</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="8">
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="16">
         <v>800000</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="F101" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="8">
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="16">
         <v>1000000</v>
       </c>
-      <c r="F102" s="4" t="s">
+      <c r="F102" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="8">
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="16">
         <v>1008000</v>
       </c>
-      <c r="F103" s="4" t="s">
+      <c r="F103" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E104" s="8">
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="16">
         <v>1200000</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F104" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E105" s="8">
+      <c r="B105" s="12"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="16">
         <v>1488000</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F105" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E106" s="8">
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="16">
         <v>1584000</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F106" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" s="8">
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="16">
         <v>2016000</v>
       </c>
-      <c r="F107" s="4" t="s">
+      <c r="F107" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E108" s="8">
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="16">
         <v>2136000</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="F108" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E109" s="8">
+      <c r="B109" s="12"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="16">
         <v>3000000</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F109" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E110" s="8">
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="16">
         <v>3780000</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="F110" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E111" s="8">
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="16">
         <v>4050000</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F111" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E112" s="8">
+      <c r="B112" s="12"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="16">
         <v>4482000</v>
       </c>
-      <c r="F112" s="4" t="s">
+      <c r="F112" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E113" s="8">
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="16">
         <v>4752000</v>
       </c>
-      <c r="F113" s="4" t="s">
+      <c r="F113" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E114" s="8">
+      <c r="B114" s="12"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="16">
         <v>5130000</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="F114" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E115" s="8">
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="16">
         <v>5562000</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="F115" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E116" s="8">
+      <c r="B116" s="12"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="16">
         <v>6210000</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="F116" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E117" s="8">
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="16">
         <v>13680000</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="F117" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E118" s="8">
+      <c r="B118" s="12"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="16">
         <v>14400000</v>
       </c>
-      <c r="F118" s="4" t="s">
+      <c r="F118" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E119" s="8">
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="16">
         <v>16020000</v>
       </c>
-      <c r="F119" s="4" t="s">
+      <c r="F119" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" s="8">
+      <c r="B120" s="12"/>
+      <c r="C120" s="12"/>
+      <c r="D120" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="16">
         <v>17280000</v>
       </c>
-      <c r="F120" s="4" t="s">
+      <c r="F120" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E121" s="8">
+      <c r="B121" s="12"/>
+      <c r="C121" s="12"/>
+      <c r="D121" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="16">
         <v>19224000</v>
       </c>
-      <c r="F121" s="4" t="s">
+      <c r="F121" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E122" s="8">
+      <c r="B122" s="12"/>
+      <c r="C122" s="12"/>
+      <c r="D122" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="16">
         <v>21024000</v>
       </c>
-      <c r="F122" s="4" t="s">
+      <c r="F122" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E123" s="8">
+      <c r="B123" s="12"/>
+      <c r="C123" s="12"/>
+      <c r="D123" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="16">
         <v>24624000</v>
       </c>
-      <c r="F123" s="4" t="s">
+      <c r="F123" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B124" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E124" s="8">
+      <c r="B124" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="16">
         <v>15000</v>
       </c>
-      <c r="F124" s="4" t="s">
+      <c r="F124" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B125" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E125" s="8">
+      <c r="B125" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="16">
         <v>19500</v>
       </c>
-      <c r="F125" s="4" t="s">
+      <c r="F125" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B126" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E126" s="8">
+      <c r="B126" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" s="16">
         <v>25000</v>
       </c>
-      <c r="F126" s="4" t="s">
+      <c r="F126" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B127" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E127" s="8">
+      <c r="B127" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="16">
         <v>30000</v>
       </c>
-      <c r="F127" s="4" t="s">
+      <c r="F127" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B128" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E128" s="8">
+      <c r="B128" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="16">
         <v>40000</v>
       </c>
-      <c r="F128" s="4" t="s">
+      <c r="F128" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B129" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E129" s="8">
+      <c r="B129" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" s="16">
         <v>45000</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="F129" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B130" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E130" s="8">
+      <c r="B130" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="16">
         <v>78000</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="F130" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B131" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C131" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E131" s="8">
+      <c r="B131" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C131" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" s="16">
         <v>87000</v>
       </c>
-      <c r="F131" s="4" t="s">
+      <c r="F131" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B132" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E132" s="8">
+      <c r="B132" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="16">
         <v>96000</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="F132" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B133" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C133" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E133" s="8">
+      <c r="B133" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" s="16">
         <v>105000</v>
       </c>
-      <c r="F133" s="4" t="s">
+      <c r="F133" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B134" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C134" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E134" s="8">
+      <c r="B134" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="16">
         <v>114000</v>
       </c>
-      <c r="F134" s="4" t="s">
+      <c r="F134" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="B135" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E135" s="8">
+      <c r="B135" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="16">
         <v>142500</v>
       </c>
-      <c r="F135" s="4" t="s">
+      <c r="F135" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E136" s="8">
+      <c r="B136" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" s="16">
         <v>153000</v>
       </c>
-      <c r="F136" s="4" t="s">
+      <c r="F136" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B137" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C137" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E137" s="8">
+      <c r="B137" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" s="16">
         <v>163500</v>
       </c>
-      <c r="F137" s="4" t="s">
+      <c r="F137" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B138" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C138" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E138" s="8">
+      <c r="B138" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" s="16">
         <v>232500</v>
       </c>
-      <c r="F138" s="4" t="s">
+      <c r="F138" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B139" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C139" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E139" s="8">
+      <c r="B139" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="16">
         <v>247500</v>
       </c>
-      <c r="F139" s="4" t="s">
+      <c r="F139" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B140" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E140" s="8">
+      <c r="B140" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" s="16">
         <v>295500</v>
       </c>
-      <c r="F140" s="4" t="s">
+      <c r="F140" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B141" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C141" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E141" s="8">
+      <c r="B141" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="16">
         <v>312000</v>
       </c>
-      <c r="F141" s="4" t="s">
+      <c r="F141" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B142" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E142" s="8">
+      <c r="B142" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="16">
         <v>410000</v>
       </c>
-      <c r="F142" s="4" t="s">
+      <c r="F142" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B143" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C143" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E143" s="8">
+      <c r="B143" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="16">
         <v>434000</v>
       </c>
-      <c r="F143" s="4" t="s">
+      <c r="F143" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B144" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E144" s="8">
+      <c r="B144" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="16">
         <v>469500</v>
       </c>
-      <c r="F144" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="F144" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B145" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D145" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="16">
+        <v>47979000</v>
+      </c>
+      <c r="F145" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="G145" s="2"/>
+    </row>
+    <row r="146" spans="1:7" s="3" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D146" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E146" s="26"/>
+      <c r="F146" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G146" s="4"/>
+    </row>
+    <row r="147" spans="1:7" s="3" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B147" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="C147" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D147" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E147" s="26"/>
+      <c r="F147" s="27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" s="3" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B148" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D148" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E148" s="26"/>
+      <c r="F148" s="27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" s="5" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="B149" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C149" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D149" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="E149" s="31"/>
+      <c r="F149" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G149" s="3"/>
+    </row>
+    <row r="150" spans="1:7" s="6" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B150" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C150" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D150" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="E150" s="36"/>
+      <c r="F150" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B151" s="20"/>
+      <c r="C151" s="20"/>
+      <c r="D151" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="16">
+        <v>13880000</v>
+      </c>
+      <c r="F151" s="38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="B152" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D152" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="41">
+        <v>32680000</v>
+      </c>
+      <c r="F152" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="B153" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D153" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="41">
+        <v>36800000</v>
+      </c>
+      <c r="F153" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="B154" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D154" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="41">
+        <v>43680000</v>
+      </c>
+      <c r="F154" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="B155" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="41">
+        <v>48680000</v>
+      </c>
+      <c r="F155" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="B156" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D156" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="41">
+        <v>54680000</v>
+      </c>
+      <c r="F156" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="B157" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D157" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="41">
+        <v>69860000</v>
+      </c>
+      <c r="F157" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="B158" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D158" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="41">
+        <v>99680000</v>
+      </c>
+      <c r="F158" s="37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" s="8" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B159" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D159" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" s="42"/>
+      <c r="F159" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G159" s="2"/>
+    </row>
+    <row r="160" spans="1:7" s="6" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="B160" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="E160" s="42"/>
+      <c r="F160" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G160" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -500,9 +500,6 @@
 gối bi ngâm dầu</t>
   </si>
   <si>
-    <t>Bộ</t>
-  </si>
-  <si>
     <t>Thép SS400
 ?mm</t>
   </si>
@@ -517,82 +514,327 @@
     <t>Đường ống nối từ thùng lọc đến tháp lọc D?</t>
   </si>
   <si>
-    <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 Extraction performance / Hiệu suất hút : Q= 16.000-22.000m3/h
 Residual pressure / Áp suất: P = 3000-4200 Pa
 Rate Power / Công suất định mức: P =18.5 Kw , 
 Tightness / Độ kín :  IP 55
 Supply voltage / Điện áp:3P/380V
 Main frequency / Tần số chính: 50Hz</t>
-  </si>
-  <si>
-    <t>THÁP LỌC D2000
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>THÁP LỌC D2000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 H=mm
 2 dàn phun mưa 
 1 lớp đệm
 1 lớp tách ẩm</t>
-  </si>
-  <si>
-    <t>THÙNG THAN HOẠT TÍNH 
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">THÙNG THAN HOẠT TÍNH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 Kích thước: DxRxCmm
  Có ? khay đựng than kích thước:?x?x?mm
 ? viên than kích thước 100x100x100mm
 có cửa thay than</t>
-  </si>
-  <si>
-    <t>SÀN THAO TÁC LẤY MẪU KHÍ THẢI
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SÀN THAO TÁC LẤY MẪU KHÍ THẢI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 Kích thước: ?x?x?mm
 Sàn thao tác làm dày 3mm-u100
 mặt sàn lưới dập dãn dày 3mm, bao gồm thang leo có lồng bảo vệ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ỐNG KHÓI D?
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ỐNG KHÓI D?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 Kích thước: D?x?mm,  giá đỡ ống thoát khí </t>
-  </si>
-  <si>
-    <t>TỦ HÚT BỤI STHB-1 1.5KW
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-1 1.5KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 6 túi D150xL500
 Lưu lượng:  m3/h</t>
-  </si>
-  <si>
-    <t>TỦ HÚT BỤI STHB-2 2.2KW
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-2 2.2KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 6 túi D150xL500
 Lưu lượng:  m3/h</t>
-  </si>
-  <si>
-    <t>TỦ HÚT BỤI STHB-3 3KW
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-3 3KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 6 túi D150xL500
 Lưu lượng:  m3/h</t>
-  </si>
-  <si>
-    <t>TỦ HÚT BỤI STHB-4 4KW
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-4 4KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 8 túi D150xL500
 Lưu lượng:  m3/h</t>
-  </si>
-  <si>
-    <t>TỦ HÚT BỤI STHB-5 5.5KW
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-5 5.5KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 12 túi D150xL500
 Lưu lượng:  m3/h</t>
-  </si>
-  <si>
-    <t>TỦ HÚT BỤI STHB-6 7.5KW
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-6 7.5KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 16 túi D150xL500
 Lưu lượng:  m3/h</t>
-  </si>
-  <si>
-    <t>TỦ HÚT BỤI STHB-7 1KW
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-7 1KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 24 túi D150xL500
 Lưu lượng:  m3/h</t>
-  </si>
-  <si>
-    <t>TỦ HÚT BỤI STHB-8 15KW
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-8 15KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 25 túi D150xL500
 Lưu lượng:  m3/h</t>
-  </si>
-  <si>
-    <t>CYCLONE D?
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CYCLONE D?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
 thân vỏ 2mm , H=?mm
 khung đỡ thép hộp 50x50x2,3mm</t>
+    </r>
+  </si>
+  <si>
+    <t>Kg</t>
   </si>
 </sst>
 </file>
@@ -604,7 +846,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -706,6 +948,19 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -810,7 +1065,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -836,124 +1091,120 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1240,16 +1491,16 @@
   <dimension ref="A1:G160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" style="50" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="45" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="45" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="44" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" style="37" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="38" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="38" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="39" customWidth="1"/>
     <col min="5" max="5" width="14" style="46" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" style="44" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1258,13 +1509,13 @@
       <c r="C1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1281,10 +1532,10 @@
       <c r="D2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="41">
         <v>120000</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1301,10 +1552,10 @@
       <c r="D3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="41">
         <v>160000</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1321,10 +1572,10 @@
       <c r="D4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="41">
         <v>210000</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1341,10 +1592,10 @@
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="41">
         <v>250000</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1361,10 +1612,10 @@
       <c r="D6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="41">
         <v>310000</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1381,10 +1632,10 @@
       <c r="D7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="41">
         <v>330000</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1401,10 +1652,10 @@
       <c r="D8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="41">
         <v>420000</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1421,10 +1672,10 @@
       <c r="D9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="41">
         <v>460000</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1441,10 +1692,10 @@
       <c r="D10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="41">
         <v>660000</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1461,10 +1712,10 @@
       <c r="D11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="41">
         <v>700000</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1481,10 +1732,10 @@
       <c r="D12" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="41">
         <v>750000</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1501,10 +1752,10 @@
       <c r="D13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="41">
         <v>830000</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1521,10 +1772,10 @@
       <c r="D14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="41">
         <v>880000</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1541,10 +1792,10 @@
       <c r="D15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="41">
         <v>950000</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1561,10 +1812,10 @@
       <c r="D16" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="41">
         <v>1030000</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1581,10 +1832,10 @@
       <c r="D17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="41">
         <v>1150000</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1601,10 +1852,10 @@
       <c r="D18" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="41">
         <v>1190000</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1621,10 +1872,10 @@
       <c r="D19" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="41">
         <v>1280000</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1641,10 +1892,10 @@
       <c r="D20" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="41">
         <v>1350000</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1661,10 +1912,10 @@
       <c r="D21" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="41">
         <v>1450000</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1681,10 +1932,10 @@
       <c r="D22" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="41">
         <v>1580000</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1701,10 +1952,10 @@
       <c r="D23" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="41">
         <v>1680000</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1721,10 +1972,10 @@
       <c r="D24" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="41">
         <v>1880000</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1741,10 +1992,10 @@
       <c r="D25" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="41">
         <v>75000</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1761,10 +2012,10 @@
       <c r="D26" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="41">
         <v>123000</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1781,10 +2032,10 @@
       <c r="D27" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="41">
         <v>180000</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1801,10 +2052,10 @@
       <c r="D28" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="41">
         <v>285000</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1821,10 +2072,10 @@
       <c r="D29" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="41">
         <v>405000</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1841,10 +2092,10 @@
       <c r="D30" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="41">
         <v>495000</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1861,10 +2112,10 @@
       <c r="D31" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="41">
         <v>660000</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1881,10 +2132,10 @@
       <c r="D32" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="41">
         <v>840000</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1901,10 +2152,10 @@
       <c r="D33" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="41">
         <v>1552500</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1921,10 +2172,10 @@
       <c r="D34" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="41">
         <v>1905000</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1941,10 +2192,10 @@
       <c r="D35" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="41">
         <v>2130000</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1961,10 +2212,10 @@
       <c r="D36" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="41">
         <v>2535000</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F36" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1981,10 +2232,10 @@
       <c r="D37" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="41">
         <v>2812500</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F37" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2001,10 +2252,10 @@
       <c r="D38" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="41">
         <v>3255000</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2021,10 +2272,10 @@
       <c r="D39" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="41">
         <v>3570000</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2041,10 +2292,10 @@
       <c r="D40" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="41">
         <v>4080000</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2061,10 +2312,10 @@
       <c r="D41" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="41">
         <v>4605000</v>
       </c>
-      <c r="F41" s="15" t="s">
+      <c r="F41" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2081,10 +2332,10 @@
       <c r="D42" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="41">
         <v>4965000</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2101,10 +2352,10 @@
       <c r="D43" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="41">
         <v>5550000</v>
       </c>
-      <c r="F43" s="15" t="s">
+      <c r="F43" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2121,10 +2372,10 @@
       <c r="D44" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="41">
         <v>6165000</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2141,10 +2392,10 @@
       <c r="D45" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="41">
         <v>9135000</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" s="14" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2161,7 +2412,7 @@
       <c r="D46" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="42">
         <v>34500</v>
       </c>
       <c r="F46" s="12" t="s">
@@ -2181,7 +2432,7 @@
       <c r="D47" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="42">
         <v>135000</v>
       </c>
       <c r="F47" s="12" t="s">
@@ -2201,7 +2452,7 @@
       <c r="D48" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="42">
         <v>135000</v>
       </c>
       <c r="F48" s="12" t="s">
@@ -2221,7 +2472,7 @@
       <c r="D49" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="42">
         <v>180000</v>
       </c>
       <c r="F49" s="12" t="s">
@@ -2241,7 +2492,7 @@
       <c r="D50" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="42">
         <v>190000</v>
       </c>
       <c r="F50" s="12" t="s">
@@ -2261,7 +2512,7 @@
       <c r="D51" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="42">
         <v>210000</v>
       </c>
       <c r="F51" s="12" t="s">
@@ -2279,7 +2530,7 @@
       <c r="D52" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="42">
         <v>160000</v>
       </c>
       <c r="F52" s="12" t="s">
@@ -2297,7 +2548,7 @@
       <c r="D53" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="42">
         <v>220000</v>
       </c>
       <c r="F53" s="12" t="s">
@@ -2315,7 +2566,7 @@
       <c r="D54" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="42">
         <v>280000</v>
       </c>
       <c r="F54" s="12" t="s">
@@ -2331,7 +2582,7 @@
       <c r="D55" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="42">
         <v>550000</v>
       </c>
       <c r="F55" s="12" t="s">
@@ -2347,7 +2598,7 @@
       <c r="D56" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="42">
         <v>900000</v>
       </c>
       <c r="F56" s="12" t="s">
@@ -2363,7 +2614,7 @@
       <c r="D57" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="42">
         <v>1050000</v>
       </c>
       <c r="F57" s="12" t="s">
@@ -2379,7 +2630,7 @@
       <c r="D58" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="42">
         <v>1450000</v>
       </c>
       <c r="F58" s="12" t="s">
@@ -2395,7 +2646,7 @@
       <c r="D59" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="42">
         <v>1780000</v>
       </c>
       <c r="F59" s="12" t="s">
@@ -2411,7 +2662,7 @@
       <c r="D60" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="42">
         <v>2000000</v>
       </c>
       <c r="F60" s="12" t="s">
@@ -2427,7 +2678,7 @@
       <c r="D61" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="42">
         <v>2500000</v>
       </c>
       <c r="F61" s="12" t="s">
@@ -2443,7 +2694,7 @@
       <c r="D62" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="42">
         <v>2800000</v>
       </c>
       <c r="F62" s="12" t="s">
@@ -2459,7 +2710,7 @@
       <c r="D63" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="42">
         <v>3300000</v>
       </c>
       <c r="F63" s="12" t="s">
@@ -2475,7 +2726,7 @@
       <c r="D64" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="42">
         <v>3800000</v>
       </c>
       <c r="F64" s="12" t="s">
@@ -2491,7 +2742,7 @@
       <c r="D65" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="42">
         <v>4500000</v>
       </c>
       <c r="F65" s="12" t="s">
@@ -2507,7 +2758,7 @@
       <c r="D66" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="42">
         <v>4800000</v>
       </c>
       <c r="F66" s="12" t="s">
@@ -2523,7 +2774,7 @@
       <c r="D67" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="42">
         <v>5200000</v>
       </c>
       <c r="F67" s="12" t="s">
@@ -2539,7 +2790,7 @@
       <c r="D68" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E68" s="42">
         <v>5600000</v>
       </c>
       <c r="F68" s="12" t="s">
@@ -2555,7 +2806,7 @@
       <c r="D69" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="42">
         <v>6500000</v>
       </c>
       <c r="F69" s="12" t="s">
@@ -2571,7 +2822,7 @@
       <c r="D70" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="42">
         <v>7200000</v>
       </c>
       <c r="F70" s="12" t="s">
@@ -2587,7 +2838,7 @@
       <c r="D71" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="42">
         <v>7600000</v>
       </c>
       <c r="F71" s="12" t="s">
@@ -2603,7 +2854,7 @@
       <c r="D72" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="42">
         <v>8000000</v>
       </c>
       <c r="F72" s="12" t="s">
@@ -2619,7 +2870,7 @@
       <c r="D73" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="42">
         <v>8900000</v>
       </c>
       <c r="F73" s="12" t="s">
@@ -2635,7 +2886,7 @@
       <c r="D74" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E74" s="16">
+      <c r="E74" s="42">
         <v>9600000</v>
       </c>
       <c r="F74" s="12" t="s">
@@ -2651,7 +2902,7 @@
       <c r="D75" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E75" s="16">
+      <c r="E75" s="42">
         <v>10680000</v>
       </c>
       <c r="F75" s="12" t="s">
@@ -2667,7 +2918,7 @@
       <c r="D76" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="16">
+      <c r="E76" s="42">
         <v>11680000</v>
       </c>
       <c r="F76" s="12" t="s">
@@ -2683,7 +2934,7 @@
       <c r="D77" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="42">
         <v>12500000</v>
       </c>
       <c r="F77" s="12" t="s">
@@ -2694,16 +2945,16 @@
       <c r="A78" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" s="18" t="s">
+      <c r="B78" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E78" s="16">
+      <c r="E78" s="42">
         <v>240000</v>
       </c>
       <c r="F78" s="12" t="s">
@@ -2714,16 +2965,16 @@
       <c r="A79" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" s="18" t="s">
+      <c r="B79" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D79" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="42">
         <v>320000</v>
       </c>
       <c r="F79" s="12" t="s">
@@ -2734,16 +2985,16 @@
       <c r="A80" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" s="18" t="s">
+      <c r="B80" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E80" s="16">
+      <c r="E80" s="42">
         <v>420000</v>
       </c>
       <c r="F80" s="12" t="s">
@@ -2754,16 +3005,16 @@
       <c r="A81" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B81" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" s="18" t="s">
+      <c r="B81" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D81" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E81" s="16">
+      <c r="E81" s="42">
         <v>500000</v>
       </c>
       <c r="F81" s="12" t="s">
@@ -2774,16 +3025,16 @@
       <c r="A82" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" s="18" t="s">
+      <c r="B82" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E82" s="16">
+      <c r="E82" s="42">
         <v>620000</v>
       </c>
       <c r="F82" s="12" t="s">
@@ -2794,16 +3045,16 @@
       <c r="A83" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B83" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" s="18" t="s">
+      <c r="B83" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D83" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E83" s="16">
+      <c r="E83" s="42">
         <v>660000</v>
       </c>
       <c r="F83" s="12" t="s">
@@ -2814,16 +3065,16 @@
       <c r="A84" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" s="18" t="s">
+      <c r="B84" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D84" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="16">
+      <c r="E84" s="42">
         <v>840000</v>
       </c>
       <c r="F84" s="12" t="s">
@@ -2834,16 +3085,16 @@
       <c r="A85" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B85" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" s="18" t="s">
+      <c r="B85" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D85" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E85" s="16">
+      <c r="E85" s="42">
         <v>890000</v>
       </c>
       <c r="F85" s="12" t="s">
@@ -2854,16 +3105,16 @@
       <c r="A86" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B86" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" s="18" t="s">
+      <c r="B86" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E86" s="16">
+      <c r="E86" s="42">
         <v>1980000</v>
       </c>
       <c r="F86" s="12" t="s">
@@ -2874,16 +3125,16 @@
       <c r="A87" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B87" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="18" t="s">
+      <c r="B87" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D87" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E87" s="16">
+      <c r="E87" s="42">
         <v>2100000</v>
       </c>
       <c r="F87" s="12" t="s">
@@ -2894,16 +3145,16 @@
       <c r="A88" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" s="18" t="s">
+      <c r="B88" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E88" s="16">
+      <c r="E88" s="42">
         <v>2250000</v>
       </c>
       <c r="F88" s="12" t="s">
@@ -2914,16 +3165,16 @@
       <c r="A89" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B89" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" s="18" t="s">
+      <c r="B89" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D89" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E89" s="16">
+      <c r="E89" s="42">
         <v>2490000</v>
       </c>
       <c r="F89" s="12" t="s">
@@ -2934,16 +3185,16 @@
       <c r="A90" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="18" t="s">
+      <c r="B90" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E90" s="16">
+      <c r="E90" s="42">
         <v>2640000</v>
       </c>
       <c r="F90" s="12" t="s">
@@ -2954,16 +3205,16 @@
       <c r="A91" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" s="18" t="s">
+      <c r="B91" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D91" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E91" s="16">
+      <c r="E91" s="42">
         <v>2850000</v>
       </c>
       <c r="F91" s="12" t="s">
@@ -2974,16 +3225,16 @@
       <c r="A92" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B92" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" s="18" t="s">
+      <c r="B92" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E92" s="16">
+      <c r="E92" s="42">
         <v>3090000</v>
       </c>
       <c r="F92" s="12" t="s">
@@ -2994,16 +3245,16 @@
       <c r="A93" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B93" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C93" s="18" t="s">
+      <c r="B93" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E93" s="16">
+      <c r="E93" s="42">
         <v>3450000</v>
       </c>
       <c r="F93" s="12" t="s">
@@ -3014,16 +3265,16 @@
       <c r="A94" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" s="18" t="s">
+      <c r="B94" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E94" s="16">
+      <c r="E94" s="42">
         <v>7600000</v>
       </c>
       <c r="F94" s="12" t="s">
@@ -3034,16 +3285,16 @@
       <c r="A95" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B95" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="18" t="s">
+      <c r="B95" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D95" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E95" s="16">
+      <c r="E95" s="42">
         <v>8000000</v>
       </c>
       <c r="F95" s="12" t="s">
@@ -3054,16 +3305,16 @@
       <c r="A96" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B96" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" s="18" t="s">
+      <c r="B96" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D96" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E96" s="16">
+      <c r="E96" s="42">
         <v>8900000</v>
       </c>
       <c r="F96" s="12" t="s">
@@ -3074,16 +3325,16 @@
       <c r="A97" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B97" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="18" t="s">
+      <c r="B97" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D97" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E97" s="16">
+      <c r="E97" s="42">
         <v>9600000</v>
       </c>
       <c r="F97" s="12" t="s">
@@ -3094,16 +3345,16 @@
       <c r="A98" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B98" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="18" t="s">
+      <c r="B98" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D98" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E98" s="16">
+      <c r="E98" s="42">
         <v>10680000</v>
       </c>
       <c r="F98" s="12" t="s">
@@ -3114,16 +3365,16 @@
       <c r="A99" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B99" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" s="18" t="s">
+      <c r="B99" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E99" s="16">
+      <c r="E99" s="42">
         <v>11680000</v>
       </c>
       <c r="F99" s="12" t="s">
@@ -3134,16 +3385,16 @@
       <c r="A100" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B100" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="18" t="s">
+      <c r="B100" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E100" s="16">
+      <c r="E100" s="42">
         <v>13680000</v>
       </c>
       <c r="F100" s="12" t="s">
@@ -3159,7 +3410,7 @@
       <c r="D101" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E101" s="16">
+      <c r="E101" s="42">
         <v>800000</v>
       </c>
       <c r="F101" s="12" t="s">
@@ -3175,7 +3426,7 @@
       <c r="D102" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E102" s="16">
+      <c r="E102" s="42">
         <v>1000000</v>
       </c>
       <c r="F102" s="12" t="s">
@@ -3191,7 +3442,7 @@
       <c r="D103" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E103" s="16">
+      <c r="E103" s="42">
         <v>1008000</v>
       </c>
       <c r="F103" s="12" t="s">
@@ -3207,7 +3458,7 @@
       <c r="D104" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E104" s="16">
+      <c r="E104" s="42">
         <v>1200000</v>
       </c>
       <c r="F104" s="12" t="s">
@@ -3223,7 +3474,7 @@
       <c r="D105" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E105" s="16">
+      <c r="E105" s="42">
         <v>1488000</v>
       </c>
       <c r="F105" s="12" t="s">
@@ -3239,7 +3490,7 @@
       <c r="D106" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E106" s="16">
+      <c r="E106" s="42">
         <v>1584000</v>
       </c>
       <c r="F106" s="12" t="s">
@@ -3255,7 +3506,7 @@
       <c r="D107" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E107" s="16">
+      <c r="E107" s="42">
         <v>2016000</v>
       </c>
       <c r="F107" s="12" t="s">
@@ -3271,7 +3522,7 @@
       <c r="D108" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E108" s="16">
+      <c r="E108" s="42">
         <v>2136000</v>
       </c>
       <c r="F108" s="12" t="s">
@@ -3287,7 +3538,7 @@
       <c r="D109" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E109" s="16">
+      <c r="E109" s="42">
         <v>3000000</v>
       </c>
       <c r="F109" s="12" t="s">
@@ -3303,7 +3554,7 @@
       <c r="D110" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E110" s="16">
+      <c r="E110" s="42">
         <v>3780000</v>
       </c>
       <c r="F110" s="12" t="s">
@@ -3319,7 +3570,7 @@
       <c r="D111" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E111" s="16">
+      <c r="E111" s="42">
         <v>4050000</v>
       </c>
       <c r="F111" s="12" t="s">
@@ -3335,7 +3586,7 @@
       <c r="D112" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E112" s="16">
+      <c r="E112" s="42">
         <v>4482000</v>
       </c>
       <c r="F112" s="12" t="s">
@@ -3351,7 +3602,7 @@
       <c r="D113" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E113" s="16">
+      <c r="E113" s="42">
         <v>4752000</v>
       </c>
       <c r="F113" s="12" t="s">
@@ -3367,7 +3618,7 @@
       <c r="D114" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E114" s="16">
+      <c r="E114" s="42">
         <v>5130000</v>
       </c>
       <c r="F114" s="12" t="s">
@@ -3383,7 +3634,7 @@
       <c r="D115" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E115" s="16">
+      <c r="E115" s="42">
         <v>5562000</v>
       </c>
       <c r="F115" s="12" t="s">
@@ -3399,7 +3650,7 @@
       <c r="D116" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E116" s="16">
+      <c r="E116" s="42">
         <v>6210000</v>
       </c>
       <c r="F116" s="12" t="s">
@@ -3415,7 +3666,7 @@
       <c r="D117" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E117" s="16">
+      <c r="E117" s="42">
         <v>13680000</v>
       </c>
       <c r="F117" s="12" t="s">
@@ -3431,7 +3682,7 @@
       <c r="D118" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E118" s="16">
+      <c r="E118" s="42">
         <v>14400000</v>
       </c>
       <c r="F118" s="12" t="s">
@@ -3447,7 +3698,7 @@
       <c r="D119" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E119" s="16">
+      <c r="E119" s="42">
         <v>16020000</v>
       </c>
       <c r="F119" s="12" t="s">
@@ -3463,7 +3714,7 @@
       <c r="D120" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E120" s="16">
+      <c r="E120" s="42">
         <v>17280000</v>
       </c>
       <c r="F120" s="12" t="s">
@@ -3479,7 +3730,7 @@
       <c r="D121" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E121" s="16">
+      <c r="E121" s="42">
         <v>19224000</v>
       </c>
       <c r="F121" s="12" t="s">
@@ -3495,7 +3746,7 @@
       <c r="D122" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E122" s="16">
+      <c r="E122" s="42">
         <v>21024000</v>
       </c>
       <c r="F122" s="12" t="s">
@@ -3511,7 +3762,7 @@
       <c r="D123" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E123" s="16">
+      <c r="E123" s="42">
         <v>24624000</v>
       </c>
       <c r="F123" s="12" t="s">
@@ -3525,13 +3776,13 @@
       <c r="B124" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C124" s="18" t="s">
+      <c r="C124" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D124" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E124" s="16">
+      <c r="E124" s="42">
         <v>15000</v>
       </c>
       <c r="F124" s="12" t="s">
@@ -3545,13 +3796,13 @@
       <c r="B125" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C125" s="18" t="s">
+      <c r="C125" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D125" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E125" s="16">
+      <c r="E125" s="42">
         <v>19500</v>
       </c>
       <c r="F125" s="12" t="s">
@@ -3565,13 +3816,13 @@
       <c r="B126" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="18" t="s">
+      <c r="C126" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D126" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E126" s="16">
+      <c r="E126" s="42">
         <v>25000</v>
       </c>
       <c r="F126" s="12" t="s">
@@ -3585,13 +3836,13 @@
       <c r="B127" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C127" s="18" t="s">
+      <c r="C127" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D127" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E127" s="16">
+      <c r="E127" s="42">
         <v>30000</v>
       </c>
       <c r="F127" s="12" t="s">
@@ -3605,13 +3856,13 @@
       <c r="B128" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="18" t="s">
+      <c r="C128" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D128" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E128" s="16">
+      <c r="E128" s="42">
         <v>40000</v>
       </c>
       <c r="F128" s="12" t="s">
@@ -3625,13 +3876,13 @@
       <c r="B129" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="18" t="s">
+      <c r="C129" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D129" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E129" s="16">
+      <c r="E129" s="42">
         <v>45000</v>
       </c>
       <c r="F129" s="12" t="s">
@@ -3645,13 +3896,13 @@
       <c r="B130" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C130" s="18" t="s">
+      <c r="C130" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D130" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E130" s="16">
+      <c r="E130" s="42">
         <v>78000</v>
       </c>
       <c r="F130" s="12" t="s">
@@ -3665,13 +3916,13 @@
       <c r="B131" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C131" s="18" t="s">
+      <c r="C131" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D131" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E131" s="16">
+      <c r="E131" s="42">
         <v>87000</v>
       </c>
       <c r="F131" s="12" t="s">
@@ -3685,13 +3936,13 @@
       <c r="B132" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="18" t="s">
+      <c r="C132" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D132" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E132" s="16">
+      <c r="E132" s="42">
         <v>96000</v>
       </c>
       <c r="F132" s="12" t="s">
@@ -3705,13 +3956,13 @@
       <c r="B133" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C133" s="18" t="s">
+      <c r="C133" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D133" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E133" s="16">
+      <c r="E133" s="42">
         <v>105000</v>
       </c>
       <c r="F133" s="12" t="s">
@@ -3725,13 +3976,13 @@
       <c r="B134" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C134" s="18" t="s">
+      <c r="C134" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D134" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E134" s="16">
+      <c r="E134" s="42">
         <v>114000</v>
       </c>
       <c r="F134" s="12" t="s">
@@ -3745,13 +3996,13 @@
       <c r="B135" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C135" s="18" t="s">
+      <c r="C135" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D135" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E135" s="16">
+      <c r="E135" s="42">
         <v>142500</v>
       </c>
       <c r="F135" s="12" t="s">
@@ -3765,13 +4016,13 @@
       <c r="B136" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C136" s="18" t="s">
+      <c r="C136" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D136" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E136" s="16">
+      <c r="E136" s="42">
         <v>153000</v>
       </c>
       <c r="F136" s="12" t="s">
@@ -3785,13 +4036,13 @@
       <c r="B137" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C137" s="18" t="s">
+      <c r="C137" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D137" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E137" s="16">
+      <c r="E137" s="42">
         <v>163500</v>
       </c>
       <c r="F137" s="12" t="s">
@@ -3805,13 +4056,13 @@
       <c r="B138" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C138" s="18" t="s">
+      <c r="C138" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D138" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E138" s="16">
+      <c r="E138" s="42">
         <v>232500</v>
       </c>
       <c r="F138" s="12" t="s">
@@ -3825,13 +4076,13 @@
       <c r="B139" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C139" s="18" t="s">
+      <c r="C139" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D139" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E139" s="16">
+      <c r="E139" s="42">
         <v>247500</v>
       </c>
       <c r="F139" s="12" t="s">
@@ -3845,13 +4096,13 @@
       <c r="B140" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C140" s="18" t="s">
+      <c r="C140" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D140" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E140" s="16">
+      <c r="E140" s="42">
         <v>295500</v>
       </c>
       <c r="F140" s="12" t="s">
@@ -3865,13 +4116,13 @@
       <c r="B141" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C141" s="18" t="s">
+      <c r="C141" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D141" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E141" s="16">
+      <c r="E141" s="42">
         <v>312000</v>
       </c>
       <c r="F141" s="12" t="s">
@@ -3885,13 +4136,13 @@
       <c r="B142" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C142" s="18" t="s">
+      <c r="C142" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D142" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E142" s="16">
+      <c r="E142" s="42">
         <v>410000</v>
       </c>
       <c r="F142" s="12" t="s">
@@ -3905,13 +4156,13 @@
       <c r="B143" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C143" s="18" t="s">
+      <c r="C143" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D143" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E143" s="16">
+      <c r="E143" s="42">
         <v>434000</v>
       </c>
       <c r="F143" s="12" t="s">
@@ -3925,13 +4176,13 @@
       <c r="B144" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C144" s="18" t="s">
+      <c r="C144" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D144" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E144" s="16">
+      <c r="E144" s="42">
         <v>469500</v>
       </c>
       <c r="F144" s="12" t="s">
@@ -3939,308 +4190,322 @@
       </c>
     </row>
     <row r="145" spans="1:7" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="19" t="s">
+      <c r="A145" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B145" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D145" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="42">
+        <v>47979000</v>
+      </c>
+      <c r="F145" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G145" s="2"/>
+    </row>
+    <row r="146" spans="1:7" s="3" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B145" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C145" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D145" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E145" s="16">
-        <v>47979000</v>
-      </c>
-      <c r="F145" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7" s="3" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="28" t="s">
+      <c r="B146" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D146" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E146" s="43">
+        <v>75000</v>
+      </c>
+      <c r="F146" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G146" s="4"/>
+    </row>
+    <row r="147" spans="1:7" s="3" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B146" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D146" s="25" t="s">
+      <c r="B147" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="E146" s="26"/>
-      <c r="F146" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="G146" s="4"/>
-    </row>
-    <row r="147" spans="1:7" s="3" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="19" t="s">
+      <c r="C147" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D147" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E147" s="43">
+        <v>75000</v>
+      </c>
+      <c r="F147" s="25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" s="3" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="B147" s="20" t="s">
+      <c r="B148" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D148" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E148" s="43">
+        <v>75000</v>
+      </c>
+      <c r="F148" s="25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" s="5" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B149" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="C147" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D147" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E147" s="26"/>
-      <c r="F147" s="27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" s="3" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B148" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D148" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E148" s="26"/>
-      <c r="F148" s="27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" s="5" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="19" t="s">
+      <c r="C149" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D149" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E149" s="43">
+        <v>75000</v>
+      </c>
+      <c r="F149" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G149" s="3"/>
+    </row>
+    <row r="150" spans="1:7" s="6" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B150" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C150" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D150" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E150" s="43">
+        <v>75000</v>
+      </c>
+      <c r="F150" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B151" s="18"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="42">
+        <v>13880000</v>
+      </c>
+      <c r="F151" s="31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="B149" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="C149" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D149" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="E149" s="31"/>
-      <c r="F149" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="G149" s="3"/>
-    </row>
-    <row r="150" spans="1:7" s="6" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="B150" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="C150" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D150" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="E150" s="36"/>
-      <c r="F150" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="B151" s="20"/>
-      <c r="C151" s="20"/>
-      <c r="D151" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E151" s="16">
-        <v>13880000</v>
-      </c>
-      <c r="F151" s="38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="48" t="s">
+      <c r="B152" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D152" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="44">
+        <v>32680000</v>
+      </c>
+      <c r="F152" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="B152" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C152" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D152" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E152" s="41">
-        <v>32680000</v>
-      </c>
-      <c r="F152" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="48" t="s">
+      <c r="B153" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D153" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="44">
+        <v>36800000</v>
+      </c>
+      <c r="F153" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="B153" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C153" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D153" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E153" s="41">
-        <v>36800000</v>
-      </c>
-      <c r="F153" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="48" t="s">
+      <c r="B154" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D154" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="44">
+        <v>43680000</v>
+      </c>
+      <c r="F154" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="B154" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C154" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D154" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E154" s="41">
-        <v>43680000</v>
-      </c>
-      <c r="F154" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="48" t="s">
+      <c r="B155" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="44">
+        <v>48680000</v>
+      </c>
+      <c r="F155" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="B155" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D155" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E155" s="41">
-        <v>48680000</v>
-      </c>
-      <c r="F155" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="48" t="s">
+      <c r="B156" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D156" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="44">
+        <v>54680000</v>
+      </c>
+      <c r="F156" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="B156" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D156" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E156" s="41">
-        <v>54680000</v>
-      </c>
-      <c r="F156" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="48" t="s">
+      <c r="B157" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D157" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="44">
+        <v>69860000</v>
+      </c>
+      <c r="F157" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="B157" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C157" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D157" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E157" s="41">
-        <v>69860000</v>
-      </c>
-      <c r="F157" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="48" t="s">
+      <c r="B158" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D158" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="44">
+        <v>99680000</v>
+      </c>
+      <c r="F158" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" s="8" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="B158" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D158" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E158" s="41">
-        <v>99680000</v>
-      </c>
-      <c r="F158" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" s="8" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="48" t="s">
+      <c r="B159" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D159" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E159" s="45">
+        <v>75000</v>
+      </c>
+      <c r="F159" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G159" s="2"/>
+    </row>
+    <row r="160" spans="1:7" s="6" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="B159" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C159" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D159" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E159" s="42"/>
-      <c r="F159" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="1:7" s="6" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="49" t="s">
+      <c r="B160" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="B160" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C160" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D160" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="E160" s="42"/>
-      <c r="F160" s="43" t="s">
+      <c r="E160" s="45">
+        <v>75000</v>
+      </c>
+      <c r="F160" s="35" t="s">
         <v>8</v>
       </c>
       <c r="G160" s="2"/>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\quote-web-main\quote-web-main\quote-web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\quote-web-main (1)\quote-web-main\quote-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="234">
   <si>
     <t>Ống D650</t>
   </si>
@@ -835,6 +835,770 @@
   </si>
   <si>
     <t>Kg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">THÙNG THAN HOẠT TÍNH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kích thước: DxRxCmm
+Có ? cửa thay lọc</t>
+    </r>
+  </si>
+  <si>
+    <t>THAN HOẠT TÍNH</t>
+  </si>
+  <si>
+    <t>NK</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D250 về D200 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D800 về D750 rẽ 1 nhánh D450</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D750 về D600 rẽ 1 nhánh D450</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D600 về D350 rẽ 1 nhánh D450</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D450 về D400 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D350 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D350 về D300 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D300 về D250 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D300 về D200 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D600 về D600 rẽ 2 nhánh D500 và D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D500 về D400 rẽ 1 nhánh D300</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D400 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D300 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 10.000-12.000m3/h
+Residual pressure / Áp suất: P = 2700-3500 Pa
+Rate Power / Công suất định mức: P =5.5 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H5.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 12.000-14.000m3/h
+Residual pressure / Áp suất: P = 2700-3500 Pa
+Rate Power / Công suất định mức: P =7.5 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H6.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 10.000-15.000m3/h
+Residual pressure / Áp suất: P = 2800-3800 Pa
+Rate Power / Công suất định mức: P =11 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H6.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 14.000-18.000m3/h
+Residual pressure / Áp suất: P = 2900-4000 Pa
+Rate Power / Công suất định mức: P =15 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 18.000-24.000m3/h
+Residual pressure / Áp suất: P = 3000-4300 Pa
+Rate Power / Công suất định mức: P =22 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 22.000-28.000m3/h
+Residual pressure / Áp suất: P = 3200-4300 Pa
+Rate Power / Công suất định mức: P =22 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 24.000-30.000m3/h
+Residual pressure / Áp suất: P = 3200-4500 Pa
+Rate Power / Công suất định mức: P =30 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 28.000-35.000m3/h
+Residual pressure / Áp suất: P = 3200-4500 Pa
+Rate Power / Công suất định mức: P =30 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 34.000-42.000m3/h
+Residual pressure / Áp suất: P = 3300-4500 Pa
+Rate Power / Công suất định mức: P =37 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 38.000-45.000m3/h
+Residual pressure / Áp suất: P = 3300-4500 Pa
+Rate Power / Công suất định mức: P =45 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 40.000-48.000m3/h
+Residual pressure / Áp suất: P = 3300-4500 Pa
+Rate Power / Công suất định mức: P =45 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 40.000-52.000m3/h
+Residual pressure / Áp suất: P = 3400-4500 Pa
+Rate Power / Công suất định mức: P =55 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 50.000-60.000m3/h
+Residual pressure / Áp suất: P = 3500-4600 Pa
+Rate Power / Công suất định mức: P =75 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 60.000-66.000m3/h
+Residual pressure / Áp suất: P = 3500-4600 Pa
+Rate Power / Công suất định mức: P =90 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 65.000-72.000m3/h
+Residual pressure / Áp suất: P = 3500-4600 Pa
+Rate Power / Công suất định mức: P =75 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 70.000-80.000m3/h
+Residual pressure / Áp suất: P = 3500-4600 Pa
+Rate Power / Công suất định mức: P =90 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 78.000-90.000m3/h
+Residual pressure / Áp suất: P = 3300-4700 Pa
+Rate Power / Công suất định mức: P =90 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 90.000-100.000m3/h
+Residual pressure / Áp suất: P = 3500-5000 Pa
+Rate Power / Công suất định mức: P =110 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 100.000-110.000m3/h
+Residual pressure / Áp suất: P = 3300-4700 Pa
+Rate Power / Công suất định mức: P =110 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 110.000-120.000m3/h
+Residual pressure / Áp suất: P = 3500-5000 Pa
+Rate Power / Công suất định mức: P =160 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 120.000-150.000m3/h
+Residual pressure / Áp suất: P = 3500-5200 Pa
+Rate Power / Công suất định mức: P =200 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 150.000-190.000m3/h
+Residual pressure / Áp suất: P = 3800-5500 Pa
+Rate Power / Công suất định mức: P =250 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 190.000-250.000m3/h
+Residual pressure / Áp suất: P = 3300-4700 Pa
+Rate Power / Công suất định mức: P =300 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 250.000-290.000m3/h
+Residual pressure / Áp suất: P = 3500-5200 Pa
+Rate Power / Công suất định mức: P =350 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 290.000-350.000m3/h
+Residual pressure / Áp suất: P = 3500-5500 Pa
+Rate Power / Công suất định mức: P =400 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 350.000-400.000m3/h
+Residual pressure / Áp suất: P = 3800-5600 Pa
+Rate Power / Công suất định mức: P =500 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <t>VAN NỔ ASCOR PHI 34</t>
+  </si>
+  <si>
+    <t>TÚI CADTRIGE PHI 150 L=500</t>
+  </si>
+  <si>
+    <t>VAN NỔ PHI 34</t>
+  </si>
+  <si>
+    <t>VAN NỔ PHI 48</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 135 L=2500</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 135 L=3000</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 135 L=4000</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 150 L=2500</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 150 L=3000</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 150 L=4000</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 135 L=2500</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 135 L=3000</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 135 L=4000</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 150 L=2500</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 150 L=3000</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 150 L=4000</t>
   </si>
 </sst>
 </file>
@@ -882,12 +1646,6 @@
     <font>
       <b/>
       <sz val="12.5"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -962,6 +1720,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -989,7 +1753,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1049,15 +1813,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1065,36 +1820,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1103,16 +1849,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1127,16 +1873,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1145,65 +1888,76 @@
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="38" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="10" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1488,3029 +2242,5363 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:AC218"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" style="37" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="38" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="38" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="39" customWidth="1"/>
-    <col min="5" max="5" width="14" style="46" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" style="39" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="33" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="33" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="34" customWidth="1"/>
+    <col min="5" max="5" width="14" style="42" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="41">
+      <c r="E2" s="37">
         <v>120000</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="41">
+      <c r="E3" s="37">
         <v>160000</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="37">
         <v>210000</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="37">
         <v>250000</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="37">
         <v>310000</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="37">
         <v>330000</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="37">
         <v>420000</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="37">
         <v>460000</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="37">
         <v>660000</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="37">
         <v>700000</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="37">
         <v>750000</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="37">
         <v>830000</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="37">
         <v>880000</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="37">
         <v>950000</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="37">
         <v>1030000</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="37">
         <v>1150000</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="37">
         <v>1190000</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="37">
         <v>1280000</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="37">
         <v>1350000</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="37">
         <v>1450000</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="37">
         <v>1580000</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="37">
         <v>1680000</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="37">
         <v>1880000</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="41">
+      <c r="D25" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="37">
         <v>75000</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="41">
+      <c r="D26" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="37">
         <v>123000</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="41">
+      <c r="D27" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="37">
         <v>180000</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="41">
+      <c r="D28" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="37">
         <v>285000</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="41">
+      <c r="D29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="37">
         <v>405000</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="41">
+      <c r="D30" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="37">
         <v>495000</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="41">
+      <c r="D31" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="37">
         <v>660000</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="41">
+      <c r="D32" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="37">
         <v>840000</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="41">
+      <c r="D33" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="37">
         <v>1552500</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="41">
+      <c r="D34" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="37">
         <v>1905000</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="41">
+      <c r="D35" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="37">
         <v>2130000</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="41">
+      <c r="D36" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="37">
         <v>2535000</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="41">
+      <c r="D37" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="37">
         <v>2812500</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="41">
+      <c r="D38" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="37">
         <v>3255000</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="41">
+      <c r="D39" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="37">
         <v>3570000</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E40" s="41">
+      <c r="D40" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="37">
         <v>4080000</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D41" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E41" s="41">
+      <c r="D41" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="37">
         <v>4605000</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="41">
+      <c r="D42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="37">
         <v>4965000</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="41">
+      <c r="D43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="37">
         <v>5550000</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="41">
+      <c r="D44" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="37">
         <v>6165000</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="41">
+      <c r="D45" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="37">
         <v>9135000</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" s="42">
+      <c r="D46" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="38">
         <v>34500</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D47" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="42">
+      <c r="D47" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="38">
         <v>135000</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="42">
+      <c r="D48" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="38">
         <v>135000</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F48" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="42">
+      <c r="D49" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="38">
         <v>180000</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F49" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="42">
+      <c r="D50" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="38">
         <v>190000</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D51" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E51" s="42">
+      <c r="D51" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="38">
         <v>210000</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="35">
+        <v>442500</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="35">
+        <v>447000</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="35">
+        <v>470000</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A55" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="B55" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="44">
+        <v>447000</v>
+      </c>
+      <c r="F55" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="35">
+        <v>528000</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A57" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="44">
+        <v>508500</v>
+      </c>
+      <c r="F57" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="35">
+        <v>560000</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A59" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="B59" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="44">
+        <v>682500</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="35">
+        <v>666000</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A61" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="44">
+        <v>957000</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="35">
+        <v>3120000</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="35">
+        <v>2860000</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="35">
+        <v>2100000</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A65" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="B65" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="44">
+        <v>3255000</v>
+      </c>
+      <c r="F65" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B66" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="42">
+      <c r="C66" s="9"/>
+      <c r="D66" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="38">
         <v>160000</v>
       </c>
-      <c r="F52" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
+      <c r="F66" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B67" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="42">
+      <c r="C67" s="9"/>
+      <c r="D67" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="38">
         <v>220000</v>
       </c>
-      <c r="F53" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
+      <c r="F67" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B68" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" s="42">
+      <c r="C68" s="9"/>
+      <c r="D68" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="38">
         <v>280000</v>
       </c>
-      <c r="F54" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
+      <c r="F68" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="42">
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="38">
         <v>550000</v>
       </c>
-      <c r="F55" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
+      <c r="F69" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="42">
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="38">
         <v>900000</v>
       </c>
-      <c r="F56" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
+      <c r="F70" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E57" s="42">
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="38">
         <v>1050000</v>
       </c>
-      <c r="F57" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
+      <c r="F71" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E58" s="42">
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="38">
         <v>1450000</v>
       </c>
-      <c r="F58" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
+      <c r="F72" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" s="42">
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="38">
         <v>1780000</v>
       </c>
-      <c r="F59" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
+      <c r="F73" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E60" s="42">
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="38">
         <v>2000000</v>
       </c>
-      <c r="F60" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
+      <c r="F74" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E61" s="42">
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="38">
         <v>2500000</v>
       </c>
-      <c r="F61" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
+      <c r="F75" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="42">
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="38">
         <v>2800000</v>
       </c>
-      <c r="F62" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
+      <c r="F76" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="42">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="38">
         <v>3300000</v>
       </c>
-      <c r="F63" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
+      <c r="F77" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="42">
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="38">
         <v>3800000</v>
       </c>
-      <c r="F64" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
+      <c r="F78" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="42">
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="38">
         <v>4500000</v>
       </c>
-      <c r="F65" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
+      <c r="F79" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="42">
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="38">
         <v>4800000</v>
       </c>
-      <c r="F66" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
+      <c r="F80" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="42">
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="38">
         <v>5200000</v>
       </c>
-      <c r="F67" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
+      <c r="F81" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A82" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="42">
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="38">
         <v>5600000</v>
       </c>
-      <c r="F68" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
+      <c r="F82" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A83" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="42">
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="38">
         <v>6500000</v>
       </c>
-      <c r="F69" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
+      <c r="F83" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A84" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="42">
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="38">
         <v>7200000</v>
       </c>
-      <c r="F70" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
+      <c r="F84" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="42">
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="38">
         <v>7600000</v>
       </c>
-      <c r="F71" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
+      <c r="F85" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A86" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="42">
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="38">
         <v>8000000</v>
       </c>
-      <c r="F72" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
+      <c r="F86" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="42">
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="38">
         <v>8900000</v>
       </c>
-      <c r="F73" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
+      <c r="F87" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="42">
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="38">
         <v>9600000</v>
       </c>
-      <c r="F74" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
+      <c r="F88" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A89" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="42">
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="38">
         <v>10680000</v>
       </c>
-      <c r="F75" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
+      <c r="F89" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="42">
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="38">
         <v>11680000</v>
       </c>
-      <c r="F76" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
+      <c r="F90" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A91" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="42">
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="38">
         <v>12500000</v>
       </c>
-      <c r="F77" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
+      <c r="F91" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A92" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" s="16" t="s">
+      <c r="B92" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D78" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="42">
+      <c r="D92" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="38">
         <v>240000</v>
       </c>
-      <c r="F78" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
+      <c r="F92" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A93" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" s="16" t="s">
+      <c r="B93" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D79" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="42">
+      <c r="D93" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="38">
         <v>320000</v>
       </c>
-      <c r="F79" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
+      <c r="F93" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A94" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" s="16" t="s">
+      <c r="B94" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D80" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="42">
+      <c r="D94" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="38">
         <v>420000</v>
       </c>
-      <c r="F80" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
+      <c r="F94" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A95" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B81" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81" s="16" t="s">
+      <c r="B95" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D81" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="42">
+      <c r="D95" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="38">
         <v>500000</v>
       </c>
-      <c r="F81" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
+      <c r="F95" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A96" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" s="16" t="s">
+      <c r="B96" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D82" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="42">
+      <c r="D96" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="38">
         <v>620000</v>
       </c>
-      <c r="F82" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
+      <c r="F96" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A97" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B83" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" s="16" t="s">
+      <c r="B97" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D83" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="42">
+      <c r="D97" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="38">
         <v>660000</v>
       </c>
-      <c r="F83" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
+      <c r="F97" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A98" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" s="16" t="s">
+      <c r="B98" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D84" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" s="42">
+      <c r="D98" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="38">
         <v>840000</v>
       </c>
-      <c r="F84" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
+      <c r="F98" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A99" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B85" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" s="16" t="s">
+      <c r="B99" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D85" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E85" s="42">
+      <c r="D99" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="38">
         <v>890000</v>
       </c>
-      <c r="F85" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
+      <c r="F99" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A100" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B86" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" s="16" t="s">
+      <c r="B100" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" s="42">
+      <c r="D100" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="38">
         <v>1980000</v>
       </c>
-      <c r="F86" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
+      <c r="F100" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A101" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B87" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="16" t="s">
+      <c r="B101" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="42">
+      <c r="D101" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="38">
         <v>2100000</v>
       </c>
-      <c r="F87" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
+      <c r="F101" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A102" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" s="16" t="s">
+      <c r="B102" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D88" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="42">
+      <c r="D102" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="38">
         <v>2250000</v>
       </c>
-      <c r="F88" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A89" s="12" t="s">
+      <c r="F102" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A103" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B89" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" s="16" t="s">
+      <c r="B103" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D89" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="42">
+      <c r="D103" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="38">
         <v>2490000</v>
       </c>
-      <c r="F89" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A90" s="12" t="s">
+      <c r="F103" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A104" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="16" t="s">
+      <c r="B104" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D90" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E90" s="42">
+      <c r="D104" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="38">
         <v>2640000</v>
       </c>
-      <c r="F90" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A91" s="12" t="s">
+      <c r="F104" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A105" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" s="16" t="s">
+      <c r="B105" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D91" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E91" s="42">
+      <c r="D105" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="38">
         <v>2850000</v>
       </c>
-      <c r="F91" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A92" s="12" t="s">
+      <c r="F105" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A106" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B92" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" s="16" t="s">
+      <c r="B106" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D92" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E92" s="42">
+      <c r="D106" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="38">
         <v>3090000</v>
       </c>
-      <c r="F92" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A93" s="12" t="s">
+      <c r="F106" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A107" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B93" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C93" s="16" t="s">
+      <c r="B107" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D93" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E93" s="42">
+      <c r="D107" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="38">
         <v>3450000</v>
       </c>
-      <c r="F93" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A94" s="12" t="s">
+      <c r="F107" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A108" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" s="16" t="s">
+      <c r="B108" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D94" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E94" s="42">
+      <c r="D108" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="38">
         <v>7600000</v>
       </c>
-      <c r="F94" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A95" s="12" t="s">
+      <c r="F108" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A109" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B95" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="16" t="s">
+      <c r="B109" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D95" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="42">
+      <c r="D109" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="38">
         <v>8000000</v>
       </c>
-      <c r="F95" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A96" s="12" t="s">
+      <c r="F109" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A110" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B96" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" s="16" t="s">
+      <c r="B110" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D96" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="42">
+      <c r="D110" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="38">
         <v>8900000</v>
       </c>
-      <c r="F96" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A97" s="12" t="s">
+      <c r="F110" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B97" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="16" t="s">
+      <c r="B111" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D97" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="42">
+      <c r="D111" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="38">
         <v>9600000</v>
       </c>
-      <c r="F97" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A98" s="12" t="s">
+      <c r="F111" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A112" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B98" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="16" t="s">
+      <c r="B112" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D98" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E98" s="42">
+      <c r="D112" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="38">
         <v>10680000</v>
       </c>
-      <c r="F98" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A99" s="12" t="s">
+      <c r="F112" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A113" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B99" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" s="16" t="s">
+      <c r="B113" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D99" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E99" s="42">
+      <c r="D113" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="38">
         <v>11680000</v>
       </c>
-      <c r="F99" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A100" s="12" t="s">
+      <c r="F113" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A114" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B100" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="16" t="s">
+      <c r="B114" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="42">
+      <c r="D114" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="38">
         <v>13680000</v>
       </c>
-      <c r="F100" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A101" s="12" t="s">
+      <c r="F114" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B101" s="12"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="42">
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="38">
         <v>800000</v>
       </c>
-      <c r="F101" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A102" s="12" t="s">
+      <c r="F115" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A116" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="42">
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="38">
         <v>1000000</v>
       </c>
-      <c r="F102" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A103" s="12" t="s">
+      <c r="F116" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="12"/>
-      <c r="C103" s="12"/>
-      <c r="D103" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="42">
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="38">
         <v>1008000</v>
       </c>
-      <c r="F103" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A104" s="12" t="s">
+      <c r="F117" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A118" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E104" s="42">
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="38">
         <v>1200000</v>
       </c>
-      <c r="F104" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
+      <c r="F118" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A119" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B105" s="12"/>
-      <c r="C105" s="12"/>
-      <c r="D105" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E105" s="42">
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="38">
         <v>1488000</v>
       </c>
-      <c r="F105" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
+      <c r="F119" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A120" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E106" s="42">
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="38">
         <v>1584000</v>
       </c>
-      <c r="F106" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A107" s="12" t="s">
+      <c r="F120" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A121" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B107" s="12"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" s="42">
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="38">
         <v>2016000</v>
       </c>
-      <c r="F107" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
+      <c r="F121" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A122" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B108" s="12"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E108" s="42">
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="38">
         <v>2136000</v>
       </c>
-      <c r="F108" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
+      <c r="F122" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A123" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B109" s="12"/>
-      <c r="C109" s="12"/>
-      <c r="D109" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E109" s="42">
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="38">
         <v>3000000</v>
       </c>
-      <c r="F109" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A110" s="12" t="s">
+      <c r="F123" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A124" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E110" s="42">
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="38">
         <v>3780000</v>
       </c>
-      <c r="F110" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A111" s="12" t="s">
+      <c r="F124" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B111" s="12"/>
-      <c r="C111" s="12"/>
-      <c r="D111" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E111" s="42">
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="38">
         <v>4050000</v>
       </c>
-      <c r="F111" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A112" s="12" t="s">
+      <c r="F125" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B112" s="12"/>
-      <c r="C112" s="12"/>
-      <c r="D112" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E112" s="42">
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" s="38">
         <v>4482000</v>
       </c>
-      <c r="F112" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A113" s="12" t="s">
+      <c r="F126" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A127" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B113" s="12"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E113" s="42">
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="38">
         <v>4752000</v>
       </c>
-      <c r="F113" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A114" s="12" t="s">
+      <c r="F127" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B114" s="12"/>
-      <c r="C114" s="12"/>
-      <c r="D114" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E114" s="42">
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="38">
         <v>5130000</v>
       </c>
-      <c r="F114" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A115" s="12" t="s">
+      <c r="F128" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B115" s="12"/>
-      <c r="C115" s="12"/>
-      <c r="D115" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E115" s="42">
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" s="38">
         <v>5562000</v>
       </c>
-      <c r="F115" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A116" s="12" t="s">
+      <c r="F129" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A130" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B116" s="12"/>
-      <c r="C116" s="12"/>
-      <c r="D116" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E116" s="42">
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="38">
         <v>6210000</v>
       </c>
-      <c r="F116" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A117" s="12" t="s">
+      <c r="F130" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A131" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B117" s="12"/>
-      <c r="C117" s="12"/>
-      <c r="D117" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E117" s="42">
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" s="38">
         <v>13680000</v>
       </c>
-      <c r="F117" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A118" s="12" t="s">
+      <c r="F131" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A132" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B118" s="12"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E118" s="42">
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="38">
         <v>14400000</v>
       </c>
-      <c r="F118" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A119" s="12" t="s">
+      <c r="F132" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A133" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B119" s="12"/>
-      <c r="C119" s="12"/>
-      <c r="D119" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E119" s="42">
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" s="38">
         <v>16020000</v>
       </c>
-      <c r="F119" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A120" s="12" t="s">
+      <c r="F133" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A134" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B120" s="12"/>
-      <c r="C120" s="12"/>
-      <c r="D120" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" s="42">
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="38">
         <v>17280000</v>
       </c>
-      <c r="F120" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A121" s="12" t="s">
+      <c r="F134" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A135" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B121" s="12"/>
-      <c r="C121" s="12"/>
-      <c r="D121" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E121" s="42">
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="38">
         <v>19224000</v>
       </c>
-      <c r="F121" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A122" s="12" t="s">
+      <c r="F135" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A136" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B122" s="12"/>
-      <c r="C122" s="12"/>
-      <c r="D122" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E122" s="42">
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" s="38">
         <v>21024000</v>
       </c>
-      <c r="F122" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A123" s="12" t="s">
+      <c r="F136" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A137" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B123" s="12"/>
-      <c r="C123" s="12"/>
-      <c r="D123" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E123" s="42">
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" s="38">
         <v>24624000</v>
       </c>
-      <c r="F123" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A124" s="12" t="s">
+      <c r="F137" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A138" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B124" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" s="16" t="s">
+      <c r="B138" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D124" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E124" s="42">
+      <c r="D138" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" s="38">
         <v>15000</v>
       </c>
-      <c r="F124" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A125" s="12" t="s">
+      <c r="F138" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A139" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B125" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C125" s="16" t="s">
+      <c r="B139" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D125" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E125" s="42">
+      <c r="D139" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="38">
         <v>19500</v>
       </c>
-      <c r="F125" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A126" s="12" t="s">
+      <c r="F139" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A140" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B126" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" s="16" t="s">
+      <c r="B140" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D126" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E126" s="42">
+      <c r="D140" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" s="38">
         <v>25000</v>
       </c>
-      <c r="F126" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A127" s="12" t="s">
+      <c r="F140" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A141" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B127" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C127" s="16" t="s">
+      <c r="B141" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D127" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E127" s="42">
+      <c r="D141" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="38">
         <v>30000</v>
       </c>
-      <c r="F127" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
+      <c r="F141" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A142" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B128" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" s="16" t="s">
+      <c r="B142" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D128" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E128" s="42">
+      <c r="D142" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="38">
         <v>40000</v>
       </c>
-      <c r="F128" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A129" s="12" t="s">
+      <c r="F142" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A143" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B129" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C129" s="16" t="s">
+      <c r="B143" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D129" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E129" s="42">
+      <c r="D143" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="38">
         <v>45000</v>
       </c>
-      <c r="F129" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A130" s="12" t="s">
+      <c r="F143" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A144" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B130" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" s="16" t="s">
+      <c r="B144" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D130" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E130" s="42">
+      <c r="D144" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="38">
         <v>78000</v>
       </c>
-      <c r="F130" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A131" s="12" t="s">
+      <c r="F144" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A145" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B131" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C131" s="16" t="s">
+      <c r="B145" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D131" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E131" s="42">
+      <c r="D145" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="38">
         <v>87000</v>
       </c>
-      <c r="F131" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A132" s="12" t="s">
+      <c r="F145" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A146" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B132" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C132" s="16" t="s">
+      <c r="B146" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D132" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E132" s="42">
+      <c r="D146" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E146" s="38">
         <v>96000</v>
       </c>
-      <c r="F132" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A133" s="12" t="s">
+      <c r="F146" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A147" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B133" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C133" s="16" t="s">
+      <c r="B147" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D133" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E133" s="42">
+      <c r="D147" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" s="38">
         <v>105000</v>
       </c>
-      <c r="F133" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A134" s="12" t="s">
+      <c r="F147" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A148" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B134" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C134" s="16" t="s">
+      <c r="B148" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D134" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E134" s="42">
+      <c r="D148" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" s="38">
         <v>114000</v>
       </c>
-      <c r="F134" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A135" s="12" t="s">
+      <c r="F148" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A149" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B135" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C135" s="16" t="s">
+      <c r="B149" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D135" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E135" s="42">
+      <c r="D149" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E149" s="38">
         <v>142500</v>
       </c>
-      <c r="F135" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A136" s="12" t="s">
+      <c r="F149" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A150" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B136" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" s="16" t="s">
+      <c r="B150" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D136" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E136" s="42">
+      <c r="D150" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" s="38">
         <v>153000</v>
       </c>
-      <c r="F136" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A137" s="12" t="s">
+      <c r="F150" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A151" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B137" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C137" s="16" t="s">
+      <c r="B151" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C151" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D137" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E137" s="42">
+      <c r="D151" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="38">
         <v>163500</v>
       </c>
-      <c r="F137" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A138" s="12" t="s">
+      <c r="F151" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A152" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B138" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C138" s="16" t="s">
+      <c r="B152" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D138" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E138" s="42">
+      <c r="D152" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="38">
         <v>232500</v>
       </c>
-      <c r="F138" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A139" s="12" t="s">
+      <c r="F152" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A153" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B139" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C139" s="16" t="s">
+      <c r="B153" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D139" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E139" s="42">
+      <c r="D153" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="38">
         <v>247500</v>
       </c>
-      <c r="F139" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A140" s="12" t="s">
+      <c r="F153" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A154" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B140" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" s="16" t="s">
+      <c r="B154" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D140" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E140" s="42">
+      <c r="D154" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="38">
         <v>295500</v>
       </c>
-      <c r="F140" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A141" s="12" t="s">
+      <c r="F154" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A155" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B141" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C141" s="16" t="s">
+      <c r="B155" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D141" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E141" s="42">
+      <c r="D155" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="38">
         <v>312000</v>
       </c>
-      <c r="F141" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A142" s="12" t="s">
+      <c r="F155" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A156" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B142" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" s="16" t="s">
+      <c r="B156" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D142" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E142" s="42">
+      <c r="D156" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="38">
         <v>410000</v>
       </c>
-      <c r="F142" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A143" s="12" t="s">
+      <c r="F156" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A157" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B143" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C143" s="16" t="s">
+      <c r="B157" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D143" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E143" s="42">
+      <c r="D157" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="38">
         <v>434000</v>
       </c>
-      <c r="F143" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A144" s="12" t="s">
+      <c r="F157" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A158" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B144" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" s="16" t="s">
+      <c r="B158" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D144" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E144" s="42">
+      <c r="D158" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="38">
         <v>469500</v>
       </c>
-      <c r="F144" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="17" t="s">
+      <c r="F158" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B159" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D159" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" s="38">
+        <v>19860000</v>
+      </c>
+      <c r="F159" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G159" s="45"/>
+      <c r="H159" s="45"/>
+      <c r="I159" s="45"/>
+      <c r="J159" s="45"/>
+      <c r="K159" s="45"/>
+      <c r="L159" s="45"/>
+      <c r="M159" s="45"/>
+      <c r="N159" s="45"/>
+      <c r="O159" s="45"/>
+      <c r="P159" s="45"/>
+      <c r="Q159" s="45"/>
+      <c r="R159" s="45"/>
+      <c r="S159" s="45"/>
+      <c r="T159" s="45"/>
+      <c r="U159" s="45"/>
+      <c r="V159" s="45"/>
+      <c r="W159" s="45"/>
+      <c r="X159" s="45"/>
+      <c r="Y159" s="45"/>
+      <c r="Z159" s="45"/>
+      <c r="AA159" s="45"/>
+      <c r="AB159" s="45"/>
+      <c r="AC159" s="45"/>
+    </row>
+    <row r="160" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D160" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E160" s="38">
+        <v>24980000</v>
+      </c>
+      <c r="F160" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G160" s="45"/>
+      <c r="H160" s="45"/>
+      <c r="I160" s="45"/>
+      <c r="J160" s="45"/>
+      <c r="K160" s="45"/>
+      <c r="L160" s="45"/>
+      <c r="M160" s="45"/>
+      <c r="N160" s="45"/>
+      <c r="O160" s="45"/>
+      <c r="P160" s="45"/>
+      <c r="Q160" s="45"/>
+      <c r="R160" s="45"/>
+      <c r="S160" s="45"/>
+      <c r="T160" s="45"/>
+      <c r="U160" s="45"/>
+      <c r="V160" s="45"/>
+      <c r="W160" s="45"/>
+      <c r="X160" s="45"/>
+      <c r="Y160" s="45"/>
+      <c r="Z160" s="45"/>
+      <c r="AA160" s="45"/>
+      <c r="AB160" s="45"/>
+      <c r="AC160" s="45"/>
+    </row>
+    <row r="161" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="B161" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C161" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D161" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" s="38">
+        <v>35680000</v>
+      </c>
+      <c r="F161" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G161" s="45"/>
+      <c r="H161" s="45"/>
+      <c r="I161" s="45"/>
+      <c r="J161" s="45"/>
+      <c r="K161" s="45"/>
+      <c r="L161" s="45"/>
+      <c r="M161" s="45"/>
+      <c r="N161" s="45"/>
+      <c r="O161" s="45"/>
+      <c r="P161" s="45"/>
+      <c r="Q161" s="45"/>
+      <c r="R161" s="45"/>
+      <c r="S161" s="45"/>
+      <c r="T161" s="45"/>
+      <c r="U161" s="45"/>
+      <c r="V161" s="45"/>
+      <c r="W161" s="45"/>
+      <c r="X161" s="45"/>
+      <c r="Y161" s="45"/>
+      <c r="Z161" s="45"/>
+      <c r="AA161" s="45"/>
+      <c r="AB161" s="45"/>
+      <c r="AC161" s="45"/>
+    </row>
+    <row r="162" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B162" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D162" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="38">
+        <v>39860000</v>
+      </c>
+      <c r="F162" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G162" s="45"/>
+      <c r="H162" s="45"/>
+      <c r="I162" s="45"/>
+      <c r="J162" s="45"/>
+      <c r="K162" s="45"/>
+      <c r="L162" s="45"/>
+      <c r="M162" s="45"/>
+      <c r="N162" s="45"/>
+      <c r="O162" s="45"/>
+      <c r="P162" s="45"/>
+      <c r="Q162" s="45"/>
+      <c r="R162" s="45"/>
+      <c r="S162" s="45"/>
+      <c r="T162" s="45"/>
+      <c r="U162" s="45"/>
+      <c r="V162" s="45"/>
+      <c r="W162" s="45"/>
+      <c r="X162" s="45"/>
+      <c r="Y162" s="45"/>
+      <c r="Z162" s="45"/>
+      <c r="AA162" s="45"/>
+      <c r="AB162" s="45"/>
+      <c r="AC162" s="45"/>
+    </row>
+    <row r="163" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="B145" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C145" s="19" t="s">
+      <c r="B163" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D145" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E145" s="42">
+      <c r="D163" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" s="38">
         <v>47979000</v>
       </c>
-      <c r="F145" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7" s="3" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="22" t="s">
+      <c r="F163" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G163"/>
+      <c r="H163"/>
+      <c r="I163"/>
+      <c r="J163"/>
+      <c r="K163"/>
+      <c r="L163"/>
+      <c r="M163"/>
+      <c r="N163"/>
+      <c r="O163"/>
+      <c r="P163"/>
+      <c r="Q163"/>
+      <c r="R163"/>
+      <c r="S163"/>
+      <c r="T163"/>
+      <c r="U163"/>
+      <c r="V163"/>
+      <c r="W163"/>
+      <c r="X163"/>
+      <c r="Y163"/>
+      <c r="Z163"/>
+      <c r="AA163"/>
+      <c r="AB163"/>
+      <c r="AC163"/>
+    </row>
+    <row r="164" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B164" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D164" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" s="38">
+        <v>52680000</v>
+      </c>
+      <c r="F164" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G164" s="45"/>
+      <c r="H164" s="45"/>
+      <c r="I164" s="45"/>
+      <c r="J164" s="45"/>
+      <c r="K164" s="45"/>
+      <c r="L164" s="45"/>
+      <c r="M164" s="45"/>
+      <c r="N164" s="45"/>
+      <c r="O164" s="45"/>
+      <c r="P164" s="45"/>
+      <c r="Q164" s="45"/>
+      <c r="R164" s="45"/>
+      <c r="S164" s="45"/>
+      <c r="T164" s="45"/>
+      <c r="U164" s="45"/>
+      <c r="V164" s="45"/>
+      <c r="W164" s="45"/>
+      <c r="X164" s="45"/>
+      <c r="Y164" s="45"/>
+      <c r="Z164" s="45"/>
+      <c r="AA164" s="45"/>
+      <c r="AB164" s="45"/>
+      <c r="AC164" s="45"/>
+    </row>
+    <row r="165" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B165" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D165" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" s="38">
+        <v>62680000</v>
+      </c>
+      <c r="F165" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G165" s="45"/>
+      <c r="H165" s="45"/>
+      <c r="I165" s="45"/>
+      <c r="J165" s="45"/>
+      <c r="K165" s="45"/>
+      <c r="L165" s="45"/>
+      <c r="M165" s="45"/>
+      <c r="N165" s="45"/>
+      <c r="O165" s="45"/>
+      <c r="P165" s="45"/>
+      <c r="Q165" s="45"/>
+      <c r="R165" s="45"/>
+      <c r="S165" s="45"/>
+      <c r="T165" s="45"/>
+      <c r="U165" s="45"/>
+      <c r="V165" s="45"/>
+      <c r="W165" s="45"/>
+      <c r="X165" s="45"/>
+      <c r="Y165" s="45"/>
+      <c r="Z165" s="45"/>
+      <c r="AA165" s="45"/>
+      <c r="AB165" s="45"/>
+      <c r="AC165" s="45"/>
+    </row>
+    <row r="166" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B166" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D166" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E166" s="38">
+        <v>68680000</v>
+      </c>
+      <c r="F166" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G166" s="45"/>
+      <c r="H166" s="45"/>
+      <c r="I166" s="45"/>
+      <c r="J166" s="45"/>
+      <c r="K166" s="45"/>
+      <c r="L166" s="45"/>
+      <c r="M166" s="45"/>
+      <c r="N166" s="45"/>
+      <c r="O166" s="45"/>
+      <c r="P166" s="45"/>
+      <c r="Q166" s="45"/>
+      <c r="R166" s="45"/>
+      <c r="S166" s="45"/>
+      <c r="T166" s="45"/>
+      <c r="U166" s="45"/>
+      <c r="V166" s="45"/>
+      <c r="W166" s="45"/>
+      <c r="X166" s="45"/>
+      <c r="Y166" s="45"/>
+      <c r="Z166" s="45"/>
+      <c r="AA166" s="45"/>
+      <c r="AB166" s="45"/>
+      <c r="AC166" s="45"/>
+    </row>
+    <row r="167" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B167" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D167" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" s="38">
+        <v>75500000</v>
+      </c>
+      <c r="F167" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G167" s="45"/>
+      <c r="H167" s="45"/>
+      <c r="I167" s="45"/>
+      <c r="J167" s="45"/>
+      <c r="K167" s="45"/>
+      <c r="L167" s="45"/>
+      <c r="M167" s="45"/>
+      <c r="N167" s="45"/>
+      <c r="O167" s="45"/>
+      <c r="P167" s="45"/>
+      <c r="Q167" s="45"/>
+      <c r="R167" s="45"/>
+      <c r="S167" s="45"/>
+      <c r="T167" s="45"/>
+      <c r="U167" s="45"/>
+      <c r="V167" s="45"/>
+      <c r="W167" s="45"/>
+      <c r="X167" s="45"/>
+      <c r="Y167" s="45"/>
+      <c r="Z167" s="45"/>
+      <c r="AA167" s="45"/>
+      <c r="AB167" s="45"/>
+      <c r="AC167" s="45"/>
+    </row>
+    <row r="168" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B168" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C168" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D168" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E168" s="38">
+        <v>89580000</v>
+      </c>
+      <c r="F168" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G168" s="45"/>
+      <c r="H168" s="45"/>
+      <c r="I168" s="45"/>
+      <c r="J168" s="45"/>
+      <c r="K168" s="45"/>
+      <c r="L168" s="45"/>
+      <c r="M168" s="45"/>
+      <c r="N168" s="45"/>
+      <c r="O168" s="45"/>
+      <c r="P168" s="45"/>
+      <c r="Q168" s="45"/>
+      <c r="R168" s="45"/>
+      <c r="S168" s="45"/>
+      <c r="T168" s="45"/>
+      <c r="U168" s="45"/>
+      <c r="V168" s="45"/>
+      <c r="W168" s="45"/>
+      <c r="X168" s="45"/>
+      <c r="Y168" s="45"/>
+      <c r="Z168" s="45"/>
+      <c r="AA168" s="45"/>
+      <c r="AB168" s="45"/>
+      <c r="AC168" s="45"/>
+    </row>
+    <row r="169" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B169" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C169" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D169" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E169" s="38">
+        <v>99880000</v>
+      </c>
+      <c r="F169" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G169" s="45"/>
+      <c r="H169" s="45"/>
+      <c r="I169" s="45"/>
+      <c r="J169" s="45"/>
+      <c r="K169" s="45"/>
+      <c r="L169" s="45"/>
+      <c r="M169" s="45"/>
+      <c r="N169" s="45"/>
+      <c r="O169" s="45"/>
+      <c r="P169" s="45"/>
+      <c r="Q169" s="45"/>
+      <c r="R169" s="45"/>
+      <c r="S169" s="45"/>
+      <c r="T169" s="45"/>
+      <c r="U169" s="45"/>
+      <c r="V169" s="45"/>
+      <c r="W169" s="45"/>
+      <c r="X169" s="45"/>
+      <c r="Y169" s="45"/>
+      <c r="Z169" s="45"/>
+      <c r="AA169" s="45"/>
+      <c r="AB169" s="45"/>
+      <c r="AC169" s="45"/>
+    </row>
+    <row r="170" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B170" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D170" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E170" s="38">
+        <v>109680000</v>
+      </c>
+      <c r="F170" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G170" s="45"/>
+      <c r="H170" s="45"/>
+      <c r="I170" s="45"/>
+      <c r="J170" s="45"/>
+      <c r="K170" s="45"/>
+      <c r="L170" s="45"/>
+      <c r="M170" s="45"/>
+      <c r="N170" s="45"/>
+      <c r="O170" s="45"/>
+      <c r="P170" s="45"/>
+      <c r="Q170" s="45"/>
+      <c r="R170" s="45"/>
+      <c r="S170" s="45"/>
+      <c r="T170" s="45"/>
+      <c r="U170" s="45"/>
+      <c r="V170" s="45"/>
+      <c r="W170" s="45"/>
+      <c r="X170" s="45"/>
+      <c r="Y170" s="45"/>
+      <c r="Z170" s="45"/>
+      <c r="AA170" s="45"/>
+      <c r="AB170" s="45"/>
+      <c r="AC170" s="45"/>
+    </row>
+    <row r="171" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B171" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C171" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D171" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E171" s="38">
+        <v>129860000</v>
+      </c>
+      <c r="F171" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G171" s="45"/>
+      <c r="H171" s="45"/>
+      <c r="I171" s="45"/>
+      <c r="J171" s="45"/>
+      <c r="K171" s="45"/>
+      <c r="L171" s="45"/>
+      <c r="M171" s="45"/>
+      <c r="N171" s="45"/>
+      <c r="O171" s="45"/>
+      <c r="P171" s="45"/>
+      <c r="Q171" s="45"/>
+      <c r="R171" s="45"/>
+      <c r="S171" s="45"/>
+      <c r="T171" s="45"/>
+      <c r="U171" s="45"/>
+      <c r="V171" s="45"/>
+      <c r="W171" s="45"/>
+      <c r="X171" s="45"/>
+      <c r="Y171" s="45"/>
+      <c r="Z171" s="45"/>
+      <c r="AA171" s="45"/>
+      <c r="AB171" s="45"/>
+      <c r="AC171" s="45"/>
+    </row>
+    <row r="172" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B172" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D172" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E172" s="38">
+        <v>144910000</v>
+      </c>
+      <c r="F172" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G172" s="45"/>
+      <c r="H172" s="45"/>
+      <c r="I172" s="45"/>
+      <c r="J172" s="45"/>
+      <c r="K172" s="45"/>
+      <c r="L172" s="45"/>
+      <c r="M172" s="45"/>
+      <c r="N172" s="45"/>
+      <c r="O172" s="45"/>
+      <c r="P172" s="45"/>
+      <c r="Q172" s="45"/>
+      <c r="R172" s="45"/>
+      <c r="S172" s="45"/>
+      <c r="T172" s="45"/>
+      <c r="U172" s="45"/>
+      <c r="V172" s="45"/>
+      <c r="W172" s="45"/>
+      <c r="X172" s="45"/>
+      <c r="Y172" s="45"/>
+      <c r="Z172" s="45"/>
+      <c r="AA172" s="45"/>
+      <c r="AB172" s="45"/>
+      <c r="AC172" s="45"/>
+    </row>
+    <row r="173" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B173" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C173" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D173" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E173" s="38">
+        <v>155910000</v>
+      </c>
+      <c r="F173" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G173" s="45"/>
+      <c r="H173" s="45"/>
+      <c r="I173" s="45"/>
+      <c r="J173" s="45"/>
+      <c r="K173" s="45"/>
+      <c r="L173" s="45"/>
+      <c r="M173" s="45"/>
+      <c r="N173" s="45"/>
+      <c r="O173" s="45"/>
+      <c r="P173" s="45"/>
+      <c r="Q173" s="45"/>
+      <c r="R173" s="45"/>
+      <c r="S173" s="45"/>
+      <c r="T173" s="45"/>
+      <c r="U173" s="45"/>
+      <c r="V173" s="45"/>
+      <c r="W173" s="45"/>
+      <c r="X173" s="45"/>
+      <c r="Y173" s="45"/>
+      <c r="Z173" s="45"/>
+      <c r="AA173" s="45"/>
+      <c r="AB173" s="45"/>
+      <c r="AC173" s="45"/>
+    </row>
+    <row r="174" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B174" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D174" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E174" s="38">
+        <v>156560000</v>
+      </c>
+      <c r="F174" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G174" s="45"/>
+      <c r="H174" s="45"/>
+      <c r="I174" s="45"/>
+      <c r="J174" s="45"/>
+      <c r="K174" s="45"/>
+      <c r="L174" s="45"/>
+      <c r="M174" s="45"/>
+      <c r="N174" s="45"/>
+      <c r="O174" s="45"/>
+      <c r="P174" s="45"/>
+      <c r="Q174" s="45"/>
+      <c r="R174" s="45"/>
+      <c r="S174" s="45"/>
+      <c r="T174" s="45"/>
+      <c r="U174" s="45"/>
+      <c r="V174" s="45"/>
+      <c r="W174" s="45"/>
+      <c r="X174" s="45"/>
+      <c r="Y174" s="45"/>
+      <c r="Z174" s="45"/>
+      <c r="AA174" s="45"/>
+      <c r="AB174" s="45"/>
+      <c r="AC174" s="45"/>
+    </row>
+    <row r="175" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B175" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C175" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D175" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E175" s="38">
+        <v>184370000</v>
+      </c>
+      <c r="F175" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G175" s="45"/>
+      <c r="H175" s="45"/>
+      <c r="I175" s="45"/>
+      <c r="J175" s="45"/>
+      <c r="K175" s="45"/>
+      <c r="L175" s="45"/>
+      <c r="M175" s="45"/>
+      <c r="N175" s="45"/>
+      <c r="O175" s="45"/>
+      <c r="P175" s="45"/>
+      <c r="Q175" s="45"/>
+      <c r="R175" s="45"/>
+      <c r="S175" s="45"/>
+      <c r="T175" s="45"/>
+      <c r="U175" s="45"/>
+      <c r="V175" s="45"/>
+      <c r="W175" s="45"/>
+      <c r="X175" s="45"/>
+      <c r="Y175" s="45"/>
+      <c r="Z175" s="45"/>
+      <c r="AA175" s="45"/>
+      <c r="AB175" s="45"/>
+      <c r="AC175" s="45"/>
+    </row>
+    <row r="176" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B176" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C176" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D176" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176" s="38">
+        <v>243080000</v>
+      </c>
+      <c r="F176" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G176" s="45"/>
+      <c r="H176" s="45"/>
+      <c r="I176" s="45"/>
+      <c r="J176" s="45"/>
+      <c r="K176" s="45"/>
+      <c r="L176" s="45"/>
+      <c r="M176" s="45"/>
+      <c r="N176" s="45"/>
+      <c r="O176" s="45"/>
+      <c r="P176" s="45"/>
+      <c r="Q176" s="45"/>
+      <c r="R176" s="45"/>
+      <c r="S176" s="45"/>
+      <c r="T176" s="45"/>
+      <c r="U176" s="45"/>
+      <c r="V176" s="45"/>
+      <c r="W176" s="45"/>
+      <c r="X176" s="45"/>
+      <c r="Y176" s="45"/>
+      <c r="Z176" s="45"/>
+      <c r="AA176" s="45"/>
+      <c r="AB176" s="45"/>
+      <c r="AC176" s="45"/>
+    </row>
+    <row r="177" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B177" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D177" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" s="38">
+        <v>276040000</v>
+      </c>
+      <c r="F177" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G177" s="45"/>
+      <c r="H177" s="45"/>
+      <c r="I177" s="45"/>
+      <c r="J177" s="45"/>
+      <c r="K177" s="45"/>
+      <c r="L177" s="45"/>
+      <c r="M177" s="45"/>
+      <c r="N177" s="45"/>
+      <c r="O177" s="45"/>
+      <c r="P177" s="45"/>
+      <c r="Q177" s="45"/>
+      <c r="R177" s="45"/>
+      <c r="S177" s="45"/>
+      <c r="T177" s="45"/>
+      <c r="U177" s="45"/>
+      <c r="V177" s="45"/>
+      <c r="W177" s="45"/>
+      <c r="X177" s="45"/>
+      <c r="Y177" s="45"/>
+      <c r="Z177" s="45"/>
+      <c r="AA177" s="45"/>
+      <c r="AB177" s="45"/>
+      <c r="AC177" s="45"/>
+    </row>
+    <row r="178" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B178" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C178" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D178" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" s="38">
+        <v>313680000</v>
+      </c>
+      <c r="F178" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G178" s="45"/>
+      <c r="H178" s="45"/>
+      <c r="I178" s="45"/>
+      <c r="J178" s="45"/>
+      <c r="K178" s="45"/>
+      <c r="L178" s="45"/>
+      <c r="M178" s="45"/>
+      <c r="N178" s="45"/>
+      <c r="O178" s="45"/>
+      <c r="P178" s="45"/>
+      <c r="Q178" s="45"/>
+      <c r="R178" s="45"/>
+      <c r="S178" s="45"/>
+      <c r="T178" s="45"/>
+      <c r="U178" s="45"/>
+      <c r="V178" s="45"/>
+      <c r="W178" s="45"/>
+      <c r="X178" s="45"/>
+      <c r="Y178" s="45"/>
+      <c r="Z178" s="45"/>
+      <c r="AA178" s="45"/>
+      <c r="AB178" s="45"/>
+      <c r="AC178" s="45"/>
+    </row>
+    <row r="179" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B179" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D179" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E179" s="38">
+        <v>358200000</v>
+      </c>
+      <c r="F179" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G179" s="45"/>
+      <c r="H179" s="45"/>
+      <c r="I179" s="45"/>
+      <c r="J179" s="45"/>
+      <c r="K179" s="45"/>
+      <c r="L179" s="45"/>
+      <c r="M179" s="45"/>
+      <c r="N179" s="45"/>
+      <c r="O179" s="45"/>
+      <c r="P179" s="45"/>
+      <c r="Q179" s="45"/>
+      <c r="R179" s="45"/>
+      <c r="S179" s="45"/>
+      <c r="T179" s="45"/>
+      <c r="U179" s="45"/>
+      <c r="V179" s="45"/>
+      <c r="W179" s="45"/>
+      <c r="X179" s="45"/>
+      <c r="Y179" s="45"/>
+      <c r="Z179" s="45"/>
+      <c r="AA179" s="45"/>
+      <c r="AB179" s="45"/>
+      <c r="AC179" s="45"/>
+    </row>
+    <row r="180" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B180" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C180" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D180" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E180" s="38">
+        <v>389600000</v>
+      </c>
+      <c r="F180" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G180" s="45"/>
+      <c r="H180" s="45"/>
+      <c r="I180" s="45"/>
+      <c r="J180" s="45"/>
+      <c r="K180" s="45"/>
+      <c r="L180" s="45"/>
+      <c r="M180" s="45"/>
+      <c r="N180" s="45"/>
+      <c r="O180" s="45"/>
+      <c r="P180" s="45"/>
+      <c r="Q180" s="45"/>
+      <c r="R180" s="45"/>
+      <c r="S180" s="45"/>
+      <c r="T180" s="45"/>
+      <c r="U180" s="45"/>
+      <c r="V180" s="45"/>
+      <c r="W180" s="45"/>
+      <c r="X180" s="45"/>
+      <c r="Y180" s="45"/>
+      <c r="Z180" s="45"/>
+      <c r="AA180" s="45"/>
+      <c r="AB180" s="45"/>
+      <c r="AC180" s="45"/>
+    </row>
+    <row r="181" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B181" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C181" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D181" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181" s="38">
+        <v>433800000</v>
+      </c>
+      <c r="F181" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G181" s="45"/>
+      <c r="H181" s="45"/>
+      <c r="I181" s="45"/>
+      <c r="J181" s="45"/>
+      <c r="K181" s="45"/>
+      <c r="L181" s="45"/>
+      <c r="M181" s="45"/>
+      <c r="N181" s="45"/>
+      <c r="O181" s="45"/>
+      <c r="P181" s="45"/>
+      <c r="Q181" s="45"/>
+      <c r="R181" s="45"/>
+      <c r="S181" s="45"/>
+      <c r="T181" s="45"/>
+      <c r="U181" s="45"/>
+      <c r="V181" s="45"/>
+      <c r="W181" s="45"/>
+      <c r="X181" s="45"/>
+      <c r="Y181" s="45"/>
+      <c r="Z181" s="45"/>
+      <c r="AA181" s="45"/>
+      <c r="AB181" s="45"/>
+      <c r="AC181" s="45"/>
+    </row>
+    <row r="182" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B182" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D182" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E182" s="38">
+        <v>656580000</v>
+      </c>
+      <c r="F182" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G182" s="45"/>
+      <c r="H182" s="45"/>
+      <c r="I182" s="45"/>
+      <c r="J182" s="45"/>
+      <c r="K182" s="45"/>
+      <c r="L182" s="45"/>
+      <c r="M182" s="45"/>
+      <c r="N182" s="45"/>
+      <c r="O182" s="45"/>
+      <c r="P182" s="45"/>
+      <c r="Q182" s="45"/>
+      <c r="R182" s="45"/>
+      <c r="S182" s="45"/>
+      <c r="T182" s="45"/>
+      <c r="U182" s="45"/>
+      <c r="V182" s="45"/>
+      <c r="W182" s="45"/>
+      <c r="X182" s="45"/>
+      <c r="Y182" s="45"/>
+      <c r="Z182" s="45"/>
+      <c r="AA182" s="45"/>
+      <c r="AB182" s="45"/>
+      <c r="AC182" s="45"/>
+    </row>
+    <row r="183" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B183" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D183" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E183" s="38">
+        <v>762670000</v>
+      </c>
+      <c r="F183" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G183" s="45"/>
+      <c r="H183" s="45"/>
+      <c r="I183" s="45"/>
+      <c r="J183" s="45"/>
+      <c r="K183" s="45"/>
+      <c r="L183" s="45"/>
+      <c r="M183" s="45"/>
+      <c r="N183" s="45"/>
+      <c r="O183" s="45"/>
+      <c r="P183" s="45"/>
+      <c r="Q183" s="45"/>
+      <c r="R183" s="45"/>
+      <c r="S183" s="45"/>
+      <c r="T183" s="45"/>
+      <c r="U183" s="45"/>
+      <c r="V183" s="45"/>
+      <c r="W183" s="45"/>
+      <c r="X183" s="45"/>
+      <c r="Y183" s="45"/>
+      <c r="Z183" s="45"/>
+      <c r="AA183" s="45"/>
+      <c r="AB183" s="45"/>
+      <c r="AC183" s="45"/>
+    </row>
+    <row r="184" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B184" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C184" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D184" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E184" s="38">
+        <v>874940000</v>
+      </c>
+      <c r="F184" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G184" s="45"/>
+      <c r="H184" s="45"/>
+      <c r="I184" s="45"/>
+      <c r="J184" s="45"/>
+      <c r="K184" s="45"/>
+      <c r="L184" s="45"/>
+      <c r="M184" s="45"/>
+      <c r="N184" s="45"/>
+      <c r="O184" s="45"/>
+      <c r="P184" s="45"/>
+      <c r="Q184" s="45"/>
+      <c r="R184" s="45"/>
+      <c r="S184" s="45"/>
+      <c r="T184" s="45"/>
+      <c r="U184" s="45"/>
+      <c r="V184" s="45"/>
+      <c r="W184" s="45"/>
+      <c r="X184" s="45"/>
+      <c r="Y184" s="45"/>
+      <c r="Z184" s="45"/>
+      <c r="AA184" s="45"/>
+      <c r="AB184" s="45"/>
+      <c r="AC184" s="45"/>
+    </row>
+    <row r="185" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B185" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D185" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E185" s="38">
+        <v>1062400000</v>
+      </c>
+      <c r="F185" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G185" s="45"/>
+      <c r="H185" s="45"/>
+      <c r="I185" s="45"/>
+      <c r="J185" s="45"/>
+      <c r="K185" s="45"/>
+      <c r="L185" s="45"/>
+      <c r="M185" s="45"/>
+      <c r="N185" s="45"/>
+      <c r="O185" s="45"/>
+      <c r="P185" s="45"/>
+      <c r="Q185" s="45"/>
+      <c r="R185" s="45"/>
+      <c r="S185" s="45"/>
+      <c r="T185" s="45"/>
+      <c r="U185" s="45"/>
+      <c r="V185" s="45"/>
+      <c r="W185" s="45"/>
+      <c r="X185" s="45"/>
+      <c r="Y185" s="45"/>
+      <c r="Z185" s="45"/>
+      <c r="AA185" s="45"/>
+      <c r="AB185" s="45"/>
+      <c r="AC185" s="45"/>
+    </row>
+    <row r="186" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="B146" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="23" t="s">
+      <c r="B186" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C186" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D146" s="24" t="s">
+      <c r="D186" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E146" s="43">
+      <c r="E186" s="39">
         <v>75000</v>
       </c>
-      <c r="F146" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="G146" s="4"/>
-    </row>
-    <row r="147" spans="1:7" s="3" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="17" t="s">
+      <c r="F186" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G186"/>
+      <c r="H186"/>
+      <c r="I186"/>
+      <c r="J186"/>
+      <c r="K186"/>
+      <c r="L186"/>
+      <c r="M186"/>
+      <c r="N186"/>
+      <c r="O186"/>
+      <c r="P186"/>
+      <c r="Q186"/>
+      <c r="R186"/>
+      <c r="S186"/>
+      <c r="T186"/>
+      <c r="U186"/>
+      <c r="V186"/>
+      <c r="W186"/>
+      <c r="X186"/>
+      <c r="Y186"/>
+      <c r="Z186"/>
+      <c r="AA186"/>
+      <c r="AB186"/>
+      <c r="AC186"/>
+    </row>
+    <row r="187" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B187" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C187" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D187" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="E187" s="39">
+        <v>33000</v>
+      </c>
+      <c r="F187" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G187"/>
+      <c r="H187"/>
+      <c r="I187"/>
+      <c r="J187"/>
+      <c r="K187"/>
+      <c r="L187"/>
+      <c r="M187"/>
+      <c r="N187"/>
+      <c r="O187"/>
+      <c r="P187"/>
+      <c r="Q187"/>
+      <c r="R187"/>
+      <c r="S187"/>
+      <c r="T187"/>
+      <c r="U187"/>
+      <c r="V187"/>
+      <c r="W187"/>
+      <c r="X187"/>
+      <c r="Y187"/>
+      <c r="Z187"/>
+      <c r="AA187"/>
+      <c r="AB187"/>
+      <c r="AC187"/>
+    </row>
+    <row r="188" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B188" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C188" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D188" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="E188" s="39">
+        <v>75000</v>
+      </c>
+      <c r="F188" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G188"/>
+      <c r="H188"/>
+      <c r="I188"/>
+      <c r="J188"/>
+      <c r="K188"/>
+      <c r="L188"/>
+      <c r="M188"/>
+      <c r="N188"/>
+      <c r="O188"/>
+      <c r="P188"/>
+      <c r="Q188"/>
+      <c r="R188"/>
+      <c r="S188"/>
+      <c r="T188"/>
+      <c r="U188"/>
+      <c r="V188"/>
+      <c r="W188"/>
+      <c r="X188"/>
+      <c r="Y188"/>
+      <c r="Z188"/>
+      <c r="AA188"/>
+      <c r="AB188"/>
+      <c r="AC188"/>
+    </row>
+    <row r="189" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="B147" s="18" t="s">
+      <c r="B189" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C147" s="23" t="s">
+      <c r="C189" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D147" s="24" t="s">
+      <c r="D189" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E147" s="43">
+      <c r="E189" s="39">
         <v>75000</v>
       </c>
-      <c r="F147" s="25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" s="3" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="22" t="s">
+      <c r="F189" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G189"/>
+      <c r="H189"/>
+      <c r="I189"/>
+      <c r="J189"/>
+      <c r="K189"/>
+      <c r="L189"/>
+      <c r="M189"/>
+      <c r="N189"/>
+      <c r="O189"/>
+      <c r="P189"/>
+      <c r="Q189"/>
+      <c r="R189"/>
+      <c r="S189"/>
+      <c r="T189"/>
+      <c r="U189"/>
+      <c r="V189"/>
+      <c r="W189"/>
+      <c r="X189"/>
+      <c r="Y189"/>
+      <c r="Z189"/>
+      <c r="AA189"/>
+      <c r="AB189"/>
+      <c r="AC189"/>
+    </row>
+    <row r="190" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="B148" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" s="23" t="s">
+      <c r="B190" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D148" s="24" t="s">
+      <c r="D190" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E148" s="43">
+      <c r="E190" s="39">
         <v>75000</v>
       </c>
-      <c r="F148" s="25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" s="5" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="17" t="s">
+      <c r="F190" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G190"/>
+      <c r="H190"/>
+      <c r="I190"/>
+      <c r="J190"/>
+      <c r="K190"/>
+      <c r="L190"/>
+      <c r="M190"/>
+      <c r="N190"/>
+      <c r="O190"/>
+      <c r="P190"/>
+      <c r="Q190"/>
+      <c r="R190"/>
+      <c r="S190"/>
+      <c r="T190"/>
+      <c r="U190"/>
+      <c r="V190"/>
+      <c r="W190"/>
+      <c r="X190"/>
+      <c r="Y190"/>
+      <c r="Z190"/>
+      <c r="AA190"/>
+      <c r="AB190"/>
+      <c r="AC190"/>
+    </row>
+    <row r="191" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B149" s="26" t="s">
+      <c r="B191" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="C149" s="23" t="s">
+      <c r="C191" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D149" s="24" t="s">
+      <c r="D191" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E149" s="43">
+      <c r="E191" s="39">
         <v>75000</v>
       </c>
-      <c r="F149" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="G149" s="3"/>
-    </row>
-    <row r="150" spans="1:7" s="6" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="27" t="s">
+      <c r="F191" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G191"/>
+      <c r="H191"/>
+      <c r="I191"/>
+      <c r="J191"/>
+      <c r="K191"/>
+      <c r="L191"/>
+      <c r="M191"/>
+      <c r="N191"/>
+      <c r="O191"/>
+      <c r="P191"/>
+      <c r="Q191"/>
+      <c r="R191"/>
+      <c r="S191"/>
+      <c r="T191"/>
+      <c r="U191"/>
+      <c r="V191"/>
+      <c r="W191"/>
+      <c r="X191"/>
+      <c r="Y191"/>
+      <c r="Z191"/>
+      <c r="AA191"/>
+      <c r="AB191"/>
+      <c r="AC191"/>
+    </row>
+    <row r="192" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="B150" s="28" t="s">
+      <c r="B192" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="C150" s="29" t="s">
+      <c r="C192" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D150" s="24" t="s">
+      <c r="D192" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E150" s="43">
+      <c r="E192" s="39">
         <v>75000</v>
       </c>
-      <c r="F150" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="22" t="s">
+      <c r="F192" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G192"/>
+      <c r="H192"/>
+      <c r="I192"/>
+      <c r="J192"/>
+      <c r="K192"/>
+      <c r="L192"/>
+      <c r="M192"/>
+      <c r="N192"/>
+      <c r="O192"/>
+      <c r="P192"/>
+      <c r="Q192"/>
+      <c r="R192"/>
+      <c r="S192"/>
+      <c r="T192"/>
+      <c r="U192"/>
+      <c r="V192"/>
+      <c r="W192"/>
+      <c r="X192"/>
+      <c r="Y192"/>
+      <c r="Z192"/>
+      <c r="AA192"/>
+      <c r="AB192"/>
+      <c r="AC192"/>
+    </row>
+    <row r="193" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B193" s="46"/>
+      <c r="C193" s="47"/>
+      <c r="D193" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E193" s="39">
+        <v>1000000</v>
+      </c>
+      <c r="F193" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G193"/>
+      <c r="H193"/>
+      <c r="I193"/>
+      <c r="J193"/>
+      <c r="K193"/>
+      <c r="L193"/>
+      <c r="M193"/>
+      <c r="N193"/>
+      <c r="O193"/>
+      <c r="P193"/>
+      <c r="Q193"/>
+      <c r="R193"/>
+      <c r="S193"/>
+      <c r="T193"/>
+      <c r="U193"/>
+      <c r="V193"/>
+      <c r="W193"/>
+      <c r="X193"/>
+      <c r="Y193"/>
+      <c r="Z193"/>
+      <c r="AA193"/>
+      <c r="AB193"/>
+      <c r="AC193"/>
+    </row>
+    <row r="194" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="B194" s="46"/>
+      <c r="C194" s="47"/>
+      <c r="D194" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E194" s="39">
+        <v>880000</v>
+      </c>
+      <c r="F194" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G194"/>
+      <c r="H194"/>
+      <c r="I194"/>
+      <c r="J194"/>
+      <c r="K194"/>
+      <c r="L194"/>
+      <c r="M194"/>
+      <c r="N194"/>
+      <c r="O194"/>
+      <c r="P194"/>
+      <c r="Q194"/>
+      <c r="R194"/>
+      <c r="S194"/>
+      <c r="T194"/>
+      <c r="U194"/>
+      <c r="V194"/>
+      <c r="W194"/>
+      <c r="X194"/>
+      <c r="Y194"/>
+      <c r="Z194"/>
+      <c r="AA194"/>
+      <c r="AB194"/>
+      <c r="AC194"/>
+    </row>
+    <row r="195" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B195" s="46"/>
+      <c r="C195" s="47"/>
+      <c r="D195" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E195" s="39">
+        <v>1380000</v>
+      </c>
+      <c r="F195" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G195"/>
+      <c r="H195"/>
+      <c r="I195"/>
+      <c r="J195"/>
+      <c r="K195"/>
+      <c r="L195"/>
+      <c r="M195"/>
+      <c r="N195"/>
+      <c r="O195"/>
+      <c r="P195"/>
+      <c r="Q195"/>
+      <c r="R195"/>
+      <c r="S195"/>
+      <c r="T195"/>
+      <c r="U195"/>
+      <c r="V195"/>
+      <c r="W195"/>
+      <c r="X195"/>
+      <c r="Y195"/>
+      <c r="Z195"/>
+      <c r="AA195"/>
+      <c r="AB195"/>
+      <c r="AC195"/>
+    </row>
+    <row r="196" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B151" s="18"/>
-      <c r="C151" s="18"/>
-      <c r="D151" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E151" s="42">
+      <c r="B196" s="15"/>
+      <c r="C196" s="15"/>
+      <c r="D196" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196" s="38">
         <v>13880000</v>
       </c>
-      <c r="F151" s="31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="32" t="s">
+      <c r="F196" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G196"/>
+      <c r="H196"/>
+      <c r="I196"/>
+      <c r="J196"/>
+      <c r="K196"/>
+      <c r="L196"/>
+      <c r="M196"/>
+      <c r="N196"/>
+      <c r="O196"/>
+      <c r="P196"/>
+      <c r="Q196"/>
+      <c r="R196"/>
+      <c r="S196"/>
+      <c r="T196"/>
+      <c r="U196"/>
+      <c r="V196"/>
+      <c r="W196"/>
+      <c r="X196"/>
+      <c r="Y196"/>
+      <c r="Z196"/>
+      <c r="AA196"/>
+      <c r="AB196"/>
+      <c r="AC196"/>
+    </row>
+    <row r="197" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B197" s="15"/>
+      <c r="C197" s="15"/>
+      <c r="D197" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E197" s="38">
+        <v>750000</v>
+      </c>
+      <c r="F197" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G197"/>
+      <c r="H197"/>
+      <c r="I197"/>
+      <c r="J197"/>
+      <c r="K197"/>
+      <c r="L197"/>
+      <c r="M197"/>
+      <c r="N197"/>
+      <c r="O197"/>
+      <c r="P197"/>
+      <c r="Q197"/>
+      <c r="R197"/>
+      <c r="S197"/>
+      <c r="T197"/>
+      <c r="U197"/>
+      <c r="V197"/>
+      <c r="W197"/>
+      <c r="X197"/>
+      <c r="Y197"/>
+      <c r="Z197"/>
+      <c r="AA197"/>
+      <c r="AB197"/>
+      <c r="AC197"/>
+    </row>
+    <row r="198" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B198" s="15"/>
+      <c r="C198" s="15"/>
+      <c r="D198" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E198" s="38">
+        <v>155000</v>
+      </c>
+      <c r="F198" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G198"/>
+      <c r="H198"/>
+      <c r="I198"/>
+      <c r="J198"/>
+      <c r="K198"/>
+      <c r="L198"/>
+      <c r="M198"/>
+      <c r="N198"/>
+      <c r="O198"/>
+      <c r="P198"/>
+      <c r="Q198"/>
+      <c r="R198"/>
+      <c r="S198"/>
+      <c r="T198"/>
+      <c r="U198"/>
+      <c r="V198"/>
+      <c r="W198"/>
+      <c r="X198"/>
+      <c r="Y198"/>
+      <c r="Z198"/>
+      <c r="AA198"/>
+      <c r="AB198"/>
+      <c r="AC198"/>
+    </row>
+    <row r="199" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B199" s="15"/>
+      <c r="C199" s="15"/>
+      <c r="D199" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E199" s="38">
+        <v>176000</v>
+      </c>
+      <c r="F199" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G199"/>
+      <c r="H199"/>
+      <c r="I199"/>
+      <c r="J199"/>
+      <c r="K199"/>
+      <c r="L199"/>
+      <c r="M199"/>
+      <c r="N199"/>
+      <c r="O199"/>
+      <c r="P199"/>
+      <c r="Q199"/>
+      <c r="R199"/>
+      <c r="S199"/>
+      <c r="T199"/>
+      <c r="U199"/>
+      <c r="V199"/>
+      <c r="W199"/>
+      <c r="X199"/>
+      <c r="Y199"/>
+      <c r="Z199"/>
+      <c r="AA199"/>
+      <c r="AB199"/>
+      <c r="AC199"/>
+    </row>
+    <row r="200" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B200" s="15"/>
+      <c r="C200" s="15"/>
+      <c r="D200" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E200" s="38">
+        <v>198000</v>
+      </c>
+      <c r="F200" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G200"/>
+      <c r="H200"/>
+      <c r="I200"/>
+      <c r="J200"/>
+      <c r="K200"/>
+      <c r="L200"/>
+      <c r="M200"/>
+      <c r="N200"/>
+      <c r="O200"/>
+      <c r="P200"/>
+      <c r="Q200"/>
+      <c r="R200"/>
+      <c r="S200"/>
+      <c r="T200"/>
+      <c r="U200"/>
+      <c r="V200"/>
+      <c r="W200"/>
+      <c r="X200"/>
+      <c r="Y200"/>
+      <c r="Z200"/>
+      <c r="AA200"/>
+      <c r="AB200"/>
+      <c r="AC200"/>
+    </row>
+    <row r="201" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B201" s="15"/>
+      <c r="C201" s="15"/>
+      <c r="D201" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E201" s="38">
+        <v>186000</v>
+      </c>
+      <c r="F201" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G201"/>
+      <c r="H201"/>
+      <c r="I201"/>
+      <c r="J201"/>
+      <c r="K201"/>
+      <c r="L201"/>
+      <c r="M201"/>
+      <c r="N201"/>
+      <c r="O201"/>
+      <c r="P201"/>
+      <c r="Q201"/>
+      <c r="R201"/>
+      <c r="S201"/>
+      <c r="T201"/>
+      <c r="U201"/>
+      <c r="V201"/>
+      <c r="W201"/>
+      <c r="X201"/>
+      <c r="Y201"/>
+      <c r="Z201"/>
+      <c r="AA201"/>
+      <c r="AB201"/>
+      <c r="AC201"/>
+    </row>
+    <row r="202" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B202" s="15"/>
+      <c r="C202" s="15"/>
+      <c r="D202" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E202" s="38">
+        <v>198000</v>
+      </c>
+      <c r="F202" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G202"/>
+      <c r="H202"/>
+      <c r="I202"/>
+      <c r="J202"/>
+      <c r="K202"/>
+      <c r="L202"/>
+      <c r="M202"/>
+      <c r="N202"/>
+      <c r="O202"/>
+      <c r="P202"/>
+      <c r="Q202"/>
+      <c r="R202"/>
+      <c r="S202"/>
+      <c r="T202"/>
+      <c r="U202"/>
+      <c r="V202"/>
+      <c r="W202"/>
+      <c r="X202"/>
+      <c r="Y202"/>
+      <c r="Z202"/>
+      <c r="AA202"/>
+      <c r="AB202"/>
+      <c r="AC202"/>
+    </row>
+    <row r="203" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B203" s="15"/>
+      <c r="C203" s="15"/>
+      <c r="D203" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E203" s="38">
+        <v>228000</v>
+      </c>
+      <c r="F203" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G203"/>
+      <c r="H203"/>
+      <c r="I203"/>
+      <c r="J203"/>
+      <c r="K203"/>
+      <c r="L203"/>
+      <c r="M203"/>
+      <c r="N203"/>
+      <c r="O203"/>
+      <c r="P203"/>
+      <c r="Q203"/>
+      <c r="R203"/>
+      <c r="S203"/>
+      <c r="T203"/>
+      <c r="U203"/>
+      <c r="V203"/>
+      <c r="W203"/>
+      <c r="X203"/>
+      <c r="Y203"/>
+      <c r="Z203"/>
+      <c r="AA203"/>
+      <c r="AB203"/>
+      <c r="AC203"/>
+    </row>
+    <row r="204" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B204" s="15"/>
+      <c r="C204" s="15"/>
+      <c r="D204" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E204" s="38">
+        <v>175000</v>
+      </c>
+      <c r="F204" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G204"/>
+      <c r="H204"/>
+      <c r="I204"/>
+      <c r="J204"/>
+      <c r="K204"/>
+      <c r="L204"/>
+      <c r="M204"/>
+      <c r="N204"/>
+      <c r="O204"/>
+      <c r="P204"/>
+      <c r="Q204"/>
+      <c r="R204"/>
+      <c r="S204"/>
+      <c r="T204"/>
+      <c r="U204"/>
+      <c r="V204"/>
+      <c r="W204"/>
+      <c r="X204"/>
+      <c r="Y204"/>
+      <c r="Z204"/>
+      <c r="AA204"/>
+      <c r="AB204"/>
+      <c r="AC204"/>
+    </row>
+    <row r="205" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B205" s="15"/>
+      <c r="C205" s="15"/>
+      <c r="D205" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E205" s="38">
+        <v>296000</v>
+      </c>
+      <c r="F205" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G205"/>
+      <c r="H205"/>
+      <c r="I205"/>
+      <c r="J205"/>
+      <c r="K205"/>
+      <c r="L205"/>
+      <c r="M205"/>
+      <c r="N205"/>
+      <c r="O205"/>
+      <c r="P205"/>
+      <c r="Q205"/>
+      <c r="R205"/>
+      <c r="S205"/>
+      <c r="T205"/>
+      <c r="U205"/>
+      <c r="V205"/>
+      <c r="W205"/>
+      <c r="X205"/>
+      <c r="Y205"/>
+      <c r="Z205"/>
+      <c r="AA205"/>
+      <c r="AB205"/>
+      <c r="AC205"/>
+    </row>
+    <row r="206" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B206" s="15"/>
+      <c r="C206" s="15"/>
+      <c r="D206" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E206" s="38">
+        <v>258000</v>
+      </c>
+      <c r="F206" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G206"/>
+      <c r="H206"/>
+      <c r="I206"/>
+      <c r="J206"/>
+      <c r="K206"/>
+      <c r="L206"/>
+      <c r="M206"/>
+      <c r="N206"/>
+      <c r="O206"/>
+      <c r="P206"/>
+      <c r="Q206"/>
+      <c r="R206"/>
+      <c r="S206"/>
+      <c r="T206"/>
+      <c r="U206"/>
+      <c r="V206"/>
+      <c r="W206"/>
+      <c r="X206"/>
+      <c r="Y206"/>
+      <c r="Z206"/>
+      <c r="AA206"/>
+      <c r="AB206"/>
+      <c r="AC206"/>
+    </row>
+    <row r="207" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="B207" s="15"/>
+      <c r="C207" s="15"/>
+      <c r="D207" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E207" s="38">
+        <v>228000</v>
+      </c>
+      <c r="F207" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G207"/>
+      <c r="H207"/>
+      <c r="I207"/>
+      <c r="J207"/>
+      <c r="K207"/>
+      <c r="L207"/>
+      <c r="M207"/>
+      <c r="N207"/>
+      <c r="O207"/>
+      <c r="P207"/>
+      <c r="Q207"/>
+      <c r="R207"/>
+      <c r="S207"/>
+      <c r="T207"/>
+      <c r="U207"/>
+      <c r="V207"/>
+      <c r="W207"/>
+      <c r="X207"/>
+      <c r="Y207"/>
+      <c r="Z207"/>
+      <c r="AA207"/>
+      <c r="AB207"/>
+      <c r="AC207"/>
+    </row>
+    <row r="208" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="B208" s="15"/>
+      <c r="C208" s="15"/>
+      <c r="D208" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E208" s="38">
+        <v>248000</v>
+      </c>
+      <c r="F208" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G208"/>
+      <c r="H208"/>
+      <c r="I208"/>
+      <c r="J208"/>
+      <c r="K208"/>
+      <c r="L208"/>
+      <c r="M208"/>
+      <c r="N208"/>
+      <c r="O208"/>
+      <c r="P208"/>
+      <c r="Q208"/>
+      <c r="R208"/>
+      <c r="S208"/>
+      <c r="T208"/>
+      <c r="U208"/>
+      <c r="V208"/>
+      <c r="W208"/>
+      <c r="X208"/>
+      <c r="Y208"/>
+      <c r="Z208"/>
+      <c r="AA208"/>
+      <c r="AB208"/>
+      <c r="AC208"/>
+    </row>
+    <row r="209" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B209" s="15"/>
+      <c r="C209" s="15"/>
+      <c r="D209" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E209" s="38">
+        <v>278000</v>
+      </c>
+      <c r="F209" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G209"/>
+      <c r="H209"/>
+      <c r="I209"/>
+      <c r="J209"/>
+      <c r="K209"/>
+      <c r="L209"/>
+      <c r="M209"/>
+      <c r="N209"/>
+      <c r="O209"/>
+      <c r="P209"/>
+      <c r="Q209"/>
+      <c r="R209"/>
+      <c r="S209"/>
+      <c r="T209"/>
+      <c r="U209"/>
+      <c r="V209"/>
+      <c r="W209"/>
+      <c r="X209"/>
+      <c r="Y209"/>
+      <c r="Z209"/>
+      <c r="AA209"/>
+      <c r="AB209"/>
+      <c r="AC209"/>
+    </row>
+    <row r="210" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="B152" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C152" s="29" t="s">
+      <c r="B210" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D152" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E152" s="44">
+      <c r="D210" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E210" s="40">
         <v>32680000</v>
       </c>
-      <c r="F152" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="32" t="s">
+      <c r="F210" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G210"/>
+      <c r="H210"/>
+      <c r="I210"/>
+      <c r="J210"/>
+      <c r="K210"/>
+      <c r="L210"/>
+      <c r="M210"/>
+      <c r="N210"/>
+      <c r="O210"/>
+      <c r="P210"/>
+      <c r="Q210"/>
+      <c r="R210"/>
+      <c r="S210"/>
+      <c r="T210"/>
+      <c r="U210"/>
+      <c r="V210"/>
+      <c r="W210"/>
+      <c r="X210"/>
+      <c r="Y210"/>
+      <c r="Z210"/>
+      <c r="AA210"/>
+      <c r="AB210"/>
+      <c r="AC210"/>
+    </row>
+    <row r="211" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="B153" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C153" s="29" t="s">
+      <c r="B211" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D153" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E153" s="44">
+      <c r="D211" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E211" s="40">
         <v>36800000</v>
       </c>
-      <c r="F153" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="32" t="s">
+      <c r="F211" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G211"/>
+      <c r="H211"/>
+      <c r="I211"/>
+      <c r="J211"/>
+      <c r="K211"/>
+      <c r="L211"/>
+      <c r="M211"/>
+      <c r="N211"/>
+      <c r="O211"/>
+      <c r="P211"/>
+      <c r="Q211"/>
+      <c r="R211"/>
+      <c r="S211"/>
+      <c r="T211"/>
+      <c r="U211"/>
+      <c r="V211"/>
+      <c r="W211"/>
+      <c r="X211"/>
+      <c r="Y211"/>
+      <c r="Z211"/>
+      <c r="AA211"/>
+      <c r="AB211"/>
+      <c r="AC211"/>
+    </row>
+    <row r="212" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="B154" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C154" s="29" t="s">
+      <c r="B212" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D154" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E154" s="44">
+      <c r="D212" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E212" s="40">
         <v>43680000</v>
       </c>
-      <c r="F154" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="32" t="s">
+      <c r="F212" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G212"/>
+      <c r="H212"/>
+      <c r="I212"/>
+      <c r="J212"/>
+      <c r="K212"/>
+      <c r="L212"/>
+      <c r="M212"/>
+      <c r="N212"/>
+      <c r="O212"/>
+      <c r="P212"/>
+      <c r="Q212"/>
+      <c r="R212"/>
+      <c r="S212"/>
+      <c r="T212"/>
+      <c r="U212"/>
+      <c r="V212"/>
+      <c r="W212"/>
+      <c r="X212"/>
+      <c r="Y212"/>
+      <c r="Z212"/>
+      <c r="AA212"/>
+      <c r="AB212"/>
+      <c r="AC212"/>
+    </row>
+    <row r="213" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A213" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="B155" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" s="29" t="s">
+      <c r="B213" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C213" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D155" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E155" s="44">
+      <c r="D213" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E213" s="40">
         <v>48680000</v>
       </c>
-      <c r="F155" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="32" t="s">
+      <c r="F213" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A214" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="B156" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" s="29" t="s">
+      <c r="B214" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D156" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E156" s="44">
+      <c r="D214" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E214" s="40">
         <v>54680000</v>
       </c>
-      <c r="F156" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="32" t="s">
+      <c r="F214" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A215" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="B157" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C157" s="29" t="s">
+      <c r="B215" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C215" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D157" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E157" s="44">
+      <c r="D215" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E215" s="40">
         <v>69860000</v>
       </c>
-      <c r="F157" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" s="7" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="32" t="s">
+      <c r="F215" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A216" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="B158" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158" s="29" t="s">
+      <c r="B216" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C216" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D158" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E158" s="44">
+      <c r="D216" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E216" s="40">
         <v>99680000</v>
       </c>
-      <c r="F158" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" s="8" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="32" t="s">
+      <c r="F216" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A217" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="B159" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C159" s="29" t="s">
+      <c r="B217" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C217" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D159" s="34" t="s">
+      <c r="D217" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="E159" s="45">
+      <c r="E217" s="41">
         <v>75000</v>
       </c>
-      <c r="F159" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="1:7" s="6" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="36" t="s">
+      <c r="F217" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A218" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="B160" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C160" s="29" t="s">
+      <c r="B218" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D160" s="34" t="s">
+      <c r="D218" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="E160" s="45">
+      <c r="E218" s="41">
         <v>75000</v>
       </c>
-      <c r="F160" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="G160" s="2"/>
+      <c r="F218" s="26" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -521,7 +521,519 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7</t>
+      <t>THÁP LỌC D2000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+H=mm
+2 dàn phun mưa 
+1 lớp đệm
+1 lớp tách ẩm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">THÙNG THAN HOẠT TÍNH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kích thước: DxRxCmm
+ Có ? khay đựng than kích thước:?x?x?mm
+? viên than kích thước 100x100x100mm
+có cửa thay than</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SÀN THAO TÁC LẤY MẪU KHÍ THẢI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kích thước: ?x?x?mm
+Sàn thao tác làm dày 3mm-u100
+mặt sàn lưới dập dãn dày 3mm, bao gồm thang leo có lồng bảo vệ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ỐNG KHÓI D?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kích thước: D?x?mm,  giá đỡ ống thoát khí </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-1 1.5KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+6 túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-2 2.2KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+6 túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-3 3KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+6 túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-4 4KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+8 túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-5 5.5KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+12 túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-6 7.5KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+16 túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-7 1KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+24 túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TỦ HÚT BỤI STHB-8 15KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+25 túi D150xL500
+Lưu lượng:  m3/h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CYCLONE D?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+thân vỏ 2mm , H=?mm
+khung đỡ thép hộp 50x50x2,3mm</t>
+    </r>
+  </si>
+  <si>
+    <t>Kg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">THÙNG THAN HOẠT TÍNH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Kích thước: DxRxCmm
+Có ? cửa thay lọc</t>
+    </r>
+  </si>
+  <si>
+    <t>THAN HOẠT TÍNH</t>
+  </si>
+  <si>
+    <t>NK</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D250 về D200 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D800 về D750 rẽ 1 nhánh D450</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D750 về D600 rẽ 1 nhánh D450</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D600 về D350 rẽ 1 nhánh D450</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D450 về D400 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D350 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D350 về D300 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D300 về D250 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D300 về D200 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D600 về D600 rẽ 2 nhánh D500 và D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D500 về D400 rẽ 1 nhánh D300</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D400 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D300 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H6.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 10.000-15.000m3/h
+Residual pressure / Áp suất: P = 2800-3800 Pa
+Rate Power / Công suất định mức: P =11 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <t>VAN NỔ ASCOR PHI 34</t>
+  </si>
+  <si>
+    <t>TÚI CADTRIGE PHI 150 L=500</t>
+  </si>
+  <si>
+    <t>VAN NỔ PHI 34</t>
+  </si>
+  <si>
+    <t>VAN NỔ PHI 48</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 135 L=2500</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 135 L=3000</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 135 L=4000</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 150 L=2500</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 150 L=3000</t>
+  </si>
+  <si>
+    <t>TÚI LỌC PHI 150 L=4000</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 135 L=2500</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 135 L=3000</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 135 L=4000</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 150 L=2500</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 150 L=3000</t>
+  </si>
+  <si>
+    <t>KHUNG RỌ PHI 150 L=4000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H5-5.5KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 10.000-12.000m3/h
+Residual pressure / Áp suất: P = 2700-3500 Pa
+Rate Power / Công suất định mức: P =5.5 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H5.5-7.5KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 12.000-14.000m3/h
+Residual pressure / Áp suất: P = 2700-3500 Pa
+Rate Power / Công suất định mức: P =7.5 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H6.3-15KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 14.000-18.000m3/h
+Residual pressure / Áp suất: P = 2900-4000 Pa
+Rate Power / Công suất định mức: P =15 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7-18.5KW</t>
     </r>
     <r>
       <rPr>
@@ -546,7 +1058,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>THÁP LỌC D2000</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H8-22KW</t>
     </r>
     <r>
       <rPr>
@@ -555,373 +1067,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
-H=mm
-2 dàn phun mưa 
-1 lớp đệm
-1 lớp tách ẩm</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">THÙNG THAN HOẠT TÍNH </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Kích thước: DxRxCmm
- Có ? khay đựng than kích thước:?x?x?mm
-? viên than kích thước 100x100x100mm
-có cửa thay than</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SÀN THAO TÁC LẤY MẪU KHÍ THẢI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Kích thước: ?x?x?mm
-Sàn thao tác làm dày 3mm-u100
-mặt sàn lưới dập dãn dày 3mm, bao gồm thang leo có lồng bảo vệ</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ỐNG KHÓI D?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Kích thước: D?x?mm,  giá đỡ ống thoát khí </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TỦ HÚT BỤI STHB-1 1.5KW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-6 túi D150xL500
-Lưu lượng:  m3/h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TỦ HÚT BỤI STHB-2 2.2KW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-6 túi D150xL500
-Lưu lượng:  m3/h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TỦ HÚT BỤI STHB-3 3KW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-6 túi D150xL500
-Lưu lượng:  m3/h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TỦ HÚT BỤI STHB-4 4KW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-8 túi D150xL500
-Lưu lượng:  m3/h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TỦ HÚT BỤI STHB-5 5.5KW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-12 túi D150xL500
-Lưu lượng:  m3/h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TỦ HÚT BỤI STHB-6 7.5KW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-16 túi D150xL500
-Lưu lượng:  m3/h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TỦ HÚT BỤI STHB-7 1KW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-24 túi D150xL500
-Lưu lượng:  m3/h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TỦ HÚT BỤI STHB-8 15KW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-25 túi D150xL500
-Lưu lượng:  m3/h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CYCLONE D?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-thân vỏ 2mm , H=?mm
-khung đỡ thép hộp 50x50x2,3mm</t>
-    </r>
-  </si>
-  <si>
-    <t>Kg</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">THÙNG THAN HOẠT TÍNH </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Kích thước: DxRxCmm
-Có ? cửa thay lọc</t>
-    </r>
-  </si>
-  <si>
-    <t>THAN HOẠT TÍNH</t>
-  </si>
-  <si>
-    <t>NK</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D250 về D200 rẽ 1 nhánh D200</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D800 về D750 rẽ 1 nhánh D450</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D750 về D600 rẽ 1 nhánh D450</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D600 về D350 rẽ 1 nhánh D450</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D450 về D400 rẽ 1 nhánh D200</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D400 về D350 rẽ 1 nhánh D200</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D350 về D300 rẽ 1 nhánh D200</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D300 về D250 rẽ 1 nhánh D200</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D300 về D200 rẽ 1 nhánh D200</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D600 về D600 rẽ 2 nhánh D500 và D200</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D500 về D400 rẽ 1 nhánh D300</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D400 về D400 rẽ 1 nhánh D200</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D400 về D300 rẽ 1 nhánh D200</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Extraction performance / Hiệu suất hút : Q= 10.000-12.000m3/h
-Residual pressure / Áp suất: P = 2700-3500 Pa
-Rate Power / Công suất định mức: P =5.5 Kw , 
+Extraction performance / Hiệu suất hút : Q= 22.000-28.000m3/h
+Residual pressure / Áp suất: P = 3200-4300 Pa
+Rate Power / Công suất định mức: P =22 Kw , 
 Tightness / Độ kín :  IP 55
 Supply voltage / Điện áp:3P/380V
 Main frequency / Tần số chính: 50Hz</t>
@@ -935,82 +1083,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H5.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Extraction performance / Hiệu suất hút : Q= 12.000-14.000m3/h
-Residual pressure / Áp suất: P = 2700-3500 Pa
-Rate Power / Công suất định mức: P =7.5 Kw , 
-Tightness / Độ kín :  IP 55
-Supply voltage / Điện áp:3P/380V
-Main frequency / Tần số chính: 50Hz</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H6.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Extraction performance / Hiệu suất hút : Q= 10.000-15.000m3/h
-Residual pressure / Áp suất: P = 2800-3800 Pa
-Rate Power / Công suất định mức: P =11 Kw , 
-Tightness / Độ kín :  IP 55
-Supply voltage / Điện áp:3P/380V
-Main frequency / Tần số chính: 50Hz</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H6.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Extraction performance / Hiệu suất hút : Q= 14.000-18.000m3/h
-Residual pressure / Áp suất: P = 2900-4000 Pa
-Rate Power / Công suất định mức: P =15 Kw , 
-Tightness / Độ kín :  IP 55
-Supply voltage / Điện áp:3P/380V
-Main frequency / Tần số chính: 50Hz</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H7-22KW</t>
     </r>
     <r>
       <rPr>
@@ -1035,32 +1108,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Extraction performance / Hiệu suất hút : Q= 22.000-28.000m3/h
-Residual pressure / Áp suất: P = 3200-4300 Pa
-Rate Power / Công suất định mức: P =22 Kw , 
-Tightness / Độ kín :  IP 55
-Supply voltage / Điện áp:3P/380V
-Main frequency / Tần số chính: 50Hz</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H8</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H8-30KW</t>
     </r>
     <r>
       <rPr>
@@ -1085,7 +1133,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H9</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H9-30KW</t>
     </r>
     <r>
       <rPr>
@@ -1110,7 +1158,32 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H10</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H10-45KW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Extraction performance / Hiệu suất hút : Q= 38.000-45.000m3/h
+Residual pressure / Áp suất: P = 3300-4500 Pa
+Rate Power / Công suất định mức: P =45 Kw , 
+Tightness / Độ kín :  IP 55
+Supply voltage / Điện áp:3P/380V
+Main frequency / Tần số chính: 50Hz</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H10-37KW</t>
     </r>
     <r>
       <rPr>
@@ -1135,32 +1208,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Extraction performance / Hiệu suất hút : Q= 38.000-45.000m3/h
-Residual pressure / Áp suất: P = 3300-4500 Pa
-Rate Power / Công suất định mức: P =45 Kw , 
-Tightness / Độ kín :  IP 55
-Supply voltage / Điện áp:3P/380V
-Main frequency / Tần số chính: 50Hz</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12-45KW</t>
     </r>
     <r>
       <rPr>
@@ -1185,7 +1233,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12-55KW</t>
     </r>
     <r>
       <rPr>
@@ -1210,7 +1258,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12-75KW</t>
     </r>
     <r>
       <rPr>
@@ -1235,7 +1283,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H12-90KW</t>
     </r>
     <r>
       <rPr>
@@ -1260,7 +1308,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H13</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H13-75KW</t>
     </r>
     <r>
       <rPr>
@@ -1285,7 +1333,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H13</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H13-90KW</t>
     </r>
     <r>
       <rPr>
@@ -1310,7 +1358,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H14</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H14-90KW</t>
     </r>
     <r>
       <rPr>
@@ -1335,7 +1383,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H14</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H14-110KW</t>
     </r>
     <r>
       <rPr>
@@ -1360,7 +1408,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16-110KW</t>
     </r>
     <r>
       <rPr>
@@ -1385,7 +1433,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16-160KW</t>
     </r>
     <r>
       <rPr>
@@ -1410,7 +1458,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16-200KW</t>
     </r>
     <r>
       <rPr>
@@ -1435,7 +1483,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H16-250KW</t>
     </r>
     <r>
       <rPr>
@@ -1460,7 +1508,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H18</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H18-300KW</t>
     </r>
     <r>
       <rPr>
@@ -1485,7 +1533,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H18</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H18-350KW</t>
     </r>
     <r>
       <rPr>
@@ -1510,7 +1558,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H22</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H22-400KW</t>
     </r>
     <r>
       <rPr>
@@ -1535,7 +1583,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H22</t>
+      <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H22-500KW</t>
     </r>
     <r>
       <rPr>
@@ -1551,54 +1599,6 @@
 Supply voltage / Điện áp:3P/380V
 Main frequency / Tần số chính: 50Hz</t>
     </r>
-  </si>
-  <si>
-    <t>VAN NỔ ASCOR PHI 34</t>
-  </si>
-  <si>
-    <t>TÚI CADTRIGE PHI 150 L=500</t>
-  </si>
-  <si>
-    <t>VAN NỔ PHI 34</t>
-  </si>
-  <si>
-    <t>VAN NỔ PHI 48</t>
-  </si>
-  <si>
-    <t>TÚI LỌC PHI 135 L=2500</t>
-  </si>
-  <si>
-    <t>TÚI LỌC PHI 135 L=3000</t>
-  </si>
-  <si>
-    <t>TÚI LỌC PHI 135 L=4000</t>
-  </si>
-  <si>
-    <t>TÚI LỌC PHI 150 L=2500</t>
-  </si>
-  <si>
-    <t>TÚI LỌC PHI 150 L=3000</t>
-  </si>
-  <si>
-    <t>TÚI LỌC PHI 150 L=4000</t>
-  </si>
-  <si>
-    <t>KHUNG RỌ PHI 135 L=2500</t>
-  </si>
-  <si>
-    <t>KHUNG RỌ PHI 135 L=3000</t>
-  </si>
-  <si>
-    <t>KHUNG RỌ PHI 135 L=4000</t>
-  </si>
-  <si>
-    <t>KHUNG RỌ PHI 150 L=2500</t>
-  </si>
-  <si>
-    <t>KHUNG RỌ PHI 150 L=3000</t>
-  </si>
-  <si>
-    <t>KHUNG RỌ PHI 150 L=4000</t>
   </si>
 </sst>
 </file>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="52" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>10</v>
@@ -3295,7 +3295,7 @@
     </row>
     <row r="53" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>10</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="54" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B54" s="15" t="s">
         <v>10</v>
@@ -3335,7 +3335,7 @@
     </row>
     <row r="55" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A55" s="43" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B55" s="29" t="s">
         <v>10</v>
@@ -3355,7 +3355,7 @@
     </row>
     <row r="56" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B56" s="15" t="s">
         <v>10</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="57" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B57" s="29" t="s">
         <v>10</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="58" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B58" s="15" t="s">
         <v>10</v>
@@ -3415,7 +3415,7 @@
     </row>
     <row r="59" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="43" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B59" s="29" t="s">
         <v>10</v>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="60" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A60" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B60" s="15" t="s">
         <v>10</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="61" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B61" s="29" t="s">
         <v>10</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="62" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B62" s="15" t="s">
         <v>10</v>
@@ -3495,7 +3495,7 @@
     </row>
     <row r="63" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B63" s="15" t="s">
         <v>10</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="64" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B64" s="15" t="s">
         <v>10</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="65" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B65" s="29" t="s">
         <v>10</v>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="159" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="14" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="B159" s="15" t="s">
         <v>9</v>
@@ -5268,7 +5268,7 @@
     </row>
     <row r="160" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="B160" s="15" t="s">
         <v>9</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="161" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B161" s="15" t="s">
         <v>9</v>
@@ -5354,7 +5354,7 @@
     </row>
     <row r="162" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="14" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="B162" s="15" t="s">
         <v>9</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="163" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="14" t="s">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="B163" s="15" t="s">
         <v>9</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="164" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="14" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B164" s="15" t="s">
         <v>9</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="165" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="14" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B165" s="15" t="s">
         <v>9</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="166" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="14" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="B166" s="15" t="s">
         <v>9</v>
@@ -5569,7 +5569,7 @@
     </row>
     <row r="167" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="14" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="B167" s="15" t="s">
         <v>9</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="168" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="14" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B168" s="15" t="s">
         <v>9</v>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="169" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="14" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B169" s="15" t="s">
         <v>9</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="170" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="14" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="B170" s="15" t="s">
         <v>9</v>
@@ -5741,7 +5741,7 @@
     </row>
     <row r="171" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="14" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B171" s="15" t="s">
         <v>9</v>
@@ -5784,7 +5784,7 @@
     </row>
     <row r="172" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="14" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B172" s="15" t="s">
         <v>9</v>
@@ -5827,7 +5827,7 @@
     </row>
     <row r="173" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="14" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B173" s="15" t="s">
         <v>9</v>
@@ -5870,7 +5870,7 @@
     </row>
     <row r="174" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="14" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B174" s="15" t="s">
         <v>9</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="175" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="14" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B175" s="15" t="s">
         <v>9</v>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="176" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="14" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B176" s="15" t="s">
         <v>9</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="177" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="14" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>9</v>
@@ -6042,7 +6042,7 @@
     </row>
     <row r="178" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="14" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B178" s="15" t="s">
         <v>9</v>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="179" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="14" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B179" s="15" t="s">
         <v>9</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="180" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="14" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="B180" s="15" t="s">
         <v>9</v>
@@ -6171,7 +6171,7 @@
     </row>
     <row r="181" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="14" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B181" s="15" t="s">
         <v>9</v>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="182" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="14" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B182" s="15" t="s">
         <v>9</v>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="183" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="14" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B183" s="15" t="s">
         <v>9</v>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="184" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="14" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B184" s="15" t="s">
         <v>9</v>
@@ -6343,7 +6343,7 @@
     </row>
     <row r="185" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="14" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B185" s="15" t="s">
         <v>9</v>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="186" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B186" s="15" t="s">
         <v>9</v>
@@ -6395,7 +6395,7 @@
         <v>89</v>
       </c>
       <c r="D186" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E186" s="39">
         <v>75000</v>
@@ -6429,16 +6429,16 @@
     </row>
     <row r="187" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B187" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B187" s="15" t="s">
-        <v>178</v>
-      </c>
       <c r="C187" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D187" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E187" s="39">
         <v>33000</v>
@@ -6472,7 +6472,7 @@
     </row>
     <row r="188" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B188" s="15" t="s">
         <v>157</v>
@@ -6481,7 +6481,7 @@
         <v>89</v>
       </c>
       <c r="D188" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E188" s="39">
         <v>75000</v>
@@ -6515,7 +6515,7 @@
     </row>
     <row r="189" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B189" s="15" t="s">
         <v>157</v>
@@ -6524,7 +6524,7 @@
         <v>89</v>
       </c>
       <c r="D189" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E189" s="39">
         <v>75000</v>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="190" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B190" s="15" t="s">
         <v>9</v>
@@ -6567,7 +6567,7 @@
         <v>89</v>
       </c>
       <c r="D190" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E190" s="39">
         <v>75000</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="191" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B191" s="22" t="s">
         <v>158</v>
@@ -6610,7 +6610,7 @@
         <v>89</v>
       </c>
       <c r="D191" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E191" s="39">
         <v>75000</v>
@@ -6653,7 +6653,7 @@
         <v>89</v>
       </c>
       <c r="D192" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E192" s="39">
         <v>75000</v>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="193" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="23" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="B193" s="46"/>
       <c r="C193" s="47"/>
@@ -6726,7 +6726,7 @@
     </row>
     <row r="194" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="23" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="B194" s="46"/>
       <c r="C194" s="47"/>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="195" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="23" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="B195" s="46"/>
       <c r="C195" s="47"/>
@@ -6843,7 +6843,7 @@
     </row>
     <row r="197" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
@@ -6882,7 +6882,7 @@
     </row>
     <row r="198" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="18" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -6921,7 +6921,7 @@
     </row>
     <row r="199" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="18" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
@@ -6960,7 +6960,7 @@
     </row>
     <row r="200" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="18" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
@@ -6999,7 +6999,7 @@
     </row>
     <row r="201" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="18" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="202" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="18" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="203" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="18" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -7116,7 +7116,7 @@
     </row>
     <row r="204" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="18" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
@@ -7155,7 +7155,7 @@
     </row>
     <row r="205" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="18" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="206" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="18" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -7233,7 +7233,7 @@
     </row>
     <row r="207" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="18" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -7272,7 +7272,7 @@
     </row>
     <row r="208" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="18" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -7311,7 +7311,7 @@
     </row>
     <row r="209" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="18" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="210" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B210" s="29" t="s">
         <v>9</v>
@@ -7393,7 +7393,7 @@
     </row>
     <row r="211" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B211" s="29" t="s">
         <v>9</v>
@@ -7436,7 +7436,7 @@
     </row>
     <row r="212" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B212" s="29" t="s">
         <v>9</v>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="213" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A213" s="28" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B213" s="29" t="s">
         <v>9</v>
@@ -7499,7 +7499,7 @@
     </row>
     <row r="214" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A214" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B214" s="29" t="s">
         <v>9</v>
@@ -7519,7 +7519,7 @@
     </row>
     <row r="215" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A215" s="28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B215" s="29" t="s">
         <v>9</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="216" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A216" s="28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B216" s="29" t="s">
         <v>9</v>
@@ -7559,7 +7559,7 @@
     </row>
     <row r="217" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A217" s="28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B217" s="29" t="s">
         <v>9</v>
@@ -7568,7 +7568,7 @@
         <v>89</v>
       </c>
       <c r="D217" s="30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E217" s="41">
         <v>75000</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="218" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A218" s="31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B218" s="29" t="s">
         <v>9</v>
@@ -7588,7 +7588,7 @@
         <v>89</v>
       </c>
       <c r="D218" s="30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E218" s="41">
         <v>75000</v>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="253">
   <si>
     <t>Ống D650</t>
   </si>
@@ -955,6 +955,33 @@
     <t>CYCLONE D?
 thân vỏ 2mm , H=?mm
 khung đỡ thép hộp 50x50x2,3mm</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D800 về D800 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D800 về D750 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D750 về D750 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D750 về D700 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D700 về D650 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D600 về D550 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D550 về D500 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D500 về D450 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Cút 45 độ D200</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1098,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1131,23 +1158,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1237,13 +1256,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1286,9 +1299,17 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
+    <cellStyle name="Comma 2" xfId="4"/>
     <cellStyle name="Dấu phẩy 2" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2"/>
@@ -1569,34 +1590,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC228"/>
+  <dimension ref="A1:AC237"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" style="42" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="42" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="42" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="42" customWidth="1"/>
-    <col min="5" max="5" width="14" style="47" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" style="42" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" style="40" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="40" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="40" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="40" customWidth="1"/>
+    <col min="5" max="5" width="14" style="45" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="41" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1604,19 +1625,19 @@
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="34" t="s">
+      <c r="B2" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="45">
+      <c r="E2" s="43">
         <v>120000</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1624,19 +1645,19 @@
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="34" t="s">
+      <c r="B3" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="43">
         <v>160000</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1644,19 +1665,19 @@
       <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="34" t="s">
+      <c r="B4" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="43">
         <v>210000</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1664,19 +1685,19 @@
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="34" t="s">
+      <c r="B5" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="43">
         <v>250000</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1684,19 +1705,19 @@
       <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="34" t="s">
+      <c r="B6" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="43">
         <v>310000</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1704,19 +1725,19 @@
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="43">
         <v>330000</v>
       </c>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1724,19 +1745,19 @@
       <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="34" t="s">
+      <c r="B8" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="43">
         <v>420000</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1744,19 +1765,19 @@
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="34" t="s">
+      <c r="B9" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="43">
         <v>460000</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1764,19 +1785,19 @@
       <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="34" t="s">
+      <c r="B10" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="43">
         <v>660000</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1784,19 +1805,19 @@
       <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="34" t="s">
+      <c r="B11" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="43">
         <v>700000</v>
       </c>
-      <c r="F11" s="34" t="s">
+      <c r="F11" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1804,19 +1825,19 @@
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="34" t="s">
+      <c r="B12" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="43">
         <v>750000</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1824,19 +1845,19 @@
       <c r="A13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="34" t="s">
+      <c r="B13" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="43">
         <v>830000</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1844,19 +1865,19 @@
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="34" t="s">
+      <c r="B14" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="43">
         <v>880000</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1864,19 +1885,19 @@
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="34" t="s">
+      <c r="B15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="43">
         <v>950000</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1884,19 +1905,19 @@
       <c r="A16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="34" t="s">
+      <c r="B16" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="43">
         <v>1030000</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1904,19 +1925,19 @@
       <c r="A17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="34" t="s">
+      <c r="B17" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="43">
         <v>1150000</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1924,19 +1945,19 @@
       <c r="A18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="34" t="s">
+      <c r="B18" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="43">
         <v>1190000</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1944,19 +1965,19 @@
       <c r="A19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="34" t="s">
+      <c r="B19" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="43">
         <v>1280000</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="F19" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1964,19 +1985,19 @@
       <c r="A20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="34" t="s">
+      <c r="B20" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="43">
         <v>1350000</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1984,19 +2005,19 @@
       <c r="A21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="34" t="s">
+      <c r="B21" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="43">
         <v>1450000</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2004,19 +2025,19 @@
       <c r="A22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="34" t="s">
+      <c r="B22" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="43">
         <v>1580000</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2024,19 +2045,19 @@
       <c r="A23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="34" t="s">
+      <c r="B23" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="43">
         <v>1680000</v>
       </c>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2044,19 +2065,19 @@
       <c r="A24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="34" t="s">
+      <c r="B24" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E24" s="43">
         <v>1880000</v>
       </c>
-      <c r="F24" s="34" t="s">
+      <c r="F24" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2064,19 +2085,19 @@
       <c r="A25" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="34" t="s">
+      <c r="B25" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E25" s="43">
         <v>75000</v>
       </c>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2084,19 +2105,19 @@
       <c r="A26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="34" t="s">
+      <c r="B26" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="45">
+      <c r="E26" s="43">
         <v>123000</v>
       </c>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2104,19 +2125,19 @@
       <c r="A27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="34" t="s">
+      <c r="B27" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="45">
+      <c r="E27" s="43">
         <v>180000</v>
       </c>
-      <c r="F27" s="34" t="s">
+      <c r="F27" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2124,19 +2145,19 @@
       <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="34" t="s">
+      <c r="B28" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E28" s="45">
+      <c r="E28" s="43">
         <v>285000</v>
       </c>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2144,19 +2165,19 @@
       <c r="A29" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="34" t="s">
+      <c r="B29" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="45">
+      <c r="E29" s="43">
         <v>405000</v>
       </c>
-      <c r="F29" s="34" t="s">
+      <c r="F29" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2164,19 +2185,19 @@
       <c r="A30" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="34" t="s">
+      <c r="B30" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="45">
+      <c r="E30" s="43">
         <v>495000</v>
       </c>
-      <c r="F30" s="34" t="s">
+      <c r="F30" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2184,19 +2205,19 @@
       <c r="A31" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="34" t="s">
+      <c r="B31" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="45">
+      <c r="E31" s="43">
         <v>660000</v>
       </c>
-      <c r="F31" s="34" t="s">
+      <c r="F31" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2204,303 +2225,303 @@
       <c r="A32" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="34" t="s">
+      <c r="B32" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="45">
+      <c r="E32" s="43">
         <v>840000</v>
       </c>
-      <c r="F32" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F32" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="34" t="s">
+      <c r="B33" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E33" s="45">
+      <c r="E33" s="43">
         <v>1552500</v>
       </c>
-      <c r="F33" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F33" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="34" t="s">
+      <c r="B34" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="45">
+      <c r="E34" s="43">
         <v>1905000</v>
       </c>
-      <c r="F34" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F34" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="34" t="s">
+      <c r="B35" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="45">
+      <c r="E35" s="43">
         <v>2130000</v>
       </c>
-      <c r="F35" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F35" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="34" t="s">
+      <c r="B36" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E36" s="45">
+      <c r="E36" s="43">
         <v>2535000</v>
       </c>
-      <c r="F36" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F36" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="34" t="s">
+      <c r="B37" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="45">
+      <c r="E37" s="43">
         <v>2812500</v>
       </c>
-      <c r="F37" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F37" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="34" t="s">
+      <c r="B38" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="45">
+      <c r="E38" s="43">
         <v>3255000</v>
       </c>
-      <c r="F38" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F38" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="34" t="s">
+      <c r="B39" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="45">
+      <c r="E39" s="43">
         <v>3570000</v>
       </c>
-      <c r="F39" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F39" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="34" t="s">
+      <c r="B40" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E40" s="45">
+      <c r="E40" s="43">
         <v>4080000</v>
       </c>
-      <c r="F40" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F40" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="34" t="s">
+      <c r="B41" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E41" s="45">
+      <c r="E41" s="43">
         <v>4605000</v>
       </c>
-      <c r="F41" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F41" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="34" t="s">
+      <c r="B42" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E42" s="45">
+      <c r="E42" s="43">
         <v>4965000</v>
       </c>
-      <c r="F42" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F42" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="34" t="s">
+      <c r="B43" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E43" s="45">
+      <c r="E43" s="43">
         <v>5550000</v>
       </c>
-      <c r="F43" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F43" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="34" t="s">
+      <c r="B44" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E44" s="45">
+      <c r="E44" s="43">
         <v>6165000</v>
       </c>
-      <c r="F44" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F44" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="34" t="s">
+      <c r="B45" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E45" s="45">
+      <c r="E45" s="43">
         <v>9135000</v>
       </c>
-      <c r="F45" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="6" t="s">
+      <c r="F45" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" s="48" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="23">
-        <v>34500</v>
+        <v>110000</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>56</v>
       </c>
@@ -2520,7 +2541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>57</v>
       </c>
@@ -2533,15 +2554,27 @@
       <c r="D48" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="46">
+      <c r="E48" s="44">
         <v>135000</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="31"/>
-    </row>
-    <row r="49" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+      <c r="P48"/>
+      <c r="Q48"/>
+      <c r="R48"/>
+      <c r="S48"/>
+    </row>
+    <row r="49" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>58</v>
       </c>
@@ -2561,7 +2594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>59</v>
       </c>
@@ -2581,7 +2614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>60</v>
       </c>
@@ -2601,7 +2634,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>193</v>
       </c>
@@ -2614,15 +2647,26 @@
       <c r="D52" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E52" s="46">
+      <c r="E52" s="44">
         <v>250500</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="31"/>
-    </row>
-    <row r="53" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52"/>
+      <c r="P52"/>
+      <c r="Q52"/>
+      <c r="R52"/>
+    </row>
+    <row r="53" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>194</v>
       </c>
@@ -2635,15 +2679,26 @@
       <c r="D53" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E53" s="46">
+      <c r="E53" s="44">
         <v>244500</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G53" s="33"/>
-    </row>
-    <row r="54" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
+      <c r="P53"/>
+      <c r="Q53"/>
+      <c r="R53"/>
+    </row>
+    <row r="54" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>195</v>
       </c>
@@ -2656,15 +2711,26 @@
       <c r="D54" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E54" s="46">
+      <c r="E54" s="44">
         <v>253500</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="33"/>
-    </row>
-    <row r="55" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="R54"/>
+    </row>
+    <row r="55" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>196</v>
       </c>
@@ -2677,15 +2743,26 @@
       <c r="D55" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E55" s="46">
+      <c r="E55" s="44">
         <v>276000</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G55" s="33"/>
-    </row>
-    <row r="56" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55"/>
+      <c r="Q55"/>
+      <c r="R55"/>
+    </row>
+    <row r="56" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>197</v>
       </c>
@@ -2698,15 +2775,26 @@
       <c r="D56" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="46">
+      <c r="E56" s="44">
         <v>289500</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G56" s="33"/>
-    </row>
-    <row r="57" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="Q56"/>
+      <c r="R56"/>
+    </row>
+    <row r="57" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>198</v>
       </c>
@@ -2719,15 +2807,26 @@
       <c r="D57" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E57" s="46">
+      <c r="E57" s="44">
         <v>306000</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="33"/>
-    </row>
-    <row r="58" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+      <c r="R57"/>
+    </row>
+    <row r="58" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>199</v>
       </c>
@@ -2740,15 +2839,26 @@
       <c r="D58" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E58" s="46">
+      <c r="E58" s="44">
         <v>313500</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="33"/>
-    </row>
-    <row r="59" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="R58"/>
+    </row>
+    <row r="59" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>200</v>
       </c>
@@ -2761,15 +2871,26 @@
       <c r="D59" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E59" s="46">
+      <c r="E59" s="44">
         <v>340500</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="33"/>
-    </row>
-    <row r="60" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+      <c r="R59"/>
+    </row>
+    <row r="60" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>201</v>
       </c>
@@ -2782,15 +2903,26 @@
       <c r="D60" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E60" s="46">
+      <c r="E60" s="44">
         <v>355500</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G60" s="33"/>
-    </row>
-    <row r="61" spans="1:7" s="32" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
+      <c r="L60"/>
+      <c r="M60"/>
+      <c r="N60"/>
+      <c r="O60"/>
+      <c r="P60"/>
+      <c r="Q60"/>
+      <c r="R60"/>
+    </row>
+    <row r="61" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>202</v>
       </c>
@@ -2803,15 +2935,26 @@
       <c r="D61" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E61" s="46">
+      <c r="E61" s="44">
         <v>370500</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G61" s="33"/>
-    </row>
-    <row r="62" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="Q61"/>
+      <c r="R61"/>
+    </row>
+    <row r="62" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>164</v>
       </c>
@@ -2831,7 +2974,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>172</v>
       </c>
@@ -2851,407 +2994,574 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
+    <row r="64" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="47">
+        <v>450000</v>
+      </c>
+      <c r="F64" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="O64"/>
+      <c r="P64"/>
+      <c r="Q64"/>
+      <c r="R64"/>
+      <c r="S64"/>
+      <c r="T64"/>
+      <c r="U64"/>
+    </row>
+    <row r="65" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="22">
+      <c r="B65" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="22">
         <v>470000</v>
       </c>
-      <c r="F64" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="27" t="s">
+      <c r="F65" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="B65" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="35">
+      <c r="B66" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="33">
         <v>447000</v>
       </c>
-      <c r="F65" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="F66" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="22">
+      <c r="B67" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="22">
         <v>528000</v>
       </c>
-      <c r="F66" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A67" s="27" t="s">
+      <c r="F67" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A68" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="B67" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="35">
+      <c r="B68" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="33">
         <v>508500</v>
       </c>
-      <c r="F67" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="F68" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="22">
+      <c r="B69" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="22">
         <v>560000</v>
       </c>
-      <c r="F68" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="27" t="s">
+      <c r="F69" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="B69" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="35">
+      <c r="B70" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="33">
         <v>682500</v>
       </c>
-      <c r="F69" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
+      <c r="F70" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="22">
+      <c r="B71" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="22">
         <v>666000</v>
       </c>
-      <c r="F70" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="27" t="s">
+      <c r="F71" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="47">
+        <v>1125000</v>
+      </c>
+      <c r="F72" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="S72"/>
+      <c r="T72"/>
+      <c r="U72"/>
+    </row>
+    <row r="73" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="47">
+        <v>1150000</v>
+      </c>
+      <c r="F73" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73"/>
+      <c r="N73"/>
+      <c r="O73"/>
+      <c r="P73"/>
+      <c r="Q73"/>
+      <c r="R73"/>
+      <c r="S73"/>
+      <c r="T73"/>
+      <c r="U73"/>
+    </row>
+    <row r="74" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="B71" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="35">
+      <c r="B74" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="33">
         <v>957000</v>
       </c>
-      <c r="F71" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="F74" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="47">
+        <v>750000</v>
+      </c>
+      <c r="F75" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G75"/>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75"/>
+      <c r="N75"/>
+      <c r="O75"/>
+      <c r="P75"/>
+      <c r="Q75"/>
+      <c r="R75"/>
+      <c r="S75"/>
+      <c r="T75"/>
+      <c r="U75"/>
+    </row>
+    <row r="76" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="47">
+        <v>1550000</v>
+      </c>
+      <c r="F76" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76"/>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76"/>
+      <c r="K76"/>
+      <c r="L76"/>
+      <c r="M76"/>
+      <c r="N76"/>
+      <c r="O76"/>
+      <c r="P76"/>
+      <c r="Q76"/>
+      <c r="R76"/>
+      <c r="S76"/>
+      <c r="T76"/>
+      <c r="U76"/>
+    </row>
+    <row r="77" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="47">
+        <v>1650000</v>
+      </c>
+      <c r="F77" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+      <c r="N77"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+      <c r="R77"/>
+      <c r="S77"/>
+      <c r="T77"/>
+      <c r="U77"/>
+    </row>
+    <row r="78" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="47">
+        <v>1700000</v>
+      </c>
+      <c r="F78" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G78"/>
+      <c r="H78"/>
+      <c r="I78"/>
+      <c r="J78"/>
+      <c r="K78"/>
+      <c r="L78"/>
+      <c r="M78"/>
+      <c r="N78"/>
+      <c r="O78"/>
+      <c r="P78"/>
+      <c r="Q78"/>
+      <c r="R78"/>
+      <c r="S78"/>
+      <c r="T78"/>
+      <c r="U78"/>
+    </row>
+    <row r="79" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="47">
+        <v>1800000</v>
+      </c>
+      <c r="F79" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G79"/>
+      <c r="H79"/>
+      <c r="I79"/>
+      <c r="J79"/>
+      <c r="K79"/>
+      <c r="L79"/>
+      <c r="M79"/>
+      <c r="N79"/>
+      <c r="O79"/>
+      <c r="P79"/>
+      <c r="Q79"/>
+      <c r="R79"/>
+      <c r="S79"/>
+      <c r="T79"/>
+      <c r="U79"/>
+    </row>
+    <row r="80" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="47">
+        <v>1850000</v>
+      </c>
+      <c r="F80" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G80"/>
+      <c r="H80"/>
+      <c r="I80"/>
+      <c r="J80"/>
+      <c r="K80"/>
+      <c r="L80"/>
+      <c r="M80"/>
+      <c r="N80"/>
+      <c r="O80"/>
+      <c r="P80"/>
+      <c r="Q80"/>
+      <c r="R80"/>
+      <c r="S80"/>
+      <c r="T80"/>
+      <c r="U80"/>
+    </row>
+    <row r="81" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="22">
+      <c r="B81" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="22">
         <v>3120000</v>
       </c>
-      <c r="F72" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
+      <c r="F81" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A82" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="22">
+      <c r="B82" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="22">
         <v>2860000</v>
       </c>
-      <c r="F73" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A74" s="11" t="s">
+      <c r="F82" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A83" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="22">
+      <c r="B83" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="22">
         <v>2100000</v>
       </c>
-      <c r="F74" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="27" t="s">
+      <c r="F83" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="B75" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="35">
+      <c r="B84" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="33">
         <v>3255000</v>
       </c>
-      <c r="F75" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="23">
-        <v>160000</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="23">
-        <v>220000</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="23">
-        <v>280000</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="23">
-        <v>550000</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="23">
-        <v>900000</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="23">
-        <v>1050000</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="23">
-        <v>1450000</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="23">
-        <v>1780000</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" s="23">
-        <v>2000000</v>
-      </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="17" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B85" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="C85" s="6"/>
       <c r="D85" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E85" s="23">
-        <v>2500000</v>
+        <v>160000</v>
       </c>
       <c r="F85" s="6" t="s">
         <v>8</v>
@@ -3259,15 +3569,17 @@
     </row>
     <row r="86" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B86" s="6"/>
+        <v>63</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="C86" s="6"/>
       <c r="D86" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E86" s="23">
-        <v>2800000</v>
+        <v>220000</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>8</v>
@@ -3275,15 +3587,17 @@
     </row>
     <row r="87" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B87" s="6"/>
+        <v>64</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="C87" s="6"/>
       <c r="D87" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E87" s="23">
-        <v>3300000</v>
+        <v>280000</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>8</v>
@@ -3291,7 +3605,7 @@
     </row>
     <row r="88" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -3299,7 +3613,7 @@
         <v>35</v>
       </c>
       <c r="E88" s="23">
-        <v>3800000</v>
+        <v>550000</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>8</v>
@@ -3307,7 +3621,7 @@
     </row>
     <row r="89" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -3315,7 +3629,7 @@
         <v>35</v>
       </c>
       <c r="E89" s="23">
-        <v>4500000</v>
+        <v>900000</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>8</v>
@@ -3323,7 +3637,7 @@
     </row>
     <row r="90" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -3331,7 +3645,7 @@
         <v>35</v>
       </c>
       <c r="E90" s="23">
-        <v>4800000</v>
+        <v>1050000</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>8</v>
@@ -3339,7 +3653,7 @@
     </row>
     <row r="91" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -3347,7 +3661,7 @@
         <v>35</v>
       </c>
       <c r="E91" s="23">
-        <v>5200000</v>
+        <v>1450000</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>8</v>
@@ -3355,7 +3669,7 @@
     </row>
     <row r="92" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -3363,7 +3677,7 @@
         <v>35</v>
       </c>
       <c r="E92" s="23">
-        <v>5600000</v>
+        <v>1780000</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>8</v>
@@ -3371,7 +3685,7 @@
     </row>
     <row r="93" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -3379,7 +3693,7 @@
         <v>35</v>
       </c>
       <c r="E93" s="23">
-        <v>6500000</v>
+        <v>2000000</v>
       </c>
       <c r="F93" s="6" t="s">
         <v>8</v>
@@ -3387,7 +3701,7 @@
     </row>
     <row r="94" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -3395,7 +3709,7 @@
         <v>35</v>
       </c>
       <c r="E94" s="23">
-        <v>7200000</v>
+        <v>2500000</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>8</v>
@@ -3403,7 +3717,7 @@
     </row>
     <row r="95" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -3411,7 +3725,7 @@
         <v>35</v>
       </c>
       <c r="E95" s="23">
-        <v>7600000</v>
+        <v>2800000</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>8</v>
@@ -3419,7 +3733,7 @@
     </row>
     <row r="96" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -3427,7 +3741,7 @@
         <v>35</v>
       </c>
       <c r="E96" s="23">
-        <v>8000000</v>
+        <v>3300000</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>8</v>
@@ -3435,7 +3749,7 @@
     </row>
     <row r="97" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -3443,7 +3757,7 @@
         <v>35</v>
       </c>
       <c r="E97" s="23">
-        <v>8900000</v>
+        <v>3800000</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>8</v>
@@ -3451,7 +3765,7 @@
     </row>
     <row r="98" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -3459,7 +3773,7 @@
         <v>35</v>
       </c>
       <c r="E98" s="23">
-        <v>9600000</v>
+        <v>4500000</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>8</v>
@@ -3467,7 +3781,7 @@
     </row>
     <row r="99" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -3475,7 +3789,7 @@
         <v>35</v>
       </c>
       <c r="E99" s="23">
-        <v>10680000</v>
+        <v>4800000</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>8</v>
@@ -3483,7 +3797,7 @@
     </row>
     <row r="100" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -3491,7 +3805,7 @@
         <v>35</v>
       </c>
       <c r="E100" s="23">
-        <v>11680000</v>
+        <v>5200000</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>8</v>
@@ -3499,7 +3813,7 @@
     </row>
     <row r="101" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -3507,187 +3821,151 @@
         <v>35</v>
       </c>
       <c r="E101" s="23">
+        <v>5600000</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="23">
+        <v>6500000</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A103" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="23">
+        <v>7200000</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A104" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="23">
+        <v>7600000</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A105" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="23">
+        <v>8000000</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A106" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="23">
+        <v>8900000</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A107" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="23">
+        <v>9600000</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="23">
+        <v>10680000</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="23">
+        <v>11680000</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="23">
         <v>12500000</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B102" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="23">
-        <v>240000</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B103" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="23">
-        <v>320000</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A104" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B104" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E104" s="23">
-        <v>420000</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A105" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B105" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E105" s="23">
-        <v>500000</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A106" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B106" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E106" s="23">
-        <v>620000</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A107" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B107" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" s="23">
-        <v>660000</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A108" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B108" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E108" s="23">
-        <v>840000</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A109" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B109" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C109" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E109" s="23">
-        <v>890000</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B110" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E110" s="23">
-        <v>1980000</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>8</v>
@@ -3695,19 +3973,19 @@
     </row>
     <row r="111" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B111" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C111" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B111" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E111" s="23">
-        <v>2100000</v>
+        <v>240000</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>8</v>
@@ -3715,19 +3993,19 @@
     </row>
     <row r="112" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B112" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C112" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B112" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E112" s="23">
-        <v>2250000</v>
+        <v>320000</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>8</v>
@@ -3735,19 +4013,19 @@
     </row>
     <row r="113" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B113" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B113" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E113" s="23">
-        <v>2490000</v>
+        <v>420000</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>8</v>
@@ -3755,19 +4033,19 @@
     </row>
     <row r="114" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B114" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="B114" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E114" s="23">
-        <v>2640000</v>
+        <v>500000</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>8</v>
@@ -3775,19 +4053,19 @@
     </row>
     <row r="115" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B115" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C115" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="B115" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E115" s="23">
-        <v>2850000</v>
+        <v>620000</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>8</v>
@@ -3795,19 +4073,19 @@
     </row>
     <row r="116" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B116" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B116" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E116" s="23">
-        <v>3090000</v>
+        <v>660000</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>8</v>
@@ -3815,19 +4093,19 @@
     </row>
     <row r="117" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B117" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C117" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B117" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E117" s="23">
-        <v>3450000</v>
+        <v>840000</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>8</v>
@@ -3835,19 +4113,19 @@
     </row>
     <row r="118" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B118" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C118" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B118" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E118" s="23">
-        <v>7600000</v>
+        <v>890000</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>8</v>
@@ -3855,19 +4133,19 @@
     </row>
     <row r="119" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B119" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C119" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B119" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E119" s="23">
-        <v>8000000</v>
+        <v>1980000</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>8</v>
@@ -3875,19 +4153,19 @@
     </row>
     <row r="120" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B120" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B120" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E120" s="23">
-        <v>8900000</v>
+        <v>2100000</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>8</v>
@@ -3895,19 +4173,19 @@
     </row>
     <row r="121" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B121" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C121" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B121" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E121" s="23">
-        <v>9600000</v>
+        <v>2250000</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>8</v>
@@ -3915,19 +4193,19 @@
     </row>
     <row r="122" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B122" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C122" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B122" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E122" s="23">
-        <v>10680000</v>
+        <v>2490000</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>8</v>
@@ -3935,19 +4213,19 @@
     </row>
     <row r="123" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B123" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C123" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B123" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E123" s="23">
-        <v>11680000</v>
+        <v>2640000</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>8</v>
@@ -3955,163 +4233,199 @@
     </row>
     <row r="124" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B124" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="23">
+        <v>2850000</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A125" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B125" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="23">
+        <v>3090000</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A126" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B126" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" s="23">
+        <v>3450000</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A127" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B127" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="23">
+        <v>7600000</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A128" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B128" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="23">
+        <v>8000000</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A129" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B129" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" s="23">
+        <v>8900000</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B130" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="23">
+        <v>9600000</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A131" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B131" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C131" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" s="23">
+        <v>10680000</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A132" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B132" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="23">
+        <v>11680000</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A133" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B124" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" s="37" t="s">
+      <c r="B133" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D124" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E124" s="23">
+      <c r="D133" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" s="23">
         <v>13680000</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A125" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E125" s="23">
-        <v>800000</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A126" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E126" s="23">
-        <v>1000000</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A127" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E127" s="23">
-        <v>1008000</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A128" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E128" s="23">
-        <v>1200000</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A129" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E129" s="23">
-        <v>1488000</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A130" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E130" s="23">
-        <v>1584000</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A131" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E131" s="23">
-        <v>2016000</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A132" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E132" s="23">
-        <v>2136000</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A133" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E133" s="23">
-        <v>3000000</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>8</v>
@@ -4119,7 +4433,7 @@
     </row>
     <row r="134" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -4127,7 +4441,7 @@
         <v>35</v>
       </c>
       <c r="E134" s="23">
-        <v>3780000</v>
+        <v>800000</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>8</v>
@@ -4135,7 +4449,7 @@
     </row>
     <row r="135" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
@@ -4143,7 +4457,7 @@
         <v>35</v>
       </c>
       <c r="E135" s="23">
-        <v>4050000</v>
+        <v>1000000</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>8</v>
@@ -4151,7 +4465,7 @@
     </row>
     <row r="136" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -4159,7 +4473,7 @@
         <v>35</v>
       </c>
       <c r="E136" s="23">
-        <v>4482000</v>
+        <v>1008000</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>8</v>
@@ -4167,7 +4481,7 @@
     </row>
     <row r="137" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -4175,7 +4489,7 @@
         <v>35</v>
       </c>
       <c r="E137" s="23">
-        <v>4752000</v>
+        <v>1200000</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>8</v>
@@ -4183,7 +4497,7 @@
     </row>
     <row r="138" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
@@ -4191,7 +4505,7 @@
         <v>35</v>
       </c>
       <c r="E138" s="23">
-        <v>5130000</v>
+        <v>1488000</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>8</v>
@@ -4199,7 +4513,7 @@
     </row>
     <row r="139" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -4207,7 +4521,7 @@
         <v>35</v>
       </c>
       <c r="E139" s="23">
-        <v>5562000</v>
+        <v>1584000</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>8</v>
@@ -4215,7 +4529,7 @@
     </row>
     <row r="140" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -4223,7 +4537,7 @@
         <v>35</v>
       </c>
       <c r="E140" s="23">
-        <v>6210000</v>
+        <v>2016000</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>8</v>
@@ -4231,7 +4545,7 @@
     </row>
     <row r="141" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -4239,7 +4553,7 @@
         <v>35</v>
       </c>
       <c r="E141" s="23">
-        <v>13680000</v>
+        <v>2136000</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>8</v>
@@ -4247,7 +4561,7 @@
     </row>
     <row r="142" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -4255,7 +4569,7 @@
         <v>35</v>
       </c>
       <c r="E142" s="23">
-        <v>14400000</v>
+        <v>3000000</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>8</v>
@@ -4263,7 +4577,7 @@
     </row>
     <row r="143" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -4271,7 +4585,7 @@
         <v>35</v>
       </c>
       <c r="E143" s="23">
-        <v>16020000</v>
+        <v>3780000</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>8</v>
@@ -4279,7 +4593,7 @@
     </row>
     <row r="144" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -4287,7 +4601,7 @@
         <v>35</v>
       </c>
       <c r="E144" s="23">
-        <v>17280000</v>
+        <v>4050000</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>8</v>
@@ -4295,7 +4609,7 @@
     </row>
     <row r="145" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -4303,7 +4617,7 @@
         <v>35</v>
       </c>
       <c r="E145" s="23">
-        <v>19224000</v>
+        <v>4482000</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>8</v>
@@ -4311,7 +4625,7 @@
     </row>
     <row r="146" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -4319,7 +4633,7 @@
         <v>35</v>
       </c>
       <c r="E146" s="23">
-        <v>21024000</v>
+        <v>4752000</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>8</v>
@@ -4327,7 +4641,7 @@
     </row>
     <row r="147" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -4335,187 +4649,151 @@
         <v>35</v>
       </c>
       <c r="E147" s="23">
+        <v>5130000</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A148" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" s="23">
+        <v>5562000</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A149" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B149" s="6"/>
+      <c r="C149" s="6"/>
+      <c r="D149" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E149" s="23">
+        <v>6210000</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A150" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B150" s="6"/>
+      <c r="C150" s="6"/>
+      <c r="D150" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" s="23">
+        <v>13680000</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A151" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B151" s="6"/>
+      <c r="C151" s="6"/>
+      <c r="D151" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="23">
+        <v>14400000</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B152" s="6"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="23">
+        <v>16020000</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A153" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B153" s="6"/>
+      <c r="C153" s="6"/>
+      <c r="D153" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="23">
+        <v>17280000</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A154" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B154" s="6"/>
+      <c r="C154" s="6"/>
+      <c r="D154" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="23">
+        <v>19224000</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A155" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B155" s="6"/>
+      <c r="C155" s="6"/>
+      <c r="D155" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="23">
+        <v>21024000</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A156" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B156" s="6"/>
+      <c r="C156" s="6"/>
+      <c r="D156" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="23">
         <v>24624000</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A148" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E148" s="23">
-        <v>15000</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A149" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C149" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E149" s="23">
-        <v>19500</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A150" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C150" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E150" s="23">
-        <v>25000</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A151" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C151" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D151" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E151" s="23">
-        <v>30000</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A152" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C152" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E152" s="23">
-        <v>40000</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A153" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C153" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E153" s="23">
-        <v>45000</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A154" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C154" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E154" s="23">
-        <v>78000</v>
-      </c>
-      <c r="F154" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A155" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E155" s="23">
-        <v>87000</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A156" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C156" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E156" s="23">
-        <v>96000</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>8</v>
@@ -4523,19 +4801,19 @@
     </row>
     <row r="157" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C157" s="37" t="s">
+      <c r="C157" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E157" s="23">
-        <v>105000</v>
+        <v>15000</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>8</v>
@@ -4543,19 +4821,19 @@
     </row>
     <row r="158" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C158" s="37" t="s">
+      <c r="C158" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E158" s="23">
-        <v>114000</v>
+        <v>19500</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>8</v>
@@ -4563,19 +4841,19 @@
     </row>
     <row r="159" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C159" s="37" t="s">
+      <c r="C159" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E159" s="23">
-        <v>142500</v>
+        <v>25000</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>8</v>
@@ -4583,574 +4861,367 @@
     </row>
     <row r="160" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E160" s="23">
+        <v>30000</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A161" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C161" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" s="23">
+        <v>40000</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A162" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="23">
+        <v>45000</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A163" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" s="23">
+        <v>78000</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A164" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" s="23">
+        <v>87000</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A165" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" s="23">
+        <v>96000</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A166" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E166" s="23">
+        <v>105000</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" s="23">
+        <v>114000</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A168" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C168" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E168" s="23">
+        <v>142500</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A169" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B160" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C160" s="37" t="s">
+      <c r="B169" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C169" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D160" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E160" s="23">
+      <c r="D169" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E169" s="23">
         <v>153000</v>
       </c>
-      <c r="F160" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A161" s="6" t="s">
+      <c r="F169" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A170" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B161" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C161" s="37" t="s">
+      <c r="B170" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C170" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D161" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E161" s="23">
+      <c r="D170" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E170" s="23">
         <v>163500</v>
       </c>
-      <c r="F161" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A162" s="6" t="s">
+      <c r="F170" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A171" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B162" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C162" s="37" t="s">
+      <c r="B171" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C171" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D162" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E162" s="23">
+      <c r="D171" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E171" s="23">
         <v>232500</v>
       </c>
-      <c r="F162" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="163" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A163" s="6" t="s">
+      <c r="F171" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A172" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B163" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C163" s="37" t="s">
+      <c r="B172" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D163" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E163" s="23">
+      <c r="D172" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E172" s="23">
         <v>247500</v>
       </c>
-      <c r="F163" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A164" s="6" t="s">
+      <c r="F172" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A173" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B164" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C164" s="37" t="s">
+      <c r="B173" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C173" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D164" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E164" s="23">
+      <c r="D173" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E173" s="23">
         <v>295500</v>
       </c>
-      <c r="F164" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A165" s="6" t="s">
+      <c r="F173" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A174" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B165" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C165" s="37" t="s">
+      <c r="B174" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D165" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E165" s="23">
+      <c r="D174" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E174" s="23">
         <v>312000</v>
       </c>
-      <c r="F165" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="166" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A166" s="6" t="s">
+      <c r="F174" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A175" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B166" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C166" s="37" t="s">
+      <c r="B175" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C175" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D166" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E166" s="23">
+      <c r="D175" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E175" s="23">
         <v>410000</v>
       </c>
-      <c r="F166" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="167" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A167" s="6" t="s">
+      <c r="F175" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B167" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C167" s="37" t="s">
+      <c r="B176" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C176" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D167" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E167" s="23">
+      <c r="D176" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176" s="23">
         <v>434000</v>
       </c>
-      <c r="F167" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="168" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A168" s="6" t="s">
+      <c r="F176" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B168" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C168" s="37" t="s">
+      <c r="B177" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D168" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E168" s="23">
+      <c r="D177" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" s="23">
         <v>469500</v>
       </c>
-      <c r="F168" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="7" t="s">
+      <c r="F177" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
         <v>203</v>
-      </c>
-      <c r="B169" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C169" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D169" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E169" s="23">
-        <v>19860000</v>
-      </c>
-      <c r="F169" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G169" s="28"/>
-      <c r="H169" s="28"/>
-      <c r="I169" s="28"/>
-      <c r="J169" s="28"/>
-      <c r="K169" s="28"/>
-      <c r="L169" s="28"/>
-      <c r="M169" s="28"/>
-      <c r="N169" s="28"/>
-      <c r="O169" s="28"/>
-      <c r="P169" s="28"/>
-      <c r="Q169" s="28"/>
-      <c r="R169" s="28"/>
-      <c r="S169" s="28"/>
-      <c r="T169" s="28"/>
-      <c r="U169" s="28"/>
-      <c r="V169" s="28"/>
-      <c r="W169" s="28"/>
-      <c r="X169" s="28"/>
-      <c r="Y169" s="28"/>
-      <c r="Z169" s="28"/>
-      <c r="AA169" s="28"/>
-      <c r="AB169" s="28"/>
-      <c r="AC169" s="28"/>
-    </row>
-    <row r="170" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C170" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D170" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E170" s="23">
-        <v>24980000</v>
-      </c>
-      <c r="F170" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G170" s="28"/>
-      <c r="H170" s="28"/>
-      <c r="I170" s="28"/>
-      <c r="J170" s="28"/>
-      <c r="K170" s="28"/>
-      <c r="L170" s="28"/>
-      <c r="M170" s="28"/>
-      <c r="N170" s="28"/>
-      <c r="O170" s="28"/>
-      <c r="P170" s="28"/>
-      <c r="Q170" s="28"/>
-      <c r="R170" s="28"/>
-      <c r="S170" s="28"/>
-      <c r="T170" s="28"/>
-      <c r="U170" s="28"/>
-      <c r="V170" s="28"/>
-      <c r="W170" s="28"/>
-      <c r="X170" s="28"/>
-      <c r="Y170" s="28"/>
-      <c r="Z170" s="28"/>
-      <c r="AA170" s="28"/>
-      <c r="AB170" s="28"/>
-      <c r="AC170" s="28"/>
-    </row>
-    <row r="171" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B171" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C171" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D171" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E171" s="23">
-        <v>35680000</v>
-      </c>
-      <c r="F171" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G171" s="28"/>
-      <c r="H171" s="28"/>
-      <c r="I171" s="28"/>
-      <c r="J171" s="28"/>
-      <c r="K171" s="28"/>
-      <c r="L171" s="28"/>
-      <c r="M171" s="28"/>
-      <c r="N171" s="28"/>
-      <c r="O171" s="28"/>
-      <c r="P171" s="28"/>
-      <c r="Q171" s="28"/>
-      <c r="R171" s="28"/>
-      <c r="S171" s="28"/>
-      <c r="T171" s="28"/>
-      <c r="U171" s="28"/>
-      <c r="V171" s="28"/>
-      <c r="W171" s="28"/>
-      <c r="X171" s="28"/>
-      <c r="Y171" s="28"/>
-      <c r="Z171" s="28"/>
-      <c r="AA171" s="28"/>
-      <c r="AB171" s="28"/>
-      <c r="AC171" s="28"/>
-    </row>
-    <row r="172" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C172" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D172" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E172" s="23">
-        <v>39860000</v>
-      </c>
-      <c r="F172" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G172" s="28"/>
-      <c r="H172" s="28"/>
-      <c r="I172" s="28"/>
-      <c r="J172" s="28"/>
-      <c r="K172" s="28"/>
-      <c r="L172" s="28"/>
-      <c r="M172" s="28"/>
-      <c r="N172" s="28"/>
-      <c r="O172" s="28"/>
-      <c r="P172" s="28"/>
-      <c r="Q172" s="28"/>
-      <c r="R172" s="28"/>
-      <c r="S172" s="28"/>
-      <c r="T172" s="28"/>
-      <c r="U172" s="28"/>
-      <c r="V172" s="28"/>
-      <c r="W172" s="28"/>
-      <c r="X172" s="28"/>
-      <c r="Y172" s="28"/>
-      <c r="Z172" s="28"/>
-      <c r="AA172" s="28"/>
-      <c r="AB172" s="28"/>
-      <c r="AC172" s="28"/>
-    </row>
-    <row r="173" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B173" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C173" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D173" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E173" s="23">
-        <v>47979000</v>
-      </c>
-      <c r="F173" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G173"/>
-      <c r="H173"/>
-      <c r="I173"/>
-      <c r="J173"/>
-      <c r="K173"/>
-      <c r="L173"/>
-      <c r="M173"/>
-      <c r="N173"/>
-      <c r="O173"/>
-      <c r="P173"/>
-      <c r="Q173"/>
-      <c r="R173"/>
-      <c r="S173"/>
-      <c r="T173"/>
-      <c r="U173"/>
-      <c r="V173"/>
-      <c r="W173"/>
-      <c r="X173"/>
-      <c r="Y173"/>
-      <c r="Z173"/>
-      <c r="AA173"/>
-      <c r="AB173"/>
-      <c r="AC173"/>
-    </row>
-    <row r="174" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B174" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C174" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D174" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E174" s="23">
-        <v>52680000</v>
-      </c>
-      <c r="F174" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G174" s="28"/>
-      <c r="H174" s="28"/>
-      <c r="I174" s="28"/>
-      <c r="J174" s="28"/>
-      <c r="K174" s="28"/>
-      <c r="L174" s="28"/>
-      <c r="M174" s="28"/>
-      <c r="N174" s="28"/>
-      <c r="O174" s="28"/>
-      <c r="P174" s="28"/>
-      <c r="Q174" s="28"/>
-      <c r="R174" s="28"/>
-      <c r="S174" s="28"/>
-      <c r="T174" s="28"/>
-      <c r="U174" s="28"/>
-      <c r="V174" s="28"/>
-      <c r="W174" s="28"/>
-      <c r="X174" s="28"/>
-      <c r="Y174" s="28"/>
-      <c r="Z174" s="28"/>
-      <c r="AA174" s="28"/>
-      <c r="AB174" s="28"/>
-      <c r="AC174" s="28"/>
-    </row>
-    <row r="175" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C175" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D175" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E175" s="23">
-        <v>62680000</v>
-      </c>
-      <c r="F175" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G175" s="28"/>
-      <c r="H175" s="28"/>
-      <c r="I175" s="28"/>
-      <c r="J175" s="28"/>
-      <c r="K175" s="28"/>
-      <c r="L175" s="28"/>
-      <c r="M175" s="28"/>
-      <c r="N175" s="28"/>
-      <c r="O175" s="28"/>
-      <c r="P175" s="28"/>
-      <c r="Q175" s="28"/>
-      <c r="R175" s="28"/>
-      <c r="S175" s="28"/>
-      <c r="T175" s="28"/>
-      <c r="U175" s="28"/>
-      <c r="V175" s="28"/>
-      <c r="W175" s="28"/>
-      <c r="X175" s="28"/>
-      <c r="Y175" s="28"/>
-      <c r="Z175" s="28"/>
-      <c r="AA175" s="28"/>
-      <c r="AB175" s="28"/>
-      <c r="AC175" s="28"/>
-    </row>
-    <row r="176" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B176" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D176" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E176" s="23">
-        <v>68680000</v>
-      </c>
-      <c r="F176" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G176" s="28"/>
-      <c r="H176" s="28"/>
-      <c r="I176" s="28"/>
-      <c r="J176" s="28"/>
-      <c r="K176" s="28"/>
-      <c r="L176" s="28"/>
-      <c r="M176" s="28"/>
-      <c r="N176" s="28"/>
-      <c r="O176" s="28"/>
-      <c r="P176" s="28"/>
-      <c r="Q176" s="28"/>
-      <c r="R176" s="28"/>
-      <c r="S176" s="28"/>
-      <c r="T176" s="28"/>
-      <c r="U176" s="28"/>
-      <c r="V176" s="28"/>
-      <c r="W176" s="28"/>
-      <c r="X176" s="28"/>
-      <c r="Y176" s="28"/>
-      <c r="Z176" s="28"/>
-      <c r="AA176" s="28"/>
-      <c r="AB176" s="28"/>
-      <c r="AC176" s="28"/>
-    </row>
-    <row r="177" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B177" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C177" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D177" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E177" s="23">
-        <v>75500000</v>
-      </c>
-      <c r="F177" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G177" s="28"/>
-      <c r="H177" s="28"/>
-      <c r="I177" s="28"/>
-      <c r="J177" s="28"/>
-      <c r="K177" s="28"/>
-      <c r="L177" s="28"/>
-      <c r="M177" s="28"/>
-      <c r="N177" s="28"/>
-      <c r="O177" s="28"/>
-      <c r="P177" s="28"/>
-      <c r="Q177" s="28"/>
-      <c r="R177" s="28"/>
-      <c r="S177" s="28"/>
-      <c r="T177" s="28"/>
-      <c r="U177" s="28"/>
-      <c r="V177" s="28"/>
-      <c r="W177" s="28"/>
-      <c r="X177" s="28"/>
-      <c r="Y177" s="28"/>
-      <c r="Z177" s="28"/>
-      <c r="AA177" s="28"/>
-      <c r="AB177" s="28"/>
-      <c r="AC177" s="28"/>
-    </row>
-    <row r="178" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
-        <v>212</v>
       </c>
       <c r="B178" s="8" t="s">
         <v>9</v>
@@ -5162,7 +5233,7 @@
         <v>35</v>
       </c>
       <c r="E178" s="23">
-        <v>89580000</v>
+        <v>19860000</v>
       </c>
       <c r="F178" s="13" t="s">
         <v>8</v>
@@ -5191,9 +5262,9 @@
       <c r="AB178" s="28"/>
       <c r="AC178" s="28"/>
     </row>
-    <row r="179" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B179" s="8" t="s">
         <v>9</v>
@@ -5205,7 +5276,7 @@
         <v>35</v>
       </c>
       <c r="E179" s="23">
-        <v>99880000</v>
+        <v>24980000</v>
       </c>
       <c r="F179" s="13" t="s">
         <v>8</v>
@@ -5234,9 +5305,9 @@
       <c r="AB179" s="28"/>
       <c r="AC179" s="28"/>
     </row>
-    <row r="180" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B180" s="8" t="s">
         <v>9</v>
@@ -5248,7 +5319,7 @@
         <v>35</v>
       </c>
       <c r="E180" s="23">
-        <v>109680000</v>
+        <v>35680000</v>
       </c>
       <c r="F180" s="13" t="s">
         <v>8</v>
@@ -5277,9 +5348,9 @@
       <c r="AB180" s="28"/>
       <c r="AC180" s="28"/>
     </row>
-    <row r="181" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B181" s="8" t="s">
         <v>9</v>
@@ -5291,7 +5362,7 @@
         <v>35</v>
       </c>
       <c r="E181" s="23">
-        <v>129860000</v>
+        <v>39860000</v>
       </c>
       <c r="F181" s="13" t="s">
         <v>8</v>
@@ -5320,9 +5391,9 @@
       <c r="AB181" s="28"/>
       <c r="AC181" s="28"/>
     </row>
-    <row r="182" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B182" s="8" t="s">
         <v>9</v>
@@ -5334,38 +5405,38 @@
         <v>35</v>
       </c>
       <c r="E182" s="23">
-        <v>144910000</v>
+        <v>47979000</v>
       </c>
       <c r="F182" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G182" s="28"/>
-      <c r="H182" s="28"/>
-      <c r="I182" s="28"/>
-      <c r="J182" s="28"/>
-      <c r="K182" s="28"/>
-      <c r="L182" s="28"/>
-      <c r="M182" s="28"/>
-      <c r="N182" s="28"/>
-      <c r="O182" s="28"/>
-      <c r="P182" s="28"/>
-      <c r="Q182" s="28"/>
-      <c r="R182" s="28"/>
-      <c r="S182" s="28"/>
-      <c r="T182" s="28"/>
-      <c r="U182" s="28"/>
-      <c r="V182" s="28"/>
-      <c r="W182" s="28"/>
-      <c r="X182" s="28"/>
-      <c r="Y182" s="28"/>
-      <c r="Z182" s="28"/>
-      <c r="AA182" s="28"/>
-      <c r="AB182" s="28"/>
-      <c r="AC182" s="28"/>
-    </row>
-    <row r="183" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G182"/>
+      <c r="H182"/>
+      <c r="I182"/>
+      <c r="J182"/>
+      <c r="K182"/>
+      <c r="L182"/>
+      <c r="M182"/>
+      <c r="N182"/>
+      <c r="O182"/>
+      <c r="P182"/>
+      <c r="Q182"/>
+      <c r="R182"/>
+      <c r="S182"/>
+      <c r="T182"/>
+      <c r="U182"/>
+      <c r="V182"/>
+      <c r="W182"/>
+      <c r="X182"/>
+      <c r="Y182"/>
+      <c r="Z182"/>
+      <c r="AA182"/>
+      <c r="AB182"/>
+      <c r="AC182"/>
+    </row>
+    <row r="183" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B183" s="8" t="s">
         <v>9</v>
@@ -5377,7 +5448,7 @@
         <v>35</v>
       </c>
       <c r="E183" s="23">
-        <v>155910000</v>
+        <v>52680000</v>
       </c>
       <c r="F183" s="13" t="s">
         <v>8</v>
@@ -5406,9 +5477,9 @@
       <c r="AB183" s="28"/>
       <c r="AC183" s="28"/>
     </row>
-    <row r="184" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B184" s="8" t="s">
         <v>9</v>
@@ -5420,7 +5491,7 @@
         <v>35</v>
       </c>
       <c r="E184" s="23">
-        <v>156560000</v>
+        <v>62680000</v>
       </c>
       <c r="F184" s="13" t="s">
         <v>8</v>
@@ -5449,9 +5520,9 @@
       <c r="AB184" s="28"/>
       <c r="AC184" s="28"/>
     </row>
-    <row r="185" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B185" s="8" t="s">
         <v>9</v>
@@ -5463,7 +5534,7 @@
         <v>35</v>
       </c>
       <c r="E185" s="23">
-        <v>184370000</v>
+        <v>68680000</v>
       </c>
       <c r="F185" s="13" t="s">
         <v>8</v>
@@ -5494,7 +5565,7 @@
     </row>
     <row r="186" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>9</v>
@@ -5506,7 +5577,7 @@
         <v>35</v>
       </c>
       <c r="E186" s="23">
-        <v>243080000</v>
+        <v>75500000</v>
       </c>
       <c r="F186" s="13" t="s">
         <v>8</v>
@@ -5537,7 +5608,7 @@
     </row>
     <row r="187" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B187" s="8" t="s">
         <v>9</v>
@@ -5549,7 +5620,7 @@
         <v>35</v>
       </c>
       <c r="E187" s="23">
-        <v>276040000</v>
+        <v>89580000</v>
       </c>
       <c r="F187" s="13" t="s">
         <v>8</v>
@@ -5580,7 +5651,7 @@
     </row>
     <row r="188" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B188" s="8" t="s">
         <v>9</v>
@@ -5592,7 +5663,7 @@
         <v>35</v>
       </c>
       <c r="E188" s="23">
-        <v>313680000</v>
+        <v>99880000</v>
       </c>
       <c r="F188" s="13" t="s">
         <v>8</v>
@@ -5623,7 +5694,7 @@
     </row>
     <row r="189" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B189" s="8" t="s">
         <v>9</v>
@@ -5635,7 +5706,7 @@
         <v>35</v>
       </c>
       <c r="E189" s="23">
-        <v>358200000</v>
+        <v>109680000</v>
       </c>
       <c r="F189" s="13" t="s">
         <v>8</v>
@@ -5666,7 +5737,7 @@
     </row>
     <row r="190" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B190" s="8" t="s">
         <v>9</v>
@@ -5678,7 +5749,7 @@
         <v>35</v>
       </c>
       <c r="E190" s="23">
-        <v>389600000</v>
+        <v>129860000</v>
       </c>
       <c r="F190" s="13" t="s">
         <v>8</v>
@@ -5709,7 +5780,7 @@
     </row>
     <row r="191" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>9</v>
@@ -5721,7 +5792,7 @@
         <v>35</v>
       </c>
       <c r="E191" s="23">
-        <v>433800000</v>
+        <v>144910000</v>
       </c>
       <c r="F191" s="13" t="s">
         <v>8</v>
@@ -5752,7 +5823,7 @@
     </row>
     <row r="192" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B192" s="8" t="s">
         <v>9</v>
@@ -5764,7 +5835,7 @@
         <v>35</v>
       </c>
       <c r="E192" s="23">
-        <v>656580000</v>
+        <v>155910000</v>
       </c>
       <c r="F192" s="13" t="s">
         <v>8</v>
@@ -5795,7 +5866,7 @@
     </row>
     <row r="193" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B193" s="8" t="s">
         <v>9</v>
@@ -5807,7 +5878,7 @@
         <v>35</v>
       </c>
       <c r="E193" s="23">
-        <v>762670000</v>
+        <v>156560000</v>
       </c>
       <c r="F193" s="13" t="s">
         <v>8</v>
@@ -5838,7 +5909,7 @@
     </row>
     <row r="194" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B194" s="8" t="s">
         <v>9</v>
@@ -5850,7 +5921,7 @@
         <v>35</v>
       </c>
       <c r="E194" s="23">
-        <v>874940000</v>
+        <v>184370000</v>
       </c>
       <c r="F194" s="13" t="s">
         <v>8</v>
@@ -5881,7 +5952,7 @@
     </row>
     <row r="195" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B195" s="8" t="s">
         <v>9</v>
@@ -5893,7 +5964,7 @@
         <v>35</v>
       </c>
       <c r="E195" s="23">
-        <v>1062400000</v>
+        <v>243080000</v>
       </c>
       <c r="F195" s="13" t="s">
         <v>8</v>
@@ -5922,398 +5993,410 @@
       <c r="AB195" s="28"/>
       <c r="AC195" s="28"/>
     </row>
-    <row r="196" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="11" t="s">
+    <row r="196" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D196" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196" s="23">
+        <v>276040000</v>
+      </c>
+      <c r="F196" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G196" s="28"/>
+      <c r="H196" s="28"/>
+      <c r="I196" s="28"/>
+      <c r="J196" s="28"/>
+      <c r="K196" s="28"/>
+      <c r="L196" s="28"/>
+      <c r="M196" s="28"/>
+      <c r="N196" s="28"/>
+      <c r="O196" s="28"/>
+      <c r="P196" s="28"/>
+      <c r="Q196" s="28"/>
+      <c r="R196" s="28"/>
+      <c r="S196" s="28"/>
+      <c r="T196" s="28"/>
+      <c r="U196" s="28"/>
+      <c r="V196" s="28"/>
+      <c r="W196" s="28"/>
+      <c r="X196" s="28"/>
+      <c r="Y196" s="28"/>
+      <c r="Z196" s="28"/>
+      <c r="AA196" s="28"/>
+      <c r="AB196" s="28"/>
+      <c r="AC196" s="28"/>
+    </row>
+    <row r="197" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E197" s="23">
+        <v>313680000</v>
+      </c>
+      <c r="F197" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G197" s="28"/>
+      <c r="H197" s="28"/>
+      <c r="I197" s="28"/>
+      <c r="J197" s="28"/>
+      <c r="K197" s="28"/>
+      <c r="L197" s="28"/>
+      <c r="M197" s="28"/>
+      <c r="N197" s="28"/>
+      <c r="O197" s="28"/>
+      <c r="P197" s="28"/>
+      <c r="Q197" s="28"/>
+      <c r="R197" s="28"/>
+      <c r="S197" s="28"/>
+      <c r="T197" s="28"/>
+      <c r="U197" s="28"/>
+      <c r="V197" s="28"/>
+      <c r="W197" s="28"/>
+      <c r="X197" s="28"/>
+      <c r="Y197" s="28"/>
+      <c r="Z197" s="28"/>
+      <c r="AA197" s="28"/>
+      <c r="AB197" s="28"/>
+      <c r="AC197" s="28"/>
+    </row>
+    <row r="198" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C198" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D198" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E198" s="23">
+        <v>358200000</v>
+      </c>
+      <c r="F198" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G198" s="28"/>
+      <c r="H198" s="28"/>
+      <c r="I198" s="28"/>
+      <c r="J198" s="28"/>
+      <c r="K198" s="28"/>
+      <c r="L198" s="28"/>
+      <c r="M198" s="28"/>
+      <c r="N198" s="28"/>
+      <c r="O198" s="28"/>
+      <c r="P198" s="28"/>
+      <c r="Q198" s="28"/>
+      <c r="R198" s="28"/>
+      <c r="S198" s="28"/>
+      <c r="T198" s="28"/>
+      <c r="U198" s="28"/>
+      <c r="V198" s="28"/>
+      <c r="W198" s="28"/>
+      <c r="X198" s="28"/>
+      <c r="Y198" s="28"/>
+      <c r="Z198" s="28"/>
+      <c r="AA198" s="28"/>
+      <c r="AB198" s="28"/>
+      <c r="AC198" s="28"/>
+    </row>
+    <row r="199" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E199" s="23">
+        <v>389600000</v>
+      </c>
+      <c r="F199" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G199" s="28"/>
+      <c r="H199" s="28"/>
+      <c r="I199" s="28"/>
+      <c r="J199" s="28"/>
+      <c r="K199" s="28"/>
+      <c r="L199" s="28"/>
+      <c r="M199" s="28"/>
+      <c r="N199" s="28"/>
+      <c r="O199" s="28"/>
+      <c r="P199" s="28"/>
+      <c r="Q199" s="28"/>
+      <c r="R199" s="28"/>
+      <c r="S199" s="28"/>
+      <c r="T199" s="28"/>
+      <c r="U199" s="28"/>
+      <c r="V199" s="28"/>
+      <c r="W199" s="28"/>
+      <c r="X199" s="28"/>
+      <c r="Y199" s="28"/>
+      <c r="Z199" s="28"/>
+      <c r="AA199" s="28"/>
+      <c r="AB199" s="28"/>
+      <c r="AC199" s="28"/>
+    </row>
+    <row r="200" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D200" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E200" s="23">
+        <v>433800000</v>
+      </c>
+      <c r="F200" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G200" s="28"/>
+      <c r="H200" s="28"/>
+      <c r="I200" s="28"/>
+      <c r="J200" s="28"/>
+      <c r="K200" s="28"/>
+      <c r="L200" s="28"/>
+      <c r="M200" s="28"/>
+      <c r="N200" s="28"/>
+      <c r="O200" s="28"/>
+      <c r="P200" s="28"/>
+      <c r="Q200" s="28"/>
+      <c r="R200" s="28"/>
+      <c r="S200" s="28"/>
+      <c r="T200" s="28"/>
+      <c r="U200" s="28"/>
+      <c r="V200" s="28"/>
+      <c r="W200" s="28"/>
+      <c r="X200" s="28"/>
+      <c r="Y200" s="28"/>
+      <c r="Z200" s="28"/>
+      <c r="AA200" s="28"/>
+      <c r="AB200" s="28"/>
+      <c r="AC200" s="28"/>
+    </row>
+    <row r="201" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E201" s="23">
+        <v>656580000</v>
+      </c>
+      <c r="F201" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G201" s="28"/>
+      <c r="H201" s="28"/>
+      <c r="I201" s="28"/>
+      <c r="J201" s="28"/>
+      <c r="K201" s="28"/>
+      <c r="L201" s="28"/>
+      <c r="M201" s="28"/>
+      <c r="N201" s="28"/>
+      <c r="O201" s="28"/>
+      <c r="P201" s="28"/>
+      <c r="Q201" s="28"/>
+      <c r="R201" s="28"/>
+      <c r="S201" s="28"/>
+      <c r="T201" s="28"/>
+      <c r="U201" s="28"/>
+      <c r="V201" s="28"/>
+      <c r="W201" s="28"/>
+      <c r="X201" s="28"/>
+      <c r="Y201" s="28"/>
+      <c r="Z201" s="28"/>
+      <c r="AA201" s="28"/>
+      <c r="AB201" s="28"/>
+      <c r="AC201" s="28"/>
+    </row>
+    <row r="202" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D202" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E202" s="23">
+        <v>762670000</v>
+      </c>
+      <c r="F202" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G202" s="28"/>
+      <c r="H202" s="28"/>
+      <c r="I202" s="28"/>
+      <c r="J202" s="28"/>
+      <c r="K202" s="28"/>
+      <c r="L202" s="28"/>
+      <c r="M202" s="28"/>
+      <c r="N202" s="28"/>
+      <c r="O202" s="28"/>
+      <c r="P202" s="28"/>
+      <c r="Q202" s="28"/>
+      <c r="R202" s="28"/>
+      <c r="S202" s="28"/>
+      <c r="T202" s="28"/>
+      <c r="U202" s="28"/>
+      <c r="V202" s="28"/>
+      <c r="W202" s="28"/>
+      <c r="X202" s="28"/>
+      <c r="Y202" s="28"/>
+      <c r="Z202" s="28"/>
+      <c r="AA202" s="28"/>
+      <c r="AB202" s="28"/>
+      <c r="AC202" s="28"/>
+    </row>
+    <row r="203" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D203" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E203" s="23">
+        <v>874940000</v>
+      </c>
+      <c r="F203" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G203" s="28"/>
+      <c r="H203" s="28"/>
+      <c r="I203" s="28"/>
+      <c r="J203" s="28"/>
+      <c r="K203" s="28"/>
+      <c r="L203" s="28"/>
+      <c r="M203" s="28"/>
+      <c r="N203" s="28"/>
+      <c r="O203" s="28"/>
+      <c r="P203" s="28"/>
+      <c r="Q203" s="28"/>
+      <c r="R203" s="28"/>
+      <c r="S203" s="28"/>
+      <c r="T203" s="28"/>
+      <c r="U203" s="28"/>
+      <c r="V203" s="28"/>
+      <c r="W203" s="28"/>
+      <c r="X203" s="28"/>
+      <c r="Y203" s="28"/>
+      <c r="Z203" s="28"/>
+      <c r="AA203" s="28"/>
+      <c r="AB203" s="28"/>
+      <c r="AC203" s="28"/>
+    </row>
+    <row r="204" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D204" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E204" s="23">
+        <v>1062400000</v>
+      </c>
+      <c r="F204" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G204" s="28"/>
+      <c r="H204" s="28"/>
+      <c r="I204" s="28"/>
+      <c r="J204" s="28"/>
+      <c r="K204" s="28"/>
+      <c r="L204" s="28"/>
+      <c r="M204" s="28"/>
+      <c r="N204" s="28"/>
+      <c r="O204" s="28"/>
+      <c r="P204" s="28"/>
+      <c r="Q204" s="28"/>
+      <c r="R204" s="28"/>
+      <c r="S204" s="28"/>
+      <c r="T204" s="28"/>
+      <c r="U204" s="28"/>
+      <c r="V204" s="28"/>
+      <c r="W204" s="28"/>
+      <c r="X204" s="28"/>
+      <c r="Y204" s="28"/>
+      <c r="Z204" s="28"/>
+      <c r="AA204" s="28"/>
+      <c r="AB204" s="28"/>
+      <c r="AC204" s="28"/>
+    </row>
+    <row r="205" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B196" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C196" s="12" t="s">
+      <c r="B205" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C205" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D196" s="38" t="s">
+      <c r="D205" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="E196" s="24">
+      <c r="E205" s="24">
         <v>75000</v>
       </c>
-      <c r="F196" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G196"/>
-      <c r="H196"/>
-      <c r="I196"/>
-      <c r="J196"/>
-      <c r="K196"/>
-      <c r="L196"/>
-      <c r="M196"/>
-      <c r="N196"/>
-      <c r="O196"/>
-      <c r="P196"/>
-      <c r="Q196"/>
-      <c r="R196"/>
-      <c r="S196"/>
-      <c r="T196"/>
-      <c r="U196"/>
-      <c r="V196"/>
-      <c r="W196"/>
-      <c r="X196"/>
-      <c r="Y196"/>
-      <c r="Z196"/>
-      <c r="AA196"/>
-      <c r="AB196"/>
-      <c r="AC196"/>
-    </row>
-    <row r="197" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C197" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="D197" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E197" s="24">
-        <v>33000</v>
-      </c>
-      <c r="F197" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G197"/>
-      <c r="H197"/>
-      <c r="I197"/>
-      <c r="J197"/>
-      <c r="K197"/>
-      <c r="L197"/>
-      <c r="M197"/>
-      <c r="N197"/>
-      <c r="O197"/>
-      <c r="P197"/>
-      <c r="Q197"/>
-      <c r="R197"/>
-      <c r="S197"/>
-      <c r="T197"/>
-      <c r="U197"/>
-      <c r="V197"/>
-      <c r="W197"/>
-      <c r="X197"/>
-      <c r="Y197"/>
-      <c r="Z197"/>
-      <c r="AA197"/>
-      <c r="AB197"/>
-      <c r="AC197"/>
-    </row>
-    <row r="198" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B198" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C198" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D198" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E198" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F198" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G198"/>
-      <c r="H198"/>
-      <c r="I198"/>
-      <c r="J198"/>
-      <c r="K198"/>
-      <c r="L198"/>
-      <c r="M198"/>
-      <c r="N198"/>
-      <c r="O198"/>
-      <c r="P198"/>
-      <c r="Q198"/>
-      <c r="R198"/>
-      <c r="S198"/>
-      <c r="T198"/>
-      <c r="U198"/>
-      <c r="V198"/>
-      <c r="W198"/>
-      <c r="X198"/>
-      <c r="Y198"/>
-      <c r="Z198"/>
-      <c r="AA198"/>
-      <c r="AB198"/>
-      <c r="AC198"/>
-    </row>
-    <row r="199" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B199" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C199" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D199" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E199" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F199" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G199"/>
-      <c r="H199"/>
-      <c r="I199"/>
-      <c r="J199"/>
-      <c r="K199"/>
-      <c r="L199"/>
-      <c r="M199"/>
-      <c r="N199"/>
-      <c r="O199"/>
-      <c r="P199"/>
-      <c r="Q199"/>
-      <c r="R199"/>
-      <c r="S199"/>
-      <c r="T199"/>
-      <c r="U199"/>
-      <c r="V199"/>
-      <c r="W199"/>
-      <c r="X199"/>
-      <c r="Y199"/>
-      <c r="Z199"/>
-      <c r="AA199"/>
-      <c r="AB199"/>
-      <c r="AC199"/>
-    </row>
-    <row r="200" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B200" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C200" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D200" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E200" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F200" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G200"/>
-      <c r="H200"/>
-      <c r="I200"/>
-      <c r="J200"/>
-      <c r="K200"/>
-      <c r="L200"/>
-      <c r="M200"/>
-      <c r="N200"/>
-      <c r="O200"/>
-      <c r="P200"/>
-      <c r="Q200"/>
-      <c r="R200"/>
-      <c r="S200"/>
-      <c r="T200"/>
-      <c r="U200"/>
-      <c r="V200"/>
-      <c r="W200"/>
-      <c r="X200"/>
-      <c r="Y200"/>
-      <c r="Z200"/>
-      <c r="AA200"/>
-      <c r="AB200"/>
-      <c r="AC200"/>
-    </row>
-    <row r="201" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B201" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="C201" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D201" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E201" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F201" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G201"/>
-      <c r="H201"/>
-      <c r="I201"/>
-      <c r="J201"/>
-      <c r="K201"/>
-      <c r="L201"/>
-      <c r="M201"/>
-      <c r="N201"/>
-      <c r="O201"/>
-      <c r="P201"/>
-      <c r="Q201"/>
-      <c r="R201"/>
-      <c r="S201"/>
-      <c r="T201"/>
-      <c r="U201"/>
-      <c r="V201"/>
-      <c r="W201"/>
-      <c r="X201"/>
-      <c r="Y201"/>
-      <c r="Z201"/>
-      <c r="AA201"/>
-      <c r="AB201"/>
-      <c r="AC201"/>
-    </row>
-    <row r="202" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B202" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="C202" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D202" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E202" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F202" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G202"/>
-      <c r="H202"/>
-      <c r="I202"/>
-      <c r="J202"/>
-      <c r="K202"/>
-      <c r="L202"/>
-      <c r="M202"/>
-      <c r="N202"/>
-      <c r="O202"/>
-      <c r="P202"/>
-      <c r="Q202"/>
-      <c r="R202"/>
-      <c r="S202"/>
-      <c r="T202"/>
-      <c r="U202"/>
-      <c r="V202"/>
-      <c r="W202"/>
-      <c r="X202"/>
-      <c r="Y202"/>
-      <c r="Z202"/>
-      <c r="AA202"/>
-      <c r="AB202"/>
-      <c r="AC202"/>
-    </row>
-    <row r="203" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="B203" s="40"/>
-      <c r="C203" s="29"/>
-      <c r="D203" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E203" s="24">
-        <v>1000000</v>
-      </c>
-      <c r="F203" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G203"/>
-      <c r="H203"/>
-      <c r="I203"/>
-      <c r="J203"/>
-      <c r="K203"/>
-      <c r="L203"/>
-      <c r="M203"/>
-      <c r="N203"/>
-      <c r="O203"/>
-      <c r="P203"/>
-      <c r="Q203"/>
-      <c r="R203"/>
-      <c r="S203"/>
-      <c r="T203"/>
-      <c r="U203"/>
-      <c r="V203"/>
-      <c r="W203"/>
-      <c r="X203"/>
-      <c r="Y203"/>
-      <c r="Z203"/>
-      <c r="AA203"/>
-      <c r="AB203"/>
-      <c r="AC203"/>
-    </row>
-    <row r="204" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B204" s="40"/>
-      <c r="C204" s="29"/>
-      <c r="D204" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E204" s="24">
-        <v>880000</v>
-      </c>
-      <c r="F204" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G204"/>
-      <c r="H204"/>
-      <c r="I204"/>
-      <c r="J204"/>
-      <c r="K204"/>
-      <c r="L204"/>
-      <c r="M204"/>
-      <c r="N204"/>
-      <c r="O204"/>
-      <c r="P204"/>
-      <c r="Q204"/>
-      <c r="R204"/>
-      <c r="S204"/>
-      <c r="T204"/>
-      <c r="U204"/>
-      <c r="V204"/>
-      <c r="W204"/>
-      <c r="X204"/>
-      <c r="Y204"/>
-      <c r="Z204"/>
-      <c r="AA204"/>
-      <c r="AB204"/>
-      <c r="AC204"/>
-    </row>
-    <row r="205" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B205" s="40"/>
-      <c r="C205" s="29"/>
-      <c r="D205" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E205" s="24">
-        <v>1380000</v>
-      </c>
-      <c r="F205" s="17" t="s">
+      <c r="F205" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G205"/>
@@ -6342,17 +6425,21 @@
     </row>
     <row r="206" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B206" s="8"/>
-      <c r="C206" s="8"/>
-      <c r="D206" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E206" s="23">
-        <v>13880000</v>
-      </c>
-      <c r="F206" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D206" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E206" s="24">
+        <v>33000</v>
+      </c>
+      <c r="F206" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G206"/>
@@ -6379,19 +6466,23 @@
       <c r="AB206"/>
       <c r="AC206"/>
     </row>
-    <row r="207" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B207" s="8"/>
-      <c r="C207" s="8"/>
-      <c r="D207" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E207" s="23">
-        <v>750000</v>
-      </c>
-      <c r="F207" s="18" t="s">
+    <row r="207" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D207" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E207" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F207" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G207"/>
@@ -6418,19 +6509,23 @@
       <c r="AB207"/>
       <c r="AC207"/>
     </row>
-    <row r="208" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B208" s="8"/>
-      <c r="C208" s="8"/>
-      <c r="D208" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E208" s="23">
-        <v>155000</v>
-      </c>
-      <c r="F208" s="18" t="s">
+    <row r="208" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D208" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E208" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F208" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G208"/>
@@ -6457,19 +6552,23 @@
       <c r="AB208"/>
       <c r="AC208"/>
     </row>
-    <row r="209" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B209" s="8"/>
-      <c r="C209" s="8"/>
-      <c r="D209" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E209" s="23">
-        <v>176000</v>
-      </c>
-      <c r="F209" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D209" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E209" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F209" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G209"/>
@@ -6497,18 +6596,22 @@
       <c r="AC209"/>
     </row>
     <row r="210" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B210" s="8"/>
-      <c r="C210" s="8"/>
-      <c r="D210" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E210" s="23">
-        <v>198000</v>
-      </c>
-      <c r="F210" s="18" t="s">
+      <c r="A210" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B210" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D210" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E210" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F210" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G210"/>
@@ -6536,18 +6639,22 @@
       <c r="AC210"/>
     </row>
     <row r="211" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B211" s="8"/>
-      <c r="C211" s="8"/>
-      <c r="D211" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E211" s="23">
-        <v>186000</v>
-      </c>
-      <c r="F211" s="18" t="s">
+      <c r="A211" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B211" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="C211" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D211" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E211" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F211" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G211"/>
@@ -6575,18 +6682,18 @@
       <c r="AC211"/>
     </row>
     <row r="212" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B212" s="8"/>
-      <c r="C212" s="8"/>
+      <c r="A212" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B212" s="38"/>
+      <c r="C212" s="29"/>
       <c r="D212" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E212" s="23">
-        <v>198000</v>
-      </c>
-      <c r="F212" s="18" t="s">
+      <c r="E212" s="24">
+        <v>1000000</v>
+      </c>
+      <c r="F212" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G212"/>
@@ -6614,18 +6721,18 @@
       <c r="AC212"/>
     </row>
     <row r="213" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B213" s="8"/>
-      <c r="C213" s="8"/>
+      <c r="A213" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B213" s="38"/>
+      <c r="C213" s="29"/>
       <c r="D213" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E213" s="23">
-        <v>228000</v>
-      </c>
-      <c r="F213" s="18" t="s">
+      <c r="E213" s="24">
+        <v>880000</v>
+      </c>
+      <c r="F213" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G213"/>
@@ -6653,18 +6760,18 @@
       <c r="AC213"/>
     </row>
     <row r="214" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="B214" s="8"/>
-      <c r="C214" s="8"/>
+      <c r="A214" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B214" s="38"/>
+      <c r="C214" s="29"/>
       <c r="D214" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E214" s="23">
-        <v>175000</v>
-      </c>
-      <c r="F214" s="18" t="s">
+      <c r="E214" s="24">
+        <v>1380000</v>
+      </c>
+      <c r="F214" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G214"/>
@@ -6693,7 +6800,7 @@
     </row>
     <row r="215" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -6701,7 +6808,7 @@
         <v>35</v>
       </c>
       <c r="E215" s="23">
-        <v>296000</v>
+        <v>13880000</v>
       </c>
       <c r="F215" s="18" t="s">
         <v>8</v>
@@ -6732,7 +6839,7 @@
     </row>
     <row r="216" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -6740,7 +6847,7 @@
         <v>35</v>
       </c>
       <c r="E216" s="23">
-        <v>258000</v>
+        <v>750000</v>
       </c>
       <c r="F216" s="18" t="s">
         <v>8</v>
@@ -6771,7 +6878,7 @@
     </row>
     <row r="217" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -6779,7 +6886,7 @@
         <v>35</v>
       </c>
       <c r="E217" s="23">
-        <v>228000</v>
+        <v>155000</v>
       </c>
       <c r="F217" s="18" t="s">
         <v>8</v>
@@ -6810,7 +6917,7 @@
     </row>
     <row r="218" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -6818,7 +6925,7 @@
         <v>35</v>
       </c>
       <c r="E218" s="23">
-        <v>248000</v>
+        <v>176000</v>
       </c>
       <c r="F218" s="18" t="s">
         <v>8</v>
@@ -6849,7 +6956,7 @@
     </row>
     <row r="219" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -6857,7 +6964,7 @@
         <v>35</v>
       </c>
       <c r="E219" s="23">
-        <v>278000</v>
+        <v>198000</v>
       </c>
       <c r="F219" s="18" t="s">
         <v>8</v>
@@ -6887,22 +6994,18 @@
       <c r="AC219"/>
     </row>
     <row r="220" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B220" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C220" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D220" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E220" s="25">
-        <v>32680000</v>
-      </c>
-      <c r="F220" s="17" t="s">
+      <c r="A220" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B220" s="8"/>
+      <c r="C220" s="8"/>
+      <c r="D220" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E220" s="23">
+        <v>186000</v>
+      </c>
+      <c r="F220" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G220"/>
@@ -6929,23 +7032,19 @@
       <c r="AB220"/>
       <c r="AC220"/>
     </row>
-    <row r="221" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="B221" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C221" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D221" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E221" s="25">
-        <v>36800000</v>
-      </c>
-      <c r="F221" s="17" t="s">
+    <row r="221" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
+      <c r="D221" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E221" s="23">
+        <v>198000</v>
+      </c>
+      <c r="F221" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G221"/>
@@ -6972,23 +7071,19 @@
       <c r="AB221"/>
       <c r="AC221"/>
     </row>
-    <row r="222" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B222" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C222" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D222" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E222" s="25">
-        <v>43680000</v>
-      </c>
-      <c r="F222" s="17" t="s">
+    <row r="222" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B222" s="8"/>
+      <c r="C222" s="8"/>
+      <c r="D222" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E222" s="23">
+        <v>228000</v>
+      </c>
+      <c r="F222" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G222"/>
@@ -7015,123 +7110,486 @@
       <c r="AB222"/>
       <c r="AC222"/>
     </row>
-    <row r="223" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A223" s="19" t="s">
+    <row r="223" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E223" s="23">
+        <v>175000</v>
+      </c>
+      <c r="F223" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G223"/>
+      <c r="H223"/>
+      <c r="I223"/>
+      <c r="J223"/>
+      <c r="K223"/>
+      <c r="L223"/>
+      <c r="M223"/>
+      <c r="N223"/>
+      <c r="O223"/>
+      <c r="P223"/>
+      <c r="Q223"/>
+      <c r="R223"/>
+      <c r="S223"/>
+      <c r="T223"/>
+      <c r="U223"/>
+      <c r="V223"/>
+      <c r="W223"/>
+      <c r="X223"/>
+      <c r="Y223"/>
+      <c r="Z223"/>
+      <c r="AA223"/>
+      <c r="AB223"/>
+      <c r="AC223"/>
+    </row>
+    <row r="224" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E224" s="23">
+        <v>296000</v>
+      </c>
+      <c r="F224" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G224"/>
+      <c r="H224"/>
+      <c r="I224"/>
+      <c r="J224"/>
+      <c r="K224"/>
+      <c r="L224"/>
+      <c r="M224"/>
+      <c r="N224"/>
+      <c r="O224"/>
+      <c r="P224"/>
+      <c r="Q224"/>
+      <c r="R224"/>
+      <c r="S224"/>
+      <c r="T224"/>
+      <c r="U224"/>
+      <c r="V224"/>
+      <c r="W224"/>
+      <c r="X224"/>
+      <c r="Y224"/>
+      <c r="Z224"/>
+      <c r="AA224"/>
+      <c r="AB224"/>
+      <c r="AC224"/>
+    </row>
+    <row r="225" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B225" s="8"/>
+      <c r="C225" s="8"/>
+      <c r="D225" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E225" s="23">
+        <v>258000</v>
+      </c>
+      <c r="F225" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G225"/>
+      <c r="H225"/>
+      <c r="I225"/>
+      <c r="J225"/>
+      <c r="K225"/>
+      <c r="L225"/>
+      <c r="M225"/>
+      <c r="N225"/>
+      <c r="O225"/>
+      <c r="P225"/>
+      <c r="Q225"/>
+      <c r="R225"/>
+      <c r="S225"/>
+      <c r="T225"/>
+      <c r="U225"/>
+      <c r="V225"/>
+      <c r="W225"/>
+      <c r="X225"/>
+      <c r="Y225"/>
+      <c r="Z225"/>
+      <c r="AA225"/>
+      <c r="AB225"/>
+      <c r="AC225"/>
+    </row>
+    <row r="226" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B226" s="8"/>
+      <c r="C226" s="8"/>
+      <c r="D226" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E226" s="23">
+        <v>228000</v>
+      </c>
+      <c r="F226" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G226"/>
+      <c r="H226"/>
+      <c r="I226"/>
+      <c r="J226"/>
+      <c r="K226"/>
+      <c r="L226"/>
+      <c r="M226"/>
+      <c r="N226"/>
+      <c r="O226"/>
+      <c r="P226"/>
+      <c r="Q226"/>
+      <c r="R226"/>
+      <c r="S226"/>
+      <c r="T226"/>
+      <c r="U226"/>
+      <c r="V226"/>
+      <c r="W226"/>
+      <c r="X226"/>
+      <c r="Y226"/>
+      <c r="Z226"/>
+      <c r="AA226"/>
+      <c r="AB226"/>
+      <c r="AC226"/>
+    </row>
+    <row r="227" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E227" s="23">
+        <v>248000</v>
+      </c>
+      <c r="F227" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G227"/>
+      <c r="H227"/>
+      <c r="I227"/>
+      <c r="J227"/>
+      <c r="K227"/>
+      <c r="L227"/>
+      <c r="M227"/>
+      <c r="N227"/>
+      <c r="O227"/>
+      <c r="P227"/>
+      <c r="Q227"/>
+      <c r="R227"/>
+      <c r="S227"/>
+      <c r="T227"/>
+      <c r="U227"/>
+      <c r="V227"/>
+      <c r="W227"/>
+      <c r="X227"/>
+      <c r="Y227"/>
+      <c r="Z227"/>
+      <c r="AA227"/>
+      <c r="AB227"/>
+      <c r="AC227"/>
+    </row>
+    <row r="228" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E228" s="23">
+        <v>278000</v>
+      </c>
+      <c r="F228" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G228"/>
+      <c r="H228"/>
+      <c r="I228"/>
+      <c r="J228"/>
+      <c r="K228"/>
+      <c r="L228"/>
+      <c r="M228"/>
+      <c r="N228"/>
+      <c r="O228"/>
+      <c r="P228"/>
+      <c r="Q228"/>
+      <c r="R228"/>
+      <c r="S228"/>
+      <c r="T228"/>
+      <c r="U228"/>
+      <c r="V228"/>
+      <c r="W228"/>
+      <c r="X228"/>
+      <c r="Y228"/>
+      <c r="Z228"/>
+      <c r="AA228"/>
+      <c r="AB228"/>
+      <c r="AC228"/>
+    </row>
+    <row r="229" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B229" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C229" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D229" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E229" s="25">
+        <v>32680000</v>
+      </c>
+      <c r="F229" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G229"/>
+      <c r="H229"/>
+      <c r="I229"/>
+      <c r="J229"/>
+      <c r="K229"/>
+      <c r="L229"/>
+      <c r="M229"/>
+      <c r="N229"/>
+      <c r="O229"/>
+      <c r="P229"/>
+      <c r="Q229"/>
+      <c r="R229"/>
+      <c r="S229"/>
+      <c r="T229"/>
+      <c r="U229"/>
+      <c r="V229"/>
+      <c r="W229"/>
+      <c r="X229"/>
+      <c r="Y229"/>
+      <c r="Z229"/>
+      <c r="AA229"/>
+      <c r="AB229"/>
+      <c r="AC229"/>
+    </row>
+    <row r="230" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B230" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C230" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D230" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E230" s="25">
+        <v>36800000</v>
+      </c>
+      <c r="F230" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G230"/>
+      <c r="H230"/>
+      <c r="I230"/>
+      <c r="J230"/>
+      <c r="K230"/>
+      <c r="L230"/>
+      <c r="M230"/>
+      <c r="N230"/>
+      <c r="O230"/>
+      <c r="P230"/>
+      <c r="Q230"/>
+      <c r="R230"/>
+      <c r="S230"/>
+      <c r="T230"/>
+      <c r="U230"/>
+      <c r="V230"/>
+      <c r="W230"/>
+      <c r="X230"/>
+      <c r="Y230"/>
+      <c r="Z230"/>
+      <c r="AA230"/>
+      <c r="AB230"/>
+      <c r="AC230"/>
+    </row>
+    <row r="231" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B231" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C231" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D231" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E231" s="25">
+        <v>43680000</v>
+      </c>
+      <c r="F231" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G231"/>
+      <c r="H231"/>
+      <c r="I231"/>
+      <c r="J231"/>
+      <c r="K231"/>
+      <c r="L231"/>
+      <c r="M231"/>
+      <c r="N231"/>
+      <c r="O231"/>
+      <c r="P231"/>
+      <c r="Q231"/>
+      <c r="R231"/>
+      <c r="S231"/>
+      <c r="T231"/>
+      <c r="U231"/>
+      <c r="V231"/>
+      <c r="W231"/>
+      <c r="X231"/>
+      <c r="Y231"/>
+      <c r="Z231"/>
+      <c r="AA231"/>
+      <c r="AB231"/>
+      <c r="AC231"/>
+    </row>
+    <row r="232" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A232" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="B223" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C223" s="16" t="s">
+      <c r="B232" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C232" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D223" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E223" s="25">
+      <c r="D232" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E232" s="25">
         <v>48680000</v>
       </c>
-      <c r="F223" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="224" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A224" s="19" t="s">
+      <c r="F232" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A233" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="B224" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C224" s="16" t="s">
+      <c r="B233" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C233" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D224" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E224" s="25">
+      <c r="D233" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E233" s="25">
         <v>54680000</v>
       </c>
-      <c r="F224" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A225" s="19" t="s">
+      <c r="F233" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A234" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="B225" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C225" s="16" t="s">
+      <c r="B234" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C234" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D225" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E225" s="25">
+      <c r="D234" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E234" s="25">
         <v>69860000</v>
       </c>
-      <c r="F225" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A226" s="19" t="s">
+      <c r="F234" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A235" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B226" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C226" s="16" t="s">
+      <c r="B235" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C235" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D226" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E226" s="25">
+      <c r="D235" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E235" s="25">
         <v>99680000</v>
       </c>
-      <c r="F226" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A227" s="19" t="s">
+      <c r="F235" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A236" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="B227" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C227" s="16" t="s">
+      <c r="B236" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C236" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D227" s="21" t="s">
+      <c r="D236" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E227" s="26">
+      <c r="E236" s="26">
         <v>75000</v>
       </c>
-      <c r="F227" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A228" s="41" t="s">
+      <c r="F236" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A237" s="39" t="s">
         <v>243</v>
       </c>
-      <c r="B228" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C228" s="16" t="s">
+      <c r="B237" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C237" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D228" s="21" t="s">
+      <c r="D237" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E228" s="26">
+      <c r="E237" s="26">
         <v>75000</v>
       </c>
-      <c r="F228" s="17" t="s">
+      <c r="F237" s="17" t="s">
         <v>8</v>
       </c>
     </row>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="258">
   <si>
     <t>Ống D650</t>
   </si>
@@ -195,21 +195,6 @@
     <t>Cút 90 độ D1100</t>
   </si>
   <si>
-    <t>Côn chuyển rẽ nhánh D150 về D100 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D200 về D150 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D200 về D200 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D250 về D200 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D250 về D250 rẽ nhánh D100</t>
-  </si>
-  <si>
     <t>Ống mềm D100</t>
   </si>
   <si>
@@ -608,36 +593,6 @@
   </si>
   <si>
     <t>KHUNG RỌ PHI 150 L=4000</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D300 về D250 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D300 về D300 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D350 về D300 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D350 về D350 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D400 về D350 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D400 về D400 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D450 về D400 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D450 về D450 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D500 về D450 rẽ nhánh D100</t>
-  </si>
-  <si>
-    <t>Côn chuyển rẽ nhánh D500 về D500 rẽ nhánh D100</t>
   </si>
   <si>
     <t>Fan Blowers / Quạt ly tâm gián tiếp SCI-H5-5.5KW
@@ -982,6 +937,66 @@
   </si>
   <si>
     <t>Cút 45 độ D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D150 về D100 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D200 về D150 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D250 về D150 rẽ 1 nhánh D200</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D300 về D250 rẽ 1 nhánh D150</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D350 về D300 rẽ 1 nhánh D150</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D350 rẽ 1 nhánh D150</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D500 về D300 rẽ 1 nhánh D400</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D450 về D400 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D450 về D450 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D350 về D350 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D350 về D300 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D300 về D300 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D300 về D250 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D250 về D250 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D250 về D200 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D200 về D200 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D350 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D400 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D500 về D500 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D500 về D450 rẽ 1 nhánh D100</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1181,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1295,9 +1310,6 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1306,6 +1318,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1590,14 +1608,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC237"/>
+  <dimension ref="A1:AC242"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5703125" style="40" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" style="40" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" style="40" customWidth="1"/>
     <col min="4" max="4" width="15.140625" style="40" customWidth="1"/>
-    <col min="5" max="5" width="14" style="45" customWidth="1"/>
+    <col min="5" max="5" width="14" style="44" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" style="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2241,7 +2259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>43</v>
       </c>
@@ -2261,7 +2279,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>44</v>
       </c>
@@ -2281,7 +2299,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>45</v>
       </c>
@@ -2301,7 +2319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>46</v>
       </c>
@@ -2321,7 +2339,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>47</v>
       </c>
@@ -2341,7 +2359,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>48</v>
       </c>
@@ -2361,7 +2379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>49</v>
       </c>
@@ -2381,7 +2399,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>50</v>
       </c>
@@ -2401,7 +2419,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>51</v>
       </c>
@@ -2421,7 +2439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>52</v>
       </c>
@@ -2441,7 +2459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>53</v>
       </c>
@@ -2461,7 +2479,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>54</v>
       </c>
@@ -2481,7 +2499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>55</v>
       </c>
@@ -2501,9 +2519,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:19" s="48" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" s="47" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>10</v>
@@ -2521,9 +2539,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>56</v>
+        <v>238</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>10</v>
@@ -2540,10 +2558,24 @@
       <c r="F47" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="47"/>
+      <c r="K47" s="47"/>
+      <c r="L47" s="47"/>
+      <c r="M47" s="47"/>
+      <c r="N47" s="47"/>
+      <c r="O47" s="47"/>
+      <c r="P47" s="47"/>
+      <c r="Q47" s="47"/>
+      <c r="R47" s="47"/>
+      <c r="S47" s="47"/>
+      <c r="T47" s="47"/>
+    </row>
+    <row r="48" spans="1:20" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>57</v>
+        <v>239</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>10</v>
@@ -2554,7 +2586,7 @@
       <c r="D48" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="44">
+      <c r="E48" s="49">
         <v>135000</v>
       </c>
       <c r="F48" s="6" t="s">
@@ -2574,9 +2606,9 @@
       <c r="R48"/>
       <c r="S48"/>
     </row>
-    <row r="49" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>58</v>
+        <v>253</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>10</v>
@@ -2594,9 +2626,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>59</v>
+        <v>252</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>10</v>
@@ -2614,9 +2646,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>10</v>
@@ -2634,9 +2666,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:21" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>193</v>
+        <v>250</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>10</v>
@@ -2647,7 +2679,7 @@
       <c r="D52" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E52" s="44">
+      <c r="E52" s="49">
         <v>250500</v>
       </c>
       <c r="F52" s="6" t="s">
@@ -2666,9 +2698,9 @@
       <c r="Q52"/>
       <c r="R52"/>
     </row>
-    <row r="53" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>10</v>
@@ -2679,7 +2711,7 @@
       <c r="D53" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E53" s="44">
+      <c r="E53" s="49">
         <v>244500</v>
       </c>
       <c r="F53" s="6" t="s">
@@ -2698,9 +2730,9 @@
       <c r="Q53"/>
       <c r="R53"/>
     </row>
-    <row r="54" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>10</v>
@@ -2711,7 +2743,7 @@
       <c r="D54" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E54" s="44">
+      <c r="E54" s="49">
         <v>253500</v>
       </c>
       <c r="F54" s="6" t="s">
@@ -2730,9 +2762,9 @@
       <c r="Q54"/>
       <c r="R54"/>
     </row>
-    <row r="55" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>10</v>
@@ -2743,7 +2775,7 @@
       <c r="D55" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E55" s="44">
+      <c r="E55" s="49">
         <v>276000</v>
       </c>
       <c r="F55" s="6" t="s">
@@ -2762,9 +2794,9 @@
       <c r="Q55"/>
       <c r="R55"/>
     </row>
-    <row r="56" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>10</v>
@@ -2775,7 +2807,7 @@
       <c r="D56" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="44">
+      <c r="E56" s="49">
         <v>289500</v>
       </c>
       <c r="F56" s="6" t="s">
@@ -2794,9 +2826,9 @@
       <c r="Q56"/>
       <c r="R56"/>
     </row>
-    <row r="57" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>10</v>
@@ -2807,7 +2839,7 @@
       <c r="D57" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E57" s="44">
+      <c r="E57" s="49">
         <v>306000</v>
       </c>
       <c r="F57" s="6" t="s">
@@ -2826,9 +2858,9 @@
       <c r="Q57"/>
       <c r="R57"/>
     </row>
-    <row r="58" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>10</v>
@@ -2839,7 +2871,7 @@
       <c r="D58" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E58" s="44">
+      <c r="E58" s="49">
         <v>313500</v>
       </c>
       <c r="F58" s="6" t="s">
@@ -2858,9 +2890,9 @@
       <c r="Q58"/>
       <c r="R58"/>
     </row>
-    <row r="59" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>10</v>
@@ -2871,7 +2903,7 @@
       <c r="D59" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E59" s="44">
+      <c r="E59" s="49">
         <v>340500</v>
       </c>
       <c r="F59" s="6" t="s">
@@ -2890,9 +2922,9 @@
       <c r="Q59"/>
       <c r="R59"/>
     </row>
-    <row r="60" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>201</v>
+        <v>257</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>10</v>
@@ -2903,7 +2935,7 @@
       <c r="D60" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E60" s="44">
+      <c r="E60" s="49">
         <v>355500</v>
       </c>
       <c r="F60" s="6" t="s">
@@ -2922,9 +2954,9 @@
       <c r="Q60"/>
       <c r="R60"/>
     </row>
-    <row r="61" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>10</v>
@@ -2935,7 +2967,7 @@
       <c r="D61" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E61" s="44">
+      <c r="E61" s="49">
         <v>370500</v>
       </c>
       <c r="F61" s="6" t="s">
@@ -2954,124 +2986,165 @@
       <c r="Q61"/>
       <c r="R61"/>
     </row>
-    <row r="62" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="22">
+    <row r="62" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="48">
+        <v>369000</v>
+      </c>
+      <c r="F62" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="47"/>
+      <c r="H62" s="47"/>
+      <c r="I62" s="47"/>
+      <c r="J62" s="47"/>
+      <c r="K62" s="47"/>
+      <c r="L62" s="47"/>
+      <c r="M62" s="47"/>
+      <c r="N62" s="47"/>
+      <c r="O62" s="47"/>
+      <c r="P62" s="47"/>
+      <c r="Q62" s="47"/>
+      <c r="R62" s="47"/>
+      <c r="S62" s="47"/>
+      <c r="T62" s="47"/>
+    </row>
+    <row r="63" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="48">
+        <v>416000</v>
+      </c>
+      <c r="F63" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+      <c r="K63"/>
+      <c r="L63"/>
+      <c r="M63"/>
+      <c r="N63"/>
+      <c r="O63"/>
+      <c r="P63"/>
+      <c r="Q63"/>
+      <c r="R63"/>
+      <c r="S63"/>
+      <c r="T63"/>
+    </row>
+    <row r="64" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="48">
+        <v>420000</v>
+      </c>
+      <c r="F64" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64" s="47"/>
+      <c r="H64" s="47"/>
+      <c r="I64" s="47"/>
+      <c r="J64" s="47"/>
+      <c r="K64" s="47"/>
+      <c r="L64" s="47"/>
+      <c r="M64" s="47"/>
+      <c r="N64" s="47"/>
+      <c r="O64" s="47"/>
+      <c r="P64" s="47"/>
+      <c r="Q64" s="47"/>
+      <c r="R64" s="47"/>
+      <c r="S64" s="47"/>
+      <c r="T64" s="47"/>
+    </row>
+    <row r="65" spans="1:21" s="31" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="48">
+        <v>366000</v>
+      </c>
+      <c r="F65" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="P65"/>
+      <c r="Q65"/>
+      <c r="R65"/>
+      <c r="S65"/>
+      <c r="T65"/>
+    </row>
+    <row r="66" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="22">
         <v>442500</v>
       </c>
-      <c r="F62" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="22">
-        <v>447000</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="47">
-        <v>450000</v>
-      </c>
-      <c r="F64" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64"/>
-      <c r="M64"/>
-      <c r="N64"/>
-      <c r="O64"/>
-      <c r="P64"/>
-      <c r="Q64"/>
-      <c r="R64"/>
-      <c r="S64"/>
-      <c r="T64"/>
-      <c r="U64"/>
-    </row>
-    <row r="65" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="22">
-        <v>470000</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A66" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="33">
-        <v>447000</v>
-      </c>
-      <c r="F66" s="17" t="s">
+      <c r="F66" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>10</v>
@@ -3083,35 +3156,50 @@
         <v>35</v>
       </c>
       <c r="E67" s="22">
-        <v>528000</v>
+        <v>447000</v>
       </c>
       <c r="F67" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="B68" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="33">
-        <v>508500</v>
-      </c>
-      <c r="F68" s="17" t="s">
-        <v>8</v>
-      </c>
+    <row r="68" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="46">
+        <v>450000</v>
+      </c>
+      <c r="F68" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G68"/>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68"/>
+      <c r="M68"/>
+      <c r="N68"/>
+      <c r="O68"/>
+      <c r="P68"/>
+      <c r="Q68"/>
+      <c r="R68"/>
+      <c r="S68"/>
+      <c r="T68"/>
+      <c r="U68"/>
     </row>
     <row r="69" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>10</v>
@@ -3123,7 +3211,7 @@
         <v>35</v>
       </c>
       <c r="E69" s="22">
-        <v>560000</v>
+        <v>470000</v>
       </c>
       <c r="F69" s="13" t="s">
         <v>8</v>
@@ -3131,7 +3219,7 @@
     </row>
     <row r="70" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A70" s="27" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B70" s="20" t="s">
         <v>10</v>
@@ -3143,7 +3231,7 @@
         <v>35</v>
       </c>
       <c r="E70" s="33">
-        <v>682500</v>
+        <v>447000</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>8</v>
@@ -3151,7 +3239,7 @@
     </row>
     <row r="71" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>10</v>
@@ -3163,85 +3251,55 @@
         <v>35</v>
       </c>
       <c r="E71" s="22">
-        <v>666000</v>
+        <v>528000</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="47">
-        <v>1125000</v>
-      </c>
-      <c r="F72" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72"/>
-      <c r="M72"/>
-      <c r="N72"/>
-      <c r="O72"/>
-      <c r="P72"/>
-      <c r="Q72"/>
-      <c r="R72"/>
-      <c r="S72"/>
-      <c r="T72"/>
-      <c r="U72"/>
-    </row>
-    <row r="73" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="47">
-        <v>1150000</v>
-      </c>
-      <c r="F73" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="G73"/>
-      <c r="H73"/>
-      <c r="I73"/>
-      <c r="J73"/>
-      <c r="K73"/>
-      <c r="L73"/>
-      <c r="M73"/>
-      <c r="N73"/>
-      <c r="O73"/>
-      <c r="P73"/>
-      <c r="Q73"/>
-      <c r="R73"/>
-      <c r="S73"/>
-      <c r="T73"/>
-      <c r="U73"/>
+    <row r="72" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="33">
+        <v>508500</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="22">
+        <v>560000</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="74" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A74" s="27" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B74" s="20" t="s">
         <v>10</v>
@@ -3253,50 +3311,35 @@
         <v>35</v>
       </c>
       <c r="E74" s="33">
-        <v>957000</v>
+        <v>682500</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="47">
-        <v>750000</v>
-      </c>
-      <c r="F75" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="G75"/>
-      <c r="H75"/>
-      <c r="I75"/>
-      <c r="J75"/>
-      <c r="K75"/>
-      <c r="L75"/>
-      <c r="M75"/>
-      <c r="N75"/>
-      <c r="O75"/>
-      <c r="P75"/>
-      <c r="Q75"/>
-      <c r="R75"/>
-      <c r="S75"/>
-      <c r="T75"/>
-      <c r="U75"/>
+    <row r="75" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="22">
+        <v>666000</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="76" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>10</v>
@@ -3307,10 +3350,10 @@
       <c r="D76" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="47">
-        <v>1550000</v>
-      </c>
-      <c r="F76" s="46" t="s">
+      <c r="E76" s="46">
+        <v>1125000</v>
+      </c>
+      <c r="F76" s="45" t="s">
         <v>8</v>
       </c>
       <c r="G76"/>
@@ -3331,7 +3374,7 @@
     </row>
     <row r="77" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>10</v>
@@ -3342,10 +3385,10 @@
       <c r="D77" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E77" s="47">
-        <v>1650000</v>
-      </c>
-      <c r="F77" s="46" t="s">
+      <c r="E77" s="46">
+        <v>1150000</v>
+      </c>
+      <c r="F77" s="45" t="s">
         <v>8</v>
       </c>
       <c r="G77"/>
@@ -3364,44 +3407,29 @@
       <c r="T77"/>
       <c r="U77"/>
     </row>
-    <row r="78" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="47">
-        <v>1700000</v>
-      </c>
-      <c r="F78" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-      <c r="J78"/>
-      <c r="K78"/>
-      <c r="L78"/>
-      <c r="M78"/>
-      <c r="N78"/>
-      <c r="O78"/>
-      <c r="P78"/>
-      <c r="Q78"/>
-      <c r="R78"/>
-      <c r="S78"/>
-      <c r="T78"/>
-      <c r="U78"/>
+    <row r="78" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="33">
+        <v>957000</v>
+      </c>
+      <c r="F78" s="17" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="79" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>10</v>
@@ -3412,10 +3440,10 @@
       <c r="D79" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E79" s="47">
-        <v>1800000</v>
-      </c>
-      <c r="F79" s="46" t="s">
+      <c r="E79" s="46">
+        <v>750000</v>
+      </c>
+      <c r="F79" s="45" t="s">
         <v>8</v>
       </c>
       <c r="G79"/>
@@ -3436,7 +3464,7 @@
     </row>
     <row r="80" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>10</v>
@@ -3447,10 +3475,10 @@
       <c r="D80" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E80" s="47">
-        <v>1850000</v>
-      </c>
-      <c r="F80" s="46" t="s">
+      <c r="E80" s="46">
+        <v>1550000</v>
+      </c>
+      <c r="F80" s="45" t="s">
         <v>8</v>
       </c>
       <c r="G80"/>
@@ -3469,223 +3497,317 @@
       <c r="T80"/>
       <c r="U80"/>
     </row>
-    <row r="81" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="22">
+    <row r="81" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="46">
+        <v>1650000</v>
+      </c>
+      <c r="F81" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
+      <c r="N81"/>
+      <c r="O81"/>
+      <c r="P81"/>
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="S81"/>
+      <c r="T81"/>
+      <c r="U81"/>
+    </row>
+    <row r="82" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="46">
+        <v>1700000</v>
+      </c>
+      <c r="F82" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
+      <c r="L82"/>
+      <c r="M82"/>
+      <c r="N82"/>
+      <c r="O82"/>
+      <c r="P82"/>
+      <c r="Q82"/>
+      <c r="R82"/>
+      <c r="S82"/>
+      <c r="T82"/>
+      <c r="U82"/>
+    </row>
+    <row r="83" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="46">
+        <v>1800000</v>
+      </c>
+      <c r="F83" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="I83"/>
+      <c r="J83"/>
+      <c r="K83"/>
+      <c r="L83"/>
+      <c r="M83"/>
+      <c r="N83"/>
+      <c r="O83"/>
+      <c r="P83"/>
+      <c r="Q83"/>
+      <c r="R83"/>
+      <c r="S83"/>
+      <c r="T83"/>
+      <c r="U83"/>
+    </row>
+    <row r="84" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="46">
+        <v>1850000</v>
+      </c>
+      <c r="F84" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G84"/>
+      <c r="H84"/>
+      <c r="I84"/>
+      <c r="J84"/>
+      <c r="K84"/>
+      <c r="L84"/>
+      <c r="M84"/>
+      <c r="N84"/>
+      <c r="O84"/>
+      <c r="P84"/>
+      <c r="Q84"/>
+      <c r="R84"/>
+      <c r="S84"/>
+      <c r="T84"/>
+      <c r="U84"/>
+    </row>
+    <row r="85" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="48">
+        <v>1200000</v>
+      </c>
+      <c r="F85" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G85"/>
+      <c r="H85"/>
+      <c r="I85"/>
+      <c r="J85"/>
+      <c r="K85"/>
+      <c r="L85"/>
+      <c r="M85"/>
+      <c r="N85"/>
+      <c r="O85"/>
+      <c r="P85"/>
+      <c r="Q85"/>
+      <c r="R85"/>
+      <c r="S85"/>
+      <c r="T85"/>
+    </row>
+    <row r="86" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A86" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="22">
         <v>3120000</v>
       </c>
-      <c r="F81" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A82" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="22">
+      <c r="F86" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="22">
         <v>2860000</v>
       </c>
-      <c r="F82" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A83" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="22">
+      <c r="F87" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="22">
         <v>2100000</v>
       </c>
-      <c r="F83" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="B84" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" s="33">
+      <c r="F88" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="B89" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="33">
         <v>3255000</v>
       </c>
-      <c r="F84" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E85" s="23">
-        <v>160000</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" s="23">
-        <v>220000</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="23">
-        <v>280000</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="23">
-        <v>550000</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="23">
-        <v>900000</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="F89" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B90" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C90" s="6"/>
       <c r="D90" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E90" s="23">
-        <v>1050000</v>
+        <v>160000</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B91" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C91" s="6"/>
       <c r="D91" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E91" s="23">
-        <v>1450000</v>
+        <v>220000</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B92" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C92" s="6"/>
       <c r="D92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E92" s="23">
-        <v>1780000</v>
+        <v>280000</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -3693,15 +3815,15 @@
         <v>35</v>
       </c>
       <c r="E93" s="23">
-        <v>2000000</v>
+        <v>550000</v>
       </c>
       <c r="F93" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -3709,15 +3831,15 @@
         <v>35</v>
       </c>
       <c r="E94" s="23">
-        <v>2500000</v>
+        <v>900000</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -3725,15 +3847,15 @@
         <v>35</v>
       </c>
       <c r="E95" s="23">
-        <v>2800000</v>
+        <v>1050000</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -3741,7 +3863,7 @@
         <v>35</v>
       </c>
       <c r="E96" s="23">
-        <v>3300000</v>
+        <v>1450000</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>8</v>
@@ -3749,7 +3871,7 @@
     </row>
     <row r="97" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -3757,7 +3879,7 @@
         <v>35</v>
       </c>
       <c r="E97" s="23">
-        <v>3800000</v>
+        <v>1780000</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>8</v>
@@ -3765,7 +3887,7 @@
     </row>
     <row r="98" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -3773,7 +3895,7 @@
         <v>35</v>
       </c>
       <c r="E98" s="23">
-        <v>4500000</v>
+        <v>2000000</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>8</v>
@@ -3781,7 +3903,7 @@
     </row>
     <row r="99" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -3789,7 +3911,7 @@
         <v>35</v>
       </c>
       <c r="E99" s="23">
-        <v>4800000</v>
+        <v>2500000</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>8</v>
@@ -3797,7 +3919,7 @@
     </row>
     <row r="100" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -3805,7 +3927,7 @@
         <v>35</v>
       </c>
       <c r="E100" s="23">
-        <v>5200000</v>
+        <v>2800000</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>8</v>
@@ -3813,7 +3935,7 @@
     </row>
     <row r="101" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -3821,7 +3943,7 @@
         <v>35</v>
       </c>
       <c r="E101" s="23">
-        <v>5600000</v>
+        <v>3300000</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>8</v>
@@ -3829,7 +3951,7 @@
     </row>
     <row r="102" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -3837,7 +3959,7 @@
         <v>35</v>
       </c>
       <c r="E102" s="23">
-        <v>6500000</v>
+        <v>3800000</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>8</v>
@@ -3845,7 +3967,7 @@
     </row>
     <row r="103" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -3853,7 +3975,7 @@
         <v>35</v>
       </c>
       <c r="E103" s="23">
-        <v>7200000</v>
+        <v>4500000</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>8</v>
@@ -3861,7 +3983,7 @@
     </row>
     <row r="104" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -3869,7 +3991,7 @@
         <v>35</v>
       </c>
       <c r="E104" s="23">
-        <v>7600000</v>
+        <v>4800000</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>8</v>
@@ -3877,7 +3999,7 @@
     </row>
     <row r="105" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -3885,7 +4007,7 @@
         <v>35</v>
       </c>
       <c r="E105" s="23">
-        <v>8000000</v>
+        <v>5200000</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>8</v>
@@ -3893,7 +4015,7 @@
     </row>
     <row r="106" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -3901,7 +4023,7 @@
         <v>35</v>
       </c>
       <c r="E106" s="23">
-        <v>8900000</v>
+        <v>5600000</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>8</v>
@@ -3909,7 +4031,7 @@
     </row>
     <row r="107" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -3917,7 +4039,7 @@
         <v>35</v>
       </c>
       <c r="E107" s="23">
-        <v>9600000</v>
+        <v>6500000</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>8</v>
@@ -3925,7 +4047,7 @@
     </row>
     <row r="108" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -3933,7 +4055,7 @@
         <v>35</v>
       </c>
       <c r="E108" s="23">
-        <v>10680000</v>
+        <v>7200000</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>8</v>
@@ -3941,7 +4063,7 @@
     </row>
     <row r="109" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -3949,7 +4071,7 @@
         <v>35</v>
       </c>
       <c r="E109" s="23">
-        <v>11680000</v>
+        <v>7600000</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>8</v>
@@ -3957,7 +4079,7 @@
     </row>
     <row r="110" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -3965,107 +4087,87 @@
         <v>35</v>
       </c>
       <c r="E110" s="23">
+        <v>8000000</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A111" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="23">
+        <v>8900000</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A112" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="23">
+        <v>9600000</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A113" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="23">
+        <v>10680000</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A114" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B114" s="6"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="23">
+        <v>11680000</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="23">
         <v>12500000</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B111" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C111" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E111" s="23">
-        <v>240000</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B112" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C112" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E112" s="23">
-        <v>320000</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B113" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E113" s="23">
-        <v>420000</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B114" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E114" s="23">
-        <v>500000</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B115" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C115" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E115" s="23">
-        <v>620000</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>8</v>
@@ -4073,19 +4175,19 @@
     </row>
     <row r="116" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B116" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C116" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E116" s="23">
-        <v>660000</v>
+        <v>240000</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>8</v>
@@ -4093,19 +4195,19 @@
     </row>
     <row r="117" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B117" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C117" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E117" s="23">
-        <v>840000</v>
+        <v>320000</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>8</v>
@@ -4113,19 +4215,19 @@
     </row>
     <row r="118" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B118" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C118" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E118" s="23">
-        <v>890000</v>
+        <v>420000</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>8</v>
@@ -4133,19 +4235,19 @@
     </row>
     <row r="119" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B119" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C119" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E119" s="23">
-        <v>1980000</v>
+        <v>500000</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>8</v>
@@ -4153,19 +4255,19 @@
     </row>
     <row r="120" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B120" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C120" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E120" s="23">
-        <v>2100000</v>
+        <v>620000</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>8</v>
@@ -4173,19 +4275,19 @@
     </row>
     <row r="121" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B121" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C121" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E121" s="23">
-        <v>2250000</v>
+        <v>660000</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>8</v>
@@ -4193,19 +4295,19 @@
     </row>
     <row r="122" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B122" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C122" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E122" s="23">
-        <v>2490000</v>
+        <v>840000</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>8</v>
@@ -4213,19 +4315,19 @@
     </row>
     <row r="123" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B123" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C123" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E123" s="23">
-        <v>2640000</v>
+        <v>890000</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>8</v>
@@ -4233,19 +4335,19 @@
     </row>
     <row r="124" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B124" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C124" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E124" s="23">
-        <v>2850000</v>
+        <v>1980000</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>8</v>
@@ -4253,19 +4355,19 @@
     </row>
     <row r="125" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B125" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C125" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E125" s="23">
-        <v>3090000</v>
+        <v>2100000</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>8</v>
@@ -4273,19 +4375,19 @@
     </row>
     <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B126" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C126" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E126" s="23">
-        <v>3450000</v>
+        <v>2250000</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>8</v>
@@ -4293,19 +4395,19 @@
     </row>
     <row r="127" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B127" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C127" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E127" s="23">
-        <v>7600000</v>
+        <v>2490000</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>8</v>
@@ -4313,19 +4415,19 @@
     </row>
     <row r="128" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B128" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C128" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E128" s="23">
-        <v>8000000</v>
+        <v>2640000</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>8</v>
@@ -4333,19 +4435,19 @@
     </row>
     <row r="129" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B129" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C129" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E129" s="23">
-        <v>8900000</v>
+        <v>2850000</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>8</v>
@@ -4353,19 +4455,19 @@
     </row>
     <row r="130" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B130" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C130" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E130" s="23">
-        <v>9600000</v>
+        <v>3090000</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>8</v>
@@ -4373,19 +4475,19 @@
     </row>
     <row r="131" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B131" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C131" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E131" s="23">
-        <v>10680000</v>
+        <v>3450000</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>8</v>
@@ -4393,19 +4495,19 @@
     </row>
     <row r="132" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B132" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C132" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E132" s="23">
-        <v>11680000</v>
+        <v>7600000</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>8</v>
@@ -4413,99 +4515,119 @@
     </row>
     <row r="133" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B133" s="34" t="s">
         <v>9</v>
       </c>
       <c r="C133" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E133" s="23">
+        <v>8000000</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A134" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B134" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="23">
+        <v>8900000</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A135" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B135" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="23">
+        <v>9600000</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A136" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B136" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" s="23">
+        <v>10680000</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A137" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B137" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" s="23">
+        <v>11680000</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A138" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B138" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" s="23">
         <v>13680000</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E134" s="23">
-        <v>800000</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A135" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E135" s="23">
-        <v>1000000</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E136" s="23">
-        <v>1008000</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E137" s="23">
-        <v>1200000</v>
-      </c>
-      <c r="F137" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E138" s="23">
-        <v>1488000</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>8</v>
@@ -4513,7 +4635,7 @@
     </row>
     <row r="139" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
@@ -4521,7 +4643,7 @@
         <v>35</v>
       </c>
       <c r="E139" s="23">
-        <v>1584000</v>
+        <v>800000</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>8</v>
@@ -4529,7 +4651,7 @@
     </row>
     <row r="140" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
@@ -4537,7 +4659,7 @@
         <v>35</v>
       </c>
       <c r="E140" s="23">
-        <v>2016000</v>
+        <v>1000000</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>8</v>
@@ -4545,7 +4667,7 @@
     </row>
     <row r="141" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
@@ -4553,7 +4675,7 @@
         <v>35</v>
       </c>
       <c r="E141" s="23">
-        <v>2136000</v>
+        <v>1008000</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>8</v>
@@ -4561,7 +4683,7 @@
     </row>
     <row r="142" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
@@ -4569,7 +4691,7 @@
         <v>35</v>
       </c>
       <c r="E142" s="23">
-        <v>3000000</v>
+        <v>1200000</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>8</v>
@@ -4577,7 +4699,7 @@
     </row>
     <row r="143" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
@@ -4585,7 +4707,7 @@
         <v>35</v>
       </c>
       <c r="E143" s="23">
-        <v>3780000</v>
+        <v>1488000</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>8</v>
@@ -4593,7 +4715,7 @@
     </row>
     <row r="144" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
@@ -4601,7 +4723,7 @@
         <v>35</v>
       </c>
       <c r="E144" s="23">
-        <v>4050000</v>
+        <v>1584000</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>8</v>
@@ -4609,7 +4731,7 @@
     </row>
     <row r="145" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
@@ -4617,7 +4739,7 @@
         <v>35</v>
       </c>
       <c r="E145" s="23">
-        <v>4482000</v>
+        <v>2016000</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>8</v>
@@ -4625,7 +4747,7 @@
     </row>
     <row r="146" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
@@ -4633,7 +4755,7 @@
         <v>35</v>
       </c>
       <c r="E146" s="23">
-        <v>4752000</v>
+        <v>2136000</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>8</v>
@@ -4641,7 +4763,7 @@
     </row>
     <row r="147" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -4649,7 +4771,7 @@
         <v>35</v>
       </c>
       <c r="E147" s="23">
-        <v>5130000</v>
+        <v>3000000</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>8</v>
@@ -4657,7 +4779,7 @@
     </row>
     <row r="148" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -4665,7 +4787,7 @@
         <v>35</v>
       </c>
       <c r="E148" s="23">
-        <v>5562000</v>
+        <v>3780000</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>8</v>
@@ -4673,7 +4795,7 @@
     </row>
     <row r="149" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -4681,7 +4803,7 @@
         <v>35</v>
       </c>
       <c r="E149" s="23">
-        <v>6210000</v>
+        <v>4050000</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>8</v>
@@ -4689,7 +4811,7 @@
     </row>
     <row r="150" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -4697,7 +4819,7 @@
         <v>35</v>
       </c>
       <c r="E150" s="23">
-        <v>13680000</v>
+        <v>4482000</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>8</v>
@@ -4705,7 +4827,7 @@
     </row>
     <row r="151" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -4713,7 +4835,7 @@
         <v>35</v>
       </c>
       <c r="E151" s="23">
-        <v>14400000</v>
+        <v>4752000</v>
       </c>
       <c r="F151" s="6" t="s">
         <v>8</v>
@@ -4721,7 +4843,7 @@
     </row>
     <row r="152" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -4729,7 +4851,7 @@
         <v>35</v>
       </c>
       <c r="E152" s="23">
-        <v>16020000</v>
+        <v>5130000</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>8</v>
@@ -4737,7 +4859,7 @@
     </row>
     <row r="153" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -4745,7 +4867,7 @@
         <v>35</v>
       </c>
       <c r="E153" s="23">
-        <v>17280000</v>
+        <v>5562000</v>
       </c>
       <c r="F153" s="6" t="s">
         <v>8</v>
@@ -4753,7 +4875,7 @@
     </row>
     <row r="154" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -4761,7 +4883,7 @@
         <v>35</v>
       </c>
       <c r="E154" s="23">
-        <v>19224000</v>
+        <v>6210000</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>8</v>
@@ -4769,7 +4891,7 @@
     </row>
     <row r="155" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -4777,7 +4899,7 @@
         <v>35</v>
       </c>
       <c r="E155" s="23">
-        <v>21024000</v>
+        <v>13680000</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>8</v>
@@ -4785,7 +4907,7 @@
     </row>
     <row r="156" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -4793,107 +4915,87 @@
         <v>35</v>
       </c>
       <c r="E156" s="23">
+        <v>14400000</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A157" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B157" s="6"/>
+      <c r="C157" s="6"/>
+      <c r="D157" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="23">
+        <v>16020000</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A158" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B158" s="6"/>
+      <c r="C158" s="6"/>
+      <c r="D158" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="23">
+        <v>17280000</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A159" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B159" s="6"/>
+      <c r="C159" s="6"/>
+      <c r="D159" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" s="23">
+        <v>19224000</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A160" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B160" s="6"/>
+      <c r="C160" s="6"/>
+      <c r="D160" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E160" s="23">
+        <v>21024000</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A161" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B161" s="6"/>
+      <c r="C161" s="6"/>
+      <c r="D161" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" s="23">
         <v>24624000</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A157" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C157" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E157" s="23">
-        <v>15000</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A158" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E158" s="23">
-        <v>19500</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A159" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C159" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E159" s="23">
-        <v>25000</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A160" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C160" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E160" s="23">
-        <v>30000</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A161" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C161" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E161" s="23">
-        <v>40000</v>
       </c>
       <c r="F161" s="6" t="s">
         <v>8</v>
@@ -4901,19 +5003,19 @@
     </row>
     <row r="162" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C162" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E162" s="23">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>8</v>
@@ -4921,19 +5023,19 @@
     </row>
     <row r="163" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C163" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E163" s="23">
-        <v>78000</v>
+        <v>19500</v>
       </c>
       <c r="F163" s="6" t="s">
         <v>8</v>
@@ -4941,19 +5043,19 @@
     </row>
     <row r="164" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C164" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E164" s="23">
-        <v>87000</v>
+        <v>25000</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>8</v>
@@ -4961,19 +5063,19 @@
     </row>
     <row r="165" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C165" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E165" s="23">
-        <v>96000</v>
+        <v>30000</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>8</v>
@@ -4981,19 +5083,19 @@
     </row>
     <row r="166" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E166" s="23">
-        <v>105000</v>
+        <v>40000</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>8</v>
@@ -5001,19 +5103,19 @@
     </row>
     <row r="167" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C167" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D167" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E167" s="23">
-        <v>114000</v>
+        <v>45000</v>
       </c>
       <c r="F167" s="6" t="s">
         <v>8</v>
@@ -5021,19 +5123,19 @@
     </row>
     <row r="168" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C168" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E168" s="23">
-        <v>142500</v>
+        <v>78000</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>8</v>
@@ -5041,19 +5143,19 @@
     </row>
     <row r="169" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C169" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E169" s="23">
-        <v>153000</v>
+        <v>87000</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>8</v>
@@ -5061,19 +5163,19 @@
     </row>
     <row r="170" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C170" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E170" s="23">
-        <v>163500</v>
+        <v>96000</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>8</v>
@@ -5081,19 +5183,19 @@
     </row>
     <row r="171" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C171" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D171" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E171" s="23">
-        <v>232500</v>
+        <v>105000</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>8</v>
@@ -5101,19 +5203,19 @@
     </row>
     <row r="172" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E172" s="23">
-        <v>247500</v>
+        <v>114000</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>8</v>
@@ -5121,19 +5223,19 @@
     </row>
     <row r="173" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C173" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E173" s="23">
-        <v>295500</v>
+        <v>142500</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>8</v>
@@ -5141,19 +5243,19 @@
     </row>
     <row r="174" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C174" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D174" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E174" s="23">
-        <v>312000</v>
+        <v>153000</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>8</v>
@@ -5161,19 +5263,19 @@
     </row>
     <row r="175" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C175" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E175" s="23">
-        <v>410000</v>
+        <v>163500</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>8</v>
@@ -5181,19 +5283,19 @@
     </row>
     <row r="176" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C176" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E176" s="23">
-        <v>434000</v>
+        <v>232500</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>8</v>
@@ -5201,254 +5303,139 @@
     </row>
     <row r="177" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C177" s="35" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E177" s="23">
+        <v>247500</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A178" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C178" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" s="23">
+        <v>295500</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A179" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E179" s="23">
+        <v>312000</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A180" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C180" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E180" s="23">
+        <v>410000</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A181" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C181" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181" s="23">
+        <v>434000</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A182" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E182" s="23">
         <v>469500</v>
       </c>
-      <c r="F177" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="178" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B178" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C178" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D178" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E178" s="23">
+      <c r="F182" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E183" s="23">
         <v>19860000</v>
-      </c>
-      <c r="F178" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G178" s="28"/>
-      <c r="H178" s="28"/>
-      <c r="I178" s="28"/>
-      <c r="J178" s="28"/>
-      <c r="K178" s="28"/>
-      <c r="L178" s="28"/>
-      <c r="M178" s="28"/>
-      <c r="N178" s="28"/>
-      <c r="O178" s="28"/>
-      <c r="P178" s="28"/>
-      <c r="Q178" s="28"/>
-      <c r="R178" s="28"/>
-      <c r="S178" s="28"/>
-      <c r="T178" s="28"/>
-      <c r="U178" s="28"/>
-      <c r="V178" s="28"/>
-      <c r="W178" s="28"/>
-      <c r="X178" s="28"/>
-      <c r="Y178" s="28"/>
-      <c r="Z178" s="28"/>
-      <c r="AA178" s="28"/>
-      <c r="AB178" s="28"/>
-      <c r="AC178" s="28"/>
-    </row>
-    <row r="179" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B179" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C179" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D179" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E179" s="23">
-        <v>24980000</v>
-      </c>
-      <c r="F179" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G179" s="28"/>
-      <c r="H179" s="28"/>
-      <c r="I179" s="28"/>
-      <c r="J179" s="28"/>
-      <c r="K179" s="28"/>
-      <c r="L179" s="28"/>
-      <c r="M179" s="28"/>
-      <c r="N179" s="28"/>
-      <c r="O179" s="28"/>
-      <c r="P179" s="28"/>
-      <c r="Q179" s="28"/>
-      <c r="R179" s="28"/>
-      <c r="S179" s="28"/>
-      <c r="T179" s="28"/>
-      <c r="U179" s="28"/>
-      <c r="V179" s="28"/>
-      <c r="W179" s="28"/>
-      <c r="X179" s="28"/>
-      <c r="Y179" s="28"/>
-      <c r="Z179" s="28"/>
-      <c r="AA179" s="28"/>
-      <c r="AB179" s="28"/>
-      <c r="AC179" s="28"/>
-    </row>
-    <row r="180" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B180" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C180" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D180" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E180" s="23">
-        <v>35680000</v>
-      </c>
-      <c r="F180" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G180" s="28"/>
-      <c r="H180" s="28"/>
-      <c r="I180" s="28"/>
-      <c r="J180" s="28"/>
-      <c r="K180" s="28"/>
-      <c r="L180" s="28"/>
-      <c r="M180" s="28"/>
-      <c r="N180" s="28"/>
-      <c r="O180" s="28"/>
-      <c r="P180" s="28"/>
-      <c r="Q180" s="28"/>
-      <c r="R180" s="28"/>
-      <c r="S180" s="28"/>
-      <c r="T180" s="28"/>
-      <c r="U180" s="28"/>
-      <c r="V180" s="28"/>
-      <c r="W180" s="28"/>
-      <c r="X180" s="28"/>
-      <c r="Y180" s="28"/>
-      <c r="Z180" s="28"/>
-      <c r="AA180" s="28"/>
-      <c r="AB180" s="28"/>
-      <c r="AC180" s="28"/>
-    </row>
-    <row r="181" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B181" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C181" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D181" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E181" s="23">
-        <v>39860000</v>
-      </c>
-      <c r="F181" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G181" s="28"/>
-      <c r="H181" s="28"/>
-      <c r="I181" s="28"/>
-      <c r="J181" s="28"/>
-      <c r="K181" s="28"/>
-      <c r="L181" s="28"/>
-      <c r="M181" s="28"/>
-      <c r="N181" s="28"/>
-      <c r="O181" s="28"/>
-      <c r="P181" s="28"/>
-      <c r="Q181" s="28"/>
-      <c r="R181" s="28"/>
-      <c r="S181" s="28"/>
-      <c r="T181" s="28"/>
-      <c r="U181" s="28"/>
-      <c r="V181" s="28"/>
-      <c r="W181" s="28"/>
-      <c r="X181" s="28"/>
-      <c r="Y181" s="28"/>
-      <c r="Z181" s="28"/>
-      <c r="AA181" s="28"/>
-      <c r="AB181" s="28"/>
-      <c r="AC181" s="28"/>
-    </row>
-    <row r="182" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C182" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D182" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E182" s="23">
-        <v>47979000</v>
-      </c>
-      <c r="F182" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G182"/>
-      <c r="H182"/>
-      <c r="I182"/>
-      <c r="J182"/>
-      <c r="K182"/>
-      <c r="L182"/>
-      <c r="M182"/>
-      <c r="N182"/>
-      <c r="O182"/>
-      <c r="P182"/>
-      <c r="Q182"/>
-      <c r="R182"/>
-      <c r="S182"/>
-      <c r="T182"/>
-      <c r="U182"/>
-      <c r="V182"/>
-      <c r="W182"/>
-      <c r="X182"/>
-      <c r="Y182"/>
-      <c r="Z182"/>
-      <c r="AA182"/>
-      <c r="AB182"/>
-      <c r="AC182"/>
-    </row>
-    <row r="183" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B183" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C183" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D183" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E183" s="23">
-        <v>52680000</v>
       </c>
       <c r="F183" s="13" t="s">
         <v>8</v>
@@ -5477,21 +5464,21 @@
       <c r="AB183" s="28"/>
       <c r="AC183" s="28"/>
     </row>
-    <row r="184" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B184" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E184" s="23">
-        <v>62680000</v>
+        <v>24980000</v>
       </c>
       <c r="F184" s="13" t="s">
         <v>8</v>
@@ -5520,21 +5507,21 @@
       <c r="AB184" s="28"/>
       <c r="AC184" s="28"/>
     </row>
-    <row r="185" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="B185" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E185" s="23">
-        <v>68680000</v>
+        <v>35680000</v>
       </c>
       <c r="F185" s="13" t="s">
         <v>8</v>
@@ -5563,21 +5550,21 @@
       <c r="AB185" s="28"/>
       <c r="AC185" s="28"/>
     </row>
-    <row r="186" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E186" s="23">
-        <v>75500000</v>
+        <v>39860000</v>
       </c>
       <c r="F186" s="13" t="s">
         <v>8</v>
@@ -5606,64 +5593,64 @@
       <c r="AB186" s="28"/>
       <c r="AC186" s="28"/>
     </row>
-    <row r="187" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="B187" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D187" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E187" s="23">
-        <v>89580000</v>
+        <v>47979000</v>
       </c>
       <c r="F187" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G187" s="28"/>
-      <c r="H187" s="28"/>
-      <c r="I187" s="28"/>
-      <c r="J187" s="28"/>
-      <c r="K187" s="28"/>
-      <c r="L187" s="28"/>
-      <c r="M187" s="28"/>
-      <c r="N187" s="28"/>
-      <c r="O187" s="28"/>
-      <c r="P187" s="28"/>
-      <c r="Q187" s="28"/>
-      <c r="R187" s="28"/>
-      <c r="S187" s="28"/>
-      <c r="T187" s="28"/>
-      <c r="U187" s="28"/>
-      <c r="V187" s="28"/>
-      <c r="W187" s="28"/>
-      <c r="X187" s="28"/>
-      <c r="Y187" s="28"/>
-      <c r="Z187" s="28"/>
-      <c r="AA187" s="28"/>
-      <c r="AB187" s="28"/>
-      <c r="AC187" s="28"/>
-    </row>
-    <row r="188" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G187"/>
+      <c r="H187"/>
+      <c r="I187"/>
+      <c r="J187"/>
+      <c r="K187"/>
+      <c r="L187"/>
+      <c r="M187"/>
+      <c r="N187"/>
+      <c r="O187"/>
+      <c r="P187"/>
+      <c r="Q187"/>
+      <c r="R187"/>
+      <c r="S187"/>
+      <c r="T187"/>
+      <c r="U187"/>
+      <c r="V187"/>
+      <c r="W187"/>
+      <c r="X187"/>
+      <c r="Y187"/>
+      <c r="Z187"/>
+      <c r="AA187"/>
+      <c r="AB187"/>
+      <c r="AC187"/>
+    </row>
+    <row r="188" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="B188" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D188" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E188" s="23">
-        <v>99880000</v>
+        <v>52680000</v>
       </c>
       <c r="F188" s="13" t="s">
         <v>8</v>
@@ -5692,21 +5679,21 @@
       <c r="AB188" s="28"/>
       <c r="AC188" s="28"/>
     </row>
-    <row r="189" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B189" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D189" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E189" s="23">
-        <v>109680000</v>
+        <v>62680000</v>
       </c>
       <c r="F189" s="13" t="s">
         <v>8</v>
@@ -5735,21 +5722,21 @@
       <c r="AB189" s="28"/>
       <c r="AC189" s="28"/>
     </row>
-    <row r="190" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="B190" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D190" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E190" s="23">
-        <v>129860000</v>
+        <v>68680000</v>
       </c>
       <c r="F190" s="13" t="s">
         <v>8</v>
@@ -5780,19 +5767,19 @@
     </row>
     <row r="191" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D191" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E191" s="23">
-        <v>144910000</v>
+        <v>75500000</v>
       </c>
       <c r="F191" s="13" t="s">
         <v>8</v>
@@ -5823,19 +5810,19 @@
     </row>
     <row r="192" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="B192" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D192" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E192" s="23">
-        <v>155910000</v>
+        <v>89580000</v>
       </c>
       <c r="F192" s="13" t="s">
         <v>8</v>
@@ -5866,19 +5853,19 @@
     </row>
     <row r="193" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="B193" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D193" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E193" s="23">
-        <v>156560000</v>
+        <v>99880000</v>
       </c>
       <c r="F193" s="13" t="s">
         <v>8</v>
@@ -5909,19 +5896,19 @@
     </row>
     <row r="194" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="B194" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D194" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E194" s="23">
-        <v>184370000</v>
+        <v>109680000</v>
       </c>
       <c r="F194" s="13" t="s">
         <v>8</v>
@@ -5952,19 +5939,19 @@
     </row>
     <row r="195" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B195" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D195" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E195" s="23">
-        <v>243080000</v>
+        <v>129860000</v>
       </c>
       <c r="F195" s="13" t="s">
         <v>8</v>
@@ -5995,19 +5982,19 @@
     </row>
     <row r="196" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="B196" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D196" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E196" s="23">
-        <v>276040000</v>
+        <v>144910000</v>
       </c>
       <c r="F196" s="13" t="s">
         <v>8</v>
@@ -6038,19 +6025,19 @@
     </row>
     <row r="197" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="B197" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D197" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E197" s="23">
-        <v>313680000</v>
+        <v>155910000</v>
       </c>
       <c r="F197" s="13" t="s">
         <v>8</v>
@@ -6081,19 +6068,19 @@
     </row>
     <row r="198" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="B198" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D198" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E198" s="23">
-        <v>358200000</v>
+        <v>156560000</v>
       </c>
       <c r="F198" s="13" t="s">
         <v>8</v>
@@ -6124,19 +6111,19 @@
     </row>
     <row r="199" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B199" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D199" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E199" s="23">
-        <v>389600000</v>
+        <v>184370000</v>
       </c>
       <c r="F199" s="13" t="s">
         <v>8</v>
@@ -6167,19 +6154,19 @@
     </row>
     <row r="200" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D200" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E200" s="23">
-        <v>433800000</v>
+        <v>243080000</v>
       </c>
       <c r="F200" s="13" t="s">
         <v>8</v>
@@ -6210,19 +6197,19 @@
     </row>
     <row r="201" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D201" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E201" s="23">
-        <v>656580000</v>
+        <v>276040000</v>
       </c>
       <c r="F201" s="13" t="s">
         <v>8</v>
@@ -6253,19 +6240,19 @@
     </row>
     <row r="202" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C202" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E202" s="23">
-        <v>762670000</v>
+        <v>313680000</v>
       </c>
       <c r="F202" s="13" t="s">
         <v>8</v>
@@ -6296,19 +6283,19 @@
     </row>
     <row r="203" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C203" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D203" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E203" s="23">
-        <v>874940000</v>
+        <v>358200000</v>
       </c>
       <c r="F203" s="13" t="s">
         <v>8</v>
@@ -6339,19 +6326,19 @@
     </row>
     <row r="204" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="B204" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D204" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E204" s="23">
-        <v>1062400000</v>
+        <v>389600000</v>
       </c>
       <c r="F204" s="13" t="s">
         <v>8</v>
@@ -6380,233 +6367,233 @@
       <c r="AB204" s="28"/>
       <c r="AC204" s="28"/>
     </row>
-    <row r="205" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="11" t="s">
-        <v>230</v>
+    <row r="205" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C205" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D205" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E205" s="24">
-        <v>75000</v>
+      <c r="C205" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D205" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E205" s="23">
+        <v>433800000</v>
       </c>
       <c r="F205" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G205"/>
-      <c r="H205"/>
-      <c r="I205"/>
-      <c r="J205"/>
-      <c r="K205"/>
-      <c r="L205"/>
-      <c r="M205"/>
-      <c r="N205"/>
-      <c r="O205"/>
-      <c r="P205"/>
-      <c r="Q205"/>
-      <c r="R205"/>
-      <c r="S205"/>
-      <c r="T205"/>
-      <c r="U205"/>
-      <c r="V205"/>
-      <c r="W205"/>
-      <c r="X205"/>
-      <c r="Y205"/>
-      <c r="Z205"/>
-      <c r="AA205"/>
-      <c r="AB205"/>
-      <c r="AC205"/>
-    </row>
-    <row r="206" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="11" t="s">
-        <v>162</v>
+      <c r="G205" s="28"/>
+      <c r="H205" s="28"/>
+      <c r="I205" s="28"/>
+      <c r="J205" s="28"/>
+      <c r="K205" s="28"/>
+      <c r="L205" s="28"/>
+      <c r="M205" s="28"/>
+      <c r="N205" s="28"/>
+      <c r="O205" s="28"/>
+      <c r="P205" s="28"/>
+      <c r="Q205" s="28"/>
+      <c r="R205" s="28"/>
+      <c r="S205" s="28"/>
+      <c r="T205" s="28"/>
+      <c r="U205" s="28"/>
+      <c r="V205" s="28"/>
+      <c r="W205" s="28"/>
+      <c r="X205" s="28"/>
+      <c r="Y205" s="28"/>
+      <c r="Z205" s="28"/>
+      <c r="AA205" s="28"/>
+      <c r="AB205" s="28"/>
+      <c r="AC205" s="28"/>
+    </row>
+    <row r="206" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="7" t="s">
+        <v>211</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C206" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="D206" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E206" s="24">
-        <v>33000</v>
+        <v>9</v>
+      </c>
+      <c r="C206" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D206" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E206" s="23">
+        <v>656580000</v>
       </c>
       <c r="F206" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G206"/>
-      <c r="H206"/>
-      <c r="I206"/>
-      <c r="J206"/>
-      <c r="K206"/>
-      <c r="L206"/>
-      <c r="M206"/>
-      <c r="N206"/>
-      <c r="O206"/>
-      <c r="P206"/>
-      <c r="Q206"/>
-      <c r="R206"/>
-      <c r="S206"/>
-      <c r="T206"/>
-      <c r="U206"/>
-      <c r="V206"/>
-      <c r="W206"/>
-      <c r="X206"/>
-      <c r="Y206"/>
-      <c r="Z206"/>
-      <c r="AA206"/>
-      <c r="AB206"/>
-      <c r="AC206"/>
-    </row>
-    <row r="207" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G206" s="28"/>
+      <c r="H206" s="28"/>
+      <c r="I206" s="28"/>
+      <c r="J206" s="28"/>
+      <c r="K206" s="28"/>
+      <c r="L206" s="28"/>
+      <c r="M206" s="28"/>
+      <c r="N206" s="28"/>
+      <c r="O206" s="28"/>
+      <c r="P206" s="28"/>
+      <c r="Q206" s="28"/>
+      <c r="R206" s="28"/>
+      <c r="S206" s="28"/>
+      <c r="T206" s="28"/>
+      <c r="U206" s="28"/>
+      <c r="V206" s="28"/>
+      <c r="W206" s="28"/>
+      <c r="X206" s="28"/>
+      <c r="Y206" s="28"/>
+      <c r="Z206" s="28"/>
+      <c r="AA206" s="28"/>
+      <c r="AB206" s="28"/>
+      <c r="AC206" s="28"/>
+    </row>
+    <row r="207" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C207" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D207" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E207" s="24">
-        <v>75000</v>
+        <v>9</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D207" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E207" s="23">
+        <v>762670000</v>
       </c>
       <c r="F207" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G207"/>
-      <c r="H207"/>
-      <c r="I207"/>
-      <c r="J207"/>
-      <c r="K207"/>
-      <c r="L207"/>
-      <c r="M207"/>
-      <c r="N207"/>
-      <c r="O207"/>
-      <c r="P207"/>
-      <c r="Q207"/>
-      <c r="R207"/>
-      <c r="S207"/>
-      <c r="T207"/>
-      <c r="U207"/>
-      <c r="V207"/>
-      <c r="W207"/>
-      <c r="X207"/>
-      <c r="Y207"/>
-      <c r="Z207"/>
-      <c r="AA207"/>
-      <c r="AB207"/>
-      <c r="AC207"/>
-    </row>
-    <row r="208" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G207" s="28"/>
+      <c r="H207" s="28"/>
+      <c r="I207" s="28"/>
+      <c r="J207" s="28"/>
+      <c r="K207" s="28"/>
+      <c r="L207" s="28"/>
+      <c r="M207" s="28"/>
+      <c r="N207" s="28"/>
+      <c r="O207" s="28"/>
+      <c r="P207" s="28"/>
+      <c r="Q207" s="28"/>
+      <c r="R207" s="28"/>
+      <c r="S207" s="28"/>
+      <c r="T207" s="28"/>
+      <c r="U207" s="28"/>
+      <c r="V207" s="28"/>
+      <c r="W207" s="28"/>
+      <c r="X207" s="28"/>
+      <c r="Y207" s="28"/>
+      <c r="Z207" s="28"/>
+      <c r="AA207" s="28"/>
+      <c r="AB207" s="28"/>
+      <c r="AC207" s="28"/>
+    </row>
+    <row r="208" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C208" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D208" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E208" s="24">
-        <v>75000</v>
+        <v>9</v>
+      </c>
+      <c r="C208" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D208" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E208" s="23">
+        <v>874940000</v>
       </c>
       <c r="F208" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G208"/>
-      <c r="H208"/>
-      <c r="I208"/>
-      <c r="J208"/>
-      <c r="K208"/>
-      <c r="L208"/>
-      <c r="M208"/>
-      <c r="N208"/>
-      <c r="O208"/>
-      <c r="P208"/>
-      <c r="Q208"/>
-      <c r="R208"/>
-      <c r="S208"/>
-      <c r="T208"/>
-      <c r="U208"/>
-      <c r="V208"/>
-      <c r="W208"/>
-      <c r="X208"/>
-      <c r="Y208"/>
-      <c r="Z208"/>
-      <c r="AA208"/>
-      <c r="AB208"/>
-      <c r="AC208"/>
-    </row>
-    <row r="209" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="11" t="s">
-        <v>233</v>
+      <c r="G208" s="28"/>
+      <c r="H208" s="28"/>
+      <c r="I208" s="28"/>
+      <c r="J208" s="28"/>
+      <c r="K208" s="28"/>
+      <c r="L208" s="28"/>
+      <c r="M208" s="28"/>
+      <c r="N208" s="28"/>
+      <c r="O208" s="28"/>
+      <c r="P208" s="28"/>
+      <c r="Q208" s="28"/>
+      <c r="R208" s="28"/>
+      <c r="S208" s="28"/>
+      <c r="T208" s="28"/>
+      <c r="U208" s="28"/>
+      <c r="V208" s="28"/>
+      <c r="W208" s="28"/>
+      <c r="X208" s="28"/>
+      <c r="Y208" s="28"/>
+      <c r="Z208" s="28"/>
+      <c r="AA208" s="28"/>
+      <c r="AB208" s="28"/>
+      <c r="AC208" s="28"/>
+    </row>
+    <row r="209" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="B209" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C209" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D209" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E209" s="24">
-        <v>75000</v>
+      <c r="C209" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E209" s="23">
+        <v>1062400000</v>
       </c>
       <c r="F209" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G209"/>
-      <c r="H209"/>
-      <c r="I209"/>
-      <c r="J209"/>
-      <c r="K209"/>
-      <c r="L209"/>
-      <c r="M209"/>
-      <c r="N209"/>
-      <c r="O209"/>
-      <c r="P209"/>
-      <c r="Q209"/>
-      <c r="R209"/>
-      <c r="S209"/>
-      <c r="T209"/>
-      <c r="U209"/>
-      <c r="V209"/>
-      <c r="W209"/>
-      <c r="X209"/>
-      <c r="Y209"/>
-      <c r="Z209"/>
-      <c r="AA209"/>
-      <c r="AB209"/>
-      <c r="AC209"/>
-    </row>
-    <row r="210" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B210" s="14" t="s">
-        <v>158</v>
+      <c r="G209" s="28"/>
+      <c r="H209" s="28"/>
+      <c r="I209" s="28"/>
+      <c r="J209" s="28"/>
+      <c r="K209" s="28"/>
+      <c r="L209" s="28"/>
+      <c r="M209" s="28"/>
+      <c r="N209" s="28"/>
+      <c r="O209" s="28"/>
+      <c r="P209" s="28"/>
+      <c r="Q209" s="28"/>
+      <c r="R209" s="28"/>
+      <c r="S209" s="28"/>
+      <c r="T209" s="28"/>
+      <c r="U209" s="28"/>
+      <c r="V209" s="28"/>
+      <c r="W209" s="28"/>
+      <c r="X209" s="28"/>
+      <c r="Y209" s="28"/>
+      <c r="Z209" s="28"/>
+      <c r="AA209" s="28"/>
+      <c r="AB209" s="28"/>
+      <c r="AC209" s="28"/>
+    </row>
+    <row r="210" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D210" s="36" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E210" s="24">
         <v>75000</v>
@@ -6639,22 +6626,22 @@
       <c r="AC210"/>
     </row>
     <row r="211" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B211" s="37" t="s">
+      <c r="A211" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B211" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C211" s="16" t="s">
-        <v>89</v>
+      <c r="C211" s="12" t="s">
+        <v>158</v>
       </c>
       <c r="D211" s="36" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E211" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F211" s="17" t="s">
+        <v>33000</v>
+      </c>
+      <c r="F211" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G211"/>
@@ -6681,19 +6668,23 @@
       <c r="AB211"/>
       <c r="AC211"/>
     </row>
-    <row r="212" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="B212" s="38"/>
-      <c r="C212" s="29"/>
-      <c r="D212" s="10" t="s">
-        <v>35</v>
+    <row r="212" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D212" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E212" s="24">
-        <v>1000000</v>
-      </c>
-      <c r="F212" s="17" t="s">
+        <v>75000</v>
+      </c>
+      <c r="F212" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G212"/>
@@ -6720,19 +6711,23 @@
       <c r="AB212"/>
       <c r="AC212"/>
     </row>
-    <row r="213" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B213" s="38"/>
-      <c r="C213" s="29"/>
-      <c r="D213" s="10" t="s">
-        <v>35</v>
+    <row r="213" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B213" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D213" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E213" s="24">
-        <v>880000</v>
-      </c>
-      <c r="F213" s="17" t="s">
+        <v>75000</v>
+      </c>
+      <c r="F213" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G213"/>
@@ -6759,19 +6754,23 @@
       <c r="AB213"/>
       <c r="AC213"/>
     </row>
-    <row r="214" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B214" s="38"/>
-      <c r="C214" s="29"/>
-      <c r="D214" s="10" t="s">
-        <v>35</v>
+    <row r="214" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D214" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E214" s="24">
-        <v>1380000</v>
-      </c>
-      <c r="F214" s="17" t="s">
+        <v>75000</v>
+      </c>
+      <c r="F214" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G214"/>
@@ -6799,18 +6798,22 @@
       <c r="AC214"/>
     </row>
     <row r="215" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B215" s="8"/>
-      <c r="C215" s="8"/>
-      <c r="D215" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E215" s="23">
-        <v>13880000</v>
-      </c>
-      <c r="F215" s="18" t="s">
+      <c r="A215" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B215" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D215" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E215" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F215" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G215"/>
@@ -6838,18 +6841,22 @@
       <c r="AC215"/>
     </row>
     <row r="216" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B216" s="8"/>
-      <c r="C216" s="8"/>
-      <c r="D216" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E216" s="23">
-        <v>750000</v>
-      </c>
-      <c r="F216" s="18" t="s">
+      <c r="A216" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B216" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C216" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D216" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E216" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F216" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G216"/>
@@ -6877,18 +6884,18 @@
       <c r="AC216"/>
     </row>
     <row r="217" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B217" s="8"/>
-      <c r="C217" s="8"/>
+      <c r="A217" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B217" s="38"/>
+      <c r="C217" s="29"/>
       <c r="D217" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E217" s="23">
-        <v>155000</v>
-      </c>
-      <c r="F217" s="18" t="s">
+      <c r="E217" s="24">
+        <v>1000000</v>
+      </c>
+      <c r="F217" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G217"/>
@@ -6916,18 +6923,18 @@
       <c r="AC217"/>
     </row>
     <row r="218" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B218" s="8"/>
-      <c r="C218" s="8"/>
+      <c r="A218" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B218" s="38"/>
+      <c r="C218" s="29"/>
       <c r="D218" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E218" s="23">
-        <v>176000</v>
-      </c>
-      <c r="F218" s="18" t="s">
+      <c r="E218" s="24">
+        <v>880000</v>
+      </c>
+      <c r="F218" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G218"/>
@@ -6955,18 +6962,18 @@
       <c r="AC218"/>
     </row>
     <row r="219" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
+      <c r="A219" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B219" s="38"/>
+      <c r="C219" s="29"/>
       <c r="D219" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E219" s="23">
-        <v>198000</v>
-      </c>
-      <c r="F219" s="18" t="s">
+      <c r="E219" s="24">
+        <v>1380000</v>
+      </c>
+      <c r="F219" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G219"/>
@@ -6995,7 +7002,7 @@
     </row>
     <row r="220" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -7003,7 +7010,7 @@
         <v>35</v>
       </c>
       <c r="E220" s="23">
-        <v>186000</v>
+        <v>13880000</v>
       </c>
       <c r="F220" s="18" t="s">
         <v>8</v>
@@ -7034,7 +7041,7 @@
     </row>
     <row r="221" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -7042,7 +7049,7 @@
         <v>35</v>
       </c>
       <c r="E221" s="23">
-        <v>198000</v>
+        <v>750000</v>
       </c>
       <c r="F221" s="18" t="s">
         <v>8</v>
@@ -7073,7 +7080,7 @@
     </row>
     <row r="222" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -7081,7 +7088,7 @@
         <v>35</v>
       </c>
       <c r="E222" s="23">
-        <v>228000</v>
+        <v>155000</v>
       </c>
       <c r="F222" s="18" t="s">
         <v>8</v>
@@ -7112,7 +7119,7 @@
     </row>
     <row r="223" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="11" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -7120,7 +7127,7 @@
         <v>35</v>
       </c>
       <c r="E223" s="23">
-        <v>175000</v>
+        <v>176000</v>
       </c>
       <c r="F223" s="18" t="s">
         <v>8</v>
@@ -7151,7 +7158,7 @@
     </row>
     <row r="224" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -7159,7 +7166,7 @@
         <v>35</v>
       </c>
       <c r="E224" s="23">
-        <v>296000</v>
+        <v>198000</v>
       </c>
       <c r="F224" s="18" t="s">
         <v>8</v>
@@ -7190,7 +7197,7 @@
     </row>
     <row r="225" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -7198,7 +7205,7 @@
         <v>35</v>
       </c>
       <c r="E225" s="23">
-        <v>258000</v>
+        <v>186000</v>
       </c>
       <c r="F225" s="18" t="s">
         <v>8</v>
@@ -7229,7 +7236,7 @@
     </row>
     <row r="226" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -7237,7 +7244,7 @@
         <v>35</v>
       </c>
       <c r="E226" s="23">
-        <v>228000</v>
+        <v>198000</v>
       </c>
       <c r="F226" s="18" t="s">
         <v>8</v>
@@ -7268,7 +7275,7 @@
     </row>
     <row r="227" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -7276,7 +7283,7 @@
         <v>35</v>
       </c>
       <c r="E227" s="23">
-        <v>248000</v>
+        <v>228000</v>
       </c>
       <c r="F227" s="18" t="s">
         <v>8</v>
@@ -7307,7 +7314,7 @@
     </row>
     <row r="228" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -7315,7 +7322,7 @@
         <v>35</v>
       </c>
       <c r="E228" s="23">
-        <v>278000</v>
+        <v>175000</v>
       </c>
       <c r="F228" s="18" t="s">
         <v>8</v>
@@ -7345,22 +7352,18 @@
       <c r="AC228"/>
     </row>
     <row r="229" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B229" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C229" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D229" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E229" s="25">
-        <v>32680000</v>
-      </c>
-      <c r="F229" s="17" t="s">
+      <c r="A229" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
+      <c r="D229" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E229" s="23">
+        <v>296000</v>
+      </c>
+      <c r="F229" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G229"/>
@@ -7387,23 +7390,19 @@
       <c r="AB229"/>
       <c r="AC229"/>
     </row>
-    <row r="230" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="B230" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C230" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D230" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E230" s="25">
-        <v>36800000</v>
-      </c>
-      <c r="F230" s="17" t="s">
+    <row r="230" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B230" s="8"/>
+      <c r="C230" s="8"/>
+      <c r="D230" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E230" s="23">
+        <v>258000</v>
+      </c>
+      <c r="F230" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G230"/>
@@ -7430,23 +7429,19 @@
       <c r="AB230"/>
       <c r="AC230"/>
     </row>
-    <row r="231" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B231" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C231" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D231" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E231" s="25">
-        <v>43680000</v>
-      </c>
-      <c r="F231" s="17" t="s">
+    <row r="231" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B231" s="8"/>
+      <c r="C231" s="8"/>
+      <c r="D231" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E231" s="23">
+        <v>228000</v>
+      </c>
+      <c r="F231" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G231"/>
@@ -7473,123 +7468,330 @@
       <c r="AB231"/>
       <c r="AC231"/>
     </row>
-    <row r="232" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A232" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B232" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C232" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D232" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E232" s="25">
+    <row r="232" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B232" s="8"/>
+      <c r="C232" s="8"/>
+      <c r="D232" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E232" s="23">
+        <v>248000</v>
+      </c>
+      <c r="F232" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G232"/>
+      <c r="H232"/>
+      <c r="I232"/>
+      <c r="J232"/>
+      <c r="K232"/>
+      <c r="L232"/>
+      <c r="M232"/>
+      <c r="N232"/>
+      <c r="O232"/>
+      <c r="P232"/>
+      <c r="Q232"/>
+      <c r="R232"/>
+      <c r="S232"/>
+      <c r="T232"/>
+      <c r="U232"/>
+      <c r="V232"/>
+      <c r="W232"/>
+      <c r="X232"/>
+      <c r="Y232"/>
+      <c r="Z232"/>
+      <c r="AA232"/>
+      <c r="AB232"/>
+      <c r="AC232"/>
+    </row>
+    <row r="233" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B233" s="8"/>
+      <c r="C233" s="8"/>
+      <c r="D233" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E233" s="23">
+        <v>278000</v>
+      </c>
+      <c r="F233" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G233"/>
+      <c r="H233"/>
+      <c r="I233"/>
+      <c r="J233"/>
+      <c r="K233"/>
+      <c r="L233"/>
+      <c r="M233"/>
+      <c r="N233"/>
+      <c r="O233"/>
+      <c r="P233"/>
+      <c r="Q233"/>
+      <c r="R233"/>
+      <c r="S233"/>
+      <c r="T233"/>
+      <c r="U233"/>
+      <c r="V233"/>
+      <c r="W233"/>
+      <c r="X233"/>
+      <c r="Y233"/>
+      <c r="Z233"/>
+      <c r="AA233"/>
+      <c r="AB233"/>
+      <c r="AC233"/>
+    </row>
+    <row r="234" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B234" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C234" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D234" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E234" s="25">
+        <v>32680000</v>
+      </c>
+      <c r="F234" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G234"/>
+      <c r="H234"/>
+      <c r="I234"/>
+      <c r="J234"/>
+      <c r="K234"/>
+      <c r="L234"/>
+      <c r="M234"/>
+      <c r="N234"/>
+      <c r="O234"/>
+      <c r="P234"/>
+      <c r="Q234"/>
+      <c r="R234"/>
+      <c r="S234"/>
+      <c r="T234"/>
+      <c r="U234"/>
+      <c r="V234"/>
+      <c r="W234"/>
+      <c r="X234"/>
+      <c r="Y234"/>
+      <c r="Z234"/>
+      <c r="AA234"/>
+      <c r="AB234"/>
+      <c r="AC234"/>
+    </row>
+    <row r="235" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B235" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C235" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D235" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E235" s="25">
+        <v>36800000</v>
+      </c>
+      <c r="F235" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G235"/>
+      <c r="H235"/>
+      <c r="I235"/>
+      <c r="J235"/>
+      <c r="K235"/>
+      <c r="L235"/>
+      <c r="M235"/>
+      <c r="N235"/>
+      <c r="O235"/>
+      <c r="P235"/>
+      <c r="Q235"/>
+      <c r="R235"/>
+      <c r="S235"/>
+      <c r="T235"/>
+      <c r="U235"/>
+      <c r="V235"/>
+      <c r="W235"/>
+      <c r="X235"/>
+      <c r="Y235"/>
+      <c r="Z235"/>
+      <c r="AA235"/>
+      <c r="AB235"/>
+      <c r="AC235"/>
+    </row>
+    <row r="236" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B236" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C236" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D236" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E236" s="25">
+        <v>43680000</v>
+      </c>
+      <c r="F236" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G236"/>
+      <c r="H236"/>
+      <c r="I236"/>
+      <c r="J236"/>
+      <c r="K236"/>
+      <c r="L236"/>
+      <c r="M236"/>
+      <c r="N236"/>
+      <c r="O236"/>
+      <c r="P236"/>
+      <c r="Q236"/>
+      <c r="R236"/>
+      <c r="S236"/>
+      <c r="T236"/>
+      <c r="U236"/>
+      <c r="V236"/>
+      <c r="W236"/>
+      <c r="X236"/>
+      <c r="Y236"/>
+      <c r="Z236"/>
+      <c r="AA236"/>
+      <c r="AB236"/>
+      <c r="AC236"/>
+    </row>
+    <row r="237" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A237" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B237" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C237" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D237" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E237" s="25">
         <v>48680000</v>
       </c>
-      <c r="F232" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="233" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A233" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="B233" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C233" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D233" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E233" s="25">
+      <c r="F237" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A238" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B238" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C238" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D238" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E238" s="25">
         <v>54680000</v>
       </c>
-      <c r="F233" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="234" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A234" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="B234" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C234" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D234" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E234" s="25">
+      <c r="F238" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A239" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B239" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C239" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D239" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E239" s="25">
         <v>69860000</v>
       </c>
-      <c r="F234" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="235" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A235" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="B235" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C235" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D235" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E235" s="25">
+      <c r="F239" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A240" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B240" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C240" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D240" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E240" s="25">
         <v>99680000</v>
       </c>
-      <c r="F235" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="236" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A236" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="B236" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C236" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D236" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E236" s="26">
+      <c r="F240" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A241" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B241" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C241" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D241" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E241" s="26">
         <v>75000</v>
       </c>
-      <c r="F236" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="237" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A237" s="39" t="s">
-        <v>243</v>
-      </c>
-      <c r="B237" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C237" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D237" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E237" s="26">
+      <c r="F241" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A242" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B242" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C242" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D242" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E242" s="26">
         <v>75000</v>
       </c>
-      <c r="F237" s="17" t="s">
+      <c r="F242" s="17" t="s">
         <v>8</v>
       </c>
     </row>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="266">
   <si>
     <t>Ống D650</t>
   </si>
@@ -997,6 +997,30 @@
   </si>
   <si>
     <t>Côn chuyển rẽ nhánh D500 về D450 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D400 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D450 về D400 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D450 về D450 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D500 về D450 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D550 về D500 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D550 về D550 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D600 về D550 rẽ 1 nhánh D100</t>
+  </si>
+  <si>
+    <t>Y chia D150  rẽ 2 nhánh D100</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1032,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1086,6 +1110,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1113,7 +1142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1173,6 +1202,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1181,7 +1219,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1322,6 +1360,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="12" fillId="3" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1608,7 +1658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC242"/>
+  <dimension ref="A1:AC250"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5703125" style="40" customWidth="1"/>
@@ -2606,7 +2656,7 @@
       <c r="R48"/>
       <c r="S48"/>
     </row>
-    <row r="49" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>253</v>
       </c>
@@ -2626,7 +2676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>252</v>
       </c>
@@ -2646,7 +2696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>251</v>
       </c>
@@ -2666,7 +2716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:20" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>250</v>
       </c>
@@ -2698,7 +2748,7 @@
       <c r="Q52"/>
       <c r="R52"/>
     </row>
-    <row r="53" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>249</v>
       </c>
@@ -2730,7 +2780,7 @@
       <c r="Q53"/>
       <c r="R53"/>
     </row>
-    <row r="54" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>248</v>
       </c>
@@ -2762,7 +2812,7 @@
       <c r="Q54"/>
       <c r="R54"/>
     </row>
-    <row r="55" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>247</v>
       </c>
@@ -2794,7 +2844,7 @@
       <c r="Q55"/>
       <c r="R55"/>
     </row>
-    <row r="56" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>254</v>
       </c>
@@ -2826,7 +2876,7 @@
       <c r="Q56"/>
       <c r="R56"/>
     </row>
-    <row r="57" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>255</v>
       </c>
@@ -2858,7 +2908,7 @@
       <c r="Q57"/>
       <c r="R57"/>
     </row>
-    <row r="58" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>245</v>
       </c>
@@ -2890,153 +2940,118 @@
       <c r="Q58"/>
       <c r="R58"/>
     </row>
-    <row r="59" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="52">
+        <v>410000</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="50"/>
+    </row>
+    <row r="60" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="52">
+        <v>369000</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="50"/>
+    </row>
+    <row r="61" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="52">
+        <v>432000</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="50"/>
+    </row>
+    <row r="62" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B59" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" s="49">
+      <c r="B62" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="49">
         <v>340500</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
-      <c r="K59"/>
-      <c r="L59"/>
-      <c r="M59"/>
-      <c r="N59"/>
-      <c r="O59"/>
-      <c r="P59"/>
-      <c r="Q59"/>
-      <c r="R59"/>
-    </row>
-    <row r="60" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="F62" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="P62"/>
+      <c r="Q62"/>
+      <c r="R62"/>
+    </row>
+    <row r="63" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E60" s="49">
+      <c r="B63" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="49">
         <v>355500</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G60"/>
-      <c r="H60"/>
-      <c r="I60"/>
-      <c r="J60"/>
-      <c r="K60"/>
-      <c r="L60"/>
-      <c r="M60"/>
-      <c r="N60"/>
-      <c r="O60"/>
-      <c r="P60"/>
-      <c r="Q60"/>
-      <c r="R60"/>
-    </row>
-    <row r="61" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E61" s="49">
-        <v>370500</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G61"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61"/>
-      <c r="K61"/>
-      <c r="L61"/>
-      <c r="M61"/>
-      <c r="N61"/>
-      <c r="O61"/>
-      <c r="P61"/>
-      <c r="Q61"/>
-      <c r="R61"/>
-    </row>
-    <row r="62" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="48">
-        <v>369000</v>
-      </c>
-      <c r="F62" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G62" s="47"/>
-      <c r="H62" s="47"/>
-      <c r="I62" s="47"/>
-      <c r="J62" s="47"/>
-      <c r="K62" s="47"/>
-      <c r="L62" s="47"/>
-      <c r="M62" s="47"/>
-      <c r="N62" s="47"/>
-      <c r="O62" s="47"/>
-      <c r="P62" s="47"/>
-      <c r="Q62" s="47"/>
-      <c r="R62" s="47"/>
-      <c r="S62" s="47"/>
-      <c r="T62" s="47"/>
-    </row>
-    <row r="63" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="48">
-        <v>416000</v>
-      </c>
-      <c r="F63" s="45" t="s">
+      <c r="F63" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G63"/>
@@ -3051,60 +3066,56 @@
       <c r="P63"/>
       <c r="Q63"/>
       <c r="R63"/>
-      <c r="S63"/>
-      <c r="T63"/>
-    </row>
-    <row r="64" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="48">
-        <v>420000</v>
-      </c>
-      <c r="F64" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G64" s="47"/>
-      <c r="H64" s="47"/>
-      <c r="I64" s="47"/>
-      <c r="J64" s="47"/>
-      <c r="K64" s="47"/>
-      <c r="L64" s="47"/>
-      <c r="M64" s="47"/>
-      <c r="N64" s="47"/>
-      <c r="O64" s="47"/>
-      <c r="P64" s="47"/>
-      <c r="Q64" s="47"/>
-      <c r="R64" s="47"/>
-      <c r="S64" s="47"/>
-      <c r="T64" s="47"/>
-    </row>
-    <row r="65" spans="1:21" s="31" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E65" s="48">
-        <v>366000</v>
-      </c>
-      <c r="F65" s="45" t="s">
+    </row>
+    <row r="64" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="52">
+        <v>434000</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="O64"/>
+      <c r="P64"/>
+      <c r="Q64"/>
+      <c r="R64"/>
+    </row>
+    <row r="65" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="49">
+        <v>370500</v>
+      </c>
+      <c r="F65" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G65"/>
@@ -3119,12 +3130,10 @@
       <c r="P65"/>
       <c r="Q65"/>
       <c r="R65"/>
-      <c r="S65"/>
-      <c r="T65"/>
-    </row>
-    <row r="66" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>159</v>
+        <v>262</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>10</v>
@@ -3135,16 +3144,28 @@
       <c r="D66" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E66" s="22">
-        <v>442500</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="E66" s="53">
+        <v>386000</v>
+      </c>
+      <c r="F66" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
+      <c r="L66"/>
+      <c r="M66"/>
+      <c r="N66"/>
+      <c r="O66"/>
+      <c r="P66"/>
+      <c r="Q66"/>
+      <c r="R66"/>
+    </row>
+    <row r="67" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>10</v>
@@ -3155,28 +3176,40 @@
       <c r="D67" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E67" s="22">
-        <v>447000</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>8</v>
-      </c>
+      <c r="E67" s="53">
+        <v>420000</v>
+      </c>
+      <c r="F67" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67"/>
+      <c r="O67"/>
+      <c r="P67"/>
+      <c r="Q67"/>
+      <c r="R67"/>
     </row>
     <row r="68" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="46">
-        <v>450000</v>
+      <c r="A68" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="53">
+        <v>423000</v>
       </c>
       <c r="F68" s="45" t="s">
         <v>8</v>
@@ -3193,383 +3226,361 @@
       <c r="P68"/>
       <c r="Q68"/>
       <c r="R68"/>
-      <c r="S68"/>
-      <c r="T68"/>
-      <c r="U68"/>
-    </row>
-    <row r="69" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="22">
-        <v>470000</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="B70" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="33">
-        <v>447000</v>
-      </c>
-      <c r="F70" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="22">
-        <v>528000</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="B72" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="33">
-        <v>508500</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="69" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="48">
+        <v>369000</v>
+      </c>
+      <c r="F69" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+      <c r="M69"/>
+      <c r="N69"/>
+      <c r="O69"/>
+      <c r="P69"/>
+      <c r="Q69"/>
+      <c r="R69"/>
+      <c r="S69" s="47"/>
+      <c r="T69" s="47"/>
+    </row>
+    <row r="70" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="48">
+        <v>416000</v>
+      </c>
+      <c r="F70" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G70"/>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70"/>
+      <c r="M70"/>
+      <c r="N70"/>
+      <c r="O70"/>
+      <c r="P70"/>
+      <c r="Q70"/>
+      <c r="R70"/>
+      <c r="S70"/>
+      <c r="T70"/>
+    </row>
+    <row r="71" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="48">
+        <v>420000</v>
+      </c>
+      <c r="F71" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="Q71"/>
+      <c r="R71" s="47"/>
+      <c r="S71" s="47"/>
+      <c r="T71" s="47"/>
+    </row>
+    <row r="72" spans="1:21" s="31" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="48">
+        <v>366000</v>
+      </c>
+      <c r="F72" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="R72"/>
+      <c r="S72"/>
+      <c r="T72"/>
     </row>
     <row r="73" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="22">
+        <v>442500</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="22">
+        <v>447000</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="46">
+        <v>450000</v>
+      </c>
+      <c r="F75" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G75"/>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75"/>
+      <c r="N75"/>
+      <c r="O75"/>
+      <c r="P75"/>
+      <c r="Q75"/>
+      <c r="R75"/>
+      <c r="S75"/>
+      <c r="T75"/>
+      <c r="U75"/>
+    </row>
+    <row r="76" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="22">
+        <v>470000</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="33">
+        <v>447000</v>
+      </c>
+      <c r="F77" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="22">
+        <v>528000</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="33">
+        <v>508500</v>
+      </c>
+      <c r="F79" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="22">
+      <c r="B80" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="22">
         <v>560000</v>
       </c>
-      <c r="F73" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A74" s="27" t="s">
+      <c r="F80" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="B74" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="33">
+      <c r="B81" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="33">
         <v>682500</v>
       </c>
-      <c r="F74" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="11" t="s">
+      <c r="F81" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A82" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="22">
+      <c r="B82" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="22">
         <v>666000</v>
       </c>
-      <c r="F75" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="46">
-        <v>1125000</v>
-      </c>
-      <c r="F76" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G76"/>
-      <c r="H76"/>
-      <c r="I76"/>
-      <c r="J76"/>
-      <c r="K76"/>
-      <c r="L76"/>
-      <c r="M76"/>
-      <c r="N76"/>
-      <c r="O76"/>
-      <c r="P76"/>
-      <c r="Q76"/>
-      <c r="R76"/>
-      <c r="S76"/>
-      <c r="T76"/>
-      <c r="U76"/>
-    </row>
-    <row r="77" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="46">
-        <v>1150000</v>
-      </c>
-      <c r="F77" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G77"/>
-      <c r="H77"/>
-      <c r="I77"/>
-      <c r="J77"/>
-      <c r="K77"/>
-      <c r="L77"/>
-      <c r="M77"/>
-      <c r="N77"/>
-      <c r="O77"/>
-      <c r="P77"/>
-      <c r="Q77"/>
-      <c r="R77"/>
-      <c r="S77"/>
-      <c r="T77"/>
-      <c r="U77"/>
-    </row>
-    <row r="78" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A78" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="B78" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="33">
-        <v>957000</v>
-      </c>
-      <c r="F78" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="46">
-        <v>750000</v>
-      </c>
-      <c r="F79" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G79"/>
-      <c r="H79"/>
-      <c r="I79"/>
-      <c r="J79"/>
-      <c r="K79"/>
-      <c r="L79"/>
-      <c r="M79"/>
-      <c r="N79"/>
-      <c r="O79"/>
-      <c r="P79"/>
-      <c r="Q79"/>
-      <c r="R79"/>
-      <c r="S79"/>
-      <c r="T79"/>
-      <c r="U79"/>
-    </row>
-    <row r="80" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="46">
-        <v>1550000</v>
-      </c>
-      <c r="F80" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G80"/>
-      <c r="H80"/>
-      <c r="I80"/>
-      <c r="J80"/>
-      <c r="K80"/>
-      <c r="L80"/>
-      <c r="M80"/>
-      <c r="N80"/>
-      <c r="O80"/>
-      <c r="P80"/>
-      <c r="Q80"/>
-      <c r="R80"/>
-      <c r="S80"/>
-      <c r="T80"/>
-      <c r="U80"/>
-    </row>
-    <row r="81" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D81" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="46">
-        <v>1650000</v>
-      </c>
-      <c r="F81" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81"/>
-      <c r="H81"/>
-      <c r="I81"/>
-      <c r="J81"/>
-      <c r="K81"/>
-      <c r="L81"/>
-      <c r="M81"/>
-      <c r="N81"/>
-      <c r="O81"/>
-      <c r="P81"/>
-      <c r="Q81"/>
-      <c r="R81"/>
-      <c r="S81"/>
-      <c r="T81"/>
-      <c r="U81"/>
-    </row>
-    <row r="82" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D82" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="46">
-        <v>1700000</v>
-      </c>
-      <c r="F82" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G82"/>
-      <c r="H82"/>
-      <c r="I82"/>
-      <c r="J82"/>
-      <c r="K82"/>
-      <c r="L82"/>
-      <c r="M82"/>
-      <c r="N82"/>
-      <c r="O82"/>
-      <c r="P82"/>
-      <c r="Q82"/>
-      <c r="R82"/>
-      <c r="S82"/>
-      <c r="T82"/>
-      <c r="U82"/>
+      <c r="F82" s="13" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="83" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>10</v>
@@ -3581,7 +3592,7 @@
         <v>35</v>
       </c>
       <c r="E83" s="46">
-        <v>1800000</v>
+        <v>1125000</v>
       </c>
       <c r="F83" s="45" t="s">
         <v>8</v>
@@ -3604,7 +3615,7 @@
     </row>
     <row r="84" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>10</v>
@@ -3616,7 +3627,7 @@
         <v>35</v>
       </c>
       <c r="E84" s="46">
-        <v>1850000</v>
+        <v>1150000</v>
       </c>
       <c r="F84" s="45" t="s">
         <v>8</v>
@@ -3637,305 +3648,428 @@
       <c r="T84"/>
       <c r="U84"/>
     </row>
-    <row r="85" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
+    <row r="85" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="33">
+        <v>957000</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="46">
+        <v>750000</v>
+      </c>
+      <c r="F86" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="I86"/>
+      <c r="J86"/>
+      <c r="K86"/>
+      <c r="L86"/>
+      <c r="M86"/>
+      <c r="N86"/>
+      <c r="O86"/>
+      <c r="P86"/>
+      <c r="Q86"/>
+      <c r="R86"/>
+      <c r="S86"/>
+      <c r="T86"/>
+      <c r="U86"/>
+    </row>
+    <row r="87" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="46">
+        <v>1550000</v>
+      </c>
+      <c r="F87" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
+      <c r="L87"/>
+      <c r="M87"/>
+      <c r="N87"/>
+      <c r="O87"/>
+      <c r="P87"/>
+      <c r="Q87"/>
+      <c r="R87"/>
+      <c r="S87"/>
+      <c r="T87"/>
+      <c r="U87"/>
+    </row>
+    <row r="88" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="46">
+        <v>1650000</v>
+      </c>
+      <c r="F88" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
+      <c r="K88"/>
+      <c r="L88"/>
+      <c r="M88"/>
+      <c r="N88"/>
+      <c r="O88"/>
+      <c r="P88"/>
+      <c r="Q88"/>
+      <c r="R88"/>
+      <c r="S88"/>
+      <c r="T88"/>
+      <c r="U88"/>
+    </row>
+    <row r="89" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="46">
+        <v>1700000</v>
+      </c>
+      <c r="F89" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89"/>
+      <c r="H89"/>
+      <c r="I89"/>
+      <c r="J89"/>
+      <c r="K89"/>
+      <c r="L89"/>
+      <c r="M89"/>
+      <c r="N89"/>
+      <c r="O89"/>
+      <c r="P89"/>
+      <c r="Q89"/>
+      <c r="R89"/>
+      <c r="S89"/>
+      <c r="T89"/>
+      <c r="U89"/>
+    </row>
+    <row r="90" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="46">
+        <v>1800000</v>
+      </c>
+      <c r="F90" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G90"/>
+      <c r="H90"/>
+      <c r="I90"/>
+      <c r="J90"/>
+      <c r="K90"/>
+      <c r="L90"/>
+      <c r="M90"/>
+      <c r="N90"/>
+      <c r="O90"/>
+      <c r="P90"/>
+      <c r="Q90"/>
+      <c r="R90"/>
+      <c r="S90"/>
+      <c r="T90"/>
+      <c r="U90"/>
+    </row>
+    <row r="91" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="46">
+        <v>1850000</v>
+      </c>
+      <c r="F91" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
+      <c r="L91"/>
+      <c r="M91"/>
+      <c r="N91"/>
+      <c r="O91"/>
+      <c r="P91"/>
+      <c r="Q91"/>
+      <c r="R91"/>
+      <c r="S91"/>
+      <c r="T91"/>
+      <c r="U91"/>
+    </row>
+    <row r="92" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B85" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E85" s="48">
+      <c r="B92" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="48">
         <v>1200000</v>
       </c>
-      <c r="F85" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G85"/>
-      <c r="H85"/>
-      <c r="I85"/>
-      <c r="J85"/>
-      <c r="K85"/>
-      <c r="L85"/>
-      <c r="M85"/>
-      <c r="N85"/>
-      <c r="O85"/>
-      <c r="P85"/>
-      <c r="Q85"/>
-      <c r="R85"/>
-      <c r="S85"/>
-      <c r="T85"/>
-    </row>
-    <row r="86" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A86" s="11" t="s">
+      <c r="F92" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G92"/>
+      <c r="H92"/>
+      <c r="I92"/>
+      <c r="J92"/>
+      <c r="K92"/>
+      <c r="L92"/>
+      <c r="M92"/>
+      <c r="N92"/>
+      <c r="O92"/>
+      <c r="P92"/>
+      <c r="Q92"/>
+      <c r="R92"/>
+      <c r="S92"/>
+      <c r="T92"/>
+    </row>
+    <row r="93" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="22">
+        <v>2100000</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A94" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="22">
+        <v>2860000</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A95" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B86" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" s="22">
+      <c r="B95" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="22">
         <v>3120000</v>
       </c>
-      <c r="F86" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A87" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="22">
-        <v>2860000</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A88" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="22">
-        <v>2100000</v>
-      </c>
-      <c r="F88" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="27" t="s">
+      <c r="F95" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="B89" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="33">
+      <c r="B96" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="33">
         <v>3255000</v>
       </c>
-      <c r="F89" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+      <c r="F96" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="53">
+        <v>206000</v>
+      </c>
+      <c r="F97" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G97" s="50"/>
+    </row>
+    <row r="98" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B98" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E90" s="23">
-        <v>160000</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E91" s="23">
-        <v>220000</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E92" s="23">
-        <v>280000</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E93" s="23">
-        <v>550000</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E94" s="23">
-        <v>900000</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="23">
-        <v>1050000</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="23">
-        <v>1450000</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="23">
-        <v>1780000</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B98" s="6"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E98" s="23">
-        <v>2000000</v>
+        <v>160000</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B99" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C99" s="6"/>
       <c r="D99" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E99" s="23">
-        <v>2500000</v>
+        <v>220000</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B100" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C100" s="6"/>
       <c r="D100" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E100" s="23">
-        <v>2800000</v>
+        <v>280000</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -3943,15 +4077,15 @@
         <v>35</v>
       </c>
       <c r="E101" s="23">
-        <v>3300000</v>
+        <v>550000</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -3959,15 +4093,15 @@
         <v>35</v>
       </c>
       <c r="E102" s="23">
-        <v>3800000</v>
+        <v>900000</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -3975,15 +4109,15 @@
         <v>35</v>
       </c>
       <c r="E103" s="23">
-        <v>4500000</v>
+        <v>1050000</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -3991,15 +4125,15 @@
         <v>35</v>
       </c>
       <c r="E104" s="23">
-        <v>4800000</v>
+        <v>1450000</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -4007,15 +4141,15 @@
         <v>35</v>
       </c>
       <c r="E105" s="23">
-        <v>5200000</v>
+        <v>1780000</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -4023,15 +4157,15 @@
         <v>35</v>
       </c>
       <c r="E106" s="23">
-        <v>5600000</v>
+        <v>2000000</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -4039,15 +4173,15 @@
         <v>35</v>
       </c>
       <c r="E107" s="23">
-        <v>6500000</v>
+        <v>2500000</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -4055,15 +4189,15 @@
         <v>35</v>
       </c>
       <c r="E108" s="23">
-        <v>7200000</v>
+        <v>2800000</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -4071,15 +4205,15 @@
         <v>35</v>
       </c>
       <c r="E109" s="23">
-        <v>7600000</v>
+        <v>3300000</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -4087,15 +4221,15 @@
         <v>35</v>
       </c>
       <c r="E110" s="23">
-        <v>8000000</v>
+        <v>3800000</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -4103,15 +4237,15 @@
         <v>35</v>
       </c>
       <c r="E111" s="23">
-        <v>8900000</v>
+        <v>4500000</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -4119,7 +4253,7 @@
         <v>35</v>
       </c>
       <c r="E112" s="23">
-        <v>9600000</v>
+        <v>4800000</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>8</v>
@@ -4127,7 +4261,7 @@
     </row>
     <row r="113" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -4135,7 +4269,7 @@
         <v>35</v>
       </c>
       <c r="E113" s="23">
-        <v>10680000</v>
+        <v>5200000</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>8</v>
@@ -4143,7 +4277,7 @@
     </row>
     <row r="114" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -4151,7 +4285,7 @@
         <v>35</v>
       </c>
       <c r="E114" s="23">
-        <v>11680000</v>
+        <v>5600000</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>8</v>
@@ -4159,7 +4293,7 @@
     </row>
     <row r="115" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -4167,167 +4301,135 @@
         <v>35</v>
       </c>
       <c r="E115" s="23">
+        <v>6500000</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A116" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="23">
+        <v>7200000</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B117" s="6"/>
+      <c r="C117" s="6"/>
+      <c r="D117" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="23">
+        <v>7600000</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A118" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="23">
+        <v>8000000</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A119" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="23">
+        <v>8900000</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A120" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B120" s="6"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="23">
+        <v>9600000</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A121" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B121" s="6"/>
+      <c r="C121" s="6"/>
+      <c r="D121" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="23">
+        <v>10680000</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A122" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="23">
+        <v>11680000</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A123" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B123" s="6"/>
+      <c r="C123" s="6"/>
+      <c r="D123" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="23">
         <v>12500000</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A116" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B116" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E116" s="23">
-        <v>240000</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A117" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B117" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C117" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E117" s="23">
-        <v>320000</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A118" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B118" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C118" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E118" s="23">
-        <v>420000</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A119" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B119" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C119" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E119" s="23">
-        <v>500000</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A120" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B120" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" s="23">
-        <v>620000</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A121" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B121" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C121" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E121" s="23">
-        <v>660000</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A122" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B122" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C122" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E122" s="23">
-        <v>840000</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A123" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B123" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C123" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E123" s="23">
-        <v>890000</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>8</v>
@@ -4335,7 +4437,7 @@
     </row>
     <row r="124" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B124" s="34" t="s">
         <v>9</v>
@@ -4347,7 +4449,7 @@
         <v>35</v>
       </c>
       <c r="E124" s="23">
-        <v>1980000</v>
+        <v>240000</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>8</v>
@@ -4355,7 +4457,7 @@
     </row>
     <row r="125" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B125" s="34" t="s">
         <v>9</v>
@@ -4367,7 +4469,7 @@
         <v>35</v>
       </c>
       <c r="E125" s="23">
-        <v>2100000</v>
+        <v>320000</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>8</v>
@@ -4375,7 +4477,7 @@
     </row>
     <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B126" s="34" t="s">
         <v>9</v>
@@ -4387,7 +4489,7 @@
         <v>35</v>
       </c>
       <c r="E126" s="23">
-        <v>2250000</v>
+        <v>420000</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>8</v>
@@ -4395,7 +4497,7 @@
     </row>
     <row r="127" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B127" s="34" t="s">
         <v>9</v>
@@ -4407,7 +4509,7 @@
         <v>35</v>
       </c>
       <c r="E127" s="23">
-        <v>2490000</v>
+        <v>500000</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>8</v>
@@ -4415,7 +4517,7 @@
     </row>
     <row r="128" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B128" s="34" t="s">
         <v>9</v>
@@ -4427,7 +4529,7 @@
         <v>35</v>
       </c>
       <c r="E128" s="23">
-        <v>2640000</v>
+        <v>620000</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>8</v>
@@ -4435,7 +4537,7 @@
     </row>
     <row r="129" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B129" s="34" t="s">
         <v>9</v>
@@ -4447,7 +4549,7 @@
         <v>35</v>
       </c>
       <c r="E129" s="23">
-        <v>2850000</v>
+        <v>660000</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>8</v>
@@ -4455,7 +4557,7 @@
     </row>
     <row r="130" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B130" s="34" t="s">
         <v>9</v>
@@ -4467,7 +4569,7 @@
         <v>35</v>
       </c>
       <c r="E130" s="23">
-        <v>3090000</v>
+        <v>840000</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>8</v>
@@ -4475,7 +4577,7 @@
     </row>
     <row r="131" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B131" s="34" t="s">
         <v>9</v>
@@ -4487,7 +4589,7 @@
         <v>35</v>
       </c>
       <c r="E131" s="23">
-        <v>3450000</v>
+        <v>890000</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>8</v>
@@ -4495,7 +4597,7 @@
     </row>
     <row r="132" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B132" s="34" t="s">
         <v>9</v>
@@ -4507,7 +4609,7 @@
         <v>35</v>
       </c>
       <c r="E132" s="23">
-        <v>7600000</v>
+        <v>1980000</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>8</v>
@@ -4515,7 +4617,7 @@
     </row>
     <row r="133" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B133" s="34" t="s">
         <v>9</v>
@@ -4527,7 +4629,7 @@
         <v>35</v>
       </c>
       <c r="E133" s="23">
-        <v>8000000</v>
+        <v>2100000</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>8</v>
@@ -4535,7 +4637,7 @@
     </row>
     <row r="134" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B134" s="34" t="s">
         <v>9</v>
@@ -4547,7 +4649,7 @@
         <v>35</v>
       </c>
       <c r="E134" s="23">
-        <v>8900000</v>
+        <v>2250000</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>8</v>
@@ -4555,7 +4657,7 @@
     </row>
     <row r="135" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B135" s="34" t="s">
         <v>9</v>
@@ -4567,7 +4669,7 @@
         <v>35</v>
       </c>
       <c r="E135" s="23">
-        <v>9600000</v>
+        <v>2490000</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>8</v>
@@ -4575,7 +4677,7 @@
     </row>
     <row r="136" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B136" s="34" t="s">
         <v>9</v>
@@ -4587,7 +4689,7 @@
         <v>35</v>
       </c>
       <c r="E136" s="23">
-        <v>10680000</v>
+        <v>2640000</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>8</v>
@@ -4595,7 +4697,7 @@
     </row>
     <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B137" s="34" t="s">
         <v>9</v>
@@ -4607,7 +4709,7 @@
         <v>35</v>
       </c>
       <c r="E137" s="23">
-        <v>11680000</v>
+        <v>2850000</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>8</v>
@@ -4615,7 +4717,7 @@
     </row>
     <row r="138" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B138" s="34" t="s">
         <v>9</v>
@@ -4627,135 +4729,167 @@
         <v>35</v>
       </c>
       <c r="E138" s="23">
+        <v>3090000</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A139" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B139" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="23">
+        <v>3450000</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A140" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B140" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" s="23">
+        <v>7600000</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A141" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B141" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="23">
+        <v>8000000</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A142" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B142" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="23">
+        <v>8900000</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A143" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B143" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="23">
+        <v>9600000</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A144" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B144" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="23">
+        <v>10680000</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A145" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B145" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="23">
+        <v>11680000</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A146" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B146" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E146" s="23">
         <v>13680000</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A139" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E139" s="23">
-        <v>800000</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A140" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E140" s="23">
-        <v>1000000</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A141" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E141" s="23">
-        <v>1008000</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A142" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E142" s="23">
-        <v>1200000</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A143" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E143" s="23">
-        <v>1488000</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A144" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E144" s="23">
-        <v>1584000</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A145" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E145" s="23">
-        <v>2016000</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A146" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E146" s="23">
-        <v>2136000</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>8</v>
@@ -4763,7 +4897,7 @@
     </row>
     <row r="147" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
@@ -4771,7 +4905,7 @@
         <v>35</v>
       </c>
       <c r="E147" s="23">
-        <v>3000000</v>
+        <v>800000</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>8</v>
@@ -4779,7 +4913,7 @@
     </row>
     <row r="148" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
@@ -4787,7 +4921,7 @@
         <v>35</v>
       </c>
       <c r="E148" s="23">
-        <v>3780000</v>
+        <v>1000000</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>8</v>
@@ -4795,7 +4929,7 @@
     </row>
     <row r="149" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
@@ -4803,7 +4937,7 @@
         <v>35</v>
       </c>
       <c r="E149" s="23">
-        <v>4050000</v>
+        <v>1008000</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>8</v>
@@ -4811,7 +4945,7 @@
     </row>
     <row r="150" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
@@ -4819,7 +4953,7 @@
         <v>35</v>
       </c>
       <c r="E150" s="23">
-        <v>4482000</v>
+        <v>1200000</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>8</v>
@@ -4827,7 +4961,7 @@
     </row>
     <row r="151" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
@@ -4835,7 +4969,7 @@
         <v>35</v>
       </c>
       <c r="E151" s="23">
-        <v>4752000</v>
+        <v>1488000</v>
       </c>
       <c r="F151" s="6" t="s">
         <v>8</v>
@@ -4843,7 +4977,7 @@
     </row>
     <row r="152" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
@@ -4851,7 +4985,7 @@
         <v>35</v>
       </c>
       <c r="E152" s="23">
-        <v>5130000</v>
+        <v>1584000</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>8</v>
@@ -4859,7 +4993,7 @@
     </row>
     <row r="153" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
@@ -4867,7 +5001,7 @@
         <v>35</v>
       </c>
       <c r="E153" s="23">
-        <v>5562000</v>
+        <v>2016000</v>
       </c>
       <c r="F153" s="6" t="s">
         <v>8</v>
@@ -4875,7 +5009,7 @@
     </row>
     <row r="154" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -4883,7 +5017,7 @@
         <v>35</v>
       </c>
       <c r="E154" s="23">
-        <v>6210000</v>
+        <v>2136000</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>8</v>
@@ -4891,7 +5025,7 @@
     </row>
     <row r="155" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -4899,7 +5033,7 @@
         <v>35</v>
       </c>
       <c r="E155" s="23">
-        <v>13680000</v>
+        <v>3000000</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>8</v>
@@ -4907,7 +5041,7 @@
     </row>
     <row r="156" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -4915,7 +5049,7 @@
         <v>35</v>
       </c>
       <c r="E156" s="23">
-        <v>14400000</v>
+        <v>3780000</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>8</v>
@@ -4923,7 +5057,7 @@
     </row>
     <row r="157" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -4931,7 +5065,7 @@
         <v>35</v>
       </c>
       <c r="E157" s="23">
-        <v>16020000</v>
+        <v>4050000</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>8</v>
@@ -4939,7 +5073,7 @@
     </row>
     <row r="158" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -4947,7 +5081,7 @@
         <v>35</v>
       </c>
       <c r="E158" s="23">
-        <v>17280000</v>
+        <v>4482000</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>8</v>
@@ -4955,7 +5089,7 @@
     </row>
     <row r="159" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -4963,7 +5097,7 @@
         <v>35</v>
       </c>
       <c r="E159" s="23">
-        <v>19224000</v>
+        <v>4752000</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>8</v>
@@ -4971,7 +5105,7 @@
     </row>
     <row r="160" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -4979,7 +5113,7 @@
         <v>35</v>
       </c>
       <c r="E160" s="23">
-        <v>21024000</v>
+        <v>5130000</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>8</v>
@@ -4987,7 +5121,7 @@
     </row>
     <row r="161" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -4995,167 +5129,135 @@
         <v>35</v>
       </c>
       <c r="E161" s="23">
+        <v>5562000</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A162" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B162" s="6"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="23">
+        <v>6210000</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A163" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B163" s="6"/>
+      <c r="C163" s="6"/>
+      <c r="D163" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" s="23">
+        <v>13680000</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A164" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B164" s="6"/>
+      <c r="C164" s="6"/>
+      <c r="D164" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" s="23">
+        <v>14400000</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A165" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B165" s="6"/>
+      <c r="C165" s="6"/>
+      <c r="D165" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" s="23">
+        <v>16020000</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A166" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B166" s="6"/>
+      <c r="C166" s="6"/>
+      <c r="D166" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E166" s="23">
+        <v>17280000</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B167" s="6"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" s="23">
+        <v>19224000</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A168" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B168" s="6"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E168" s="23">
+        <v>21024000</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A169" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B169" s="6"/>
+      <c r="C169" s="6"/>
+      <c r="D169" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E169" s="23">
         <v>24624000</v>
-      </c>
-      <c r="F161" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A162" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C162" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E162" s="23">
-        <v>15000</v>
-      </c>
-      <c r="F162" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A163" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C163" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E163" s="23">
-        <v>19500</v>
-      </c>
-      <c r="F163" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A164" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C164" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E164" s="23">
-        <v>25000</v>
-      </c>
-      <c r="F164" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A165" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C165" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D165" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E165" s="23">
-        <v>30000</v>
-      </c>
-      <c r="F165" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A166" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C166" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D166" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E166" s="23">
-        <v>40000</v>
-      </c>
-      <c r="F166" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A167" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C167" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E167" s="23">
-        <v>45000</v>
-      </c>
-      <c r="F167" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A168" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C168" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D168" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E168" s="23">
-        <v>78000</v>
-      </c>
-      <c r="F168" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A169" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C169" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D169" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E169" s="23">
-        <v>87000</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>8</v>
@@ -5163,7 +5265,7 @@
     </row>
     <row r="170" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>9</v>
@@ -5175,7 +5277,7 @@
         <v>35</v>
       </c>
       <c r="E170" s="23">
-        <v>96000</v>
+        <v>15000</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>8</v>
@@ -5183,7 +5285,7 @@
     </row>
     <row r="171" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>9</v>
@@ -5195,7 +5297,7 @@
         <v>35</v>
       </c>
       <c r="E171" s="23">
-        <v>105000</v>
+        <v>19500</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>8</v>
@@ -5203,7 +5305,7 @@
     </row>
     <row r="172" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>9</v>
@@ -5215,7 +5317,7 @@
         <v>35</v>
       </c>
       <c r="E172" s="23">
-        <v>114000</v>
+        <v>25000</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>8</v>
@@ -5223,7 +5325,7 @@
     </row>
     <row r="173" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>9</v>
@@ -5235,7 +5337,7 @@
         <v>35</v>
       </c>
       <c r="E173" s="23">
-        <v>142500</v>
+        <v>30000</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>8</v>
@@ -5243,7 +5345,7 @@
     </row>
     <row r="174" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>9</v>
@@ -5255,7 +5357,7 @@
         <v>35</v>
       </c>
       <c r="E174" s="23">
-        <v>153000</v>
+        <v>40000</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>8</v>
@@ -5263,7 +5365,7 @@
     </row>
     <row r="175" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>9</v>
@@ -5275,7 +5377,7 @@
         <v>35</v>
       </c>
       <c r="E175" s="23">
-        <v>163500</v>
+        <v>45000</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>8</v>
@@ -5283,7 +5385,7 @@
     </row>
     <row r="176" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>9</v>
@@ -5295,7 +5397,7 @@
         <v>35</v>
       </c>
       <c r="E176" s="23">
-        <v>232500</v>
+        <v>78000</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>8</v>
@@ -5303,7 +5405,7 @@
     </row>
     <row r="177" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>9</v>
@@ -5315,7 +5417,7 @@
         <v>35</v>
       </c>
       <c r="E177" s="23">
-        <v>247500</v>
+        <v>87000</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>8</v>
@@ -5323,7 +5425,7 @@
     </row>
     <row r="178" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>9</v>
@@ -5335,7 +5437,7 @@
         <v>35</v>
       </c>
       <c r="E178" s="23">
-        <v>295500</v>
+        <v>96000</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>8</v>
@@ -5343,7 +5445,7 @@
     </row>
     <row r="179" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>9</v>
@@ -5355,7 +5457,7 @@
         <v>35</v>
       </c>
       <c r="E179" s="23">
-        <v>312000</v>
+        <v>105000</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>8</v>
@@ -5363,7 +5465,7 @@
     </row>
     <row r="180" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>9</v>
@@ -5375,7 +5477,7 @@
         <v>35</v>
       </c>
       <c r="E180" s="23">
-        <v>410000</v>
+        <v>114000</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>8</v>
@@ -5383,7 +5485,7 @@
     </row>
     <row r="181" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>9</v>
@@ -5395,7 +5497,7 @@
         <v>35</v>
       </c>
       <c r="E181" s="23">
-        <v>434000</v>
+        <v>142500</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>8</v>
@@ -5403,7 +5505,7 @@
     </row>
     <row r="182" spans="1:29" ht="51" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>9</v>
@@ -5415,359 +5517,175 @@
         <v>35</v>
       </c>
       <c r="E182" s="23">
+        <v>153000</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A183" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E183" s="23">
+        <v>163500</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A184" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C184" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E184" s="23">
+        <v>232500</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A185" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E185" s="23">
+        <v>247500</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A186" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C186" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E186" s="23">
+        <v>295500</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A187" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C187" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E187" s="23">
+        <v>312000</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A188" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C188" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E188" s="23">
+        <v>410000</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A189" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C189" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E189" s="23">
+        <v>434000</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A190" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E190" s="23">
         <v>469500</v>
       </c>
-      <c r="F182" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="183" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="7" t="s">
+      <c r="F190" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="B183" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C183" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D183" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E183" s="23">
-        <v>19860000</v>
-      </c>
-      <c r="F183" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G183" s="28"/>
-      <c r="H183" s="28"/>
-      <c r="I183" s="28"/>
-      <c r="J183" s="28"/>
-      <c r="K183" s="28"/>
-      <c r="L183" s="28"/>
-      <c r="M183" s="28"/>
-      <c r="N183" s="28"/>
-      <c r="O183" s="28"/>
-      <c r="P183" s="28"/>
-      <c r="Q183" s="28"/>
-      <c r="R183" s="28"/>
-      <c r="S183" s="28"/>
-      <c r="T183" s="28"/>
-      <c r="U183" s="28"/>
-      <c r="V183" s="28"/>
-      <c r="W183" s="28"/>
-      <c r="X183" s="28"/>
-      <c r="Y183" s="28"/>
-      <c r="Z183" s="28"/>
-      <c r="AA183" s="28"/>
-      <c r="AB183" s="28"/>
-      <c r="AC183" s="28"/>
-    </row>
-    <row r="184" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B184" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C184" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D184" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E184" s="23">
-        <v>24980000</v>
-      </c>
-      <c r="F184" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G184" s="28"/>
-      <c r="H184" s="28"/>
-      <c r="I184" s="28"/>
-      <c r="J184" s="28"/>
-      <c r="K184" s="28"/>
-      <c r="L184" s="28"/>
-      <c r="M184" s="28"/>
-      <c r="N184" s="28"/>
-      <c r="O184" s="28"/>
-      <c r="P184" s="28"/>
-      <c r="Q184" s="28"/>
-      <c r="R184" s="28"/>
-      <c r="S184" s="28"/>
-      <c r="T184" s="28"/>
-      <c r="U184" s="28"/>
-      <c r="V184" s="28"/>
-      <c r="W184" s="28"/>
-      <c r="X184" s="28"/>
-      <c r="Y184" s="28"/>
-      <c r="Z184" s="28"/>
-      <c r="AA184" s="28"/>
-      <c r="AB184" s="28"/>
-      <c r="AC184" s="28"/>
-    </row>
-    <row r="185" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B185" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C185" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D185" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E185" s="23">
-        <v>35680000</v>
-      </c>
-      <c r="F185" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G185" s="28"/>
-      <c r="H185" s="28"/>
-      <c r="I185" s="28"/>
-      <c r="J185" s="28"/>
-      <c r="K185" s="28"/>
-      <c r="L185" s="28"/>
-      <c r="M185" s="28"/>
-      <c r="N185" s="28"/>
-      <c r="O185" s="28"/>
-      <c r="P185" s="28"/>
-      <c r="Q185" s="28"/>
-      <c r="R185" s="28"/>
-      <c r="S185" s="28"/>
-      <c r="T185" s="28"/>
-      <c r="U185" s="28"/>
-      <c r="V185" s="28"/>
-      <c r="W185" s="28"/>
-      <c r="X185" s="28"/>
-      <c r="Y185" s="28"/>
-      <c r="Z185" s="28"/>
-      <c r="AA185" s="28"/>
-      <c r="AB185" s="28"/>
-      <c r="AC185" s="28"/>
-    </row>
-    <row r="186" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B186" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D186" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E186" s="23">
-        <v>39860000</v>
-      </c>
-      <c r="F186" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G186" s="28"/>
-      <c r="H186" s="28"/>
-      <c r="I186" s="28"/>
-      <c r="J186" s="28"/>
-      <c r="K186" s="28"/>
-      <c r="L186" s="28"/>
-      <c r="M186" s="28"/>
-      <c r="N186" s="28"/>
-      <c r="O186" s="28"/>
-      <c r="P186" s="28"/>
-      <c r="Q186" s="28"/>
-      <c r="R186" s="28"/>
-      <c r="S186" s="28"/>
-      <c r="T186" s="28"/>
-      <c r="U186" s="28"/>
-      <c r="V186" s="28"/>
-      <c r="W186" s="28"/>
-      <c r="X186" s="28"/>
-      <c r="Y186" s="28"/>
-      <c r="Z186" s="28"/>
-      <c r="AA186" s="28"/>
-      <c r="AB186" s="28"/>
-      <c r="AC186" s="28"/>
-    </row>
-    <row r="187" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B187" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C187" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D187" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E187" s="23">
-        <v>47979000</v>
-      </c>
-      <c r="F187" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G187"/>
-      <c r="H187"/>
-      <c r="I187"/>
-      <c r="J187"/>
-      <c r="K187"/>
-      <c r="L187"/>
-      <c r="M187"/>
-      <c r="N187"/>
-      <c r="O187"/>
-      <c r="P187"/>
-      <c r="Q187"/>
-      <c r="R187"/>
-      <c r="S187"/>
-      <c r="T187"/>
-      <c r="U187"/>
-      <c r="V187"/>
-      <c r="W187"/>
-      <c r="X187"/>
-      <c r="Y187"/>
-      <c r="Z187"/>
-      <c r="AA187"/>
-      <c r="AB187"/>
-      <c r="AC187"/>
-    </row>
-    <row r="188" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C188" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D188" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E188" s="23">
-        <v>52680000</v>
-      </c>
-      <c r="F188" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G188" s="28"/>
-      <c r="H188" s="28"/>
-      <c r="I188" s="28"/>
-      <c r="J188" s="28"/>
-      <c r="K188" s="28"/>
-      <c r="L188" s="28"/>
-      <c r="M188" s="28"/>
-      <c r="N188" s="28"/>
-      <c r="O188" s="28"/>
-      <c r="P188" s="28"/>
-      <c r="Q188" s="28"/>
-      <c r="R188" s="28"/>
-      <c r="S188" s="28"/>
-      <c r="T188" s="28"/>
-      <c r="U188" s="28"/>
-      <c r="V188" s="28"/>
-      <c r="W188" s="28"/>
-      <c r="X188" s="28"/>
-      <c r="Y188" s="28"/>
-      <c r="Z188" s="28"/>
-      <c r="AA188" s="28"/>
-      <c r="AB188" s="28"/>
-      <c r="AC188" s="28"/>
-    </row>
-    <row r="189" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B189" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C189" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D189" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E189" s="23">
-        <v>62680000</v>
-      </c>
-      <c r="F189" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G189" s="28"/>
-      <c r="H189" s="28"/>
-      <c r="I189" s="28"/>
-      <c r="J189" s="28"/>
-      <c r="K189" s="28"/>
-      <c r="L189" s="28"/>
-      <c r="M189" s="28"/>
-      <c r="N189" s="28"/>
-      <c r="O189" s="28"/>
-      <c r="P189" s="28"/>
-      <c r="Q189" s="28"/>
-      <c r="R189" s="28"/>
-      <c r="S189" s="28"/>
-      <c r="T189" s="28"/>
-      <c r="U189" s="28"/>
-      <c r="V189" s="28"/>
-      <c r="W189" s="28"/>
-      <c r="X189" s="28"/>
-      <c r="Y189" s="28"/>
-      <c r="Z189" s="28"/>
-      <c r="AA189" s="28"/>
-      <c r="AB189" s="28"/>
-      <c r="AC189" s="28"/>
-    </row>
-    <row r="190" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B190" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C190" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D190" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E190" s="23">
-        <v>68680000</v>
-      </c>
-      <c r="F190" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G190" s="28"/>
-      <c r="H190" s="28"/>
-      <c r="I190" s="28"/>
-      <c r="J190" s="28"/>
-      <c r="K190" s="28"/>
-      <c r="L190" s="28"/>
-      <c r="M190" s="28"/>
-      <c r="N190" s="28"/>
-      <c r="O190" s="28"/>
-      <c r="P190" s="28"/>
-      <c r="Q190" s="28"/>
-      <c r="R190" s="28"/>
-      <c r="S190" s="28"/>
-      <c r="T190" s="28"/>
-      <c r="U190" s="28"/>
-      <c r="V190" s="28"/>
-      <c r="W190" s="28"/>
-      <c r="X190" s="28"/>
-      <c r="Y190" s="28"/>
-      <c r="Z190" s="28"/>
-      <c r="AA190" s="28"/>
-      <c r="AB190" s="28"/>
-      <c r="AC190" s="28"/>
-    </row>
-    <row r="191" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="7" t="s">
-        <v>196</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>9</v>
@@ -5779,7 +5697,7 @@
         <v>35</v>
       </c>
       <c r="E191" s="23">
-        <v>75500000</v>
+        <v>19860000</v>
       </c>
       <c r="F191" s="13" t="s">
         <v>8</v>
@@ -5808,9 +5726,9 @@
       <c r="AB191" s="28"/>
       <c r="AC191" s="28"/>
     </row>
-    <row r="192" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B192" s="8" t="s">
         <v>9</v>
@@ -5822,7 +5740,7 @@
         <v>35</v>
       </c>
       <c r="E192" s="23">
-        <v>89580000</v>
+        <v>24980000</v>
       </c>
       <c r="F192" s="13" t="s">
         <v>8</v>
@@ -5851,9 +5769,9 @@
       <c r="AB192" s="28"/>
       <c r="AC192" s="28"/>
     </row>
-    <row r="193" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B193" s="8" t="s">
         <v>9</v>
@@ -5865,7 +5783,7 @@
         <v>35</v>
       </c>
       <c r="E193" s="23">
-        <v>99880000</v>
+        <v>35680000</v>
       </c>
       <c r="F193" s="13" t="s">
         <v>8</v>
@@ -5894,9 +5812,9 @@
       <c r="AB193" s="28"/>
       <c r="AC193" s="28"/>
     </row>
-    <row r="194" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B194" s="8" t="s">
         <v>9</v>
@@ -5908,7 +5826,7 @@
         <v>35</v>
       </c>
       <c r="E194" s="23">
-        <v>109680000</v>
+        <v>39860000</v>
       </c>
       <c r="F194" s="13" t="s">
         <v>8</v>
@@ -5937,9 +5855,9 @@
       <c r="AB194" s="28"/>
       <c r="AC194" s="28"/>
     </row>
-    <row r="195" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B195" s="8" t="s">
         <v>9</v>
@@ -5951,38 +5869,38 @@
         <v>35</v>
       </c>
       <c r="E195" s="23">
-        <v>129860000</v>
+        <v>47979000</v>
       </c>
       <c r="F195" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G195" s="28"/>
-      <c r="H195" s="28"/>
-      <c r="I195" s="28"/>
-      <c r="J195" s="28"/>
-      <c r="K195" s="28"/>
-      <c r="L195" s="28"/>
-      <c r="M195" s="28"/>
-      <c r="N195" s="28"/>
-      <c r="O195" s="28"/>
-      <c r="P195" s="28"/>
-      <c r="Q195" s="28"/>
-      <c r="R195" s="28"/>
-      <c r="S195" s="28"/>
-      <c r="T195" s="28"/>
-      <c r="U195" s="28"/>
-      <c r="V195" s="28"/>
-      <c r="W195" s="28"/>
-      <c r="X195" s="28"/>
-      <c r="Y195" s="28"/>
-      <c r="Z195" s="28"/>
-      <c r="AA195" s="28"/>
-      <c r="AB195" s="28"/>
-      <c r="AC195" s="28"/>
-    </row>
-    <row r="196" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G195"/>
+      <c r="H195"/>
+      <c r="I195"/>
+      <c r="J195"/>
+      <c r="K195"/>
+      <c r="L195"/>
+      <c r="M195"/>
+      <c r="N195"/>
+      <c r="O195"/>
+      <c r="P195"/>
+      <c r="Q195"/>
+      <c r="R195"/>
+      <c r="S195"/>
+      <c r="T195"/>
+      <c r="U195"/>
+      <c r="V195"/>
+      <c r="W195"/>
+      <c r="X195"/>
+      <c r="Y195"/>
+      <c r="Z195"/>
+      <c r="AA195"/>
+      <c r="AB195"/>
+      <c r="AC195"/>
+    </row>
+    <row r="196" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B196" s="8" t="s">
         <v>9</v>
@@ -5994,7 +5912,7 @@
         <v>35</v>
       </c>
       <c r="E196" s="23">
-        <v>144910000</v>
+        <v>52680000</v>
       </c>
       <c r="F196" s="13" t="s">
         <v>8</v>
@@ -6023,9 +5941,9 @@
       <c r="AB196" s="28"/>
       <c r="AC196" s="28"/>
     </row>
-    <row r="197" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B197" s="8" t="s">
         <v>9</v>
@@ -6037,7 +5955,7 @@
         <v>35</v>
       </c>
       <c r="E197" s="23">
-        <v>155910000</v>
+        <v>62680000</v>
       </c>
       <c r="F197" s="13" t="s">
         <v>8</v>
@@ -6066,9 +5984,9 @@
       <c r="AB197" s="28"/>
       <c r="AC197" s="28"/>
     </row>
-    <row r="198" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B198" s="8" t="s">
         <v>9</v>
@@ -6080,7 +5998,7 @@
         <v>35</v>
       </c>
       <c r="E198" s="23">
-        <v>156560000</v>
+        <v>68680000</v>
       </c>
       <c r="F198" s="13" t="s">
         <v>8</v>
@@ -6111,7 +6029,7 @@
     </row>
     <row r="199" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B199" s="8" t="s">
         <v>9</v>
@@ -6123,7 +6041,7 @@
         <v>35</v>
       </c>
       <c r="E199" s="23">
-        <v>184370000</v>
+        <v>75500000</v>
       </c>
       <c r="F199" s="13" t="s">
         <v>8</v>
@@ -6154,7 +6072,7 @@
     </row>
     <row r="200" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>9</v>
@@ -6166,7 +6084,7 @@
         <v>35</v>
       </c>
       <c r="E200" s="23">
-        <v>243080000</v>
+        <v>89580000</v>
       </c>
       <c r="F200" s="13" t="s">
         <v>8</v>
@@ -6197,7 +6115,7 @@
     </row>
     <row r="201" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>9</v>
@@ -6209,7 +6127,7 @@
         <v>35</v>
       </c>
       <c r="E201" s="23">
-        <v>276040000</v>
+        <v>99880000</v>
       </c>
       <c r="F201" s="13" t="s">
         <v>8</v>
@@ -6240,7 +6158,7 @@
     </row>
     <row r="202" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>9</v>
@@ -6252,7 +6170,7 @@
         <v>35</v>
       </c>
       <c r="E202" s="23">
-        <v>313680000</v>
+        <v>109680000</v>
       </c>
       <c r="F202" s="13" t="s">
         <v>8</v>
@@ -6283,7 +6201,7 @@
     </row>
     <row r="203" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>9</v>
@@ -6295,7 +6213,7 @@
         <v>35</v>
       </c>
       <c r="E203" s="23">
-        <v>358200000</v>
+        <v>129860000</v>
       </c>
       <c r="F203" s="13" t="s">
         <v>8</v>
@@ -6326,7 +6244,7 @@
     </row>
     <row r="204" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B204" s="8" t="s">
         <v>9</v>
@@ -6338,7 +6256,7 @@
         <v>35</v>
       </c>
       <c r="E204" s="23">
-        <v>389600000</v>
+        <v>144910000</v>
       </c>
       <c r="F204" s="13" t="s">
         <v>8</v>
@@ -6369,7 +6287,7 @@
     </row>
     <row r="205" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>9</v>
@@ -6381,7 +6299,7 @@
         <v>35</v>
       </c>
       <c r="E205" s="23">
-        <v>433800000</v>
+        <v>155910000</v>
       </c>
       <c r="F205" s="13" t="s">
         <v>8</v>
@@ -6412,7 +6330,7 @@
     </row>
     <row r="206" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>9</v>
@@ -6424,7 +6342,7 @@
         <v>35</v>
       </c>
       <c r="E206" s="23">
-        <v>656580000</v>
+        <v>156560000</v>
       </c>
       <c r="F206" s="13" t="s">
         <v>8</v>
@@ -6455,7 +6373,7 @@
     </row>
     <row r="207" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>9</v>
@@ -6467,7 +6385,7 @@
         <v>35</v>
       </c>
       <c r="E207" s="23">
-        <v>762670000</v>
+        <v>184370000</v>
       </c>
       <c r="F207" s="13" t="s">
         <v>8</v>
@@ -6498,7 +6416,7 @@
     </row>
     <row r="208" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B208" s="8" t="s">
         <v>9</v>
@@ -6510,7 +6428,7 @@
         <v>35</v>
       </c>
       <c r="E208" s="23">
-        <v>874940000</v>
+        <v>243080000</v>
       </c>
       <c r="F208" s="13" t="s">
         <v>8</v>
@@ -6541,7 +6459,7 @@
     </row>
     <row r="209" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B209" s="8" t="s">
         <v>9</v>
@@ -6553,7 +6471,7 @@
         <v>35</v>
       </c>
       <c r="E209" s="23">
-        <v>1062400000</v>
+        <v>276040000</v>
       </c>
       <c r="F209" s="13" t="s">
         <v>8</v>
@@ -6582,359 +6500,367 @@
       <c r="AB209" s="28"/>
       <c r="AC209" s="28"/>
     </row>
-    <row r="210" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="11" t="s">
+    <row r="210" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D210" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E210" s="23">
+        <v>313680000</v>
+      </c>
+      <c r="F210" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G210" s="28"/>
+      <c r="H210" s="28"/>
+      <c r="I210" s="28"/>
+      <c r="J210" s="28"/>
+      <c r="K210" s="28"/>
+      <c r="L210" s="28"/>
+      <c r="M210" s="28"/>
+      <c r="N210" s="28"/>
+      <c r="O210" s="28"/>
+      <c r="P210" s="28"/>
+      <c r="Q210" s="28"/>
+      <c r="R210" s="28"/>
+      <c r="S210" s="28"/>
+      <c r="T210" s="28"/>
+      <c r="U210" s="28"/>
+      <c r="V210" s="28"/>
+      <c r="W210" s="28"/>
+      <c r="X210" s="28"/>
+      <c r="Y210" s="28"/>
+      <c r="Z210" s="28"/>
+      <c r="AA210" s="28"/>
+      <c r="AB210" s="28"/>
+      <c r="AC210" s="28"/>
+    </row>
+    <row r="211" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B211" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D211" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E211" s="23">
+        <v>358200000</v>
+      </c>
+      <c r="F211" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G211" s="28"/>
+      <c r="H211" s="28"/>
+      <c r="I211" s="28"/>
+      <c r="J211" s="28"/>
+      <c r="K211" s="28"/>
+      <c r="L211" s="28"/>
+      <c r="M211" s="28"/>
+      <c r="N211" s="28"/>
+      <c r="O211" s="28"/>
+      <c r="P211" s="28"/>
+      <c r="Q211" s="28"/>
+      <c r="R211" s="28"/>
+      <c r="S211" s="28"/>
+      <c r="T211" s="28"/>
+      <c r="U211" s="28"/>
+      <c r="V211" s="28"/>
+      <c r="W211" s="28"/>
+      <c r="X211" s="28"/>
+      <c r="Y211" s="28"/>
+      <c r="Z211" s="28"/>
+      <c r="AA211" s="28"/>
+      <c r="AB211" s="28"/>
+      <c r="AC211" s="28"/>
+    </row>
+    <row r="212" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D212" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E212" s="23">
+        <v>389600000</v>
+      </c>
+      <c r="F212" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G212" s="28"/>
+      <c r="H212" s="28"/>
+      <c r="I212" s="28"/>
+      <c r="J212" s="28"/>
+      <c r="K212" s="28"/>
+      <c r="L212" s="28"/>
+      <c r="M212" s="28"/>
+      <c r="N212" s="28"/>
+      <c r="O212" s="28"/>
+      <c r="P212" s="28"/>
+      <c r="Q212" s="28"/>
+      <c r="R212" s="28"/>
+      <c r="S212" s="28"/>
+      <c r="T212" s="28"/>
+      <c r="U212" s="28"/>
+      <c r="V212" s="28"/>
+      <c r="W212" s="28"/>
+      <c r="X212" s="28"/>
+      <c r="Y212" s="28"/>
+      <c r="Z212" s="28"/>
+      <c r="AA212" s="28"/>
+      <c r="AB212" s="28"/>
+      <c r="AC212" s="28"/>
+    </row>
+    <row r="213" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B213" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C213" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D213" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E213" s="23">
+        <v>433800000</v>
+      </c>
+      <c r="F213" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G213" s="28"/>
+      <c r="H213" s="28"/>
+      <c r="I213" s="28"/>
+      <c r="J213" s="28"/>
+      <c r="K213" s="28"/>
+      <c r="L213" s="28"/>
+      <c r="M213" s="28"/>
+      <c r="N213" s="28"/>
+      <c r="O213" s="28"/>
+      <c r="P213" s="28"/>
+      <c r="Q213" s="28"/>
+      <c r="R213" s="28"/>
+      <c r="S213" s="28"/>
+      <c r="T213" s="28"/>
+      <c r="U213" s="28"/>
+      <c r="V213" s="28"/>
+      <c r="W213" s="28"/>
+      <c r="X213" s="28"/>
+      <c r="Y213" s="28"/>
+      <c r="Z213" s="28"/>
+      <c r="AA213" s="28"/>
+      <c r="AB213" s="28"/>
+      <c r="AC213" s="28"/>
+    </row>
+    <row r="214" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D214" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E214" s="23">
+        <v>656580000</v>
+      </c>
+      <c r="F214" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G214" s="28"/>
+      <c r="H214" s="28"/>
+      <c r="I214" s="28"/>
+      <c r="J214" s="28"/>
+      <c r="K214" s="28"/>
+      <c r="L214" s="28"/>
+      <c r="M214" s="28"/>
+      <c r="N214" s="28"/>
+      <c r="O214" s="28"/>
+      <c r="P214" s="28"/>
+      <c r="Q214" s="28"/>
+      <c r="R214" s="28"/>
+      <c r="S214" s="28"/>
+      <c r="T214" s="28"/>
+      <c r="U214" s="28"/>
+      <c r="V214" s="28"/>
+      <c r="W214" s="28"/>
+      <c r="X214" s="28"/>
+      <c r="Y214" s="28"/>
+      <c r="Z214" s="28"/>
+      <c r="AA214" s="28"/>
+      <c r="AB214" s="28"/>
+      <c r="AC214" s="28"/>
+    </row>
+    <row r="215" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C215" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D215" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E215" s="23">
+        <v>762670000</v>
+      </c>
+      <c r="F215" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G215" s="28"/>
+      <c r="H215" s="28"/>
+      <c r="I215" s="28"/>
+      <c r="J215" s="28"/>
+      <c r="K215" s="28"/>
+      <c r="L215" s="28"/>
+      <c r="M215" s="28"/>
+      <c r="N215" s="28"/>
+      <c r="O215" s="28"/>
+      <c r="P215" s="28"/>
+      <c r="Q215" s="28"/>
+      <c r="R215" s="28"/>
+      <c r="S215" s="28"/>
+      <c r="T215" s="28"/>
+      <c r="U215" s="28"/>
+      <c r="V215" s="28"/>
+      <c r="W215" s="28"/>
+      <c r="X215" s="28"/>
+      <c r="Y215" s="28"/>
+      <c r="Z215" s="28"/>
+      <c r="AA215" s="28"/>
+      <c r="AB215" s="28"/>
+      <c r="AC215" s="28"/>
+    </row>
+    <row r="216" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D216" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E216" s="23">
+        <v>874940000</v>
+      </c>
+      <c r="F216" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G216" s="28"/>
+      <c r="H216" s="28"/>
+      <c r="I216" s="28"/>
+      <c r="J216" s="28"/>
+      <c r="K216" s="28"/>
+      <c r="L216" s="28"/>
+      <c r="M216" s="28"/>
+      <c r="N216" s="28"/>
+      <c r="O216" s="28"/>
+      <c r="P216" s="28"/>
+      <c r="Q216" s="28"/>
+      <c r="R216" s="28"/>
+      <c r="S216" s="28"/>
+      <c r="T216" s="28"/>
+      <c r="U216" s="28"/>
+      <c r="V216" s="28"/>
+      <c r="W216" s="28"/>
+      <c r="X216" s="28"/>
+      <c r="Y216" s="28"/>
+      <c r="Z216" s="28"/>
+      <c r="AA216" s="28"/>
+      <c r="AB216" s="28"/>
+      <c r="AC216" s="28"/>
+    </row>
+    <row r="217" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C217" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E217" s="23">
+        <v>1062400000</v>
+      </c>
+      <c r="F217" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G217" s="28"/>
+      <c r="H217" s="28"/>
+      <c r="I217" s="28"/>
+      <c r="J217" s="28"/>
+      <c r="K217" s="28"/>
+      <c r="L217" s="28"/>
+      <c r="M217" s="28"/>
+      <c r="N217" s="28"/>
+      <c r="O217" s="28"/>
+      <c r="P217" s="28"/>
+      <c r="Q217" s="28"/>
+      <c r="R217" s="28"/>
+      <c r="S217" s="28"/>
+      <c r="T217" s="28"/>
+      <c r="U217" s="28"/>
+      <c r="V217" s="28"/>
+      <c r="W217" s="28"/>
+      <c r="X217" s="28"/>
+      <c r="Y217" s="28"/>
+      <c r="Z217" s="28"/>
+      <c r="AA217" s="28"/>
+      <c r="AB217" s="28"/>
+      <c r="AC217" s="28"/>
+    </row>
+    <row r="218" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="B210" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C210" s="12" t="s">
+      <c r="B218" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D210" s="36" t="s">
+      <c r="D218" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="E210" s="24">
+      <c r="E218" s="24">
         <v>75000</v>
       </c>
-      <c r="F210" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G210"/>
-      <c r="H210"/>
-      <c r="I210"/>
-      <c r="J210"/>
-      <c r="K210"/>
-      <c r="L210"/>
-      <c r="M210"/>
-      <c r="N210"/>
-      <c r="O210"/>
-      <c r="P210"/>
-      <c r="Q210"/>
-      <c r="R210"/>
-      <c r="S210"/>
-      <c r="T210"/>
-      <c r="U210"/>
-      <c r="V210"/>
-      <c r="W210"/>
-      <c r="X210"/>
-      <c r="Y210"/>
-      <c r="Z210"/>
-      <c r="AA210"/>
-      <c r="AB210"/>
-      <c r="AC210"/>
-    </row>
-    <row r="211" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B211" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C211" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D211" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E211" s="24">
-        <v>33000</v>
-      </c>
-      <c r="F211" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G211"/>
-      <c r="H211"/>
-      <c r="I211"/>
-      <c r="J211"/>
-      <c r="K211"/>
-      <c r="L211"/>
-      <c r="M211"/>
-      <c r="N211"/>
-      <c r="O211"/>
-      <c r="P211"/>
-      <c r="Q211"/>
-      <c r="R211"/>
-      <c r="S211"/>
-      <c r="T211"/>
-      <c r="U211"/>
-      <c r="V211"/>
-      <c r="W211"/>
-      <c r="X211"/>
-      <c r="Y211"/>
-      <c r="Z211"/>
-      <c r="AA211"/>
-      <c r="AB211"/>
-      <c r="AC211"/>
-    </row>
-    <row r="212" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="B212" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C212" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D212" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E212" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F212" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G212"/>
-      <c r="H212"/>
-      <c r="I212"/>
-      <c r="J212"/>
-      <c r="K212"/>
-      <c r="L212"/>
-      <c r="M212"/>
-      <c r="N212"/>
-      <c r="O212"/>
-      <c r="P212"/>
-      <c r="Q212"/>
-      <c r="R212"/>
-      <c r="S212"/>
-      <c r="T212"/>
-      <c r="U212"/>
-      <c r="V212"/>
-      <c r="W212"/>
-      <c r="X212"/>
-      <c r="Y212"/>
-      <c r="Z212"/>
-      <c r="AA212"/>
-      <c r="AB212"/>
-      <c r="AC212"/>
-    </row>
-    <row r="213" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B213" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C213" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D213" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E213" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F213" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G213"/>
-      <c r="H213"/>
-      <c r="I213"/>
-      <c r="J213"/>
-      <c r="K213"/>
-      <c r="L213"/>
-      <c r="M213"/>
-      <c r="N213"/>
-      <c r="O213"/>
-      <c r="P213"/>
-      <c r="Q213"/>
-      <c r="R213"/>
-      <c r="S213"/>
-      <c r="T213"/>
-      <c r="U213"/>
-      <c r="V213"/>
-      <c r="W213"/>
-      <c r="X213"/>
-      <c r="Y213"/>
-      <c r="Z213"/>
-      <c r="AA213"/>
-      <c r="AB213"/>
-      <c r="AC213"/>
-    </row>
-    <row r="214" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B214" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C214" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D214" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E214" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F214" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G214"/>
-      <c r="H214"/>
-      <c r="I214"/>
-      <c r="J214"/>
-      <c r="K214"/>
-      <c r="L214"/>
-      <c r="M214"/>
-      <c r="N214"/>
-      <c r="O214"/>
-      <c r="P214"/>
-      <c r="Q214"/>
-      <c r="R214"/>
-      <c r="S214"/>
-      <c r="T214"/>
-      <c r="U214"/>
-      <c r="V214"/>
-      <c r="W214"/>
-      <c r="X214"/>
-      <c r="Y214"/>
-      <c r="Z214"/>
-      <c r="AA214"/>
-      <c r="AB214"/>
-      <c r="AC214"/>
-    </row>
-    <row r="215" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B215" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="C215" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D215" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E215" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F215" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G215"/>
-      <c r="H215"/>
-      <c r="I215"/>
-      <c r="J215"/>
-      <c r="K215"/>
-      <c r="L215"/>
-      <c r="M215"/>
-      <c r="N215"/>
-      <c r="O215"/>
-      <c r="P215"/>
-      <c r="Q215"/>
-      <c r="R215"/>
-      <c r="S215"/>
-      <c r="T215"/>
-      <c r="U215"/>
-      <c r="V215"/>
-      <c r="W215"/>
-      <c r="X215"/>
-      <c r="Y215"/>
-      <c r="Z215"/>
-      <c r="AA215"/>
-      <c r="AB215"/>
-      <c r="AC215"/>
-    </row>
-    <row r="216" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B216" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="C216" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D216" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E216" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F216" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G216"/>
-      <c r="H216"/>
-      <c r="I216"/>
-      <c r="J216"/>
-      <c r="K216"/>
-      <c r="L216"/>
-      <c r="M216"/>
-      <c r="N216"/>
-      <c r="O216"/>
-      <c r="P216"/>
-      <c r="Q216"/>
-      <c r="R216"/>
-      <c r="S216"/>
-      <c r="T216"/>
-      <c r="U216"/>
-      <c r="V216"/>
-      <c r="W216"/>
-      <c r="X216"/>
-      <c r="Y216"/>
-      <c r="Z216"/>
-      <c r="AA216"/>
-      <c r="AB216"/>
-      <c r="AC216"/>
-    </row>
-    <row r="217" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B217" s="38"/>
-      <c r="C217" s="29"/>
-      <c r="D217" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E217" s="24">
-        <v>1000000</v>
-      </c>
-      <c r="F217" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G217"/>
-      <c r="H217"/>
-      <c r="I217"/>
-      <c r="J217"/>
-      <c r="K217"/>
-      <c r="L217"/>
-      <c r="M217"/>
-      <c r="N217"/>
-      <c r="O217"/>
-      <c r="P217"/>
-      <c r="Q217"/>
-      <c r="R217"/>
-      <c r="S217"/>
-      <c r="T217"/>
-      <c r="U217"/>
-      <c r="V217"/>
-      <c r="W217"/>
-      <c r="X217"/>
-      <c r="Y217"/>
-      <c r="Z217"/>
-      <c r="AA217"/>
-      <c r="AB217"/>
-      <c r="AC217"/>
-    </row>
-    <row r="218" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B218" s="38"/>
-      <c r="C218" s="29"/>
-      <c r="D218" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E218" s="24">
-        <v>880000</v>
-      </c>
-      <c r="F218" s="17" t="s">
+      <c r="F218" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G218"/>
@@ -6962,18 +6888,22 @@
       <c r="AC218"/>
     </row>
     <row r="219" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B219" s="38"/>
-      <c r="C219" s="29"/>
-      <c r="D219" s="10" t="s">
-        <v>35</v>
+      <c r="A219" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D219" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E219" s="24">
-        <v>1380000</v>
-      </c>
-      <c r="F219" s="17" t="s">
+        <v>33000</v>
+      </c>
+      <c r="F219" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G219"/>
@@ -7000,19 +6930,23 @@
       <c r="AB219"/>
       <c r="AC219"/>
     </row>
-    <row r="220" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B220" s="8"/>
-      <c r="C220" s="8"/>
-      <c r="D220" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E220" s="23">
-        <v>13880000</v>
-      </c>
-      <c r="F220" s="18" t="s">
+    <row r="220" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B220" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D220" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E220" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F220" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G220"/>
@@ -7039,19 +6973,23 @@
       <c r="AB220"/>
       <c r="AC220"/>
     </row>
-    <row r="221" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B221" s="8"/>
-      <c r="C221" s="8"/>
-      <c r="D221" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E221" s="23">
-        <v>750000</v>
-      </c>
-      <c r="F221" s="18" t="s">
+    <row r="221" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D221" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E221" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F221" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G221"/>
@@ -7078,19 +7016,23 @@
       <c r="AB221"/>
       <c r="AC221"/>
     </row>
-    <row r="222" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B222" s="8"/>
-      <c r="C222" s="8"/>
-      <c r="D222" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E222" s="23">
-        <v>155000</v>
-      </c>
-      <c r="F222" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B222" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D222" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E222" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F222" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G222"/>
@@ -7118,18 +7060,22 @@
       <c r="AC222"/>
     </row>
     <row r="223" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="B223" s="8"/>
-      <c r="C223" s="8"/>
-      <c r="D223" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E223" s="23">
-        <v>176000</v>
-      </c>
-      <c r="F223" s="18" t="s">
+      <c r="A223" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B223" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D223" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E223" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F223" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G223"/>
@@ -7157,18 +7103,22 @@
       <c r="AC223"/>
     </row>
     <row r="224" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B224" s="8"/>
-      <c r="C224" s="8"/>
-      <c r="D224" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E224" s="23">
-        <v>198000</v>
-      </c>
-      <c r="F224" s="18" t="s">
+      <c r="A224" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B224" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C224" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D224" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E224" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F224" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G224"/>
@@ -7196,18 +7146,18 @@
       <c r="AC224"/>
     </row>
     <row r="225" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B225" s="8"/>
-      <c r="C225" s="8"/>
+      <c r="A225" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B225" s="38"/>
+      <c r="C225" s="29"/>
       <c r="D225" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E225" s="23">
-        <v>186000</v>
-      </c>
-      <c r="F225" s="18" t="s">
+      <c r="E225" s="24">
+        <v>1000000</v>
+      </c>
+      <c r="F225" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G225"/>
@@ -7235,18 +7185,18 @@
       <c r="AC225"/>
     </row>
     <row r="226" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B226" s="8"/>
-      <c r="C226" s="8"/>
+      <c r="A226" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B226" s="38"/>
+      <c r="C226" s="29"/>
       <c r="D226" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E226" s="23">
-        <v>198000</v>
-      </c>
-      <c r="F226" s="18" t="s">
+      <c r="E226" s="24">
+        <v>880000</v>
+      </c>
+      <c r="F226" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G226"/>
@@ -7274,18 +7224,18 @@
       <c r="AC226"/>
     </row>
     <row r="227" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B227" s="8"/>
-      <c r="C227" s="8"/>
+      <c r="A227" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B227" s="38"/>
+      <c r="C227" s="29"/>
       <c r="D227" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E227" s="23">
-        <v>228000</v>
-      </c>
-      <c r="F227" s="18" t="s">
+      <c r="E227" s="24">
+        <v>1380000</v>
+      </c>
+      <c r="F227" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G227"/>
@@ -7314,7 +7264,7 @@
     </row>
     <row r="228" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -7322,7 +7272,7 @@
         <v>35</v>
       </c>
       <c r="E228" s="23">
-        <v>175000</v>
+        <v>13880000</v>
       </c>
       <c r="F228" s="18" t="s">
         <v>8</v>
@@ -7353,7 +7303,7 @@
     </row>
     <row r="229" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -7361,7 +7311,7 @@
         <v>35</v>
       </c>
       <c r="E229" s="23">
-        <v>296000</v>
+        <v>750000</v>
       </c>
       <c r="F229" s="18" t="s">
         <v>8</v>
@@ -7392,7 +7342,7 @@
     </row>
     <row r="230" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -7400,7 +7350,7 @@
         <v>35</v>
       </c>
       <c r="E230" s="23">
-        <v>258000</v>
+        <v>155000</v>
       </c>
       <c r="F230" s="18" t="s">
         <v>8</v>
@@ -7431,7 +7381,7 @@
     </row>
     <row r="231" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="11" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -7439,7 +7389,7 @@
         <v>35</v>
       </c>
       <c r="E231" s="23">
-        <v>228000</v>
+        <v>176000</v>
       </c>
       <c r="F231" s="18" t="s">
         <v>8</v>
@@ -7470,7 +7420,7 @@
     </row>
     <row r="232" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="11" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
@@ -7478,7 +7428,7 @@
         <v>35</v>
       </c>
       <c r="E232" s="23">
-        <v>248000</v>
+        <v>198000</v>
       </c>
       <c r="F232" s="18" t="s">
         <v>8</v>
@@ -7509,7 +7459,7 @@
     </row>
     <row r="233" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
@@ -7517,7 +7467,7 @@
         <v>35</v>
       </c>
       <c r="E233" s="23">
-        <v>278000</v>
+        <v>186000</v>
       </c>
       <c r="F233" s="18" t="s">
         <v>8</v>
@@ -7547,22 +7497,18 @@
       <c r="AC233"/>
     </row>
     <row r="234" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="B234" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C234" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D234" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E234" s="25">
-        <v>32680000</v>
-      </c>
-      <c r="F234" s="17" t="s">
+      <c r="A234" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B234" s="8"/>
+      <c r="C234" s="8"/>
+      <c r="D234" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E234" s="23">
+        <v>198000</v>
+      </c>
+      <c r="F234" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G234"/>
@@ -7589,23 +7535,19 @@
       <c r="AB234"/>
       <c r="AC234"/>
     </row>
-    <row r="235" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="B235" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C235" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D235" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E235" s="25">
-        <v>36800000</v>
-      </c>
-      <c r="F235" s="17" t="s">
+    <row r="235" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B235" s="8"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E235" s="23">
+        <v>228000</v>
+      </c>
+      <c r="F235" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G235"/>
@@ -7632,23 +7574,19 @@
       <c r="AB235"/>
       <c r="AC235"/>
     </row>
-    <row r="236" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B236" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C236" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D236" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E236" s="25">
-        <v>43680000</v>
-      </c>
-      <c r="F236" s="17" t="s">
+    <row r="236" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E236" s="23">
+        <v>175000</v>
+      </c>
+      <c r="F236" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G236"/>
@@ -7675,109 +7613,204 @@
       <c r="AB236"/>
       <c r="AC236"/>
     </row>
-    <row r="237" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A237" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B237" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C237" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D237" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E237" s="25">
-        <v>48680000</v>
-      </c>
-      <c r="F237" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="238" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A238" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="B238" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C238" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D238" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E238" s="25">
-        <v>54680000</v>
-      </c>
-      <c r="F238" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="239" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A239" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B239" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C239" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D239" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E239" s="25">
-        <v>69860000</v>
-      </c>
-      <c r="F239" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="240" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A240" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="B240" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C240" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D240" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E240" s="25">
-        <v>99680000</v>
-      </c>
-      <c r="F240" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A241" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="B241" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C241" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D241" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E241" s="26">
-        <v>75000</v>
-      </c>
-      <c r="F241" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A242" s="39" t="s">
-        <v>228</v>
+    <row r="237" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E237" s="23">
+        <v>296000</v>
+      </c>
+      <c r="F237" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G237"/>
+      <c r="H237"/>
+      <c r="I237"/>
+      <c r="J237"/>
+      <c r="K237"/>
+      <c r="L237"/>
+      <c r="M237"/>
+      <c r="N237"/>
+      <c r="O237"/>
+      <c r="P237"/>
+      <c r="Q237"/>
+      <c r="R237"/>
+      <c r="S237"/>
+      <c r="T237"/>
+      <c r="U237"/>
+      <c r="V237"/>
+      <c r="W237"/>
+      <c r="X237"/>
+      <c r="Y237"/>
+      <c r="Z237"/>
+      <c r="AA237"/>
+      <c r="AB237"/>
+      <c r="AC237"/>
+    </row>
+    <row r="238" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B238" s="8"/>
+      <c r="C238" s="8"/>
+      <c r="D238" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E238" s="23">
+        <v>258000</v>
+      </c>
+      <c r="F238" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G238"/>
+      <c r="H238"/>
+      <c r="I238"/>
+      <c r="J238"/>
+      <c r="K238"/>
+      <c r="L238"/>
+      <c r="M238"/>
+      <c r="N238"/>
+      <c r="O238"/>
+      <c r="P238"/>
+      <c r="Q238"/>
+      <c r="R238"/>
+      <c r="S238"/>
+      <c r="T238"/>
+      <c r="U238"/>
+      <c r="V238"/>
+      <c r="W238"/>
+      <c r="X238"/>
+      <c r="Y238"/>
+      <c r="Z238"/>
+      <c r="AA238"/>
+      <c r="AB238"/>
+      <c r="AC238"/>
+    </row>
+    <row r="239" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B239" s="8"/>
+      <c r="C239" s="8"/>
+      <c r="D239" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E239" s="23">
+        <v>228000</v>
+      </c>
+      <c r="F239" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G239"/>
+      <c r="H239"/>
+      <c r="I239"/>
+      <c r="J239"/>
+      <c r="K239"/>
+      <c r="L239"/>
+      <c r="M239"/>
+      <c r="N239"/>
+      <c r="O239"/>
+      <c r="P239"/>
+      <c r="Q239"/>
+      <c r="R239"/>
+      <c r="S239"/>
+      <c r="T239"/>
+      <c r="U239"/>
+      <c r="V239"/>
+      <c r="W239"/>
+      <c r="X239"/>
+      <c r="Y239"/>
+      <c r="Z239"/>
+      <c r="AA239"/>
+      <c r="AB239"/>
+      <c r="AC239"/>
+    </row>
+    <row r="240" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B240" s="8"/>
+      <c r="C240" s="8"/>
+      <c r="D240" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E240" s="23">
+        <v>248000</v>
+      </c>
+      <c r="F240" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G240"/>
+      <c r="H240"/>
+      <c r="I240"/>
+      <c r="J240"/>
+      <c r="K240"/>
+      <c r="L240"/>
+      <c r="M240"/>
+      <c r="N240"/>
+      <c r="O240"/>
+      <c r="P240"/>
+      <c r="Q240"/>
+      <c r="R240"/>
+      <c r="S240"/>
+      <c r="T240"/>
+      <c r="U240"/>
+      <c r="V240"/>
+      <c r="W240"/>
+      <c r="X240"/>
+      <c r="Y240"/>
+      <c r="Z240"/>
+      <c r="AA240"/>
+      <c r="AB240"/>
+      <c r="AC240"/>
+    </row>
+    <row r="241" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B241" s="8"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E241" s="23">
+        <v>278000</v>
+      </c>
+      <c r="F241" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G241"/>
+      <c r="H241"/>
+      <c r="I241"/>
+      <c r="J241"/>
+      <c r="K241"/>
+      <c r="L241"/>
+      <c r="M241"/>
+      <c r="N241"/>
+      <c r="O241"/>
+      <c r="P241"/>
+      <c r="Q241"/>
+      <c r="R241"/>
+      <c r="S241"/>
+      <c r="T241"/>
+      <c r="U241"/>
+      <c r="V241"/>
+      <c r="W241"/>
+      <c r="X241"/>
+      <c r="Y241"/>
+      <c r="Z241"/>
+      <c r="AA241"/>
+      <c r="AB241"/>
+      <c r="AC241"/>
+    </row>
+    <row r="242" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="19" t="s">
+        <v>220</v>
       </c>
       <c r="B242" s="20" t="s">
         <v>9</v>
@@ -7786,12 +7819,241 @@
         <v>84</v>
       </c>
       <c r="D242" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E242" s="25">
+        <v>32680000</v>
+      </c>
+      <c r="F242" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G242"/>
+      <c r="H242"/>
+      <c r="I242"/>
+      <c r="J242"/>
+      <c r="K242"/>
+      <c r="L242"/>
+      <c r="M242"/>
+      <c r="N242"/>
+      <c r="O242"/>
+      <c r="P242"/>
+      <c r="Q242"/>
+      <c r="R242"/>
+      <c r="S242"/>
+      <c r="T242"/>
+      <c r="U242"/>
+      <c r="V242"/>
+      <c r="W242"/>
+      <c r="X242"/>
+      <c r="Y242"/>
+      <c r="Z242"/>
+      <c r="AA242"/>
+      <c r="AB242"/>
+      <c r="AC242"/>
+    </row>
+    <row r="243" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B243" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C243" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D243" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E243" s="25">
+        <v>36800000</v>
+      </c>
+      <c r="F243" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G243"/>
+      <c r="H243"/>
+      <c r="I243"/>
+      <c r="J243"/>
+      <c r="K243"/>
+      <c r="L243"/>
+      <c r="M243"/>
+      <c r="N243"/>
+      <c r="O243"/>
+      <c r="P243"/>
+      <c r="Q243"/>
+      <c r="R243"/>
+      <c r="S243"/>
+      <c r="T243"/>
+      <c r="U243"/>
+      <c r="V243"/>
+      <c r="W243"/>
+      <c r="X243"/>
+      <c r="Y243"/>
+      <c r="Z243"/>
+      <c r="AA243"/>
+      <c r="AB243"/>
+      <c r="AC243"/>
+    </row>
+    <row r="244" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B244" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C244" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D244" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E244" s="25">
+        <v>43680000</v>
+      </c>
+      <c r="F244" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G244"/>
+      <c r="H244"/>
+      <c r="I244"/>
+      <c r="J244"/>
+      <c r="K244"/>
+      <c r="L244"/>
+      <c r="M244"/>
+      <c r="N244"/>
+      <c r="O244"/>
+      <c r="P244"/>
+      <c r="Q244"/>
+      <c r="R244"/>
+      <c r="S244"/>
+      <c r="T244"/>
+      <c r="U244"/>
+      <c r="V244"/>
+      <c r="W244"/>
+      <c r="X244"/>
+      <c r="Y244"/>
+      <c r="Z244"/>
+      <c r="AA244"/>
+      <c r="AB244"/>
+      <c r="AC244"/>
+    </row>
+    <row r="245" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A245" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B245" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C245" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D245" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E245" s="25">
+        <v>48680000</v>
+      </c>
+      <c r="F245" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A246" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B246" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C246" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D246" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E246" s="25">
+        <v>54680000</v>
+      </c>
+      <c r="F246" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A247" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B247" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C247" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D247" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E247" s="25">
+        <v>69860000</v>
+      </c>
+      <c r="F247" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A248" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B248" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C248" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D248" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E248" s="25">
+        <v>99680000</v>
+      </c>
+      <c r="F248" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="249" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A249" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B249" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C249" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D249" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="E242" s="26">
+      <c r="E249" s="26">
         <v>75000</v>
       </c>
-      <c r="F242" s="17" t="s">
+      <c r="F249" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A250" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B250" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C250" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D250" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E250" s="26">
+        <v>75000</v>
+      </c>
+      <c r="F250" s="17" t="s">
         <v>8</v>
       </c>
     </row>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="273">
   <si>
     <t>Ống D650</t>
   </si>
@@ -1021,6 +1021,27 @@
   </si>
   <si>
     <t>Y chia D150  rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D200 về D150 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D250 về D200 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D300 về D250 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D350 về D300 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D350 về D350 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Côn chuyển rẽ nhánh D400 về D350 rẽ 2 nhánh D100</t>
+  </si>
+  <si>
+    <t>Y chia D550  rẽ 2 nhánh D450 và D300</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC250"/>
+  <dimension ref="A1:AC257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5703125" style="40" customWidth="1"/>
@@ -2656,9 +2677,9 @@
       <c r="R48"/>
       <c r="S48"/>
     </row>
-    <row r="49" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>10</v>
@@ -2669,16 +2690,17 @@
       <c r="D49" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E49" s="23">
-        <v>180000</v>
+      <c r="E49" s="52">
+        <v>227000</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="G49" s="50"/>
     </row>
     <row r="50" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>10</v>
@@ -2690,7 +2712,7 @@
         <v>35</v>
       </c>
       <c r="E50" s="23">
-        <v>190000</v>
+        <v>180000</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>8</v>
@@ -2698,103 +2720,80 @@
     </row>
     <row r="51" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="23">
+        <v>190000</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="52">
+        <v>257000</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="50"/>
+    </row>
+    <row r="53" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E51" s="23">
+      <c r="B53" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="23">
         <v>210000</v>
       </c>
-      <c r="F51" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="F53" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="49">
+      <c r="B54" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="49">
         <v>250500</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
-      <c r="M52"/>
-      <c r="N52"/>
-      <c r="O52"/>
-      <c r="P52"/>
-      <c r="Q52"/>
-      <c r="R52"/>
-    </row>
-    <row r="53" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="49">
-        <v>244500</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
-      <c r="M53"/>
-      <c r="N53"/>
-      <c r="O53"/>
-      <c r="P53"/>
-      <c r="Q53"/>
-      <c r="R53"/>
-    </row>
-    <row r="54" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" s="49">
-        <v>253500</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>8</v>
@@ -2814,7 +2813,7 @@
     </row>
     <row r="55" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>10</v>
@@ -2825,28 +2824,17 @@
       <c r="D55" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E55" s="49">
-        <v>276000</v>
+      <c r="E55" s="52">
+        <v>306000</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
-      <c r="M55"/>
-      <c r="N55"/>
-      <c r="O55"/>
-      <c r="P55"/>
-      <c r="Q55"/>
-      <c r="R55"/>
+      <c r="G55" s="50"/>
     </row>
     <row r="56" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>10</v>
@@ -2858,7 +2846,7 @@
         <v>35</v>
       </c>
       <c r="E56" s="49">
-        <v>289500</v>
+        <v>244500</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>8</v>
@@ -2878,7 +2866,7 @@
     </row>
     <row r="57" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>10</v>
@@ -2890,7 +2878,7 @@
         <v>35</v>
       </c>
       <c r="E57" s="49">
-        <v>306000</v>
+        <v>253500</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>8</v>
@@ -2910,7 +2898,7 @@
     </row>
     <row r="58" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>10</v>
@@ -2921,28 +2909,17 @@
       <c r="D58" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E58" s="49">
-        <v>313500</v>
+      <c r="E58" s="52">
+        <v>309000</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G58"/>
-      <c r="H58"/>
-      <c r="I58"/>
-      <c r="J58"/>
-      <c r="K58"/>
-      <c r="L58"/>
-      <c r="M58"/>
-      <c r="N58"/>
-      <c r="O58"/>
-      <c r="P58"/>
-      <c r="Q58"/>
-      <c r="R58"/>
+      <c r="G58" s="50"/>
     </row>
     <row r="59" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>10</v>
@@ -2953,17 +2930,28 @@
       <c r="D59" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E59" s="52">
-        <v>410000</v>
+      <c r="E59" s="49">
+        <v>276000</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="50"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+      <c r="R59"/>
     </row>
     <row r="60" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>10</v>
@@ -2975,7 +2963,7 @@
         <v>35</v>
       </c>
       <c r="E60" s="52">
-        <v>369000</v>
+        <v>339000</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>8</v>
@@ -2984,7 +2972,7 @@
     </row>
     <row r="61" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>10</v>
@@ -2995,17 +2983,28 @@
       <c r="D61" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E61" s="52">
-        <v>432000</v>
+      <c r="E61" s="49">
+        <v>289500</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G61" s="50"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="Q61"/>
+      <c r="R61"/>
     </row>
     <row r="62" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>10</v>
@@ -3016,28 +3015,17 @@
       <c r="D62" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E62" s="49">
-        <v>340500</v>
+      <c r="E62" s="52">
+        <v>377000</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-      <c r="K62"/>
-      <c r="L62"/>
-      <c r="M62"/>
-      <c r="N62"/>
-      <c r="O62"/>
-      <c r="P62"/>
-      <c r="Q62"/>
-      <c r="R62"/>
+      <c r="G62" s="50"/>
     </row>
     <row r="63" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>10</v>
@@ -3049,7 +3037,7 @@
         <v>35</v>
       </c>
       <c r="E63" s="49">
-        <v>355500</v>
+        <v>306000</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>8</v>
@@ -3069,7 +3057,7 @@
     </row>
     <row r="64" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>10</v>
@@ -3080,8 +3068,8 @@
       <c r="D64" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E64" s="52">
-        <v>434000</v>
+      <c r="E64" s="49">
+        <v>313500</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>8</v>
@@ -3099,9 +3087,9 @@
       <c r="Q64"/>
       <c r="R64"/>
     </row>
-    <row r="65" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>10</v>
@@ -3112,106 +3100,73 @@
       <c r="D65" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E65" s="49">
-        <v>370500</v>
+      <c r="E65" s="52">
+        <v>410000</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G65"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-      <c r="K65"/>
-      <c r="L65"/>
-      <c r="M65"/>
-      <c r="N65"/>
-      <c r="O65"/>
-      <c r="P65"/>
-      <c r="Q65"/>
-      <c r="R65"/>
-    </row>
-    <row r="66" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="53">
-        <v>386000</v>
-      </c>
-      <c r="F66" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66"/>
-      <c r="M66"/>
-      <c r="N66"/>
-      <c r="O66"/>
-      <c r="P66"/>
-      <c r="Q66"/>
-      <c r="R66"/>
-    </row>
-    <row r="67" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="53">
-        <v>420000</v>
-      </c>
-      <c r="F67" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G67"/>
-      <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67"/>
-      <c r="M67"/>
-      <c r="N67"/>
-      <c r="O67"/>
-      <c r="P67"/>
-      <c r="Q67"/>
-      <c r="R67"/>
-    </row>
-    <row r="68" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="53">
-        <v>423000</v>
-      </c>
-      <c r="F68" s="45" t="s">
+      <c r="G65" s="50"/>
+    </row>
+    <row r="66" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="52">
+        <v>369000</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="50"/>
+    </row>
+    <row r="67" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="52">
+        <v>432000</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G67" s="50"/>
+    </row>
+    <row r="68" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="49">
+        <v>340500</v>
+      </c>
+      <c r="F68" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G68"/>
@@ -3227,23 +3182,23 @@
       <c r="Q68"/>
       <c r="R68"/>
     </row>
-    <row r="69" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="48">
-        <v>369000</v>
-      </c>
-      <c r="F69" s="45" t="s">
+    <row r="69" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="49">
+        <v>355500</v>
+      </c>
+      <c r="F69" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G69"/>
@@ -3258,26 +3213,24 @@
       <c r="P69"/>
       <c r="Q69"/>
       <c r="R69"/>
-      <c r="S69" s="47"/>
-      <c r="T69" s="47"/>
-    </row>
-    <row r="70" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="48">
-        <v>416000</v>
-      </c>
-      <c r="F70" s="45" t="s">
+    </row>
+    <row r="70" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="52">
+        <v>434000</v>
+      </c>
+      <c r="F70" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G70"/>
@@ -3292,26 +3245,24 @@
       <c r="P70"/>
       <c r="Q70"/>
       <c r="R70"/>
-      <c r="S70"/>
-      <c r="T70"/>
-    </row>
-    <row r="71" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="48">
-        <v>420000</v>
-      </c>
-      <c r="F71" s="45" t="s">
+    </row>
+    <row r="71" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" s="49">
+        <v>370500</v>
+      </c>
+      <c r="F71" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G71"/>
@@ -3325,25 +3276,23 @@
       <c r="O71"/>
       <c r="P71"/>
       <c r="Q71"/>
-      <c r="R71" s="47"/>
-      <c r="S71" s="47"/>
-      <c r="T71" s="47"/>
-    </row>
-    <row r="72" spans="1:21" s="31" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="48">
-        <v>366000</v>
+      <c r="R71"/>
+    </row>
+    <row r="72" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="53">
+        <v>386000</v>
       </c>
       <c r="F72" s="45" t="s">
         <v>8</v>
@@ -3360,12 +3309,10 @@
       <c r="P72"/>
       <c r="Q72"/>
       <c r="R72"/>
-      <c r="S72"/>
-      <c r="T72"/>
-    </row>
-    <row r="73" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>159</v>
+        <v>263</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>10</v>
@@ -3376,16 +3323,28 @@
       <c r="D73" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E73" s="22">
-        <v>442500</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="E73" s="53">
+        <v>420000</v>
+      </c>
+      <c r="F73" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73"/>
+      <c r="N73"/>
+      <c r="O73"/>
+      <c r="P73"/>
+      <c r="Q73"/>
+      <c r="R73"/>
+    </row>
+    <row r="74" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>10</v>
@@ -3396,16 +3355,28 @@
       <c r="D74" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E74" s="22">
-        <v>447000</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>167</v>
+      <c r="E74" s="53">
+        <v>423000</v>
+      </c>
+      <c r="F74" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74"/>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="M74"/>
+      <c r="N74"/>
+      <c r="O74"/>
+      <c r="P74"/>
+      <c r="Q74"/>
+      <c r="R74"/>
+    </row>
+    <row r="75" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>241</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>10</v>
@@ -3416,8 +3387,8 @@
       <c r="D75" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E75" s="46">
-        <v>450000</v>
+      <c r="E75" s="48">
+        <v>369000</v>
       </c>
       <c r="F75" s="45" t="s">
         <v>8</v>
@@ -3434,133 +3405,189 @@
       <c r="P75"/>
       <c r="Q75"/>
       <c r="R75"/>
-      <c r="S75"/>
-      <c r="T75"/>
-      <c r="U75"/>
-    </row>
-    <row r="76" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="22">
-        <v>470000</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="27" t="s">
+      <c r="S75" s="47"/>
+      <c r="T75" s="47"/>
+    </row>
+    <row r="76" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" s="48">
+        <v>416000</v>
+      </c>
+      <c r="F76" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76"/>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76"/>
+      <c r="K76"/>
+      <c r="L76"/>
+      <c r="M76"/>
+      <c r="N76"/>
+      <c r="O76"/>
+      <c r="P76"/>
+      <c r="Q76"/>
+      <c r="R76"/>
+      <c r="S76"/>
+      <c r="T76"/>
+    </row>
+    <row r="77" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="48">
+        <v>420000</v>
+      </c>
+      <c r="F77" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+      <c r="N77"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+      <c r="R77" s="47"/>
+      <c r="S77" s="47"/>
+      <c r="T77" s="47"/>
+    </row>
+    <row r="78" spans="1:20" s="31" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="48">
+        <v>366000</v>
+      </c>
+      <c r="F78" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G78"/>
+      <c r="H78"/>
+      <c r="I78"/>
+      <c r="J78"/>
+      <c r="K78"/>
+      <c r="L78"/>
+      <c r="M78"/>
+      <c r="N78"/>
+      <c r="O78"/>
+      <c r="P78"/>
+      <c r="Q78"/>
+      <c r="R78"/>
+      <c r="S78"/>
+      <c r="T78"/>
+    </row>
+    <row r="79" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="22">
+        <v>442500</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B77" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="33">
+      <c r="B80" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="22">
         <v>447000</v>
       </c>
-      <c r="F77" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="22">
-        <v>528000</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A79" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="B79" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="33">
-        <v>508500</v>
-      </c>
-      <c r="F79" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="22">
-        <v>560000</v>
-      </c>
       <c r="F80" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A81" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="B81" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="33">
-        <v>682500</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>8</v>
-      </c>
+    <row r="81" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="46">
+        <v>450000</v>
+      </c>
+      <c r="F81" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
+      <c r="N81"/>
+      <c r="O81"/>
+      <c r="P81"/>
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="S81"/>
+      <c r="T81"/>
+      <c r="U81"/>
     </row>
     <row r="82" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>10</v>
@@ -3572,85 +3599,55 @@
         <v>35</v>
       </c>
       <c r="E82" s="22">
-        <v>666000</v>
+        <v>470000</v>
       </c>
       <c r="F82" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" s="46">
-        <v>1125000</v>
-      </c>
-      <c r="F83" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83"/>
-      <c r="H83"/>
-      <c r="I83"/>
-      <c r="J83"/>
-      <c r="K83"/>
-      <c r="L83"/>
-      <c r="M83"/>
-      <c r="N83"/>
-      <c r="O83"/>
-      <c r="P83"/>
-      <c r="Q83"/>
-      <c r="R83"/>
-      <c r="S83"/>
-      <c r="T83"/>
-      <c r="U83"/>
-    </row>
-    <row r="84" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" s="46">
-        <v>1150000</v>
-      </c>
-      <c r="F84" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G84"/>
-      <c r="H84"/>
-      <c r="I84"/>
-      <c r="J84"/>
-      <c r="K84"/>
-      <c r="L84"/>
-      <c r="M84"/>
-      <c r="N84"/>
-      <c r="O84"/>
-      <c r="P84"/>
-      <c r="Q84"/>
-      <c r="R84"/>
-      <c r="S84"/>
-      <c r="T84"/>
-      <c r="U84"/>
+    <row r="83" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A83" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="33">
+        <v>447000</v>
+      </c>
+      <c r="F83" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A84" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="22">
+        <v>528000</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="85" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B85" s="20" t="s">
         <v>10</v>
@@ -3662,120 +3659,75 @@
         <v>35</v>
       </c>
       <c r="E85" s="33">
-        <v>957000</v>
+        <v>508500</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D86" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" s="46">
-        <v>750000</v>
-      </c>
-      <c r="F86" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G86"/>
-      <c r="H86"/>
-      <c r="I86"/>
-      <c r="J86"/>
-      <c r="K86"/>
-      <c r="L86"/>
-      <c r="M86"/>
-      <c r="N86"/>
-      <c r="O86"/>
-      <c r="P86"/>
-      <c r="Q86"/>
-      <c r="R86"/>
-      <c r="S86"/>
-      <c r="T86"/>
-      <c r="U86"/>
-    </row>
-    <row r="87" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="46">
-        <v>1550000</v>
-      </c>
-      <c r="F87" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87"/>
-      <c r="J87"/>
-      <c r="K87"/>
-      <c r="L87"/>
-      <c r="M87"/>
-      <c r="N87"/>
-      <c r="O87"/>
-      <c r="P87"/>
-      <c r="Q87"/>
-      <c r="R87"/>
-      <c r="S87"/>
-      <c r="T87"/>
-      <c r="U87"/>
-    </row>
-    <row r="88" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="46">
-        <v>1650000</v>
-      </c>
-      <c r="F88" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G88"/>
-      <c r="H88"/>
-      <c r="I88"/>
-      <c r="J88"/>
-      <c r="K88"/>
-      <c r="L88"/>
-      <c r="M88"/>
-      <c r="N88"/>
-      <c r="O88"/>
-      <c r="P88"/>
-      <c r="Q88"/>
-      <c r="R88"/>
-      <c r="S88"/>
-      <c r="T88"/>
-      <c r="U88"/>
+    <row r="86" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A86" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="22">
+        <v>560000</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="33">
+        <v>682500</v>
+      </c>
+      <c r="F87" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="22">
+        <v>666000</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="89" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>10</v>
@@ -3787,7 +3739,7 @@
         <v>35</v>
       </c>
       <c r="E89" s="46">
-        <v>1700000</v>
+        <v>1125000</v>
       </c>
       <c r="F89" s="45" t="s">
         <v>8</v>
@@ -3810,7 +3762,7 @@
     </row>
     <row r="90" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B90" s="14" t="s">
         <v>10</v>
@@ -3822,7 +3774,7 @@
         <v>35</v>
       </c>
       <c r="E90" s="46">
-        <v>1800000</v>
+        <v>1150000</v>
       </c>
       <c r="F90" s="45" t="s">
         <v>8</v>
@@ -3843,44 +3795,29 @@
       <c r="T90"/>
       <c r="U90"/>
     </row>
-    <row r="91" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E91" s="46">
-        <v>1850000</v>
-      </c>
-      <c r="F91" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91"/>
-      <c r="H91"/>
-      <c r="I91"/>
-      <c r="J91"/>
-      <c r="K91"/>
-      <c r="L91"/>
-      <c r="M91"/>
-      <c r="N91"/>
-      <c r="O91"/>
-      <c r="P91"/>
-      <c r="Q91"/>
-      <c r="R91"/>
-      <c r="S91"/>
-      <c r="T91"/>
-      <c r="U91"/>
+    <row r="91" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A91" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B91" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="33">
+        <v>957000</v>
+      </c>
+      <c r="F91" s="17" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="92" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>244</v>
+      <c r="A92" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="B92" s="14" t="s">
         <v>10</v>
@@ -3891,8 +3828,8 @@
       <c r="D92" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E92" s="48">
-        <v>1200000</v>
+      <c r="E92" s="46">
+        <v>750000</v>
       </c>
       <c r="F92" s="45" t="s">
         <v>8</v>
@@ -3911,277 +3848,396 @@
       <c r="R92"/>
       <c r="S92"/>
       <c r="T92"/>
-    </row>
-    <row r="93" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A93" s="11" t="s">
+      <c r="U92"/>
+    </row>
+    <row r="93" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="46">
+        <v>1550000</v>
+      </c>
+      <c r="F93" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G93"/>
+      <c r="H93"/>
+      <c r="I93"/>
+      <c r="J93"/>
+      <c r="K93"/>
+      <c r="L93"/>
+      <c r="M93"/>
+      <c r="N93"/>
+      <c r="O93"/>
+      <c r="P93"/>
+      <c r="Q93"/>
+      <c r="R93"/>
+      <c r="S93"/>
+      <c r="T93"/>
+      <c r="U93"/>
+    </row>
+    <row r="94" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="46">
+        <v>1650000</v>
+      </c>
+      <c r="F94" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94"/>
+      <c r="H94"/>
+      <c r="I94"/>
+      <c r="J94"/>
+      <c r="K94"/>
+      <c r="L94"/>
+      <c r="M94"/>
+      <c r="N94"/>
+      <c r="O94"/>
+      <c r="P94"/>
+      <c r="Q94"/>
+      <c r="R94"/>
+      <c r="S94"/>
+      <c r="T94"/>
+      <c r="U94"/>
+    </row>
+    <row r="95" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="46">
+        <v>1700000</v>
+      </c>
+      <c r="F95" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G95"/>
+      <c r="H95"/>
+      <c r="I95"/>
+      <c r="J95"/>
+      <c r="K95"/>
+      <c r="L95"/>
+      <c r="M95"/>
+      <c r="N95"/>
+      <c r="O95"/>
+      <c r="P95"/>
+      <c r="Q95"/>
+      <c r="R95"/>
+      <c r="S95"/>
+      <c r="T95"/>
+      <c r="U95"/>
+    </row>
+    <row r="96" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="46">
+        <v>1800000</v>
+      </c>
+      <c r="F96" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96"/>
+      <c r="H96"/>
+      <c r="I96"/>
+      <c r="J96"/>
+      <c r="K96"/>
+      <c r="L96"/>
+      <c r="M96"/>
+      <c r="N96"/>
+      <c r="O96"/>
+      <c r="P96"/>
+      <c r="Q96"/>
+      <c r="R96"/>
+      <c r="S96"/>
+      <c r="T96"/>
+      <c r="U96"/>
+    </row>
+    <row r="97" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="46">
+        <v>1850000</v>
+      </c>
+      <c r="F97" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G97"/>
+      <c r="H97"/>
+      <c r="I97"/>
+      <c r="J97"/>
+      <c r="K97"/>
+      <c r="L97"/>
+      <c r="M97"/>
+      <c r="N97"/>
+      <c r="O97"/>
+      <c r="P97"/>
+      <c r="Q97"/>
+      <c r="R97"/>
+      <c r="S97"/>
+      <c r="T97"/>
+      <c r="U97"/>
+    </row>
+    <row r="98" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="48">
+        <v>1200000</v>
+      </c>
+      <c r="F98" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G98"/>
+      <c r="H98"/>
+      <c r="I98"/>
+      <c r="J98"/>
+      <c r="K98"/>
+      <c r="L98"/>
+      <c r="M98"/>
+      <c r="N98"/>
+      <c r="O98"/>
+      <c r="P98"/>
+      <c r="Q98"/>
+      <c r="R98"/>
+      <c r="S98"/>
+      <c r="T98"/>
+    </row>
+    <row r="99" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B93" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E93" s="22">
+      <c r="B99" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="22">
         <v>2100000</v>
       </c>
-      <c r="F93" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A94" s="11" t="s">
+      <c r="F99" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A100" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B94" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E94" s="22">
+      <c r="B100" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="22">
         <v>2860000</v>
       </c>
-      <c r="F94" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A95" s="11" t="s">
+      <c r="F100" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A101" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="22">
+      <c r="B101" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="22">
         <v>3120000</v>
       </c>
-      <c r="F95" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="27" t="s">
+      <c r="F101" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="B96" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="33">
+      <c r="B102" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="33">
         <v>3255000</v>
       </c>
-      <c r="F96" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="11" t="s">
+      <c r="F102" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="53">
+        <v>1722000</v>
+      </c>
+      <c r="F103" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G103" s="50"/>
+    </row>
+    <row r="104" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="53">
+      <c r="B104" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="53">
         <v>206000</v>
       </c>
-      <c r="F97" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="G97" s="50"/>
-    </row>
-    <row r="98" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
+      <c r="F104" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G104" s="50"/>
+    </row>
+    <row r="105" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A105" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B105" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E98" s="23">
-        <v>160000</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E99" s="23">
-        <v>220000</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="23">
-        <v>280000</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="23">
-        <v>550000</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="23">
-        <v>900000</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="23">
-        <v>1050000</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A104" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E104" s="23">
-        <v>1450000</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A105" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B105" s="6"/>
       <c r="C105" s="6"/>
       <c r="D105" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E105" s="23">
-        <v>1780000</v>
+        <v>160000</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B106" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C106" s="6"/>
       <c r="D106" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E106" s="23">
-        <v>2000000</v>
+        <v>220000</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B107" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="C107" s="6"/>
       <c r="D107" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E107" s="23">
-        <v>2500000</v>
+        <v>280000</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -4189,15 +4245,15 @@
         <v>35</v>
       </c>
       <c r="E108" s="23">
-        <v>2800000</v>
+        <v>550000</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -4205,15 +4261,15 @@
         <v>35</v>
       </c>
       <c r="E109" s="23">
-        <v>3300000</v>
+        <v>900000</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -4221,15 +4277,15 @@
         <v>35</v>
       </c>
       <c r="E110" s="23">
-        <v>3800000</v>
+        <v>1050000</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
@@ -4237,15 +4293,15 @@
         <v>35</v>
       </c>
       <c r="E111" s="23">
-        <v>4500000</v>
+        <v>1450000</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
@@ -4253,7 +4309,7 @@
         <v>35</v>
       </c>
       <c r="E112" s="23">
-        <v>4800000</v>
+        <v>1780000</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>8</v>
@@ -4261,7 +4317,7 @@
     </row>
     <row r="113" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
@@ -4269,7 +4325,7 @@
         <v>35</v>
       </c>
       <c r="E113" s="23">
-        <v>5200000</v>
+        <v>2000000</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>8</v>
@@ -4277,7 +4333,7 @@
     </row>
     <row r="114" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
@@ -4285,7 +4341,7 @@
         <v>35</v>
       </c>
       <c r="E114" s="23">
-        <v>5600000</v>
+        <v>2500000</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>8</v>
@@ -4293,7 +4349,7 @@
     </row>
     <row r="115" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
@@ -4301,7 +4357,7 @@
         <v>35</v>
       </c>
       <c r="E115" s="23">
-        <v>6500000</v>
+        <v>2800000</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>8</v>
@@ -4309,7 +4365,7 @@
     </row>
     <row r="116" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
@@ -4317,7 +4373,7 @@
         <v>35</v>
       </c>
       <c r="E116" s="23">
-        <v>7200000</v>
+        <v>3300000</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>8</v>
@@ -4325,7 +4381,7 @@
     </row>
     <row r="117" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
@@ -4333,7 +4389,7 @@
         <v>35</v>
       </c>
       <c r="E117" s="23">
-        <v>7600000</v>
+        <v>3800000</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>8</v>
@@ -4341,7 +4397,7 @@
     </row>
     <row r="118" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -4349,7 +4405,7 @@
         <v>35</v>
       </c>
       <c r="E118" s="23">
-        <v>8000000</v>
+        <v>4500000</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>8</v>
@@ -4357,7 +4413,7 @@
     </row>
     <row r="119" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -4365,7 +4421,7 @@
         <v>35</v>
       </c>
       <c r="E119" s="23">
-        <v>8900000</v>
+        <v>4800000</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>8</v>
@@ -4373,7 +4429,7 @@
     </row>
     <row r="120" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
@@ -4381,7 +4437,7 @@
         <v>35</v>
       </c>
       <c r="E120" s="23">
-        <v>9600000</v>
+        <v>5200000</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>8</v>
@@ -4389,7 +4445,7 @@
     </row>
     <row r="121" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -4397,7 +4453,7 @@
         <v>35</v>
       </c>
       <c r="E121" s="23">
-        <v>10680000</v>
+        <v>5600000</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>8</v>
@@ -4405,7 +4461,7 @@
     </row>
     <row r="122" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -4413,7 +4469,7 @@
         <v>35</v>
       </c>
       <c r="E122" s="23">
-        <v>11680000</v>
+        <v>6500000</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>8</v>
@@ -4421,7 +4477,7 @@
     </row>
     <row r="123" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -4429,147 +4485,119 @@
         <v>35</v>
       </c>
       <c r="E123" s="23">
+        <v>7200000</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="23">
+        <v>7600000</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A125" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B125" s="6"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="23">
+        <v>8000000</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B126" s="6"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" s="23">
+        <v>8900000</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A127" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B127" s="6"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="23">
+        <v>9600000</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B128" s="6"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="23">
+        <v>10680000</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A129" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B129" s="6"/>
+      <c r="C129" s="6"/>
+      <c r="D129" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" s="23">
+        <v>11680000</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B130" s="6"/>
+      <c r="C130" s="6"/>
+      <c r="D130" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="23">
         <v>12500000</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A124" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B124" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E124" s="23">
-        <v>240000</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A125" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B125" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C125" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E125" s="23">
-        <v>320000</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A126" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B126" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E126" s="23">
-        <v>420000</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A127" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B127" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C127" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E127" s="23">
-        <v>500000</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A128" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B128" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E128" s="23">
-        <v>620000</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A129" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B129" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C129" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E129" s="23">
-        <v>660000</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A130" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B130" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E130" s="23">
-        <v>840000</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>8</v>
@@ -4577,7 +4605,7 @@
     </row>
     <row r="131" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B131" s="34" t="s">
         <v>9</v>
@@ -4589,7 +4617,7 @@
         <v>35</v>
       </c>
       <c r="E131" s="23">
-        <v>890000</v>
+        <v>240000</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>8</v>
@@ -4597,7 +4625,7 @@
     </row>
     <row r="132" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B132" s="34" t="s">
         <v>9</v>
@@ -4609,7 +4637,7 @@
         <v>35</v>
       </c>
       <c r="E132" s="23">
-        <v>1980000</v>
+        <v>320000</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>8</v>
@@ -4617,7 +4645,7 @@
     </row>
     <row r="133" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B133" s="34" t="s">
         <v>9</v>
@@ -4629,7 +4657,7 @@
         <v>35</v>
       </c>
       <c r="E133" s="23">
-        <v>2100000</v>
+        <v>420000</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>8</v>
@@ -4637,7 +4665,7 @@
     </row>
     <row r="134" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B134" s="34" t="s">
         <v>9</v>
@@ -4649,7 +4677,7 @@
         <v>35</v>
       </c>
       <c r="E134" s="23">
-        <v>2250000</v>
+        <v>500000</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>8</v>
@@ -4657,7 +4685,7 @@
     </row>
     <row r="135" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B135" s="34" t="s">
         <v>9</v>
@@ -4669,7 +4697,7 @@
         <v>35</v>
       </c>
       <c r="E135" s="23">
-        <v>2490000</v>
+        <v>620000</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>8</v>
@@ -4677,7 +4705,7 @@
     </row>
     <row r="136" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B136" s="34" t="s">
         <v>9</v>
@@ -4689,7 +4717,7 @@
         <v>35</v>
       </c>
       <c r="E136" s="23">
-        <v>2640000</v>
+        <v>660000</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>8</v>
@@ -4697,7 +4725,7 @@
     </row>
     <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B137" s="34" t="s">
         <v>9</v>
@@ -4709,7 +4737,7 @@
         <v>35</v>
       </c>
       <c r="E137" s="23">
-        <v>2850000</v>
+        <v>840000</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>8</v>
@@ -4717,7 +4745,7 @@
     </row>
     <row r="138" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B138" s="34" t="s">
         <v>9</v>
@@ -4729,7 +4757,7 @@
         <v>35</v>
       </c>
       <c r="E138" s="23">
-        <v>3090000</v>
+        <v>890000</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>8</v>
@@ -4737,7 +4765,7 @@
     </row>
     <row r="139" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B139" s="34" t="s">
         <v>9</v>
@@ -4749,7 +4777,7 @@
         <v>35</v>
       </c>
       <c r="E139" s="23">
-        <v>3450000</v>
+        <v>1980000</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>8</v>
@@ -4757,7 +4785,7 @@
     </row>
     <row r="140" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B140" s="34" t="s">
         <v>9</v>
@@ -4769,7 +4797,7 @@
         <v>35</v>
       </c>
       <c r="E140" s="23">
-        <v>7600000</v>
+        <v>2100000</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>8</v>
@@ -4777,7 +4805,7 @@
     </row>
     <row r="141" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B141" s="34" t="s">
         <v>9</v>
@@ -4789,7 +4817,7 @@
         <v>35</v>
       </c>
       <c r="E141" s="23">
-        <v>8000000</v>
+        <v>2250000</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>8</v>
@@ -4797,7 +4825,7 @@
     </row>
     <row r="142" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B142" s="34" t="s">
         <v>9</v>
@@ -4809,7 +4837,7 @@
         <v>35</v>
       </c>
       <c r="E142" s="23">
-        <v>8900000</v>
+        <v>2490000</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>8</v>
@@ -4817,7 +4845,7 @@
     </row>
     <row r="143" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B143" s="34" t="s">
         <v>9</v>
@@ -4829,7 +4857,7 @@
         <v>35</v>
       </c>
       <c r="E143" s="23">
-        <v>9600000</v>
+        <v>2640000</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>8</v>
@@ -4837,7 +4865,7 @@
     </row>
     <row r="144" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B144" s="34" t="s">
         <v>9</v>
@@ -4849,7 +4877,7 @@
         <v>35</v>
       </c>
       <c r="E144" s="23">
-        <v>10680000</v>
+        <v>2850000</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>8</v>
@@ -4857,7 +4885,7 @@
     </row>
     <row r="145" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B145" s="34" t="s">
         <v>9</v>
@@ -4869,7 +4897,7 @@
         <v>35</v>
       </c>
       <c r="E145" s="23">
-        <v>11680000</v>
+        <v>3090000</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>8</v>
@@ -4877,7 +4905,7 @@
     </row>
     <row r="146" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B146" s="34" t="s">
         <v>9</v>
@@ -4889,119 +4917,147 @@
         <v>35</v>
       </c>
       <c r="E146" s="23">
+        <v>3450000</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A147" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B147" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" s="23">
+        <v>7600000</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A148" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B148" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" s="23">
+        <v>8000000</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A149" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B149" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E149" s="23">
+        <v>8900000</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A150" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B150" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" s="23">
+        <v>9600000</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A151" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B151" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C151" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="23">
+        <v>10680000</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B152" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="23">
+        <v>11680000</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A153" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B153" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="23">
         <v>13680000</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A147" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E147" s="23">
-        <v>800000</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A148" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E148" s="23">
-        <v>1000000</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A149" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E149" s="23">
-        <v>1008000</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A150" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E150" s="23">
-        <v>1200000</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A151" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E151" s="23">
-        <v>1488000</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A152" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E152" s="23">
-        <v>1584000</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A153" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E153" s="23">
-        <v>2016000</v>
       </c>
       <c r="F153" s="6" t="s">
         <v>8</v>
@@ -5009,7 +5065,7 @@
     </row>
     <row r="154" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
@@ -5017,7 +5073,7 @@
         <v>35</v>
       </c>
       <c r="E154" s="23">
-        <v>2136000</v>
+        <v>800000</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>8</v>
@@ -5025,7 +5081,7 @@
     </row>
     <row r="155" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
@@ -5033,7 +5089,7 @@
         <v>35</v>
       </c>
       <c r="E155" s="23">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>8</v>
@@ -5041,7 +5097,7 @@
     </row>
     <row r="156" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
@@ -5049,7 +5105,7 @@
         <v>35</v>
       </c>
       <c r="E156" s="23">
-        <v>3780000</v>
+        <v>1008000</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>8</v>
@@ -5057,7 +5113,7 @@
     </row>
     <row r="157" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
@@ -5065,7 +5121,7 @@
         <v>35</v>
       </c>
       <c r="E157" s="23">
-        <v>4050000</v>
+        <v>1200000</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>8</v>
@@ -5073,7 +5129,7 @@
     </row>
     <row r="158" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
@@ -5081,7 +5137,7 @@
         <v>35</v>
       </c>
       <c r="E158" s="23">
-        <v>4482000</v>
+        <v>1488000</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>8</v>
@@ -5089,7 +5145,7 @@
     </row>
     <row r="159" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
@@ -5097,7 +5153,7 @@
         <v>35</v>
       </c>
       <c r="E159" s="23">
-        <v>4752000</v>
+        <v>1584000</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>8</v>
@@ -5105,7 +5161,7 @@
     </row>
     <row r="160" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
@@ -5113,7 +5169,7 @@
         <v>35</v>
       </c>
       <c r="E160" s="23">
-        <v>5130000</v>
+        <v>2016000</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>8</v>
@@ -5121,7 +5177,7 @@
     </row>
     <row r="161" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
@@ -5129,7 +5185,7 @@
         <v>35</v>
       </c>
       <c r="E161" s="23">
-        <v>5562000</v>
+        <v>2136000</v>
       </c>
       <c r="F161" s="6" t="s">
         <v>8</v>
@@ -5137,7 +5193,7 @@
     </row>
     <row r="162" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
@@ -5145,7 +5201,7 @@
         <v>35</v>
       </c>
       <c r="E162" s="23">
-        <v>6210000</v>
+        <v>3000000</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>8</v>
@@ -5153,7 +5209,7 @@
     </row>
     <row r="163" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
@@ -5161,7 +5217,7 @@
         <v>35</v>
       </c>
       <c r="E163" s="23">
-        <v>13680000</v>
+        <v>3780000</v>
       </c>
       <c r="F163" s="6" t="s">
         <v>8</v>
@@ -5169,7 +5225,7 @@
     </row>
     <row r="164" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
@@ -5177,7 +5233,7 @@
         <v>35</v>
       </c>
       <c r="E164" s="23">
-        <v>14400000</v>
+        <v>4050000</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>8</v>
@@ -5185,7 +5241,7 @@
     </row>
     <row r="165" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
@@ -5193,7 +5249,7 @@
         <v>35</v>
       </c>
       <c r="E165" s="23">
-        <v>16020000</v>
+        <v>4482000</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>8</v>
@@ -5201,7 +5257,7 @@
     </row>
     <row r="166" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -5209,7 +5265,7 @@
         <v>35</v>
       </c>
       <c r="E166" s="23">
-        <v>17280000</v>
+        <v>4752000</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>8</v>
@@ -5217,7 +5273,7 @@
     </row>
     <row r="167" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
@@ -5225,7 +5281,7 @@
         <v>35</v>
       </c>
       <c r="E167" s="23">
-        <v>19224000</v>
+        <v>5130000</v>
       </c>
       <c r="F167" s="6" t="s">
         <v>8</v>
@@ -5233,7 +5289,7 @@
     </row>
     <row r="168" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
@@ -5241,7 +5297,7 @@
         <v>35</v>
       </c>
       <c r="E168" s="23">
-        <v>21024000</v>
+        <v>5562000</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>8</v>
@@ -5249,7 +5305,7 @@
     </row>
     <row r="169" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
@@ -5257,155 +5313,127 @@
         <v>35</v>
       </c>
       <c r="E169" s="23">
+        <v>6210000</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A170" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B170" s="6"/>
+      <c r="C170" s="6"/>
+      <c r="D170" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E170" s="23">
+        <v>13680000</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A171" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B171" s="6"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E171" s="23">
+        <v>14400000</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A172" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B172" s="6"/>
+      <c r="C172" s="6"/>
+      <c r="D172" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E172" s="23">
+        <v>16020000</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A173" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B173" s="6"/>
+      <c r="C173" s="6"/>
+      <c r="D173" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E173" s="23">
+        <v>17280000</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A174" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B174" s="6"/>
+      <c r="C174" s="6"/>
+      <c r="D174" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E174" s="23">
+        <v>19224000</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A175" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B175" s="6"/>
+      <c r="C175" s="6"/>
+      <c r="D175" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E175" s="23">
+        <v>21024000</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B176" s="6"/>
+      <c r="C176" s="6"/>
+      <c r="D176" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176" s="23">
         <v>24624000</v>
       </c>
-      <c r="F169" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A170" s="6" t="s">
+      <c r="F176" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C170" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D170" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E170" s="23">
-        <v>15000</v>
-      </c>
-      <c r="F170" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A171" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C171" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E171" s="23">
-        <v>19500</v>
-      </c>
-      <c r="F171" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A172" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C172" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D172" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E172" s="23">
-        <v>25000</v>
-      </c>
-      <c r="F172" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A173" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C173" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D173" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E173" s="23">
-        <v>30000</v>
-      </c>
-      <c r="F173" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A174" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C174" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D174" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E174" s="23">
-        <v>40000</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A175" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C175" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E175" s="23">
-        <v>45000</v>
-      </c>
-      <c r="F175" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A176" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C176" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D176" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E176" s="23">
-        <v>78000</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="177" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A177" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>9</v>
@@ -5417,15 +5445,15 @@
         <v>35</v>
       </c>
       <c r="E177" s="23">
-        <v>87000</v>
+        <v>15000</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>9</v>
@@ -5437,15 +5465,15 @@
         <v>35</v>
       </c>
       <c r="E178" s="23">
-        <v>96000</v>
+        <v>19500</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>9</v>
@@ -5457,15 +5485,15 @@
         <v>35</v>
       </c>
       <c r="E179" s="23">
-        <v>105000</v>
+        <v>25000</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>9</v>
@@ -5477,15 +5505,15 @@
         <v>35</v>
       </c>
       <c r="E180" s="23">
-        <v>114000</v>
+        <v>30000</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>9</v>
@@ -5497,15 +5525,15 @@
         <v>35</v>
       </c>
       <c r="E181" s="23">
-        <v>142500</v>
+        <v>40000</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>9</v>
@@ -5517,15 +5545,15 @@
         <v>35</v>
       </c>
       <c r="E182" s="23">
-        <v>153000</v>
+        <v>45000</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>9</v>
@@ -5537,15 +5565,15 @@
         <v>35</v>
       </c>
       <c r="E183" s="23">
-        <v>163500</v>
+        <v>78000</v>
       </c>
       <c r="F183" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>9</v>
@@ -5557,15 +5585,15 @@
         <v>35</v>
       </c>
       <c r="E184" s="23">
-        <v>232500</v>
+        <v>87000</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="185" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>9</v>
@@ -5577,15 +5605,15 @@
         <v>35</v>
       </c>
       <c r="E185" s="23">
-        <v>247500</v>
+        <v>96000</v>
       </c>
       <c r="F185" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>9</v>
@@ -5597,15 +5625,15 @@
         <v>35</v>
       </c>
       <c r="E186" s="23">
-        <v>295500</v>
+        <v>105000</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>9</v>
@@ -5617,15 +5645,15 @@
         <v>35</v>
       </c>
       <c r="E187" s="23">
-        <v>312000</v>
+        <v>114000</v>
       </c>
       <c r="F187" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>9</v>
@@ -5637,15 +5665,15 @@
         <v>35</v>
       </c>
       <c r="E188" s="23">
-        <v>410000</v>
+        <v>142500</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="189" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>9</v>
@@ -5657,15 +5685,15 @@
         <v>35</v>
       </c>
       <c r="E189" s="23">
-        <v>434000</v>
+        <v>153000</v>
       </c>
       <c r="F189" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>9</v>
@@ -5677,316 +5705,155 @@
         <v>35</v>
       </c>
       <c r="E190" s="23">
+        <v>163500</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A191" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C191" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E191" s="23">
+        <v>232500</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A192" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E192" s="23">
+        <v>247500</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A193" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E193" s="23">
+        <v>295500</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A194" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C194" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E194" s="23">
+        <v>312000</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A195" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C195" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E195" s="23">
+        <v>410000</v>
+      </c>
+      <c r="F195" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A196" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C196" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196" s="23">
+        <v>434000</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A197" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E197" s="23">
         <v>469500</v>
       </c>
-      <c r="F190" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="191" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="7" t="s">
+      <c r="F197" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="B191" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C191" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D191" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E191" s="23">
-        <v>19860000</v>
-      </c>
-      <c r="F191" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G191" s="28"/>
-      <c r="H191" s="28"/>
-      <c r="I191" s="28"/>
-      <c r="J191" s="28"/>
-      <c r="K191" s="28"/>
-      <c r="L191" s="28"/>
-      <c r="M191" s="28"/>
-      <c r="N191" s="28"/>
-      <c r="O191" s="28"/>
-      <c r="P191" s="28"/>
-      <c r="Q191" s="28"/>
-      <c r="R191" s="28"/>
-      <c r="S191" s="28"/>
-      <c r="T191" s="28"/>
-      <c r="U191" s="28"/>
-      <c r="V191" s="28"/>
-      <c r="W191" s="28"/>
-      <c r="X191" s="28"/>
-      <c r="Y191" s="28"/>
-      <c r="Z191" s="28"/>
-      <c r="AA191" s="28"/>
-      <c r="AB191" s="28"/>
-      <c r="AC191" s="28"/>
-    </row>
-    <row r="192" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C192" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D192" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E192" s="23">
-        <v>24980000</v>
-      </c>
-      <c r="F192" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G192" s="28"/>
-      <c r="H192" s="28"/>
-      <c r="I192" s="28"/>
-      <c r="J192" s="28"/>
-      <c r="K192" s="28"/>
-      <c r="L192" s="28"/>
-      <c r="M192" s="28"/>
-      <c r="N192" s="28"/>
-      <c r="O192" s="28"/>
-      <c r="P192" s="28"/>
-      <c r="Q192" s="28"/>
-      <c r="R192" s="28"/>
-      <c r="S192" s="28"/>
-      <c r="T192" s="28"/>
-      <c r="U192" s="28"/>
-      <c r="V192" s="28"/>
-      <c r="W192" s="28"/>
-      <c r="X192" s="28"/>
-      <c r="Y192" s="28"/>
-      <c r="Z192" s="28"/>
-      <c r="AA192" s="28"/>
-      <c r="AB192" s="28"/>
-      <c r="AC192" s="28"/>
-    </row>
-    <row r="193" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B193" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C193" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D193" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E193" s="23">
-        <v>35680000</v>
-      </c>
-      <c r="F193" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G193" s="28"/>
-      <c r="H193" s="28"/>
-      <c r="I193" s="28"/>
-      <c r="J193" s="28"/>
-      <c r="K193" s="28"/>
-      <c r="L193" s="28"/>
-      <c r="M193" s="28"/>
-      <c r="N193" s="28"/>
-      <c r="O193" s="28"/>
-      <c r="P193" s="28"/>
-      <c r="Q193" s="28"/>
-      <c r="R193" s="28"/>
-      <c r="S193" s="28"/>
-      <c r="T193" s="28"/>
-      <c r="U193" s="28"/>
-      <c r="V193" s="28"/>
-      <c r="W193" s="28"/>
-      <c r="X193" s="28"/>
-      <c r="Y193" s="28"/>
-      <c r="Z193" s="28"/>
-      <c r="AA193" s="28"/>
-      <c r="AB193" s="28"/>
-      <c r="AC193" s="28"/>
-    </row>
-    <row r="194" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B194" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C194" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D194" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E194" s="23">
-        <v>39860000</v>
-      </c>
-      <c r="F194" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G194" s="28"/>
-      <c r="H194" s="28"/>
-      <c r="I194" s="28"/>
-      <c r="J194" s="28"/>
-      <c r="K194" s="28"/>
-      <c r="L194" s="28"/>
-      <c r="M194" s="28"/>
-      <c r="N194" s="28"/>
-      <c r="O194" s="28"/>
-      <c r="P194" s="28"/>
-      <c r="Q194" s="28"/>
-      <c r="R194" s="28"/>
-      <c r="S194" s="28"/>
-      <c r="T194" s="28"/>
-      <c r="U194" s="28"/>
-      <c r="V194" s="28"/>
-      <c r="W194" s="28"/>
-      <c r="X194" s="28"/>
-      <c r="Y194" s="28"/>
-      <c r="Z194" s="28"/>
-      <c r="AA194" s="28"/>
-      <c r="AB194" s="28"/>
-      <c r="AC194" s="28"/>
-    </row>
-    <row r="195" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B195" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C195" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D195" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E195" s="23">
-        <v>47979000</v>
-      </c>
-      <c r="F195" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G195"/>
-      <c r="H195"/>
-      <c r="I195"/>
-      <c r="J195"/>
-      <c r="K195"/>
-      <c r="L195"/>
-      <c r="M195"/>
-      <c r="N195"/>
-      <c r="O195"/>
-      <c r="P195"/>
-      <c r="Q195"/>
-      <c r="R195"/>
-      <c r="S195"/>
-      <c r="T195"/>
-      <c r="U195"/>
-      <c r="V195"/>
-      <c r="W195"/>
-      <c r="X195"/>
-      <c r="Y195"/>
-      <c r="Z195"/>
-      <c r="AA195"/>
-      <c r="AB195"/>
-      <c r="AC195"/>
-    </row>
-    <row r="196" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B196" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C196" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D196" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E196" s="23">
-        <v>52680000</v>
-      </c>
-      <c r="F196" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G196" s="28"/>
-      <c r="H196" s="28"/>
-      <c r="I196" s="28"/>
-      <c r="J196" s="28"/>
-      <c r="K196" s="28"/>
-      <c r="L196" s="28"/>
-      <c r="M196" s="28"/>
-      <c r="N196" s="28"/>
-      <c r="O196" s="28"/>
-      <c r="P196" s="28"/>
-      <c r="Q196" s="28"/>
-      <c r="R196" s="28"/>
-      <c r="S196" s="28"/>
-      <c r="T196" s="28"/>
-      <c r="U196" s="28"/>
-      <c r="V196" s="28"/>
-      <c r="W196" s="28"/>
-      <c r="X196" s="28"/>
-      <c r="Y196" s="28"/>
-      <c r="Z196" s="28"/>
-      <c r="AA196" s="28"/>
-      <c r="AB196" s="28"/>
-      <c r="AC196" s="28"/>
-    </row>
-    <row r="197" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D197" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E197" s="23">
-        <v>62680000</v>
-      </c>
-      <c r="F197" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G197" s="28"/>
-      <c r="H197" s="28"/>
-      <c r="I197" s="28"/>
-      <c r="J197" s="28"/>
-      <c r="K197" s="28"/>
-      <c r="L197" s="28"/>
-      <c r="M197" s="28"/>
-      <c r="N197" s="28"/>
-      <c r="O197" s="28"/>
-      <c r="P197" s="28"/>
-      <c r="Q197" s="28"/>
-      <c r="R197" s="28"/>
-      <c r="S197" s="28"/>
-      <c r="T197" s="28"/>
-      <c r="U197" s="28"/>
-      <c r="V197" s="28"/>
-      <c r="W197" s="28"/>
-      <c r="X197" s="28"/>
-      <c r="Y197" s="28"/>
-      <c r="Z197" s="28"/>
-      <c r="AA197" s="28"/>
-      <c r="AB197" s="28"/>
-      <c r="AC197" s="28"/>
-    </row>
-    <row r="198" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="B198" s="8" t="s">
         <v>9</v>
@@ -5998,7 +5865,7 @@
         <v>35</v>
       </c>
       <c r="E198" s="23">
-        <v>68680000</v>
+        <v>19860000</v>
       </c>
       <c r="F198" s="13" t="s">
         <v>8</v>
@@ -6027,9 +5894,9 @@
       <c r="AB198" s="28"/>
       <c r="AC198" s="28"/>
     </row>
-    <row r="199" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B199" s="8" t="s">
         <v>9</v>
@@ -6041,7 +5908,7 @@
         <v>35</v>
       </c>
       <c r="E199" s="23">
-        <v>75500000</v>
+        <v>24980000</v>
       </c>
       <c r="F199" s="13" t="s">
         <v>8</v>
@@ -6070,9 +5937,9 @@
       <c r="AB199" s="28"/>
       <c r="AC199" s="28"/>
     </row>
-    <row r="200" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>9</v>
@@ -6084,7 +5951,7 @@
         <v>35</v>
       </c>
       <c r="E200" s="23">
-        <v>89580000</v>
+        <v>35680000</v>
       </c>
       <c r="F200" s="13" t="s">
         <v>8</v>
@@ -6113,9 +5980,9 @@
       <c r="AB200" s="28"/>
       <c r="AC200" s="28"/>
     </row>
-    <row r="201" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>9</v>
@@ -6127,7 +5994,7 @@
         <v>35</v>
       </c>
       <c r="E201" s="23">
-        <v>99880000</v>
+        <v>39860000</v>
       </c>
       <c r="F201" s="13" t="s">
         <v>8</v>
@@ -6156,9 +6023,9 @@
       <c r="AB201" s="28"/>
       <c r="AC201" s="28"/>
     </row>
-    <row r="202" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29" s="1" customFormat="1" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>9</v>
@@ -6170,38 +6037,38 @@
         <v>35</v>
       </c>
       <c r="E202" s="23">
-        <v>109680000</v>
+        <v>47979000</v>
       </c>
       <c r="F202" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G202" s="28"/>
-      <c r="H202" s="28"/>
-      <c r="I202" s="28"/>
-      <c r="J202" s="28"/>
-      <c r="K202" s="28"/>
-      <c r="L202" s="28"/>
-      <c r="M202" s="28"/>
-      <c r="N202" s="28"/>
-      <c r="O202" s="28"/>
-      <c r="P202" s="28"/>
-      <c r="Q202" s="28"/>
-      <c r="R202" s="28"/>
-      <c r="S202" s="28"/>
-      <c r="T202" s="28"/>
-      <c r="U202" s="28"/>
-      <c r="V202" s="28"/>
-      <c r="W202" s="28"/>
-      <c r="X202" s="28"/>
-      <c r="Y202" s="28"/>
-      <c r="Z202" s="28"/>
-      <c r="AA202" s="28"/>
-      <c r="AB202" s="28"/>
-      <c r="AC202" s="28"/>
-    </row>
-    <row r="203" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G202"/>
+      <c r="H202"/>
+      <c r="I202"/>
+      <c r="J202"/>
+      <c r="K202"/>
+      <c r="L202"/>
+      <c r="M202"/>
+      <c r="N202"/>
+      <c r="O202"/>
+      <c r="P202"/>
+      <c r="Q202"/>
+      <c r="R202"/>
+      <c r="S202"/>
+      <c r="T202"/>
+      <c r="U202"/>
+      <c r="V202"/>
+      <c r="W202"/>
+      <c r="X202"/>
+      <c r="Y202"/>
+      <c r="Z202"/>
+      <c r="AA202"/>
+      <c r="AB202"/>
+      <c r="AC202"/>
+    </row>
+    <row r="203" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>9</v>
@@ -6213,7 +6080,7 @@
         <v>35</v>
       </c>
       <c r="E203" s="23">
-        <v>129860000</v>
+        <v>52680000</v>
       </c>
       <c r="F203" s="13" t="s">
         <v>8</v>
@@ -6242,9 +6109,9 @@
       <c r="AB203" s="28"/>
       <c r="AC203" s="28"/>
     </row>
-    <row r="204" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:29" s="2" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B204" s="8" t="s">
         <v>9</v>
@@ -6256,7 +6123,7 @@
         <v>35</v>
       </c>
       <c r="E204" s="23">
-        <v>144910000</v>
+        <v>62680000</v>
       </c>
       <c r="F204" s="13" t="s">
         <v>8</v>
@@ -6285,9 +6152,9 @@
       <c r="AB204" s="28"/>
       <c r="AC204" s="28"/>
     </row>
-    <row r="205" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:29" s="2" customFormat="1" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>9</v>
@@ -6299,7 +6166,7 @@
         <v>35</v>
       </c>
       <c r="E205" s="23">
-        <v>155910000</v>
+        <v>68680000</v>
       </c>
       <c r="F205" s="13" t="s">
         <v>8</v>
@@ -6330,7 +6197,7 @@
     </row>
     <row r="206" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>9</v>
@@ -6342,7 +6209,7 @@
         <v>35</v>
       </c>
       <c r="E206" s="23">
-        <v>156560000</v>
+        <v>75500000</v>
       </c>
       <c r="F206" s="13" t="s">
         <v>8</v>
@@ -6373,7 +6240,7 @@
     </row>
     <row r="207" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>9</v>
@@ -6385,7 +6252,7 @@
         <v>35</v>
       </c>
       <c r="E207" s="23">
-        <v>184370000</v>
+        <v>89580000</v>
       </c>
       <c r="F207" s="13" t="s">
         <v>8</v>
@@ -6416,7 +6283,7 @@
     </row>
     <row r="208" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B208" s="8" t="s">
         <v>9</v>
@@ -6428,7 +6295,7 @@
         <v>35</v>
       </c>
       <c r="E208" s="23">
-        <v>243080000</v>
+        <v>99880000</v>
       </c>
       <c r="F208" s="13" t="s">
         <v>8</v>
@@ -6459,7 +6326,7 @@
     </row>
     <row r="209" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B209" s="8" t="s">
         <v>9</v>
@@ -6471,7 +6338,7 @@
         <v>35</v>
       </c>
       <c r="E209" s="23">
-        <v>276040000</v>
+        <v>109680000</v>
       </c>
       <c r="F209" s="13" t="s">
         <v>8</v>
@@ -6502,7 +6369,7 @@
     </row>
     <row r="210" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B210" s="8" t="s">
         <v>9</v>
@@ -6514,7 +6381,7 @@
         <v>35</v>
       </c>
       <c r="E210" s="23">
-        <v>313680000</v>
+        <v>129860000</v>
       </c>
       <c r="F210" s="13" t="s">
         <v>8</v>
@@ -6545,7 +6412,7 @@
     </row>
     <row r="211" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B211" s="8" t="s">
         <v>9</v>
@@ -6557,7 +6424,7 @@
         <v>35</v>
       </c>
       <c r="E211" s="23">
-        <v>358200000</v>
+        <v>144910000</v>
       </c>
       <c r="F211" s="13" t="s">
         <v>8</v>
@@ -6588,7 +6455,7 @@
     </row>
     <row r="212" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B212" s="8" t="s">
         <v>9</v>
@@ -6600,7 +6467,7 @@
         <v>35</v>
       </c>
       <c r="E212" s="23">
-        <v>389600000</v>
+        <v>155910000</v>
       </c>
       <c r="F212" s="13" t="s">
         <v>8</v>
@@ -6631,7 +6498,7 @@
     </row>
     <row r="213" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B213" s="8" t="s">
         <v>9</v>
@@ -6643,7 +6510,7 @@
         <v>35</v>
       </c>
       <c r="E213" s="23">
-        <v>433800000</v>
+        <v>156560000</v>
       </c>
       <c r="F213" s="13" t="s">
         <v>8</v>
@@ -6674,7 +6541,7 @@
     </row>
     <row r="214" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B214" s="8" t="s">
         <v>9</v>
@@ -6686,7 +6553,7 @@
         <v>35</v>
       </c>
       <c r="E214" s="23">
-        <v>656580000</v>
+        <v>184370000</v>
       </c>
       <c r="F214" s="13" t="s">
         <v>8</v>
@@ -6717,7 +6584,7 @@
     </row>
     <row r="215" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B215" s="8" t="s">
         <v>9</v>
@@ -6729,7 +6596,7 @@
         <v>35</v>
       </c>
       <c r="E215" s="23">
-        <v>762670000</v>
+        <v>243080000</v>
       </c>
       <c r="F215" s="13" t="s">
         <v>8</v>
@@ -6760,7 +6627,7 @@
     </row>
     <row r="216" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B216" s="8" t="s">
         <v>9</v>
@@ -6772,7 +6639,7 @@
         <v>35</v>
       </c>
       <c r="E216" s="23">
-        <v>874940000</v>
+        <v>276040000</v>
       </c>
       <c r="F216" s="13" t="s">
         <v>8</v>
@@ -6803,7 +6670,7 @@
     </row>
     <row r="217" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B217" s="8" t="s">
         <v>9</v>
@@ -6815,7 +6682,7 @@
         <v>35</v>
       </c>
       <c r="E217" s="23">
-        <v>1062400000</v>
+        <v>313680000</v>
       </c>
       <c r="F217" s="13" t="s">
         <v>8</v>
@@ -6844,320 +6711,324 @@
       <c r="AB217" s="28"/>
       <c r="AC217" s="28"/>
     </row>
-    <row r="218" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="11" t="s">
-        <v>215</v>
+    <row r="218" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="B218" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C218" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D218" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E218" s="24">
-        <v>75000</v>
+      <c r="C218" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D218" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E218" s="23">
+        <v>358200000</v>
       </c>
       <c r="F218" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G218"/>
-      <c r="H218"/>
-      <c r="I218"/>
-      <c r="J218"/>
-      <c r="K218"/>
-      <c r="L218"/>
-      <c r="M218"/>
-      <c r="N218"/>
-      <c r="O218"/>
-      <c r="P218"/>
-      <c r="Q218"/>
-      <c r="R218"/>
-      <c r="S218"/>
-      <c r="T218"/>
-      <c r="U218"/>
-      <c r="V218"/>
-      <c r="W218"/>
-      <c r="X218"/>
-      <c r="Y218"/>
-      <c r="Z218"/>
-      <c r="AA218"/>
-      <c r="AB218"/>
-      <c r="AC218"/>
-    </row>
-    <row r="219" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="11" t="s">
-        <v>157</v>
+      <c r="G218" s="28"/>
+      <c r="H218" s="28"/>
+      <c r="I218" s="28"/>
+      <c r="J218" s="28"/>
+      <c r="K218" s="28"/>
+      <c r="L218" s="28"/>
+      <c r="M218" s="28"/>
+      <c r="N218" s="28"/>
+      <c r="O218" s="28"/>
+      <c r="P218" s="28"/>
+      <c r="Q218" s="28"/>
+      <c r="R218" s="28"/>
+      <c r="S218" s="28"/>
+      <c r="T218" s="28"/>
+      <c r="U218" s="28"/>
+      <c r="V218" s="28"/>
+      <c r="W218" s="28"/>
+      <c r="X218" s="28"/>
+      <c r="Y218" s="28"/>
+      <c r="Z218" s="28"/>
+      <c r="AA218" s="28"/>
+      <c r="AB218" s="28"/>
+      <c r="AC218" s="28"/>
+    </row>
+    <row r="219" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C219" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D219" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E219" s="24">
-        <v>33000</v>
+        <v>9</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D219" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E219" s="23">
+        <v>389600000</v>
       </c>
       <c r="F219" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G219"/>
-      <c r="H219"/>
-      <c r="I219"/>
-      <c r="J219"/>
-      <c r="K219"/>
-      <c r="L219"/>
-      <c r="M219"/>
-      <c r="N219"/>
-      <c r="O219"/>
-      <c r="P219"/>
-      <c r="Q219"/>
-      <c r="R219"/>
-      <c r="S219"/>
-      <c r="T219"/>
-      <c r="U219"/>
-      <c r="V219"/>
-      <c r="W219"/>
-      <c r="X219"/>
-      <c r="Y219"/>
-      <c r="Z219"/>
-      <c r="AA219"/>
-      <c r="AB219"/>
-      <c r="AC219"/>
-    </row>
-    <row r="220" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G219" s="28"/>
+      <c r="H219" s="28"/>
+      <c r="I219" s="28"/>
+      <c r="J219" s="28"/>
+      <c r="K219" s="28"/>
+      <c r="L219" s="28"/>
+      <c r="M219" s="28"/>
+      <c r="N219" s="28"/>
+      <c r="O219" s="28"/>
+      <c r="P219" s="28"/>
+      <c r="Q219" s="28"/>
+      <c r="R219" s="28"/>
+      <c r="S219" s="28"/>
+      <c r="T219" s="28"/>
+      <c r="U219" s="28"/>
+      <c r="V219" s="28"/>
+      <c r="W219" s="28"/>
+      <c r="X219" s="28"/>
+      <c r="Y219" s="28"/>
+      <c r="Z219" s="28"/>
+      <c r="AA219" s="28"/>
+      <c r="AB219" s="28"/>
+      <c r="AC219" s="28"/>
+    </row>
+    <row r="220" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C220" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D220" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E220" s="24">
-        <v>75000</v>
+        <v>9</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D220" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E220" s="23">
+        <v>433800000</v>
       </c>
       <c r="F220" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G220"/>
-      <c r="H220"/>
-      <c r="I220"/>
-      <c r="J220"/>
-      <c r="K220"/>
-      <c r="L220"/>
-      <c r="M220"/>
-      <c r="N220"/>
-      <c r="O220"/>
-      <c r="P220"/>
-      <c r="Q220"/>
-      <c r="R220"/>
-      <c r="S220"/>
-      <c r="T220"/>
-      <c r="U220"/>
-      <c r="V220"/>
-      <c r="W220"/>
-      <c r="X220"/>
-      <c r="Y220"/>
-      <c r="Z220"/>
-      <c r="AA220"/>
-      <c r="AB220"/>
-      <c r="AC220"/>
-    </row>
-    <row r="221" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G220" s="28"/>
+      <c r="H220" s="28"/>
+      <c r="I220" s="28"/>
+      <c r="J220" s="28"/>
+      <c r="K220" s="28"/>
+      <c r="L220" s="28"/>
+      <c r="M220" s="28"/>
+      <c r="N220" s="28"/>
+      <c r="O220" s="28"/>
+      <c r="P220" s="28"/>
+      <c r="Q220" s="28"/>
+      <c r="R220" s="28"/>
+      <c r="S220" s="28"/>
+      <c r="T220" s="28"/>
+      <c r="U220" s="28"/>
+      <c r="V220" s="28"/>
+      <c r="W220" s="28"/>
+      <c r="X220" s="28"/>
+      <c r="Y220" s="28"/>
+      <c r="Z220" s="28"/>
+      <c r="AA220" s="28"/>
+      <c r="AB220" s="28"/>
+      <c r="AC220" s="28"/>
+    </row>
+    <row r="221" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C221" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D221" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E221" s="24">
-        <v>75000</v>
+        <v>9</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D221" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E221" s="23">
+        <v>656580000</v>
       </c>
       <c r="F221" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G221"/>
-      <c r="H221"/>
-      <c r="I221"/>
-      <c r="J221"/>
-      <c r="K221"/>
-      <c r="L221"/>
-      <c r="M221"/>
-      <c r="N221"/>
-      <c r="O221"/>
-      <c r="P221"/>
-      <c r="Q221"/>
-      <c r="R221"/>
-      <c r="S221"/>
-      <c r="T221"/>
-      <c r="U221"/>
-      <c r="V221"/>
-      <c r="W221"/>
-      <c r="X221"/>
-      <c r="Y221"/>
-      <c r="Z221"/>
-      <c r="AA221"/>
-      <c r="AB221"/>
-      <c r="AC221"/>
-    </row>
-    <row r="222" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="11" t="s">
-        <v>218</v>
+      <c r="G221" s="28"/>
+      <c r="H221" s="28"/>
+      <c r="I221" s="28"/>
+      <c r="J221" s="28"/>
+      <c r="K221" s="28"/>
+      <c r="L221" s="28"/>
+      <c r="M221" s="28"/>
+      <c r="N221" s="28"/>
+      <c r="O221" s="28"/>
+      <c r="P221" s="28"/>
+      <c r="Q221" s="28"/>
+      <c r="R221" s="28"/>
+      <c r="S221" s="28"/>
+      <c r="T221" s="28"/>
+      <c r="U221" s="28"/>
+      <c r="V221" s="28"/>
+      <c r="W221" s="28"/>
+      <c r="X221" s="28"/>
+      <c r="Y221" s="28"/>
+      <c r="Z221" s="28"/>
+      <c r="AA221" s="28"/>
+      <c r="AB221" s="28"/>
+      <c r="AC221" s="28"/>
+    </row>
+    <row r="222" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="B222" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C222" s="12" t="s">
+      <c r="C222" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D222" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E222" s="23">
+        <v>762670000</v>
+      </c>
+      <c r="F222" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G222" s="28"/>
+      <c r="H222" s="28"/>
+      <c r="I222" s="28"/>
+      <c r="J222" s="28"/>
+      <c r="K222" s="28"/>
+      <c r="L222" s="28"/>
+      <c r="M222" s="28"/>
+      <c r="N222" s="28"/>
+      <c r="O222" s="28"/>
+      <c r="P222" s="28"/>
+      <c r="Q222" s="28"/>
+      <c r="R222" s="28"/>
+      <c r="S222" s="28"/>
+      <c r="T222" s="28"/>
+      <c r="U222" s="28"/>
+      <c r="V222" s="28"/>
+      <c r="W222" s="28"/>
+      <c r="X222" s="28"/>
+      <c r="Y222" s="28"/>
+      <c r="Z222" s="28"/>
+      <c r="AA222" s="28"/>
+      <c r="AB222" s="28"/>
+      <c r="AC222" s="28"/>
+    </row>
+    <row r="223" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D223" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E223" s="23">
+        <v>874940000</v>
+      </c>
+      <c r="F223" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G223" s="28"/>
+      <c r="H223" s="28"/>
+      <c r="I223" s="28"/>
+      <c r="J223" s="28"/>
+      <c r="K223" s="28"/>
+      <c r="L223" s="28"/>
+      <c r="M223" s="28"/>
+      <c r="N223" s="28"/>
+      <c r="O223" s="28"/>
+      <c r="P223" s="28"/>
+      <c r="Q223" s="28"/>
+      <c r="R223" s="28"/>
+      <c r="S223" s="28"/>
+      <c r="T223" s="28"/>
+      <c r="U223" s="28"/>
+      <c r="V223" s="28"/>
+      <c r="W223" s="28"/>
+      <c r="X223" s="28"/>
+      <c r="Y223" s="28"/>
+      <c r="Z223" s="28"/>
+      <c r="AA223" s="28"/>
+      <c r="AB223" s="28"/>
+      <c r="AC223" s="28"/>
+    </row>
+    <row r="224" spans="1:29" s="2" customFormat="1" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B224" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C224" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D224" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E224" s="23">
+        <v>1062400000</v>
+      </c>
+      <c r="F224" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G224" s="28"/>
+      <c r="H224" s="28"/>
+      <c r="I224" s="28"/>
+      <c r="J224" s="28"/>
+      <c r="K224" s="28"/>
+      <c r="L224" s="28"/>
+      <c r="M224" s="28"/>
+      <c r="N224" s="28"/>
+      <c r="O224" s="28"/>
+      <c r="P224" s="28"/>
+      <c r="Q224" s="28"/>
+      <c r="R224" s="28"/>
+      <c r="S224" s="28"/>
+      <c r="T224" s="28"/>
+      <c r="U224" s="28"/>
+      <c r="V224" s="28"/>
+      <c r="W224" s="28"/>
+      <c r="X224" s="28"/>
+      <c r="Y224" s="28"/>
+      <c r="Z224" s="28"/>
+      <c r="AA224" s="28"/>
+      <c r="AB224" s="28"/>
+      <c r="AC224" s="28"/>
+    </row>
+    <row r="225" spans="1:29" s="3" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B225" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C225" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D222" s="36" t="s">
+      <c r="D225" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="E222" s="24">
+      <c r="E225" s="24">
         <v>75000</v>
       </c>
-      <c r="F222" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G222"/>
-      <c r="H222"/>
-      <c r="I222"/>
-      <c r="J222"/>
-      <c r="K222"/>
-      <c r="L222"/>
-      <c r="M222"/>
-      <c r="N222"/>
-      <c r="O222"/>
-      <c r="P222"/>
-      <c r="Q222"/>
-      <c r="R222"/>
-      <c r="S222"/>
-      <c r="T222"/>
-      <c r="U222"/>
-      <c r="V222"/>
-      <c r="W222"/>
-      <c r="X222"/>
-      <c r="Y222"/>
-      <c r="Z222"/>
-      <c r="AA222"/>
-      <c r="AB222"/>
-      <c r="AC222"/>
-    </row>
-    <row r="223" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B223" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="C223" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D223" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E223" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F223" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G223"/>
-      <c r="H223"/>
-      <c r="I223"/>
-      <c r="J223"/>
-      <c r="K223"/>
-      <c r="L223"/>
-      <c r="M223"/>
-      <c r="N223"/>
-      <c r="O223"/>
-      <c r="P223"/>
-      <c r="Q223"/>
-      <c r="R223"/>
-      <c r="S223"/>
-      <c r="T223"/>
-      <c r="U223"/>
-      <c r="V223"/>
-      <c r="W223"/>
-      <c r="X223"/>
-      <c r="Y223"/>
-      <c r="Z223"/>
-      <c r="AA223"/>
-      <c r="AB223"/>
-      <c r="AC223"/>
-    </row>
-    <row r="224" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B224" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="C224" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D224" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E224" s="24">
-        <v>75000</v>
-      </c>
-      <c r="F224" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G224"/>
-      <c r="H224"/>
-      <c r="I224"/>
-      <c r="J224"/>
-      <c r="K224"/>
-      <c r="L224"/>
-      <c r="M224"/>
-      <c r="N224"/>
-      <c r="O224"/>
-      <c r="P224"/>
-      <c r="Q224"/>
-      <c r="R224"/>
-      <c r="S224"/>
-      <c r="T224"/>
-      <c r="U224"/>
-      <c r="V224"/>
-      <c r="W224"/>
-      <c r="X224"/>
-      <c r="Y224"/>
-      <c r="Z224"/>
-      <c r="AA224"/>
-      <c r="AB224"/>
-      <c r="AC224"/>
-    </row>
-    <row r="225" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B225" s="38"/>
-      <c r="C225" s="29"/>
-      <c r="D225" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E225" s="24">
-        <v>1000000</v>
-      </c>
-      <c r="F225" s="17" t="s">
+      <c r="F225" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G225"/>
@@ -7185,18 +7056,22 @@
       <c r="AC225"/>
     </row>
     <row r="226" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B226" s="38"/>
-      <c r="C226" s="29"/>
-      <c r="D226" s="10" t="s">
-        <v>35</v>
+      <c r="A226" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B226" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D226" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E226" s="24">
-        <v>880000</v>
-      </c>
-      <c r="F226" s="17" t="s">
+        <v>33000</v>
+      </c>
+      <c r="F226" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G226"/>
@@ -7223,19 +7098,23 @@
       <c r="AB226"/>
       <c r="AC226"/>
     </row>
-    <row r="227" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B227" s="38"/>
-      <c r="C227" s="29"/>
-      <c r="D227" s="10" t="s">
-        <v>35</v>
+    <row r="227" spans="1:29" s="4" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B227" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D227" s="36" t="s">
+        <v>156</v>
       </c>
       <c r="E227" s="24">
-        <v>1380000</v>
-      </c>
-      <c r="F227" s="17" t="s">
+        <v>75000</v>
+      </c>
+      <c r="F227" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G227"/>
@@ -7262,19 +7141,23 @@
       <c r="AB227"/>
       <c r="AC227"/>
     </row>
-    <row r="228" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B228" s="8"/>
-      <c r="C228" s="8"/>
-      <c r="D228" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E228" s="23">
-        <v>13880000</v>
-      </c>
-      <c r="F228" s="18" t="s">
+    <row r="228" spans="1:29" s="4" customFormat="1" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B228" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D228" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E228" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F228" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G228"/>
@@ -7301,19 +7184,23 @@
       <c r="AB228"/>
       <c r="AC228"/>
     </row>
-    <row r="229" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:29" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B229" s="8"/>
-      <c r="C229" s="8"/>
-      <c r="D229" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E229" s="23">
-        <v>750000</v>
-      </c>
-      <c r="F229" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B229" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D229" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E229" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F229" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G229"/>
@@ -7341,18 +7228,22 @@
       <c r="AC229"/>
     </row>
     <row r="230" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B230" s="8"/>
-      <c r="C230" s="8"/>
-      <c r="D230" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E230" s="23">
-        <v>155000</v>
-      </c>
-      <c r="F230" s="18" t="s">
+      <c r="A230" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B230" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D230" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E230" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F230" s="13" t="s">
         <v>8</v>
       </c>
       <c r="G230"/>
@@ -7380,18 +7271,22 @@
       <c r="AC230"/>
     </row>
     <row r="231" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="B231" s="8"/>
-      <c r="C231" s="8"/>
-      <c r="D231" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E231" s="23">
-        <v>176000</v>
-      </c>
-      <c r="F231" s="18" t="s">
+      <c r="A231" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B231" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C231" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D231" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E231" s="24">
+        <v>75000</v>
+      </c>
+      <c r="F231" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G231"/>
@@ -7419,18 +7314,18 @@
       <c r="AC231"/>
     </row>
     <row r="232" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B232" s="8"/>
-      <c r="C232" s="8"/>
+      <c r="A232" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B232" s="38"/>
+      <c r="C232" s="29"/>
       <c r="D232" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E232" s="23">
-        <v>198000</v>
-      </c>
-      <c r="F232" s="18" t="s">
+      <c r="E232" s="24">
+        <v>1000000</v>
+      </c>
+      <c r="F232" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G232"/>
@@ -7458,18 +7353,18 @@
       <c r="AC232"/>
     </row>
     <row r="233" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B233" s="8"/>
-      <c r="C233" s="8"/>
+      <c r="A233" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B233" s="38"/>
+      <c r="C233" s="29"/>
       <c r="D233" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E233" s="23">
-        <v>186000</v>
-      </c>
-      <c r="F233" s="18" t="s">
+      <c r="E233" s="24">
+        <v>880000</v>
+      </c>
+      <c r="F233" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G233"/>
@@ -7497,18 +7392,18 @@
       <c r="AC233"/>
     </row>
     <row r="234" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B234" s="8"/>
-      <c r="C234" s="8"/>
+      <c r="A234" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B234" s="38"/>
+      <c r="C234" s="29"/>
       <c r="D234" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E234" s="23">
-        <v>198000</v>
-      </c>
-      <c r="F234" s="18" t="s">
+      <c r="E234" s="24">
+        <v>1380000</v>
+      </c>
+      <c r="F234" s="17" t="s">
         <v>8</v>
       </c>
       <c r="G234"/>
@@ -7537,7 +7432,7 @@
     </row>
     <row r="235" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
@@ -7545,7 +7440,7 @@
         <v>35</v>
       </c>
       <c r="E235" s="23">
-        <v>228000</v>
+        <v>13880000</v>
       </c>
       <c r="F235" s="18" t="s">
         <v>8</v>
@@ -7576,7 +7471,7 @@
     </row>
     <row r="236" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
@@ -7584,7 +7479,7 @@
         <v>35</v>
       </c>
       <c r="E236" s="23">
-        <v>175000</v>
+        <v>750000</v>
       </c>
       <c r="F236" s="18" t="s">
         <v>8</v>
@@ -7615,7 +7510,7 @@
     </row>
     <row r="237" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
@@ -7623,7 +7518,7 @@
         <v>35</v>
       </c>
       <c r="E237" s="23">
-        <v>296000</v>
+        <v>155000</v>
       </c>
       <c r="F237" s="18" t="s">
         <v>8</v>
@@ -7654,7 +7549,7 @@
     </row>
     <row r="238" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
@@ -7662,7 +7557,7 @@
         <v>35</v>
       </c>
       <c r="E238" s="23">
-        <v>258000</v>
+        <v>176000</v>
       </c>
       <c r="F238" s="18" t="s">
         <v>8</v>
@@ -7693,7 +7588,7 @@
     </row>
     <row r="239" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
@@ -7701,7 +7596,7 @@
         <v>35</v>
       </c>
       <c r="E239" s="23">
-        <v>228000</v>
+        <v>198000</v>
       </c>
       <c r="F239" s="18" t="s">
         <v>8</v>
@@ -7732,7 +7627,7 @@
     </row>
     <row r="240" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
@@ -7740,7 +7635,7 @@
         <v>35</v>
       </c>
       <c r="E240" s="23">
-        <v>248000</v>
+        <v>186000</v>
       </c>
       <c r="F240" s="18" t="s">
         <v>8</v>
@@ -7771,7 +7666,7 @@
     </row>
     <row r="241" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
@@ -7779,7 +7674,7 @@
         <v>35</v>
       </c>
       <c r="E241" s="23">
-        <v>278000</v>
+        <v>198000</v>
       </c>
       <c r="F241" s="18" t="s">
         <v>8</v>
@@ -7809,22 +7704,18 @@
       <c r="AC241"/>
     </row>
     <row r="242" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="B242" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C242" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D242" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E242" s="25">
-        <v>32680000</v>
-      </c>
-      <c r="F242" s="17" t="s">
+      <c r="A242" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B242" s="8"/>
+      <c r="C242" s="8"/>
+      <c r="D242" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E242" s="23">
+        <v>228000</v>
+      </c>
+      <c r="F242" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G242"/>
@@ -7851,23 +7742,19 @@
       <c r="AB242"/>
       <c r="AC242"/>
     </row>
-    <row r="243" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="B243" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C243" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D243" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E243" s="25">
-        <v>36800000</v>
-      </c>
-      <c r="F243" s="17" t="s">
+    <row r="243" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B243" s="8"/>
+      <c r="C243" s="8"/>
+      <c r="D243" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E243" s="23">
+        <v>175000</v>
+      </c>
+      <c r="F243" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G243"/>
@@ -7894,23 +7781,19 @@
       <c r="AB243"/>
       <c r="AC243"/>
     </row>
-    <row r="244" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B244" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C244" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D244" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E244" s="25">
-        <v>43680000</v>
-      </c>
-      <c r="F244" s="17" t="s">
+    <row r="244" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B244" s="8"/>
+      <c r="C244" s="8"/>
+      <c r="D244" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E244" s="23">
+        <v>296000</v>
+      </c>
+      <c r="F244" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G244"/>
@@ -7937,89 +7820,165 @@
       <c r="AB244"/>
       <c r="AC244"/>
     </row>
-    <row r="245" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A245" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B245" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C245" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D245" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E245" s="25">
-        <v>48680000</v>
-      </c>
-      <c r="F245" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="246" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A246" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="B246" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C246" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D246" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E246" s="25">
-        <v>54680000</v>
-      </c>
-      <c r="F246" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="247" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A247" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B247" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C247" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D247" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E247" s="25">
-        <v>69860000</v>
-      </c>
-      <c r="F247" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="248" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A248" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="B248" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C248" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D248" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E248" s="25">
-        <v>99680000</v>
-      </c>
-      <c r="F248" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="249" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B245" s="8"/>
+      <c r="C245" s="8"/>
+      <c r="D245" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E245" s="23">
+        <v>258000</v>
+      </c>
+      <c r="F245" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G245"/>
+      <c r="H245"/>
+      <c r="I245"/>
+      <c r="J245"/>
+      <c r="K245"/>
+      <c r="L245"/>
+      <c r="M245"/>
+      <c r="N245"/>
+      <c r="O245"/>
+      <c r="P245"/>
+      <c r="Q245"/>
+      <c r="R245"/>
+      <c r="S245"/>
+      <c r="T245"/>
+      <c r="U245"/>
+      <c r="V245"/>
+      <c r="W245"/>
+      <c r="X245"/>
+      <c r="Y245"/>
+      <c r="Z245"/>
+      <c r="AA245"/>
+      <c r="AB245"/>
+      <c r="AC245"/>
+    </row>
+    <row r="246" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
+      <c r="D246" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E246" s="23">
+        <v>228000</v>
+      </c>
+      <c r="F246" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G246"/>
+      <c r="H246"/>
+      <c r="I246"/>
+      <c r="J246"/>
+      <c r="K246"/>
+      <c r="L246"/>
+      <c r="M246"/>
+      <c r="N246"/>
+      <c r="O246"/>
+      <c r="P246"/>
+      <c r="Q246"/>
+      <c r="R246"/>
+      <c r="S246"/>
+      <c r="T246"/>
+      <c r="U246"/>
+      <c r="V246"/>
+      <c r="W246"/>
+      <c r="X246"/>
+      <c r="Y246"/>
+      <c r="Z246"/>
+      <c r="AA246"/>
+      <c r="AB246"/>
+      <c r="AC246"/>
+    </row>
+    <row r="247" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E247" s="23">
+        <v>248000</v>
+      </c>
+      <c r="F247" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G247"/>
+      <c r="H247"/>
+      <c r="I247"/>
+      <c r="J247"/>
+      <c r="K247"/>
+      <c r="L247"/>
+      <c r="M247"/>
+      <c r="N247"/>
+      <c r="O247"/>
+      <c r="P247"/>
+      <c r="Q247"/>
+      <c r="R247"/>
+      <c r="S247"/>
+      <c r="T247"/>
+      <c r="U247"/>
+      <c r="V247"/>
+      <c r="W247"/>
+      <c r="X247"/>
+      <c r="Y247"/>
+      <c r="Z247"/>
+      <c r="AA247"/>
+      <c r="AB247"/>
+      <c r="AC247"/>
+    </row>
+    <row r="248" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E248" s="23">
+        <v>278000</v>
+      </c>
+      <c r="F248" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G248"/>
+      <c r="H248"/>
+      <c r="I248"/>
+      <c r="J248"/>
+      <c r="K248"/>
+      <c r="L248"/>
+      <c r="M248"/>
+      <c r="N248"/>
+      <c r="O248"/>
+      <c r="P248"/>
+      <c r="Q248"/>
+      <c r="R248"/>
+      <c r="S248"/>
+      <c r="T248"/>
+      <c r="U248"/>
+      <c r="V248"/>
+      <c r="W248"/>
+      <c r="X248"/>
+      <c r="Y248"/>
+      <c r="Z248"/>
+      <c r="AA248"/>
+      <c r="AB248"/>
+      <c r="AC248"/>
+    </row>
+    <row r="249" spans="1:29" s="4" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="19" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B249" s="20" t="s">
         <v>9</v>
@@ -8028,18 +7987,41 @@
         <v>84</v>
       </c>
       <c r="D249" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E249" s="26">
-        <v>75000</v>
+        <v>35</v>
+      </c>
+      <c r="E249" s="25">
+        <v>32680000</v>
       </c>
       <c r="F249" s="17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="250" spans="1:29" ht="51" x14ac:dyDescent="0.25">
-      <c r="A250" s="39" t="s">
-        <v>228</v>
+      <c r="G249"/>
+      <c r="H249"/>
+      <c r="I249"/>
+      <c r="J249"/>
+      <c r="K249"/>
+      <c r="L249"/>
+      <c r="M249"/>
+      <c r="N249"/>
+      <c r="O249"/>
+      <c r="P249"/>
+      <c r="Q249"/>
+      <c r="R249"/>
+      <c r="S249"/>
+      <c r="T249"/>
+      <c r="U249"/>
+      <c r="V249"/>
+      <c r="W249"/>
+      <c r="X249"/>
+      <c r="Y249"/>
+      <c r="Z249"/>
+      <c r="AA249"/>
+      <c r="AB249"/>
+      <c r="AC249"/>
+    </row>
+    <row r="250" spans="1:29" s="5" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="19" t="s">
+        <v>221</v>
       </c>
       <c r="B250" s="20" t="s">
         <v>9</v>
@@ -8048,12 +8030,198 @@
         <v>84</v>
       </c>
       <c r="D250" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E250" s="25">
+        <v>36800000</v>
+      </c>
+      <c r="F250" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G250"/>
+      <c r="H250"/>
+      <c r="I250"/>
+      <c r="J250"/>
+      <c r="K250"/>
+      <c r="L250"/>
+      <c r="M250"/>
+      <c r="N250"/>
+      <c r="O250"/>
+      <c r="P250"/>
+      <c r="Q250"/>
+      <c r="R250"/>
+      <c r="S250"/>
+      <c r="T250"/>
+      <c r="U250"/>
+      <c r="V250"/>
+      <c r="W250"/>
+      <c r="X250"/>
+      <c r="Y250"/>
+      <c r="Z250"/>
+      <c r="AA250"/>
+      <c r="AB250"/>
+      <c r="AC250"/>
+    </row>
+    <row r="251" spans="1:29" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B251" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C251" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D251" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E251" s="25">
+        <v>43680000</v>
+      </c>
+      <c r="F251" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G251"/>
+      <c r="H251"/>
+      <c r="I251"/>
+      <c r="J251"/>
+      <c r="K251"/>
+      <c r="L251"/>
+      <c r="M251"/>
+      <c r="N251"/>
+      <c r="O251"/>
+      <c r="P251"/>
+      <c r="Q251"/>
+      <c r="R251"/>
+      <c r="S251"/>
+      <c r="T251"/>
+      <c r="U251"/>
+      <c r="V251"/>
+      <c r="W251"/>
+      <c r="X251"/>
+      <c r="Y251"/>
+      <c r="Z251"/>
+      <c r="AA251"/>
+      <c r="AB251"/>
+      <c r="AC251"/>
+    </row>
+    <row r="252" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A252" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B252" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C252" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D252" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E252" s="25">
+        <v>48680000</v>
+      </c>
+      <c r="F252" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A253" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B253" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C253" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D253" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E253" s="25">
+        <v>54680000</v>
+      </c>
+      <c r="F253" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A254" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B254" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C254" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D254" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E254" s="25">
+        <v>69860000</v>
+      </c>
+      <c r="F254" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A255" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B255" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C255" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D255" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E255" s="25">
+        <v>99680000</v>
+      </c>
+      <c r="F255" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:29" ht="51" x14ac:dyDescent="0.25">
+      <c r="A256" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B256" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C256" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D256" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="E250" s="26">
+      <c r="E256" s="26">
         <v>75000</v>
       </c>
-      <c r="F250" s="17" t="s">
+      <c r="F256" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A257" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B257" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C257" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D257" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E257" s="26">
+        <v>75000</v>
+      </c>
+      <c r="F257" s="17" t="s">
         <v>8</v>
       </c>
     </row>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="287">
   <si>
     <t>Ống D650</t>
   </si>
@@ -1042,6 +1042,230 @@
   </si>
   <si>
     <t>Y chia D550  rẽ 2 nhánh D450 và D300</t>
+  </si>
+  <si>
+    <t>Vật tư ChiNT</t>
+  </si>
+  <si>
+    <t>Tủ ngoài trời, 2 lớp cánh
+Vỏ tủ sơn tĩnh điện</t>
+  </si>
+  <si>
+    <t>Bộ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1 quạt 18.5KW+ kết nối vói bơm 3KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1 quạt 55KW+ kết nối vói bơm 7.5KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2 quạt 7.5KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1 quạt 3KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <t>Tủ trong nhà, 1 lớp cánh
+Vỏ tủ sơn tĩnh điện</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2 quạt 11KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2 quạt 15KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2 quạt 22KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2 quạt 37KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2 quạt 45KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1 quạt 11KW+ kết nối vói 2 bơm 3KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1053,7 +1277,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1135,6 +1359,12 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1240,7 +1470,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1393,6 +1623,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="12" fillId="3" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1679,7 +1915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC257"/>
+  <dimension ref="A1:AC269"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5703125" style="40" customWidth="1"/>
@@ -2330,7 +2566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>43</v>
       </c>
@@ -2350,7 +2586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>44</v>
       </c>
@@ -2370,7 +2606,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>45</v>
       </c>
@@ -2390,7 +2626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>46</v>
       </c>
@@ -2410,7 +2646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>47</v>
       </c>
@@ -2430,7 +2666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>48</v>
       </c>
@@ -2450,7 +2686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>49</v>
       </c>
@@ -2470,7 +2706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>50</v>
       </c>
@@ -2490,7 +2726,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>51</v>
       </c>
@@ -2510,7 +2746,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>52</v>
       </c>
@@ -2530,7 +2766,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>53</v>
       </c>
@@ -2550,7 +2786,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>54</v>
       </c>
@@ -2570,7 +2806,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>55</v>
       </c>
@@ -2590,7 +2826,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:20" s="47" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" s="47" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>237</v>
       </c>
@@ -2610,7 +2846,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>238</v>
       </c>
@@ -2644,7 +2880,7 @@
       <c r="S47" s="47"/>
       <c r="T47" s="47"/>
     </row>
-    <row r="48" spans="1:20" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>239</v>
       </c>
@@ -2663,21 +2899,27 @@
       <c r="F48" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G48"/>
-      <c r="H48"/>
-      <c r="I48"/>
-      <c r="J48"/>
-      <c r="K48"/>
-      <c r="L48"/>
-      <c r="M48"/>
-      <c r="N48"/>
-      <c r="O48"/>
-      <c r="P48"/>
-      <c r="Q48"/>
-      <c r="R48"/>
-      <c r="S48"/>
-    </row>
-    <row r="49" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="47"/>
+      <c r="K48" s="47"/>
+      <c r="L48" s="47"/>
+      <c r="M48" s="47"/>
+      <c r="N48" s="47"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="47"/>
+      <c r="Q48" s="47"/>
+      <c r="R48" s="47"/>
+      <c r="S48" s="47"/>
+      <c r="T48" s="47"/>
+      <c r="U48"/>
+      <c r="V48"/>
+      <c r="W48"/>
+      <c r="X48"/>
+      <c r="Y48"/>
+    </row>
+    <row r="49" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>266</v>
       </c>
@@ -2696,9 +2938,27 @@
       <c r="F49" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G49" s="50"/>
-    </row>
-    <row r="50" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="47"/>
+      <c r="K49" s="47"/>
+      <c r="L49" s="47"/>
+      <c r="M49" s="47"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="47"/>
+      <c r="Q49" s="47"/>
+      <c r="R49" s="47"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="47"/>
+      <c r="U49"/>
+      <c r="V49"/>
+      <c r="W49"/>
+      <c r="X49"/>
+      <c r="Y49"/>
+    </row>
+    <row r="50" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>253</v>
       </c>
@@ -2717,8 +2977,22 @@
       <c r="F50" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="47"/>
+      <c r="L50" s="47"/>
+      <c r="M50" s="47"/>
+      <c r="N50" s="47"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="47"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47"/>
+      <c r="S50" s="47"/>
+      <c r="T50" s="47"/>
+    </row>
+    <row r="51" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>252</v>
       </c>
@@ -2737,8 +3011,22 @@
       <c r="F51" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="47"/>
+      <c r="K51" s="47"/>
+      <c r="L51" s="47"/>
+      <c r="M51" s="47"/>
+      <c r="N51" s="47"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="47"/>
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47"/>
+      <c r="S51" s="47"/>
+      <c r="T51" s="47"/>
+    </row>
+    <row r="52" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>267</v>
       </c>
@@ -2757,9 +3045,27 @@
       <c r="F52" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="50"/>
-    </row>
-    <row r="53" spans="1:18" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="47"/>
+      <c r="K52" s="47"/>
+      <c r="L52" s="47"/>
+      <c r="M52" s="47"/>
+      <c r="N52" s="47"/>
+      <c r="O52" s="47"/>
+      <c r="P52" s="47"/>
+      <c r="Q52" s="47"/>
+      <c r="R52" s="47"/>
+      <c r="S52" s="47"/>
+      <c r="T52" s="47"/>
+      <c r="U52"/>
+      <c r="V52"/>
+      <c r="W52"/>
+      <c r="X52"/>
+      <c r="Y52"/>
+    </row>
+    <row r="53" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>251</v>
       </c>
@@ -2778,8 +3084,22 @@
       <c r="F53" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="47"/>
+      <c r="K53" s="47"/>
+      <c r="L53" s="47"/>
+      <c r="M53" s="47"/>
+      <c r="N53" s="47"/>
+      <c r="O53" s="47"/>
+      <c r="P53" s="47"/>
+      <c r="Q53" s="47"/>
+      <c r="R53" s="47"/>
+      <c r="S53" s="47"/>
+      <c r="T53" s="47"/>
+    </row>
+    <row r="54" spans="1:25" s="30" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>250</v>
       </c>
@@ -2798,20 +3118,27 @@
       <c r="F54" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54"/>
-      <c r="M54"/>
-      <c r="N54"/>
-      <c r="O54"/>
-      <c r="P54"/>
-      <c r="Q54"/>
-      <c r="R54"/>
-    </row>
-    <row r="55" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="47"/>
+      <c r="K54" s="47"/>
+      <c r="L54" s="47"/>
+      <c r="M54" s="47"/>
+      <c r="N54" s="47"/>
+      <c r="O54" s="47"/>
+      <c r="P54" s="47"/>
+      <c r="Q54" s="47"/>
+      <c r="R54" s="47"/>
+      <c r="S54" s="47"/>
+      <c r="T54" s="47"/>
+      <c r="U54"/>
+      <c r="V54"/>
+      <c r="W54"/>
+      <c r="X54"/>
+      <c r="Y54"/>
+    </row>
+    <row r="55" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>268</v>
       </c>
@@ -2830,9 +3157,27 @@
       <c r="F55" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G55" s="50"/>
-    </row>
-    <row r="56" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G55" s="47"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="47"/>
+      <c r="K55" s="47"/>
+      <c r="L55" s="47"/>
+      <c r="M55" s="47"/>
+      <c r="N55" s="47"/>
+      <c r="O55" s="47"/>
+      <c r="P55" s="47"/>
+      <c r="Q55" s="47"/>
+      <c r="R55" s="47"/>
+      <c r="S55" s="47"/>
+      <c r="T55" s="47"/>
+      <c r="U55"/>
+      <c r="V55"/>
+      <c r="W55"/>
+      <c r="X55"/>
+      <c r="Y55"/>
+    </row>
+    <row r="56" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>249</v>
       </c>
@@ -2851,20 +3196,27 @@
       <c r="F56" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56"/>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56"/>
-      <c r="M56"/>
-      <c r="N56"/>
-      <c r="O56"/>
-      <c r="P56"/>
-      <c r="Q56"/>
-      <c r="R56"/>
-    </row>
-    <row r="57" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="47"/>
+      <c r="K56" s="47"/>
+      <c r="L56" s="47"/>
+      <c r="M56" s="47"/>
+      <c r="N56" s="47"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="47"/>
+      <c r="Q56" s="47"/>
+      <c r="R56" s="47"/>
+      <c r="S56" s="47"/>
+      <c r="T56" s="47"/>
+      <c r="U56"/>
+      <c r="V56"/>
+      <c r="W56"/>
+      <c r="X56"/>
+      <c r="Y56"/>
+    </row>
+    <row r="57" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>248</v>
       </c>
@@ -2883,20 +3235,27 @@
       <c r="F57" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
-      <c r="K57"/>
-      <c r="L57"/>
-      <c r="M57"/>
-      <c r="N57"/>
-      <c r="O57"/>
-      <c r="P57"/>
-      <c r="Q57"/>
-      <c r="R57"/>
-    </row>
-    <row r="58" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="47"/>
+      <c r="K57" s="47"/>
+      <c r="L57" s="47"/>
+      <c r="M57" s="47"/>
+      <c r="N57" s="47"/>
+      <c r="O57" s="47"/>
+      <c r="P57" s="47"/>
+      <c r="Q57" s="47"/>
+      <c r="R57" s="47"/>
+      <c r="S57" s="47"/>
+      <c r="T57" s="47"/>
+      <c r="U57"/>
+      <c r="V57"/>
+      <c r="W57"/>
+      <c r="X57"/>
+      <c r="Y57"/>
+    </row>
+    <row r="58" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>269</v>
       </c>
@@ -2915,9 +3274,27 @@
       <c r="F58" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="50"/>
-    </row>
-    <row r="59" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G58" s="47"/>
+      <c r="H58" s="47"/>
+      <c r="I58" s="47"/>
+      <c r="J58" s="47"/>
+      <c r="K58" s="47"/>
+      <c r="L58" s="47"/>
+      <c r="M58" s="47"/>
+      <c r="N58" s="47"/>
+      <c r="O58" s="47"/>
+      <c r="P58" s="47"/>
+      <c r="Q58" s="47"/>
+      <c r="R58" s="47"/>
+      <c r="S58" s="47"/>
+      <c r="T58" s="47"/>
+      <c r="U58"/>
+      <c r="V58"/>
+      <c r="W58"/>
+      <c r="X58"/>
+      <c r="Y58"/>
+    </row>
+    <row r="59" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>247</v>
       </c>
@@ -2936,20 +3313,27 @@
       <c r="F59" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
-      <c r="K59"/>
-      <c r="L59"/>
-      <c r="M59"/>
-      <c r="N59"/>
-      <c r="O59"/>
-      <c r="P59"/>
-      <c r="Q59"/>
-      <c r="R59"/>
-    </row>
-    <row r="60" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G59" s="47"/>
+      <c r="H59" s="47"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
+      <c r="L59" s="47"/>
+      <c r="M59" s="47"/>
+      <c r="N59" s="47"/>
+      <c r="O59" s="47"/>
+      <c r="P59" s="47"/>
+      <c r="Q59" s="47"/>
+      <c r="R59" s="47"/>
+      <c r="S59" s="47"/>
+      <c r="T59" s="47"/>
+      <c r="U59"/>
+      <c r="V59"/>
+      <c r="W59"/>
+      <c r="X59"/>
+      <c r="Y59"/>
+    </row>
+    <row r="60" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>270</v>
       </c>
@@ -2968,9 +3352,27 @@
       <c r="F60" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G60" s="50"/>
-    </row>
-    <row r="61" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G60" s="47"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="47"/>
+      <c r="K60" s="47"/>
+      <c r="L60" s="47"/>
+      <c r="M60" s="47"/>
+      <c r="N60" s="47"/>
+      <c r="O60" s="47"/>
+      <c r="P60" s="47"/>
+      <c r="Q60" s="47"/>
+      <c r="R60" s="47"/>
+      <c r="S60" s="47"/>
+      <c r="T60" s="47"/>
+      <c r="U60"/>
+      <c r="V60"/>
+      <c r="W60"/>
+      <c r="X60"/>
+      <c r="Y60"/>
+    </row>
+    <row r="61" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>254</v>
       </c>
@@ -2989,20 +3391,27 @@
       <c r="F61" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G61"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61"/>
-      <c r="K61"/>
-      <c r="L61"/>
-      <c r="M61"/>
-      <c r="N61"/>
-      <c r="O61"/>
-      <c r="P61"/>
-      <c r="Q61"/>
-      <c r="R61"/>
-    </row>
-    <row r="62" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G61" s="47"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47"/>
+      <c r="K61" s="47"/>
+      <c r="L61" s="47"/>
+      <c r="M61" s="47"/>
+      <c r="N61" s="47"/>
+      <c r="O61" s="47"/>
+      <c r="P61" s="47"/>
+      <c r="Q61" s="47"/>
+      <c r="R61" s="47"/>
+      <c r="S61" s="47"/>
+      <c r="T61" s="47"/>
+      <c r="U61"/>
+      <c r="V61"/>
+      <c r="W61"/>
+      <c r="X61"/>
+      <c r="Y61"/>
+    </row>
+    <row r="62" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>271</v>
       </c>
@@ -3021,9 +3430,27 @@
       <c r="F62" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="50"/>
-    </row>
-    <row r="63" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="47"/>
+      <c r="H62" s="47"/>
+      <c r="I62" s="47"/>
+      <c r="J62" s="47"/>
+      <c r="K62" s="47"/>
+      <c r="L62" s="47"/>
+      <c r="M62" s="47"/>
+      <c r="N62" s="47"/>
+      <c r="O62" s="47"/>
+      <c r="P62" s="47"/>
+      <c r="Q62" s="47"/>
+      <c r="R62" s="47"/>
+      <c r="S62" s="47"/>
+      <c r="T62" s="47"/>
+      <c r="U62"/>
+      <c r="V62"/>
+      <c r="W62"/>
+      <c r="X62"/>
+      <c r="Y62"/>
+    </row>
+    <row r="63" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>255</v>
       </c>
@@ -3042,20 +3469,27 @@
       <c r="F63" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G63"/>
-      <c r="H63"/>
-      <c r="I63"/>
-      <c r="J63"/>
-      <c r="K63"/>
-      <c r="L63"/>
-      <c r="M63"/>
-      <c r="N63"/>
-      <c r="O63"/>
-      <c r="P63"/>
-      <c r="Q63"/>
-      <c r="R63"/>
-    </row>
-    <row r="64" spans="1:18" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G63" s="47"/>
+      <c r="H63" s="47"/>
+      <c r="I63" s="47"/>
+      <c r="J63" s="47"/>
+      <c r="K63" s="47"/>
+      <c r="L63" s="47"/>
+      <c r="M63" s="47"/>
+      <c r="N63" s="47"/>
+      <c r="O63" s="47"/>
+      <c r="P63" s="47"/>
+      <c r="Q63" s="47"/>
+      <c r="R63" s="47"/>
+      <c r="S63" s="47"/>
+      <c r="T63" s="47"/>
+      <c r="U63"/>
+      <c r="V63"/>
+      <c r="W63"/>
+      <c r="X63"/>
+      <c r="Y63"/>
+    </row>
+    <row r="64" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>245</v>
       </c>
@@ -3074,20 +3508,27 @@
       <c r="F64" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64"/>
-      <c r="M64"/>
-      <c r="N64"/>
-      <c r="O64"/>
-      <c r="P64"/>
-      <c r="Q64"/>
-      <c r="R64"/>
-    </row>
-    <row r="65" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G64" s="47"/>
+      <c r="H64" s="47"/>
+      <c r="I64" s="47"/>
+      <c r="J64" s="47"/>
+      <c r="K64" s="47"/>
+      <c r="L64" s="47"/>
+      <c r="M64" s="47"/>
+      <c r="N64" s="47"/>
+      <c r="O64" s="47"/>
+      <c r="P64" s="47"/>
+      <c r="Q64" s="47"/>
+      <c r="R64" s="47"/>
+      <c r="S64" s="47"/>
+      <c r="T64" s="47"/>
+      <c r="U64"/>
+      <c r="V64"/>
+      <c r="W64"/>
+      <c r="X64"/>
+      <c r="Y64"/>
+    </row>
+    <row r="65" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>258</v>
       </c>
@@ -3106,9 +3547,27 @@
       <c r="F65" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G65" s="50"/>
-    </row>
-    <row r="66" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G65" s="47"/>
+      <c r="H65" s="47"/>
+      <c r="I65" s="47"/>
+      <c r="J65" s="47"/>
+      <c r="K65" s="47"/>
+      <c r="L65" s="47"/>
+      <c r="M65" s="47"/>
+      <c r="N65" s="47"/>
+      <c r="O65" s="47"/>
+      <c r="P65" s="47"/>
+      <c r="Q65" s="47"/>
+      <c r="R65" s="47"/>
+      <c r="S65" s="47"/>
+      <c r="T65" s="47"/>
+      <c r="U65"/>
+      <c r="V65"/>
+      <c r="W65"/>
+      <c r="X65"/>
+      <c r="Y65"/>
+    </row>
+    <row r="66" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>259</v>
       </c>
@@ -3127,9 +3586,27 @@
       <c r="F66" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G66" s="50"/>
-    </row>
-    <row r="67" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G66" s="47"/>
+      <c r="H66" s="47"/>
+      <c r="I66" s="47"/>
+      <c r="J66" s="47"/>
+      <c r="K66" s="47"/>
+      <c r="L66" s="47"/>
+      <c r="M66" s="47"/>
+      <c r="N66" s="47"/>
+      <c r="O66" s="47"/>
+      <c r="P66" s="47"/>
+      <c r="Q66" s="47"/>
+      <c r="R66" s="47"/>
+      <c r="S66" s="47"/>
+      <c r="T66" s="47"/>
+      <c r="U66"/>
+      <c r="V66"/>
+      <c r="W66"/>
+      <c r="X66"/>
+      <c r="Y66"/>
+    </row>
+    <row r="67" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>260</v>
       </c>
@@ -3148,9 +3625,27 @@
       <c r="F67" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G67" s="50"/>
-    </row>
-    <row r="68" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="47"/>
+      <c r="J67" s="47"/>
+      <c r="K67" s="47"/>
+      <c r="L67" s="47"/>
+      <c r="M67" s="47"/>
+      <c r="N67" s="47"/>
+      <c r="O67" s="47"/>
+      <c r="P67" s="47"/>
+      <c r="Q67" s="47"/>
+      <c r="R67" s="47"/>
+      <c r="S67" s="47"/>
+      <c r="T67" s="47"/>
+      <c r="U67"/>
+      <c r="V67"/>
+      <c r="W67"/>
+      <c r="X67"/>
+      <c r="Y67"/>
+    </row>
+    <row r="68" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>246</v>
       </c>
@@ -3169,20 +3664,27 @@
       <c r="F68" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G68"/>
-      <c r="H68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68"/>
-      <c r="M68"/>
-      <c r="N68"/>
-      <c r="O68"/>
-      <c r="P68"/>
-      <c r="Q68"/>
-      <c r="R68"/>
-    </row>
-    <row r="69" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G68" s="47"/>
+      <c r="H68" s="47"/>
+      <c r="I68" s="47"/>
+      <c r="J68" s="47"/>
+      <c r="K68" s="47"/>
+      <c r="L68" s="47"/>
+      <c r="M68" s="47"/>
+      <c r="N68" s="47"/>
+      <c r="O68" s="47"/>
+      <c r="P68" s="47"/>
+      <c r="Q68" s="47"/>
+      <c r="R68" s="47"/>
+      <c r="S68" s="47"/>
+      <c r="T68" s="47"/>
+      <c r="U68"/>
+      <c r="V68"/>
+      <c r="W68"/>
+      <c r="X68"/>
+      <c r="Y68"/>
+    </row>
+    <row r="69" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>257</v>
       </c>
@@ -3201,20 +3703,27 @@
       <c r="F69" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G69"/>
-      <c r="H69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-      <c r="K69"/>
-      <c r="L69"/>
-      <c r="M69"/>
-      <c r="N69"/>
-      <c r="O69"/>
-      <c r="P69"/>
-      <c r="Q69"/>
-      <c r="R69"/>
-    </row>
-    <row r="70" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
+      <c r="J69" s="47"/>
+      <c r="K69" s="47"/>
+      <c r="L69" s="47"/>
+      <c r="M69" s="47"/>
+      <c r="N69" s="47"/>
+      <c r="O69" s="47"/>
+      <c r="P69" s="47"/>
+      <c r="Q69" s="47"/>
+      <c r="R69" s="47"/>
+      <c r="S69" s="47"/>
+      <c r="T69" s="47"/>
+      <c r="U69"/>
+      <c r="V69"/>
+      <c r="W69"/>
+      <c r="X69"/>
+      <c r="Y69"/>
+    </row>
+    <row r="70" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>261</v>
       </c>
@@ -3233,20 +3742,27 @@
       <c r="F70" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G70"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-      <c r="K70"/>
-      <c r="L70"/>
-      <c r="M70"/>
-      <c r="N70"/>
-      <c r="O70"/>
-      <c r="P70"/>
-      <c r="Q70"/>
-      <c r="R70"/>
-    </row>
-    <row r="71" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="47"/>
+      <c r="K70" s="47"/>
+      <c r="L70" s="47"/>
+      <c r="M70" s="47"/>
+      <c r="N70" s="47"/>
+      <c r="O70" s="47"/>
+      <c r="P70" s="47"/>
+      <c r="Q70" s="47"/>
+      <c r="R70" s="47"/>
+      <c r="S70" s="47"/>
+      <c r="T70" s="47"/>
+      <c r="U70"/>
+      <c r="V70"/>
+      <c r="W70"/>
+      <c r="X70"/>
+      <c r="Y70"/>
+    </row>
+    <row r="71" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>256</v>
       </c>
@@ -3265,20 +3781,27 @@
       <c r="F71" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G71"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-      <c r="K71"/>
-      <c r="L71"/>
-      <c r="M71"/>
-      <c r="N71"/>
-      <c r="O71"/>
-      <c r="P71"/>
-      <c r="Q71"/>
-      <c r="R71"/>
-    </row>
-    <row r="72" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
+      <c r="J71" s="47"/>
+      <c r="K71" s="47"/>
+      <c r="L71" s="47"/>
+      <c r="M71" s="47"/>
+      <c r="N71" s="47"/>
+      <c r="O71" s="47"/>
+      <c r="P71" s="47"/>
+      <c r="Q71" s="47"/>
+      <c r="R71" s="47"/>
+      <c r="S71" s="47"/>
+      <c r="T71" s="47"/>
+      <c r="U71"/>
+      <c r="V71"/>
+      <c r="W71"/>
+      <c r="X71"/>
+      <c r="Y71"/>
+    </row>
+    <row r="72" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>262</v>
       </c>
@@ -3297,20 +3820,27 @@
       <c r="F72" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72"/>
-      <c r="M72"/>
-      <c r="N72"/>
-      <c r="O72"/>
-      <c r="P72"/>
-      <c r="Q72"/>
-      <c r="R72"/>
-    </row>
-    <row r="73" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G72" s="47"/>
+      <c r="H72" s="47"/>
+      <c r="I72" s="47"/>
+      <c r="J72" s="47"/>
+      <c r="K72" s="47"/>
+      <c r="L72" s="47"/>
+      <c r="M72" s="47"/>
+      <c r="N72" s="47"/>
+      <c r="O72" s="47"/>
+      <c r="P72" s="47"/>
+      <c r="Q72" s="47"/>
+      <c r="R72" s="47"/>
+      <c r="S72" s="47"/>
+      <c r="T72" s="47"/>
+      <c r="U72"/>
+      <c r="V72"/>
+      <c r="W72"/>
+      <c r="X72"/>
+      <c r="Y72"/>
+    </row>
+    <row r="73" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
         <v>263</v>
       </c>
@@ -3329,20 +3859,27 @@
       <c r="F73" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G73"/>
-      <c r="H73"/>
-      <c r="I73"/>
-      <c r="J73"/>
-      <c r="K73"/>
-      <c r="L73"/>
-      <c r="M73"/>
-      <c r="N73"/>
-      <c r="O73"/>
-      <c r="P73"/>
-      <c r="Q73"/>
-      <c r="R73"/>
-    </row>
-    <row r="74" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G73" s="47"/>
+      <c r="H73" s="47"/>
+      <c r="I73" s="47"/>
+      <c r="J73" s="47"/>
+      <c r="K73" s="47"/>
+      <c r="L73" s="47"/>
+      <c r="M73" s="47"/>
+      <c r="N73" s="47"/>
+      <c r="O73" s="47"/>
+      <c r="P73" s="47"/>
+      <c r="Q73" s="47"/>
+      <c r="R73" s="47"/>
+      <c r="S73" s="47"/>
+      <c r="T73" s="47"/>
+      <c r="U73"/>
+      <c r="V73"/>
+      <c r="W73"/>
+      <c r="X73"/>
+      <c r="Y73"/>
+    </row>
+    <row r="74" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
         <v>264</v>
       </c>
@@ -3361,20 +3898,27 @@
       <c r="F74" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G74"/>
-      <c r="H74"/>
-      <c r="I74"/>
-      <c r="J74"/>
-      <c r="K74"/>
-      <c r="L74"/>
-      <c r="M74"/>
-      <c r="N74"/>
-      <c r="O74"/>
-      <c r="P74"/>
-      <c r="Q74"/>
-      <c r="R74"/>
-    </row>
-    <row r="75" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G74" s="47"/>
+      <c r="H74" s="47"/>
+      <c r="I74" s="47"/>
+      <c r="J74" s="47"/>
+      <c r="K74" s="47"/>
+      <c r="L74" s="47"/>
+      <c r="M74" s="47"/>
+      <c r="N74" s="47"/>
+      <c r="O74" s="47"/>
+      <c r="P74" s="47"/>
+      <c r="Q74" s="47"/>
+      <c r="R74" s="47"/>
+      <c r="S74" s="47"/>
+      <c r="T74" s="47"/>
+      <c r="U74"/>
+      <c r="V74"/>
+      <c r="W74"/>
+      <c r="X74"/>
+      <c r="Y74"/>
+    </row>
+    <row r="75" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>241</v>
       </c>
@@ -3393,22 +3937,27 @@
       <c r="F75" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G75"/>
-      <c r="H75"/>
-      <c r="I75"/>
-      <c r="J75"/>
-      <c r="K75"/>
-      <c r="L75"/>
-      <c r="M75"/>
-      <c r="N75"/>
-      <c r="O75"/>
-      <c r="P75"/>
-      <c r="Q75"/>
-      <c r="R75"/>
+      <c r="G75" s="47"/>
+      <c r="H75" s="47"/>
+      <c r="I75" s="47"/>
+      <c r="J75" s="47"/>
+      <c r="K75" s="47"/>
+      <c r="L75" s="47"/>
+      <c r="M75" s="47"/>
+      <c r="N75" s="47"/>
+      <c r="O75" s="47"/>
+      <c r="P75" s="47"/>
+      <c r="Q75" s="47"/>
+      <c r="R75" s="47"/>
       <c r="S75" s="47"/>
       <c r="T75" s="47"/>
-    </row>
-    <row r="76" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U75"/>
+      <c r="V75"/>
+      <c r="W75"/>
+      <c r="X75"/>
+      <c r="Y75"/>
+    </row>
+    <row r="76" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>242</v>
       </c>
@@ -3427,22 +3976,27 @@
       <c r="F76" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G76"/>
-      <c r="H76"/>
-      <c r="I76"/>
-      <c r="J76"/>
-      <c r="K76"/>
-      <c r="L76"/>
-      <c r="M76"/>
-      <c r="N76"/>
-      <c r="O76"/>
-      <c r="P76"/>
-      <c r="Q76"/>
-      <c r="R76"/>
-      <c r="S76"/>
-      <c r="T76"/>
-    </row>
-    <row r="77" spans="1:20" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G76" s="47"/>
+      <c r="H76" s="47"/>
+      <c r="I76" s="47"/>
+      <c r="J76" s="47"/>
+      <c r="K76" s="47"/>
+      <c r="L76" s="47"/>
+      <c r="M76" s="47"/>
+      <c r="N76" s="47"/>
+      <c r="O76" s="47"/>
+      <c r="P76" s="47"/>
+      <c r="Q76" s="47"/>
+      <c r="R76" s="47"/>
+      <c r="S76" s="47"/>
+      <c r="T76" s="47"/>
+      <c r="U76"/>
+      <c r="V76"/>
+      <c r="W76"/>
+      <c r="X76"/>
+      <c r="Y76"/>
+    </row>
+    <row r="77" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>243</v>
       </c>
@@ -3461,22 +4015,27 @@
       <c r="F77" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G77"/>
-      <c r="H77"/>
-      <c r="I77"/>
-      <c r="J77"/>
-      <c r="K77"/>
-      <c r="L77"/>
-      <c r="M77"/>
-      <c r="N77"/>
-      <c r="O77"/>
-      <c r="P77"/>
-      <c r="Q77"/>
+      <c r="G77" s="47"/>
+      <c r="H77" s="47"/>
+      <c r="I77" s="47"/>
+      <c r="J77" s="47"/>
+      <c r="K77" s="47"/>
+      <c r="L77" s="47"/>
+      <c r="M77" s="47"/>
+      <c r="N77" s="47"/>
+      <c r="O77" s="47"/>
+      <c r="P77" s="47"/>
+      <c r="Q77" s="47"/>
       <c r="R77" s="47"/>
       <c r="S77" s="47"/>
       <c r="T77" s="47"/>
-    </row>
-    <row r="78" spans="1:20" s="31" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U77"/>
+      <c r="V77"/>
+      <c r="W77"/>
+      <c r="X77"/>
+      <c r="Y77"/>
+    </row>
+    <row r="78" spans="1:25" s="31" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>240</v>
       </c>
@@ -3495,22 +4054,27 @@
       <c r="F78" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-      <c r="J78"/>
-      <c r="K78"/>
-      <c r="L78"/>
-      <c r="M78"/>
-      <c r="N78"/>
-      <c r="O78"/>
-      <c r="P78"/>
-      <c r="Q78"/>
-      <c r="R78"/>
-      <c r="S78"/>
-      <c r="T78"/>
-    </row>
-    <row r="79" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G78" s="47"/>
+      <c r="H78" s="47"/>
+      <c r="I78" s="47"/>
+      <c r="J78" s="47"/>
+      <c r="K78" s="47"/>
+      <c r="L78" s="47"/>
+      <c r="M78" s="47"/>
+      <c r="N78" s="47"/>
+      <c r="O78" s="47"/>
+      <c r="P78" s="47"/>
+      <c r="Q78" s="47"/>
+      <c r="R78" s="47"/>
+      <c r="S78" s="47"/>
+      <c r="T78" s="47"/>
+      <c r="U78"/>
+      <c r="V78"/>
+      <c r="W78"/>
+      <c r="X78"/>
+      <c r="Y78"/>
+    </row>
+    <row r="79" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>159</v>
       </c>
@@ -3529,8 +4093,22 @@
       <c r="F79" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G79" s="47"/>
+      <c r="H79" s="47"/>
+      <c r="I79" s="47"/>
+      <c r="J79" s="47"/>
+      <c r="K79" s="47"/>
+      <c r="L79" s="47"/>
+      <c r="M79" s="47"/>
+      <c r="N79" s="47"/>
+      <c r="O79" s="47"/>
+      <c r="P79" s="47"/>
+      <c r="Q79" s="47"/>
+      <c r="R79" s="47"/>
+      <c r="S79" s="47"/>
+      <c r="T79" s="47"/>
+    </row>
+    <row r="80" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>167</v>
       </c>
@@ -3549,8 +4127,22 @@
       <c r="F80" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G80" s="47"/>
+      <c r="H80" s="47"/>
+      <c r="I80" s="47"/>
+      <c r="J80" s="47"/>
+      <c r="K80" s="47"/>
+      <c r="L80" s="47"/>
+      <c r="M80" s="47"/>
+      <c r="N80" s="47"/>
+      <c r="O80" s="47"/>
+      <c r="P80" s="47"/>
+      <c r="Q80" s="47"/>
+      <c r="R80" s="47"/>
+      <c r="S80" s="47"/>
+      <c r="T80" s="47"/>
+    </row>
+    <row r="81" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>167</v>
       </c>
@@ -3569,23 +4161,27 @@
       <c r="F81" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G81"/>
-      <c r="H81"/>
-      <c r="I81"/>
-      <c r="J81"/>
-      <c r="K81"/>
-      <c r="L81"/>
-      <c r="M81"/>
-      <c r="N81"/>
-      <c r="O81"/>
-      <c r="P81"/>
-      <c r="Q81"/>
-      <c r="R81"/>
-      <c r="S81"/>
-      <c r="T81"/>
+      <c r="G81" s="47"/>
+      <c r="H81" s="47"/>
+      <c r="I81" s="47"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="47"/>
+      <c r="L81" s="47"/>
+      <c r="M81" s="47"/>
+      <c r="N81" s="47"/>
+      <c r="O81" s="47"/>
+      <c r="P81" s="47"/>
+      <c r="Q81" s="47"/>
+      <c r="R81" s="47"/>
+      <c r="S81" s="47"/>
+      <c r="T81" s="47"/>
       <c r="U81"/>
-    </row>
-    <row r="82" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="V81"/>
+      <c r="W81"/>
+      <c r="X81"/>
+      <c r="Y81"/>
+    </row>
+    <row r="82" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
         <v>166</v>
       </c>
@@ -3604,8 +4200,22 @@
       <c r="F82" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="83" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G82" s="47"/>
+      <c r="H82" s="47"/>
+      <c r="I82" s="47"/>
+      <c r="J82" s="47"/>
+      <c r="K82" s="47"/>
+      <c r="L82" s="47"/>
+      <c r="M82" s="47"/>
+      <c r="N82" s="47"/>
+      <c r="O82" s="47"/>
+      <c r="P82" s="47"/>
+      <c r="Q82" s="47"/>
+      <c r="R82" s="47"/>
+      <c r="S82" s="47"/>
+      <c r="T82" s="47"/>
+    </row>
+    <row r="83" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A83" s="27" t="s">
         <v>167</v>
       </c>
@@ -3624,8 +4234,22 @@
       <c r="F83" s="17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G83" s="47"/>
+      <c r="H83" s="47"/>
+      <c r="I83" s="47"/>
+      <c r="J83" s="47"/>
+      <c r="K83" s="47"/>
+      <c r="L83" s="47"/>
+      <c r="M83" s="47"/>
+      <c r="N83" s="47"/>
+      <c r="O83" s="47"/>
+      <c r="P83" s="47"/>
+      <c r="Q83" s="47"/>
+      <c r="R83" s="47"/>
+      <c r="S83" s="47"/>
+      <c r="T83" s="47"/>
+    </row>
+    <row r="84" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
         <v>165</v>
       </c>
@@ -3644,8 +4268,22 @@
       <c r="F84" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="85" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G84" s="47"/>
+      <c r="H84" s="47"/>
+      <c r="I84" s="47"/>
+      <c r="J84" s="47"/>
+      <c r="K84" s="47"/>
+      <c r="L84" s="47"/>
+      <c r="M84" s="47"/>
+      <c r="N84" s="47"/>
+      <c r="O84" s="47"/>
+      <c r="P84" s="47"/>
+      <c r="Q84" s="47"/>
+      <c r="R84" s="47"/>
+      <c r="S84" s="47"/>
+      <c r="T84" s="47"/>
+    </row>
+    <row r="85" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A85" s="27" t="s">
         <v>171</v>
       </c>
@@ -3664,8 +4302,22 @@
       <c r="F85" s="17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G85" s="47"/>
+      <c r="H85" s="47"/>
+      <c r="I85" s="47"/>
+      <c r="J85" s="47"/>
+      <c r="K85" s="47"/>
+      <c r="L85" s="47"/>
+      <c r="M85" s="47"/>
+      <c r="N85" s="47"/>
+      <c r="O85" s="47"/>
+      <c r="P85" s="47"/>
+      <c r="Q85" s="47"/>
+      <c r="R85" s="47"/>
+      <c r="S85" s="47"/>
+      <c r="T85" s="47"/>
+    </row>
+    <row r="86" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
         <v>164</v>
       </c>
@@ -3684,8 +4336,22 @@
       <c r="F86" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G86" s="47"/>
+      <c r="H86" s="47"/>
+      <c r="I86" s="47"/>
+      <c r="J86" s="47"/>
+      <c r="K86" s="47"/>
+      <c r="L86" s="47"/>
+      <c r="M86" s="47"/>
+      <c r="N86" s="47"/>
+      <c r="O86" s="47"/>
+      <c r="P86" s="47"/>
+      <c r="Q86" s="47"/>
+      <c r="R86" s="47"/>
+      <c r="S86" s="47"/>
+      <c r="T86" s="47"/>
+    </row>
+    <row r="87" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A87" s="27" t="s">
         <v>170</v>
       </c>
@@ -3704,8 +4370,22 @@
       <c r="F87" s="17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="88" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G87" s="47"/>
+      <c r="H87" s="47"/>
+      <c r="I87" s="47"/>
+      <c r="J87" s="47"/>
+      <c r="K87" s="47"/>
+      <c r="L87" s="47"/>
+      <c r="M87" s="47"/>
+      <c r="N87" s="47"/>
+      <c r="O87" s="47"/>
+      <c r="P87" s="47"/>
+      <c r="Q87" s="47"/>
+      <c r="R87" s="47"/>
+      <c r="S87" s="47"/>
+      <c r="T87" s="47"/>
+    </row>
+    <row r="88" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>163</v>
       </c>
@@ -3724,8 +4404,22 @@
       <c r="F88" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G88" s="47"/>
+      <c r="H88" s="47"/>
+      <c r="I88" s="47"/>
+      <c r="J88" s="47"/>
+      <c r="K88" s="47"/>
+      <c r="L88" s="47"/>
+      <c r="M88" s="47"/>
+      <c r="N88" s="47"/>
+      <c r="O88" s="47"/>
+      <c r="P88" s="47"/>
+      <c r="Q88" s="47"/>
+      <c r="R88" s="47"/>
+      <c r="S88" s="47"/>
+      <c r="T88" s="47"/>
+    </row>
+    <row r="89" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
         <v>235</v>
       </c>
@@ -3744,23 +4438,27 @@
       <c r="F89" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G89"/>
-      <c r="H89"/>
-      <c r="I89"/>
-      <c r="J89"/>
-      <c r="K89"/>
-      <c r="L89"/>
-      <c r="M89"/>
-      <c r="N89"/>
-      <c r="O89"/>
-      <c r="P89"/>
-      <c r="Q89"/>
-      <c r="R89"/>
-      <c r="S89"/>
-      <c r="T89"/>
+      <c r="G89" s="47"/>
+      <c r="H89" s="47"/>
+      <c r="I89" s="47"/>
+      <c r="J89" s="47"/>
+      <c r="K89" s="47"/>
+      <c r="L89" s="47"/>
+      <c r="M89" s="47"/>
+      <c r="N89" s="47"/>
+      <c r="O89" s="47"/>
+      <c r="P89" s="47"/>
+      <c r="Q89" s="47"/>
+      <c r="R89" s="47"/>
+      <c r="S89" s="47"/>
+      <c r="T89" s="47"/>
       <c r="U89"/>
-    </row>
-    <row r="90" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V89"/>
+      <c r="W89"/>
+      <c r="X89"/>
+      <c r="Y89"/>
+    </row>
+    <row r="90" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
         <v>234</v>
       </c>
@@ -3779,23 +4477,27 @@
       <c r="F90" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G90"/>
-      <c r="H90"/>
-      <c r="I90"/>
-      <c r="J90"/>
-      <c r="K90"/>
-      <c r="L90"/>
-      <c r="M90"/>
-      <c r="N90"/>
-      <c r="O90"/>
-      <c r="P90"/>
-      <c r="Q90"/>
-      <c r="R90"/>
-      <c r="S90"/>
-      <c r="T90"/>
+      <c r="G90" s="47"/>
+      <c r="H90" s="47"/>
+      <c r="I90" s="47"/>
+      <c r="J90" s="47"/>
+      <c r="K90" s="47"/>
+      <c r="L90" s="47"/>
+      <c r="M90" s="47"/>
+      <c r="N90" s="47"/>
+      <c r="O90" s="47"/>
+      <c r="P90" s="47"/>
+      <c r="Q90" s="47"/>
+      <c r="R90" s="47"/>
+      <c r="S90" s="47"/>
+      <c r="T90" s="47"/>
       <c r="U90"/>
-    </row>
-    <row r="91" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="V90"/>
+      <c r="W90"/>
+      <c r="X90"/>
+      <c r="Y90"/>
+    </row>
+    <row r="91" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
         <v>169</v>
       </c>
@@ -3814,8 +4516,22 @@
       <c r="F91" s="17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G91" s="47"/>
+      <c r="H91" s="47"/>
+      <c r="I91" s="47"/>
+      <c r="J91" s="47"/>
+      <c r="K91" s="47"/>
+      <c r="L91" s="47"/>
+      <c r="M91" s="47"/>
+      <c r="N91" s="47"/>
+      <c r="O91" s="47"/>
+      <c r="P91" s="47"/>
+      <c r="Q91" s="47"/>
+      <c r="R91" s="47"/>
+      <c r="S91" s="47"/>
+      <c r="T91" s="47"/>
+    </row>
+    <row r="92" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
         <v>236</v>
       </c>
@@ -3834,23 +4550,27 @@
       <c r="F92" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G92"/>
-      <c r="H92"/>
-      <c r="I92"/>
-      <c r="J92"/>
-      <c r="K92"/>
-      <c r="L92"/>
-      <c r="M92"/>
-      <c r="N92"/>
-      <c r="O92"/>
-      <c r="P92"/>
-      <c r="Q92"/>
-      <c r="R92"/>
-      <c r="S92"/>
-      <c r="T92"/>
+      <c r="G92" s="47"/>
+      <c r="H92" s="47"/>
+      <c r="I92" s="47"/>
+      <c r="J92" s="47"/>
+      <c r="K92" s="47"/>
+      <c r="L92" s="47"/>
+      <c r="M92" s="47"/>
+      <c r="N92" s="47"/>
+      <c r="O92" s="47"/>
+      <c r="P92" s="47"/>
+      <c r="Q92" s="47"/>
+      <c r="R92" s="47"/>
+      <c r="S92" s="47"/>
+      <c r="T92" s="47"/>
       <c r="U92"/>
-    </row>
-    <row r="93" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V92"/>
+      <c r="W92"/>
+      <c r="X92"/>
+      <c r="Y92"/>
+    </row>
+    <row r="93" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
         <v>233</v>
       </c>
@@ -3869,23 +4589,27 @@
       <c r="F93" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G93"/>
-      <c r="H93"/>
-      <c r="I93"/>
-      <c r="J93"/>
-      <c r="K93"/>
-      <c r="L93"/>
-      <c r="M93"/>
-      <c r="N93"/>
-      <c r="O93"/>
-      <c r="P93"/>
-      <c r="Q93"/>
-      <c r="R93"/>
-      <c r="S93"/>
-      <c r="T93"/>
+      <c r="G93" s="47"/>
+      <c r="H93" s="47"/>
+      <c r="I93" s="47"/>
+      <c r="J93" s="47"/>
+      <c r="K93" s="47"/>
+      <c r="L93" s="47"/>
+      <c r="M93" s="47"/>
+      <c r="N93" s="47"/>
+      <c r="O93" s="47"/>
+      <c r="P93" s="47"/>
+      <c r="Q93" s="47"/>
+      <c r="R93" s="47"/>
+      <c r="S93" s="47"/>
+      <c r="T93" s="47"/>
       <c r="U93"/>
-    </row>
-    <row r="94" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V93"/>
+      <c r="W93"/>
+      <c r="X93"/>
+      <c r="Y93"/>
+    </row>
+    <row r="94" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
         <v>232</v>
       </c>
@@ -3904,23 +4628,27 @@
       <c r="F94" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G94"/>
-      <c r="H94"/>
-      <c r="I94"/>
-      <c r="J94"/>
-      <c r="K94"/>
-      <c r="L94"/>
-      <c r="M94"/>
-      <c r="N94"/>
-      <c r="O94"/>
-      <c r="P94"/>
-      <c r="Q94"/>
-      <c r="R94"/>
-      <c r="S94"/>
-      <c r="T94"/>
+      <c r="G94" s="47"/>
+      <c r="H94" s="47"/>
+      <c r="I94" s="47"/>
+      <c r="J94" s="47"/>
+      <c r="K94" s="47"/>
+      <c r="L94" s="47"/>
+      <c r="M94" s="47"/>
+      <c r="N94" s="47"/>
+      <c r="O94" s="47"/>
+      <c r="P94" s="47"/>
+      <c r="Q94" s="47"/>
+      <c r="R94" s="47"/>
+      <c r="S94" s="47"/>
+      <c r="T94" s="47"/>
       <c r="U94"/>
-    </row>
-    <row r="95" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V94"/>
+      <c r="W94"/>
+      <c r="X94"/>
+      <c r="Y94"/>
+    </row>
+    <row r="95" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>231</v>
       </c>
@@ -3939,23 +4667,27 @@
       <c r="F95" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G95"/>
-      <c r="H95"/>
-      <c r="I95"/>
-      <c r="J95"/>
-      <c r="K95"/>
-      <c r="L95"/>
-      <c r="M95"/>
-      <c r="N95"/>
-      <c r="O95"/>
-      <c r="P95"/>
-      <c r="Q95"/>
-      <c r="R95"/>
-      <c r="S95"/>
-      <c r="T95"/>
+      <c r="G95" s="47"/>
+      <c r="H95" s="47"/>
+      <c r="I95" s="47"/>
+      <c r="J95" s="47"/>
+      <c r="K95" s="47"/>
+      <c r="L95" s="47"/>
+      <c r="M95" s="47"/>
+      <c r="N95" s="47"/>
+      <c r="O95" s="47"/>
+      <c r="P95" s="47"/>
+      <c r="Q95" s="47"/>
+      <c r="R95" s="47"/>
+      <c r="S95" s="47"/>
+      <c r="T95" s="47"/>
       <c r="U95"/>
-    </row>
-    <row r="96" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V95"/>
+      <c r="W95"/>
+      <c r="X95"/>
+      <c r="Y95"/>
+    </row>
+    <row r="96" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>230</v>
       </c>
@@ -3974,23 +4706,27 @@
       <c r="F96" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G96"/>
-      <c r="H96"/>
-      <c r="I96"/>
-      <c r="J96"/>
-      <c r="K96"/>
-      <c r="L96"/>
-      <c r="M96"/>
-      <c r="N96"/>
-      <c r="O96"/>
-      <c r="P96"/>
-      <c r="Q96"/>
-      <c r="R96"/>
-      <c r="S96"/>
-      <c r="T96"/>
+      <c r="G96" s="47"/>
+      <c r="H96" s="47"/>
+      <c r="I96" s="47"/>
+      <c r="J96" s="47"/>
+      <c r="K96" s="47"/>
+      <c r="L96" s="47"/>
+      <c r="M96" s="47"/>
+      <c r="N96" s="47"/>
+      <c r="O96" s="47"/>
+      <c r="P96" s="47"/>
+      <c r="Q96" s="47"/>
+      <c r="R96" s="47"/>
+      <c r="S96" s="47"/>
+      <c r="T96" s="47"/>
       <c r="U96"/>
-    </row>
-    <row r="97" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V96"/>
+      <c r="W96"/>
+      <c r="X96"/>
+      <c r="Y96"/>
+    </row>
+    <row r="97" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
         <v>229</v>
       </c>
@@ -4009,23 +4745,27 @@
       <c r="F97" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G97"/>
-      <c r="H97"/>
-      <c r="I97"/>
-      <c r="J97"/>
-      <c r="K97"/>
-      <c r="L97"/>
-      <c r="M97"/>
-      <c r="N97"/>
-      <c r="O97"/>
-      <c r="P97"/>
-      <c r="Q97"/>
-      <c r="R97"/>
-      <c r="S97"/>
-      <c r="T97"/>
+      <c r="G97" s="47"/>
+      <c r="H97" s="47"/>
+      <c r="I97" s="47"/>
+      <c r="J97" s="47"/>
+      <c r="K97" s="47"/>
+      <c r="L97" s="47"/>
+      <c r="M97" s="47"/>
+      <c r="N97" s="47"/>
+      <c r="O97" s="47"/>
+      <c r="P97" s="47"/>
+      <c r="Q97" s="47"/>
+      <c r="R97" s="47"/>
+      <c r="S97" s="47"/>
+      <c r="T97" s="47"/>
       <c r="U97"/>
-    </row>
-    <row r="98" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V97"/>
+      <c r="W97"/>
+      <c r="X97"/>
+      <c r="Y97"/>
+    </row>
+    <row r="98" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>244</v>
       </c>
@@ -4044,22 +4784,27 @@
       <c r="F98" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G98"/>
-      <c r="H98"/>
-      <c r="I98"/>
-      <c r="J98"/>
-      <c r="K98"/>
-      <c r="L98"/>
-      <c r="M98"/>
-      <c r="N98"/>
-      <c r="O98"/>
-      <c r="P98"/>
-      <c r="Q98"/>
-      <c r="R98"/>
-      <c r="S98"/>
-      <c r="T98"/>
-    </row>
-    <row r="99" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G98" s="47"/>
+      <c r="H98" s="47"/>
+      <c r="I98" s="47"/>
+      <c r="J98" s="47"/>
+      <c r="K98" s="47"/>
+      <c r="L98" s="47"/>
+      <c r="M98" s="47"/>
+      <c r="N98" s="47"/>
+      <c r="O98" s="47"/>
+      <c r="P98" s="47"/>
+      <c r="Q98" s="47"/>
+      <c r="R98" s="47"/>
+      <c r="S98" s="47"/>
+      <c r="T98" s="47"/>
+      <c r="U98"/>
+      <c r="V98"/>
+      <c r="W98"/>
+      <c r="X98"/>
+      <c r="Y98"/>
+    </row>
+    <row r="99" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>162</v>
       </c>
@@ -4078,8 +4823,22 @@
       <c r="F99" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="100" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
+      <c r="J99" s="47"/>
+      <c r="K99" s="47"/>
+      <c r="L99" s="47"/>
+      <c r="M99" s="47"/>
+      <c r="N99" s="47"/>
+      <c r="O99" s="47"/>
+      <c r="P99" s="47"/>
+      <c r="Q99" s="47"/>
+      <c r="R99" s="47"/>
+      <c r="S99" s="47"/>
+      <c r="T99" s="47"/>
+    </row>
+    <row r="100" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
         <v>161</v>
       </c>
@@ -4099,7 +4858,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
         <v>160</v>
       </c>
@@ -4119,7 +4878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="27" t="s">
         <v>168</v>
       </c>
@@ -4139,7 +4898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
         <v>272</v>
       </c>
@@ -4160,7 +4919,7 @@
       </c>
       <c r="G103" s="50"/>
     </row>
-    <row r="104" spans="1:21" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" s="31" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
         <v>265</v>
       </c>
@@ -4181,7 +4940,7 @@
       </c>
       <c r="G104" s="50"/>
     </row>
-    <row r="105" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>56</v>
       </c>
@@ -4199,7 +4958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>58</v>
       </c>
@@ -4217,7 +4976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>59</v>
       </c>
@@ -4235,7 +4994,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>60</v>
       </c>
@@ -4251,7 +5010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>61</v>
       </c>
@@ -4267,7 +5026,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>62</v>
       </c>
@@ -4283,7 +5042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>63</v>
       </c>
@@ -4299,7 +5058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>64</v>
       </c>
@@ -8205,7 +8964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" ht="51" x14ac:dyDescent="0.25">
       <c r="A257" s="39" t="s">
         <v>228</v>
       </c>
@@ -8222,6 +8981,265 @@
         <v>75000</v>
       </c>
       <c r="F257" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:25" s="55" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B258" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D258" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E258" s="48">
+        <v>18450000</v>
+      </c>
+      <c r="F258" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G258"/>
+      <c r="H258"/>
+      <c r="I258"/>
+      <c r="J258"/>
+      <c r="K258"/>
+      <c r="L258"/>
+      <c r="M258"/>
+      <c r="N258"/>
+      <c r="O258"/>
+      <c r="P258"/>
+      <c r="Q258"/>
+      <c r="R258"/>
+      <c r="S258"/>
+      <c r="T258"/>
+      <c r="U258"/>
+      <c r="V258"/>
+      <c r="W258"/>
+      <c r="X258"/>
+      <c r="Y258"/>
+    </row>
+    <row r="259" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B259" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C259" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D259" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E259" s="48">
+        <v>39750000</v>
+      </c>
+      <c r="F259" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="260" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A260" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="B260" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C260" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D260" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E260" s="48">
+        <v>20250000</v>
+      </c>
+      <c r="F260" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="261" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A261" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B261" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C261" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D261" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E261" s="48">
+        <v>9000000</v>
+      </c>
+      <c r="F261" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A262" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="B262" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C262" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D262" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E262" s="48">
+        <v>21600000</v>
+      </c>
+      <c r="F262" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A263" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B263" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C263" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D263" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E263" s="48">
+        <v>9750000</v>
+      </c>
+      <c r="F263" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A264" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="B264" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C264" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D264" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E264" s="48">
+        <v>23700000</v>
+      </c>
+      <c r="F264" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="265" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A265" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B265" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C265" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D265" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E265" s="48">
+        <v>26700000</v>
+      </c>
+      <c r="F265" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A266" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="B266" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D266" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E266" s="48">
+        <v>34050000</v>
+      </c>
+      <c r="F266" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="267" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A267" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B267" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C267" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D267" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E267" s="48">
+        <v>43650000</v>
+      </c>
+      <c r="F267" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A268" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B268" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C268" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D268" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E268" s="48">
+        <v>63650000</v>
+      </c>
+      <c r="F268" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B269" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C269" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D269" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E269" s="48">
+        <v>23250000</v>
+      </c>
+      <c r="F269" s="17" t="s">
         <v>8</v>
       </c>
     </row>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="289">
   <si>
     <t>Ống D650</t>
   </si>
@@ -1264,6 +1264,48 @@
       </rPr>
       <t xml:space="preserve">
 1 quạt 11KW+ kết nối vói 2 bơm 3KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2 quạt 55KW+ kết nối vói 2 bơm 7.5KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2 quạt 55KW
 Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
     </r>
   </si>
@@ -1915,7 +1957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC269"/>
+  <dimension ref="A1:AC271"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5703125" style="40" customWidth="1"/>
@@ -9243,6 +9285,46 @@
         <v>8</v>
       </c>
     </row>
+    <row r="270" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A270" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B270" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C270" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D270" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E270" s="48">
+        <v>68224500</v>
+      </c>
+      <c r="F270" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="271" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A271" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B271" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C271" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D271" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E271" s="48">
+        <v>64416000</v>
+      </c>
+      <c r="F271" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="7215"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="291">
   <si>
     <t>Ống D650</t>
   </si>
@@ -1306,6 +1306,48 @@
       </rPr>
       <t xml:space="preserve">
 2 quạt 55KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1 quạt 37KW
+Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tủ điện điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+1 quạt 18.5KW
 Có biến tần ARINCO, bảo vệ mất pha, đèn báo pha đỏ vàng xanh</t>
     </r>
   </si>
@@ -1957,7 +1999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC271"/>
+  <dimension ref="A1:AC273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5703125" style="40" customWidth="1"/>
@@ -9325,6 +9367,46 @@
         <v>8</v>
       </c>
     </row>
+    <row r="272" spans="1:25" ht="51" x14ac:dyDescent="0.25">
+      <c r="A272" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B272" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C272" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D272" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E272" s="48">
+        <v>25200000</v>
+      </c>
+      <c r="F272" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A273" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B273" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C273" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D273" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="E273" s="48">
+        <v>18750000</v>
+      </c>
+      <c r="F273" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/quote-web/bang_gia.xlsx
+++ b/quote-web/bang_gia.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\quote-web-main\quote-web-main\quote-web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="7215"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7912,7 +7912,7 @@
         <v>156</v>
       </c>
       <c r="E226" s="24">
-        <v>33000</v>
+        <v>29000</v>
       </c>
       <c r="F226" s="13" t="s">
         <v>8</v>
